--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -1206,13 +1206,13 @@
     </font>
     <font>
       <b/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF328555"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
       <b/>
-      <color rgb="FF328555"/>
+      <color rgb="FFFF0000"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1341,10 +1341,10 @@
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4458,19 +4458,19 @@
         <v>304</v>
       </c>
       <c r="B5" s="34">
-        <v>864764</v>
+        <v>864756</v>
       </c>
       <c r="C5" s="34">
-        <v>2251192</v>
+        <v>2251184</v>
       </c>
       <c r="D5" s="34">
-        <v>4253421</v>
+        <v>4253414</v>
       </c>
       <c r="E5" s="34">
-        <v>6813766</v>
+        <v>6813759</v>
       </c>
       <c r="F5" s="34">
-        <v>9755981</v>
+        <v>9755974</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4538,19 +4538,19 @@
         <v>308</v>
       </c>
       <c r="B9" s="30">
-        <v>1061764</v>
+        <v>1061756</v>
       </c>
       <c r="C9" s="30">
-        <v>2448192</v>
+        <v>2448184</v>
       </c>
       <c r="D9" s="30">
-        <v>4450421</v>
+        <v>4450414</v>
       </c>
       <c r="E9" s="30">
-        <v>7010766</v>
+        <v>7010759</v>
       </c>
       <c r="F9" s="30">
-        <v>9952981</v>
+        <v>9952974</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4638,19 +4638,19 @@
         <v>314</v>
       </c>
       <c r="B17" s="26">
-        <v>822118</v>
+        <v>822111</v>
       </c>
       <c r="C17" s="26">
-        <v>2228131</v>
+        <v>2228123</v>
       </c>
       <c r="D17" s="26">
-        <v>4251256</v>
+        <v>4251248</v>
       </c>
       <c r="E17" s="26">
-        <v>6833896</v>
+        <v>6833888</v>
       </c>
       <c r="F17" s="26">
-        <v>9799899</v>
+        <v>9799892</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4658,18 +4658,18 @@
         <v>315</v>
       </c>
       <c r="B19" s="35">
+        <v>0</v>
+      </c>
+      <c r="C19" s="35">
+        <v>0</v>
+      </c>
+      <c r="D19" s="36">
         <v>1</v>
       </c>
-      <c r="C19" s="36">
-        <v>0</v>
-      </c>
-      <c r="D19" s="36">
-        <v>0</v>
-      </c>
       <c r="E19" s="36">
-        <v>0</v>
-      </c>
-      <c r="F19" s="36">
+        <v>1</v>
+      </c>
+      <c r="F19" s="35">
         <v>0</v>
       </c>
     </row>
@@ -4812,19 +4812,19 @@
         <v>321</v>
       </c>
       <c r="B10" s="25">
-        <v>864764</v>
+        <v>864756</v>
       </c>
       <c r="C10" s="25">
-        <v>2251192</v>
+        <v>2251184</v>
       </c>
       <c r="D10" s="25">
-        <v>4253421</v>
+        <v>4253414</v>
       </c>
       <c r="E10" s="25">
-        <v>6813766</v>
+        <v>6813759</v>
       </c>
       <c r="F10" s="25">
-        <v>9755981</v>
+        <v>9755974</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5205,7 +5205,7 @@
       <c r="A10" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="B10" s="36">
+      <c r="B10" s="35">
         <v>0</v>
       </c>
     </row>
@@ -6039,19 +6039,19 @@
         <v>357</v>
       </c>
       <c r="D16" s="25">
-        <v>864764</v>
+        <v>864756</v>
       </c>
       <c r="E16" s="25">
-        <v>2251192</v>
+        <v>2251184</v>
       </c>
       <c r="F16" s="25">
-        <v>4253421</v>
+        <v>4253414</v>
       </c>
       <c r="G16" s="25">
-        <v>6813766</v>
+        <v>6813759</v>
       </c>
       <c r="H16" s="25">
-        <v>9755981</v>
+        <v>9755974</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -72,7 +72,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 16, 2026</t>
+    <t>March 17, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -366,7 +366,7 @@
     <t>Foundation Grant</t>
   </si>
   <si>
-    <t>Grants &amp; Contributions</t>
+    <t>Philanthropy</t>
   </si>
   <si>
     <t>Annual Fixed</t>
@@ -609,10 +609,10 @@
     <t>FL FTC Scholarship (School Choice)</t>
   </si>
   <si>
-    <t>Foundation Grant (Grants &amp; Contributions)</t>
-  </si>
-  <si>
-    <t>Annual Fund (Grants &amp; Contributions)</t>
+    <t>Foundation Grant (Philanthropy)</t>
+  </si>
+  <si>
+    <t>Annual Fund (Philanthropy)</t>
   </si>
   <si>
     <t>After-School Programs (Other Revenue)</t>
@@ -1133,7 +1133,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1177,7 +1177,7 @@
     <font>
       <i/>
       <color rgb="FF999999"/>
-      <sz val="9"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1195,7 +1195,7 @@
     <font>
       <i/>
       <color rgb="FF666666"/>
-      <sz val="10"/>
+      <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1213,12 +1213,6 @@
     <font>
       <b/>
       <color rgb="FFFF0000"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <i/>
-      <color rgb="FF666666"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1293,7 +1287,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1348,7 +1342,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -5390,7 +5383,7 @@
       <c r="F3" s="13"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
+      <c r="A4" s="12" t="s">
         <v>347</v>
       </c>
     </row>
@@ -5498,19 +5491,19 @@
       <c r="A10" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="42">
         <v>24.92</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="42">
         <v>41.99</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="42">
         <v>60.07</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="42">
         <v>76.31</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="42">
         <v>87.52</v>
       </c>
     </row>
@@ -5545,7 +5538,7 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="42" t="s">
+      <c r="A14" s="12" t="s">
         <v>350</v>
       </c>
     </row>
@@ -5653,19 +5646,19 @@
       <c r="A20" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B20" s="43">
+      <c r="B20" s="42">
         <v>24.92</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="42">
         <v>41.99</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="42">
         <v>60.07</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="42">
         <v>76.31</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="42">
         <v>87.52</v>
       </c>
     </row>
@@ -5700,7 +5693,7 @@
       <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="42" t="s">
+      <c r="A24" s="12" t="s">
         <v>352</v>
       </c>
     </row>
@@ -5808,19 +5801,19 @@
       <c r="A30" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="B30" s="43">
+      <c r="B30" s="42">
         <v>24.12</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="42">
         <v>41.08</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="42">
         <v>59.04</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="42">
         <v>75.17</v>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="42">
         <v>86.29</v>
       </c>
     </row>
@@ -5958,19 +5951,19 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="44" t="s">
+      <c r="D12" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="44" t="s">
+      <c r="E12" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="44" t="s">
+      <c r="F12" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="44" t="s">
+      <c r="G12" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="44" t="s">
+      <c r="H12" s="43" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6096,19 +6089,19 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="44" t="s">
+      <c r="D20" s="43" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="44" t="s">
+      <c r="E20" s="43" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="44" t="s">
+      <c r="F20" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="44" t="s">
+      <c r="G20" s="43" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="44" t="s">
+      <c r="H20" s="43" t="s">
         <v>94</v>
       </c>
     </row>
@@ -6136,19 +6129,19 @@
       <c r="A22" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="D22" s="43">
+      <c r="D22" s="42">
         <v>24.92</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="42">
         <v>41.99</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="42">
         <v>60.07</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="42">
         <v>76.31</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="42">
         <v>87.52</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="363">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="365">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -795,6 +795,9 @@
     <t xml:space="preserve">    Maintenance</t>
   </si>
   <si>
+    <t xml:space="preserve">  Total Occupancy / Facility</t>
+  </si>
+  <si>
     <t xml:space="preserve">    Marketing</t>
   </si>
   <si>
@@ -804,6 +807,9 @@
     <t xml:space="preserve">    Accounting &amp; Legal</t>
   </si>
   <si>
+    <t xml:space="preserve">  Total Administrative / General</t>
+  </si>
+  <si>
     <t>Total Operating Expenses</t>
   </si>
   <si>
@@ -987,6 +993,9 @@
     <t>CASH FLOW &amp; DEBT</t>
   </si>
   <si>
+    <t>Revenue</t>
+  </si>
+  <si>
     <t>CFADS (Rev - Pers - OpEx)</t>
   </si>
   <si>
@@ -1075,9 +1084,6 @@
   </si>
   <si>
     <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +0%</t>
-  </si>
-  <si>
-    <t>Revenue</t>
   </si>
   <si>
     <t>LOW ENROLLMENT</t>
@@ -2207,18 +2213,23 @@
         <v>195</v>
       </c>
       <c r="B14" s="26">
+        <f>SUM(B7:B13)</f>
         <v>1975000</v>
       </c>
       <c r="C14" s="26">
+        <f>SUM(C7:C13)</f>
         <v>2621350</v>
       </c>
       <c r="D14" s="26">
+        <f>SUM(D7:D13)</f>
         <v>3304704</v>
       </c>
       <c r="E14" s="26">
+        <f>SUM(E7:E13)</f>
         <v>3922890</v>
       </c>
       <c r="F14" s="26">
+        <f>SUM(F7:F13)</f>
         <v>4361347</v>
       </c>
     </row>
@@ -2351,18 +2362,23 @@
         <v>228</v>
       </c>
       <c r="B7" s="30">
+        <f>SUM(B5:B6)</f>
         <v>504576</v>
       </c>
       <c r="C7" s="30">
+        <f>SUM(C5:C6)</f>
         <v>519713</v>
       </c>
       <c r="D7" s="30">
+        <f>SUM(D5:D6)</f>
         <v>535305</v>
       </c>
       <c r="E7" s="30">
+        <f>SUM(E5:E6)</f>
         <v>551364</v>
       </c>
       <c r="F7" s="30">
+        <f>SUM(F5:F6)</f>
         <v>567905</v>
       </c>
     </row>
@@ -2421,18 +2437,23 @@
         <v>231</v>
       </c>
       <c r="B11" s="30">
+        <f>SUM(B9:B10)</f>
         <v>225505</v>
       </c>
       <c r="C11" s="30">
+        <f>SUM(C9:C10)</f>
         <v>232270</v>
       </c>
       <c r="D11" s="30">
+        <f>SUM(D9:D10)</f>
         <v>239238</v>
       </c>
       <c r="E11" s="30">
+        <f>SUM(E9:E10)</f>
         <v>246415</v>
       </c>
       <c r="F11" s="30">
+        <f>SUM(F9:F10)</f>
         <v>253808</v>
       </c>
     </row>
@@ -2471,18 +2492,23 @@
         <v>233</v>
       </c>
       <c r="B14" s="30">
+        <f>SUM(B13:B13)</f>
         <v>68978</v>
       </c>
       <c r="C14" s="30">
+        <f>SUM(C13:C13)</f>
         <v>71047</v>
       </c>
       <c r="D14" s="30">
+        <f>SUM(D13:D13)</f>
         <v>73179</v>
       </c>
       <c r="E14" s="30">
+        <f>SUM(E13:E13)</f>
         <v>75374</v>
       </c>
       <c r="F14" s="30">
+        <f>SUM(F13:F13)</f>
         <v>77635</v>
       </c>
     </row>
@@ -2521,18 +2547,23 @@
         <v>235</v>
       </c>
       <c r="B17" s="30">
+        <f>SUM(B16:B16)</f>
         <v>55713</v>
       </c>
       <c r="C17" s="30">
+        <f>SUM(C16:C16)</f>
         <v>57384</v>
       </c>
       <c r="D17" s="30">
+        <f>SUM(D16:D16)</f>
         <v>59106</v>
       </c>
       <c r="E17" s="30">
+        <f>SUM(E16:E16)</f>
         <v>60879</v>
       </c>
       <c r="F17" s="30">
+        <f>SUM(F16:F16)</f>
         <v>62705</v>
       </c>
     </row>
@@ -2541,18 +2572,23 @@
         <v>236</v>
       </c>
       <c r="B19" s="26">
+        <f>B7+B11+B14+B17</f>
         <v>854772</v>
       </c>
       <c r="C19" s="26">
+        <f>C7+C11+C14+C17</f>
         <v>880415</v>
       </c>
       <c r="D19" s="26">
+        <f>D7+D11+D14+D17</f>
         <v>906828</v>
       </c>
       <c r="E19" s="26">
+        <f>E7+E11+E14+E17</f>
         <v>934032</v>
       </c>
       <c r="F19" s="26">
+        <f>F7+F11+F14+F17</f>
         <v>962053</v>
       </c>
     </row>
@@ -2573,7 +2609,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -2765,18 +2801,23 @@
         <v>246</v>
       </c>
       <c r="B12" s="30">
+        <f>SUM(B5:B11)</f>
         <v>1975000</v>
       </c>
       <c r="C12" s="30">
+        <f>SUM(C5:C11)</f>
         <v>2621350</v>
       </c>
       <c r="D12" s="30">
+        <f>SUM(D5:D11)</f>
         <v>3304704</v>
       </c>
       <c r="E12" s="30">
+        <f>SUM(E5:E11)</f>
         <v>3922890</v>
       </c>
       <c r="F12" s="30">
+        <f>SUM(F5:F11)</f>
         <v>4361347</v>
       </c>
     </row>
@@ -2915,18 +2956,23 @@
         <v>199</v>
       </c>
       <c r="B21" s="30">
+        <f>SUM(B15:B20)</f>
         <v>854772</v>
       </c>
       <c r="C21" s="30">
+        <f>SUM(C15:C20)</f>
         <v>880415</v>
       </c>
       <c r="D21" s="30">
+        <f>SUM(D15:D20)</f>
         <v>906828</v>
       </c>
       <c r="E21" s="30">
+        <f>SUM(E15:E20)</f>
         <v>934032</v>
       </c>
       <c r="F21" s="30">
+        <f>SUM(F15:F20)</f>
         <v>962053</v>
       </c>
     </row>
@@ -3075,29 +3121,34 @@
         <v>9004</v>
       </c>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="31" t="s">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B33" s="30">
+        <f>SUM(B29:B32)</f>
+        <v>136400</v>
+      </c>
+      <c r="C33" s="30">
+        <f>SUM(C29:C32)</f>
+        <v>140492</v>
+      </c>
+      <c r="D33" s="30">
+        <f>SUM(D29:D32)</f>
+        <v>144707</v>
+      </c>
+      <c r="E33" s="30">
+        <f>SUM(E29:E32)</f>
+        <v>149048</v>
+      </c>
+      <c r="F33" s="30">
+        <f>SUM(F29:F32)</f>
+        <v>153519</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A34" s="31" t="s">
         <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B34" s="25">
-        <v>15000</v>
-      </c>
-      <c r="C34" s="25">
-        <v>15450</v>
-      </c>
-      <c r="D34" s="25">
-        <v>15914</v>
-      </c>
-      <c r="E34" s="25">
-        <v>16391</v>
-      </c>
-      <c r="F34" s="25">
-        <v>16883</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -3105,19 +3156,19 @@
         <v>255</v>
       </c>
       <c r="B35" s="25">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="C35" s="25">
-        <v>8240</v>
+        <v>15450</v>
       </c>
       <c r="D35" s="25">
-        <v>8487</v>
+        <v>15914</v>
       </c>
       <c r="E35" s="25">
-        <v>8742</v>
+        <v>16391</v>
       </c>
       <c r="F35" s="25">
-        <v>9004</v>
+        <v>16883</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
@@ -3125,108 +3176,163 @@
         <v>256</v>
       </c>
       <c r="B36" s="25">
+        <v>8000</v>
+      </c>
+      <c r="C36" s="25">
+        <v>8240</v>
+      </c>
+      <c r="D36" s="25">
+        <v>8487</v>
+      </c>
+      <c r="E36" s="25">
+        <v>8742</v>
+      </c>
+      <c r="F36" s="25">
+        <v>9004</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="B37" s="25">
         <v>12000</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C37" s="25">
         <v>12360</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D37" s="25">
         <v>12731</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E37" s="25">
         <v>13113</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F37" s="25">
         <v>13506</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B37" s="30">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="B38" s="30">
+        <f>SUM(B35:B37)</f>
+        <v>35000</v>
+      </c>
+      <c r="C38" s="30">
+        <f>SUM(C35:C37)</f>
+        <v>36050</v>
+      </c>
+      <c r="D38" s="30">
+        <f>SUM(D35:D37)</f>
+        <v>37132</v>
+      </c>
+      <c r="E38" s="30">
+        <f>SUM(E35:E37)</f>
+        <v>38245</v>
+      </c>
+      <c r="F38" s="30">
+        <f>SUM(F35:F37)</f>
+        <v>39393</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="B39" s="30">
+        <f>B25+B27+B33+B38</f>
         <v>271400</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C39" s="30">
+        <f>C25+C27+C33+C38</f>
         <v>310442</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D39" s="30">
+        <f>D25+D27+D33+D38</f>
         <v>351582</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E39" s="30">
+        <f>E25+E27+E33+E38</f>
         <v>389448</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F39" s="30">
+        <f>F25+F27+F33+F38</f>
         <v>418014</v>
       </c>
     </row>
-    <row r="39" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="13" t="s">
-        <v>258</v>
-      </c>
-      <c r="B39" s="13"/>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>259</v>
-      </c>
-      <c r="B40" s="25">
+    <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="13" t="s">
+        <v>260</v>
+      </c>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="B42" s="25">
         <v>34064</v>
       </c>
-      <c r="C40" s="25">
+      <c r="C42" s="25">
         <v>34064</v>
       </c>
-      <c r="D40" s="25">
+      <c r="D42" s="25">
         <v>34064</v>
       </c>
-      <c r="E40" s="25">
+      <c r="E42" s="25">
         <v>34064</v>
       </c>
-      <c r="F40" s="25">
+      <c r="F42" s="25">
         <v>34064</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="4" t="s">
-        <v>260</v>
-      </c>
-      <c r="B41" s="25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="B43" s="25">
         <v>25000</v>
       </c>
-      <c r="C41" s="25">
+      <c r="C43" s="25">
         <v>10000</v>
       </c>
-      <c r="D41" s="25">
+      <c r="D43" s="25">
         <v>10000</v>
       </c>
-      <c r="E41" s="25">
+      <c r="E43" s="25">
         <v>5000</v>
       </c>
-      <c r="F41" s="25">
+      <c r="F43" s="25">
         <v>5000</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="B42" s="30">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="B44" s="30">
+        <f>SUM(B42:B43)</f>
         <v>59064</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C44" s="30">
+        <f>SUM(C42:C43)</f>
         <v>44064</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D44" s="30">
+        <f>SUM(D42:D43)</f>
         <v>44064</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E44" s="30">
+        <f>SUM(E42:E43)</f>
         <v>39064</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F44" s="30">
+        <f>SUM(F42:F43)</f>
         <v>39064</v>
       </c>
     </row>
@@ -3256,7 +3362,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3289,18 +3395,23 @@
         <v>246</v>
       </c>
       <c r="B4" s="28">
+        <f>'Budget Detail'!B12</f>
         <v>1975000</v>
       </c>
       <c r="C4" s="28">
+        <f>'Budget Detail'!C12</f>
         <v>2621350</v>
       </c>
       <c r="D4" s="28">
+        <f>'Budget Detail'!D12</f>
         <v>3304704</v>
       </c>
       <c r="E4" s="28">
+        <f>'Budget Detail'!E12</f>
         <v>3922890</v>
       </c>
       <c r="F4" s="28">
+        <f>'Budget Detail'!F12</f>
         <v>4361347</v>
       </c>
     </row>
@@ -3309,84 +3420,104 @@
         <v>199</v>
       </c>
       <c r="B5" s="28">
+        <f>'Budget Detail'!B21</f>
         <v>854772</v>
       </c>
       <c r="C5" s="28">
+        <f>'Budget Detail'!C21</f>
         <v>880415</v>
       </c>
       <c r="D5" s="28">
+        <f>'Budget Detail'!D21</f>
         <v>906828</v>
       </c>
       <c r="E5" s="28">
+        <f>'Budget Detail'!E21</f>
         <v>934032</v>
       </c>
       <c r="F5" s="28">
+        <f>'Budget Detail'!F21</f>
         <v>962053</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="B6" s="28">
+        <f>'Budget Detail'!B39</f>
         <v>271400</v>
       </c>
       <c r="C6" s="28">
+        <f>'Budget Detail'!C39</f>
         <v>310442</v>
       </c>
       <c r="D6" s="28">
+        <f>'Budget Detail'!D39</f>
         <v>351582</v>
       </c>
       <c r="E6" s="28">
+        <f>'Budget Detail'!E39</f>
         <v>389448</v>
       </c>
       <c r="F6" s="28">
+        <f>'Budget Detail'!F39</f>
         <v>418014</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="B7" s="28">
+        <f>'Budget Detail'!B44</f>
         <v>59064</v>
       </c>
       <c r="C7" s="28">
+        <f>'Budget Detail'!C44</f>
         <v>44064</v>
       </c>
       <c r="D7" s="28">
+        <f>'Budget Detail'!D44</f>
         <v>44064</v>
       </c>
       <c r="E7" s="28">
+        <f>'Budget Detail'!E44</f>
         <v>39064</v>
       </c>
       <c r="F7" s="28">
+        <f>'Budget Detail'!F44</f>
         <v>39064</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B8" s="30">
+        <f>SUM(B5:B7)</f>
         <v>1185236</v>
       </c>
       <c r="C8" s="30">
+        <f>SUM(C5:C7)</f>
         <v>1234922</v>
       </c>
       <c r="D8" s="30">
+        <f>SUM(D5:D7)</f>
         <v>1302474</v>
       </c>
       <c r="E8" s="30">
+        <f>SUM(E5:E7)</f>
         <v>1362545</v>
       </c>
       <c r="F8" s="30">
+        <f>SUM(F5:F7)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3396,47 +3527,57 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B11" s="26">
+        <f>B4-B8</f>
         <v>789764</v>
       </c>
       <c r="C11" s="26">
+        <f>C4-C8</f>
         <v>1386428</v>
       </c>
       <c r="D11" s="26">
+        <f>D4-D8</f>
         <v>2002229</v>
       </c>
       <c r="E11" s="26">
+        <f>E4-E8</f>
         <v>2560345</v>
       </c>
       <c r="F11" s="26">
+        <f>F4-F8</f>
         <v>2942215</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B12" s="24">
-        <v>0.3998803072577175</v>
+        <f>IF(B4=0,0,B11/B4)</f>
+        <v>0.39988031</v>
       </c>
       <c r="C12" s="24">
-        <v>0.5288986388059557</v>
+        <f>IF(C4=0,0,C11/C4)</f>
+        <v>0.52889864</v>
       </c>
       <c r="D12" s="24">
-        <v>0.6058725788967125</v>
+        <f>IF(D4=0,0,D11/D4)</f>
+        <v>0.60587258</v>
       </c>
       <c r="E12" s="24">
-        <v>0.6526681187789514</v>
+        <f>IF(E4=0,0,E11/E4)</f>
+        <v>0.65266812</v>
       </c>
       <c r="F12" s="24">
-        <v>0.6746115593902751</v>
+        <f>IF(F4=0,0,F11/F4)</f>
+        <v>0.67461156</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B13" s="25">
         <v>789764</v>
@@ -3476,7 +3617,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="B15" s="25">
         <v>11852</v>
@@ -3521,7 +3662,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3542,43 +3683,43 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -3645,7 +3786,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3663,7 +3804,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B7" s="25">
         <v>71231</v>
@@ -3707,7 +3848,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B8" s="25">
         <v>22617</v>
@@ -3751,7 +3892,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B9" s="25">
         <v>4922</v>
@@ -3795,7 +3936,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3813,7 +3954,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B12" s="28">
         <v>98770</v>
@@ -3857,7 +3998,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B13" s="28">
         <v>-12937</v>
@@ -3901,7 +4042,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="B14" s="32">
         <v>62063</v>
@@ -3945,7 +4086,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -3960,7 +4101,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B18" s="32">
         <v>864756</v>
@@ -3968,7 +4109,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="B19" s="25">
         <v>62063</v>
@@ -4000,7 +4141,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4058,19 +4199,9 @@
         <v>4361347</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-    </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4080,7 +4211,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="B8" s="28">
         <v>854772</v>
@@ -4100,7 +4231,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B9" s="28">
         <v>271400</v>
@@ -4120,7 +4251,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B10" s="28">
         <v>59064</v>
@@ -4140,37 +4271,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="33" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B11" s="30">
+        <f>SUM(B8:B10)</f>
         <v>1185236</v>
       </c>
       <c r="C11" s="30">
+        <f>SUM(C8:C10)</f>
         <v>1234922</v>
       </c>
       <c r="D11" s="30">
+        <f>SUM(D8:D10)</f>
         <v>1302474</v>
       </c>
       <c r="E11" s="30">
+        <f>SUM(E8:E10)</f>
         <v>1362545</v>
       </c>
       <c r="F11" s="30">
+        <f>SUM(F8:F10)</f>
         <v>1419132</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="4"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4"/>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4180,42 +4306,52 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="33" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B14" s="26">
+        <f>B5-B11</f>
         <v>789764</v>
       </c>
       <c r="C14" s="26">
+        <f>C5-C11</f>
         <v>1386428</v>
       </c>
       <c r="D14" s="26">
+        <f>D5-D11</f>
         <v>2002229</v>
       </c>
       <c r="E14" s="26">
+        <f>E5-E11</f>
         <v>2560345</v>
       </c>
       <c r="F14" s="26">
+        <f>F5-F11</f>
         <v>2942215</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B15" s="24">
-        <v>0.3998803072577175</v>
+        <f>IF(B5=0,0,B14/B5)</f>
+        <v>0.39988031</v>
       </c>
       <c r="C15" s="24">
-        <v>0.5288986388059557</v>
+        <f>IF(C5=0,0,C14/C5)</f>
+        <v>0.52889864</v>
       </c>
       <c r="D15" s="24">
-        <v>0.6058725788967125</v>
+        <f>IF(D5=0,0,D14/D5)</f>
+        <v>0.60587258</v>
       </c>
       <c r="E15" s="24">
-        <v>0.6526681187789514</v>
+        <f>IF(E5=0,0,E14/E5)</f>
+        <v>0.65266812</v>
       </c>
       <c r="F15" s="24">
-        <v>0.6746115593902751</v>
+        <f>IF(F5=0,0,F14/F5)</f>
+        <v>0.67461156</v>
       </c>
     </row>
   </sheetData>
@@ -4284,7 +4420,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="B5" s="25">
         <v>250000</v>
@@ -4304,7 +4440,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B6" s="25">
         <v>15710</v>
@@ -4324,7 +4460,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="B7" s="25">
         <v>18355</v>
@@ -4344,7 +4480,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B8" s="28">
         <v>34064</v>
@@ -4364,7 +4500,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B9" s="32">
         <v>231645</v>
@@ -4408,7 +4544,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4438,7 +4574,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4448,7 +4584,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B5" s="34">
         <v>864756</v>
@@ -4468,7 +4604,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="B6" s="25">
         <v>12000</v>
@@ -4488,7 +4624,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="B7" s="25">
         <v>180000</v>
@@ -4508,7 +4644,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B8" s="25">
         <v>5000</v>
@@ -4528,7 +4664,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B9" s="30">
         <v>1061756</v>
@@ -4548,7 +4684,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4558,7 +4694,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="B12" s="25">
         <v>8000</v>
@@ -4578,7 +4714,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B13" s="25">
         <v>231645</v>
@@ -4598,7 +4734,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="B14" s="30">
         <v>239645</v>
@@ -4618,7 +4754,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4628,7 +4764,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B17" s="26">
         <v>822111</v>
@@ -4648,7 +4784,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B19" s="35">
         <v>0</v>
@@ -4683,7 +4819,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4692,7 +4828,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4722,7 +4858,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4732,22 +4868,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="B5" s="25">
-        <v>848828</v>
+        <v>1975000</v>
       </c>
       <c r="C5" s="25">
-        <v>1430493</v>
+        <v>2621350</v>
       </c>
       <c r="D5" s="25">
-        <v>2046294</v>
+        <v>3304704</v>
       </c>
       <c r="E5" s="25">
-        <v>2599410</v>
+        <v>3922890</v>
       </c>
       <c r="F5" s="25">
-        <v>2981279</v>
+        <v>4361347</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -4755,329 +4891,409 @@
         <v>287</v>
       </c>
       <c r="B6" s="25">
+        <v>854772</v>
+      </c>
+      <c r="C6" s="25">
+        <v>880415</v>
+      </c>
+      <c r="D6" s="25">
+        <v>906828</v>
+      </c>
+      <c r="E6" s="25">
+        <v>934032</v>
+      </c>
+      <c r="F6" s="25">
+        <v>962053</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>288</v>
+      </c>
+      <c r="B7" s="25">
+        <v>271400</v>
+      </c>
+      <c r="C7" s="25">
+        <v>310442</v>
+      </c>
+      <c r="D7" s="25">
+        <v>351582</v>
+      </c>
+      <c r="E7" s="25">
+        <v>389448</v>
+      </c>
+      <c r="F7" s="25">
+        <v>418014</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B8" s="28">
+        <f>B5-B6-B7</f>
+        <v>848828</v>
+      </c>
+      <c r="C8" s="28">
+        <f>C5-C6-C7</f>
+        <v>1430493</v>
+      </c>
+      <c r="D8" s="28">
+        <f>D5-D6-D7</f>
+        <v>2046294</v>
+      </c>
+      <c r="E8" s="28">
+        <f>E5-E6-E7</f>
+        <v>2599410</v>
+      </c>
+      <c r="F8" s="28">
+        <f>F5-F6-F7</f>
+        <v>2981279</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="B9" s="25">
         <v>34064</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C9" s="25">
         <v>34064</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D9" s="25">
         <v>34064</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E9" s="25">
         <v>34064</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F9" s="25">
         <v>34064</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B7" s="37">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="B10" s="37">
+        <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>24.92</v>
       </c>
-      <c r="C7" s="37">
+      <c r="C10" s="37">
+        <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>41.99</v>
       </c>
-      <c r="D7" s="37">
+      <c r="D10" s="37">
+        <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>60.07</v>
       </c>
-      <c r="E7" s="37">
+      <c r="E10" s="37">
+        <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>76.31</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F10" s="37">
+        <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>87.52</v>
       </c>
     </row>
-    <row r="9" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="13" t="s">
-        <v>320</v>
-      </c>
-      <c r="B9" s="13"/>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
-        <v>321</v>
-      </c>
-      <c r="B10" s="25">
-        <v>864756</v>
-      </c>
-      <c r="C10" s="25">
-        <v>2251184</v>
-      </c>
-      <c r="D10" s="25">
-        <v>4253414</v>
-      </c>
-      <c r="E10" s="25">
-        <v>6813759</v>
-      </c>
-      <c r="F10" s="25">
-        <v>9755974</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B11" s="22">
-        <v>272</v>
-      </c>
-      <c r="C11" s="22">
-        <v>671</v>
-      </c>
-      <c r="D11" s="22">
-        <v>1201</v>
-      </c>
-      <c r="E11" s="22">
-        <v>1832</v>
-      </c>
-      <c r="F11" s="22">
-        <v>2518</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="B12" s="29">
-        <v>8.9</v>
-      </c>
-      <c r="C12" s="29">
-        <v>22.1</v>
-      </c>
-      <c r="D12" s="29">
-        <v>39.5</v>
-      </c>
-      <c r="E12" s="29">
-        <v>60.2</v>
-      </c>
-      <c r="F12" s="29">
-        <v>82.8</v>
-      </c>
+      <c r="B12" s="13"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="24">
-        <v>0.5</v>
-      </c>
-      <c r="C13" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="D13" s="24">
-        <v>0.8</v>
-      </c>
-      <c r="E13" s="24">
-        <v>0.925</v>
-      </c>
-      <c r="F13" s="24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="B15" s="13"/>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
+      <c r="B13" s="25">
+        <v>864756</v>
+      </c>
+      <c r="C13" s="25">
+        <v>2251184</v>
+      </c>
+      <c r="D13" s="25">
+        <v>4253414</v>
+      </c>
+      <c r="E13" s="25">
+        <v>6813759</v>
+      </c>
+      <c r="F13" s="25">
+        <v>9755974</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>325</v>
+      </c>
+      <c r="B14" s="22">
+        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
+        <v>272</v>
+      </c>
+      <c r="C14" s="22">
+        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
+        <v>671</v>
+      </c>
+      <c r="D14" s="22">
+        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
+        <v>1201</v>
+      </c>
+      <c r="E14" s="22">
+        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
+        <v>1832</v>
+      </c>
+      <c r="F14" s="22">
+        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>326</v>
+      </c>
+      <c r="B15" s="29">
+        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
+        <v>8.9</v>
+      </c>
+      <c r="C15" s="29">
+        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
+        <v>22.1</v>
+      </c>
+      <c r="D15" s="29">
+        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
+        <v>39.5</v>
+      </c>
+      <c r="E15" s="29">
+        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
+        <v>60.2</v>
+      </c>
+      <c r="F15" s="29">
+        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
+        <v>82.8</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="B16" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="C16" s="24">
+        <v>0.65</v>
+      </c>
+      <c r="D16" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="E16" s="24">
+        <v>0.925</v>
+      </c>
+      <c r="F16" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="13" t="s">
+        <v>327</v>
+      </c>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B19" s="25">
         <v>19750</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C19" s="25">
         <v>20164</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D19" s="25">
         <v>20654</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E19" s="25">
         <v>21205</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F19" s="25">
         <v>21807</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B17" s="25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="B20" s="25">
         <v>888836</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C20" s="25">
         <v>914480</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D20" s="25">
         <v>940892</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E20" s="25">
         <v>968097</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F20" s="25">
         <v>996118</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B18" s="25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>329</v>
+      </c>
+      <c r="B21" s="25">
         <v>2714</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C21" s="25">
         <v>2388</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D21" s="25">
         <v>2197</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E21" s="25">
         <v>2105</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F21" s="25">
         <v>2090</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="B19" s="38">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="B22" s="38">
         <v>53</v>
       </c>
-      <c r="C19" s="38">
+      <c r="C22" s="38">
         <v>52</v>
       </c>
-      <c r="D19" s="38">
+      <c r="D22" s="38">
         <v>51</v>
       </c>
-      <c r="E19" s="38">
+      <c r="E22" s="38">
         <v>51</v>
       </c>
-      <c r="F19" s="38">
+      <c r="F22" s="38">
         <v>51</v>
       </c>
     </row>
-    <row r="21" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B22" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="E22" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="F22" s="39" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="4" t="s">
+    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="13" t="s">
         <v>331</v>
       </c>
-      <c r="B23" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="E23" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="F23" s="39" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B24" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="D24" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="E24" s="40" t="s">
-        <v>333</v>
-      </c>
-      <c r="F24" s="40" t="s">
-        <v>333</v>
-      </c>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B25" s="39" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="C25" s="39" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="D25" s="39" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E25" s="39" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="F25" s="39" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>334</v>
+      </c>
+      <c r="B26" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="C26" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="D26" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="E26" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="F26" s="39" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="B26" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>330</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>330</v>
+      <c r="B27" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="D27" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="E27" s="40" t="s">
+        <v>336</v>
+      </c>
+      <c r="F27" s="40" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>337</v>
+      </c>
+      <c r="B28" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="C28" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="D28" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="E28" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="F28" s="39" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>338</v>
+      </c>
+      <c r="B29" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="D29" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="E29" s="39" t="s">
+        <v>333</v>
+      </c>
+      <c r="F29" s="39" t="s">
+        <v>333</v>
       </c>
     </row>
   </sheetData>
@@ -5118,13 +5334,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="41" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B3" s="41" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="41" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="E3" s="41" t="s">
         <v>100</v>
@@ -5138,7 +5354,7 @@
         <v>250000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E4" s="25">
         <v>200000</v>
@@ -5160,13 +5376,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B6" s="25">
         <v>75000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E6" s="25">
         <v>75000</v>
@@ -5174,7 +5390,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="E7" s="25">
         <v>50000</v>
@@ -5182,13 +5398,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B9" s="26">
         <v>375000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="E9" s="26">
         <v>375000</v>
@@ -5196,7 +5412,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B10" s="35">
         <v>0</v>
@@ -5364,7 +5580,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5374,7 +5590,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5384,7 +5600,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5409,7 +5625,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="B6" s="25">
         <v>1975000</v>
@@ -5429,7 +5645,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B7" s="25">
         <v>1160236</v>
@@ -5449,7 +5665,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B8" s="26">
         <v>814764</v>
@@ -5469,7 +5685,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B9" s="24">
         <v>0.4125385351058188</v>
@@ -5489,7 +5705,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B10" s="42">
         <v>24.92</v>
@@ -5509,7 +5725,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B11" s="22">
         <v>53</v>
@@ -5529,7 +5745,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5539,7 +5755,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5564,7 +5780,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="B16" s="25">
         <v>1975000</v>
@@ -5584,7 +5800,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B17" s="25">
         <v>1160236</v>
@@ -5604,7 +5820,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B18" s="26">
         <v>814764</v>
@@ -5624,7 +5840,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B19" s="24">
         <v>0.4125385351058188</v>
@@ -5644,7 +5860,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B20" s="42">
         <v>24.92</v>
@@ -5664,7 +5880,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B21" s="22">
         <v>45</v>
@@ -5684,7 +5900,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5694,7 +5910,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5719,7 +5935,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="B26" s="25">
         <v>1975000</v>
@@ -5739,7 +5955,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="B27" s="25">
         <v>1187376</v>
@@ -5759,7 +5975,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B28" s="26">
         <v>787624</v>
@@ -5779,7 +5995,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="B29" s="24">
         <v>0.39879676295392</v>
@@ -5799,7 +6015,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="B30" s="42">
         <v>24.12</v>
@@ -5819,7 +6035,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B31" s="22">
         <v>54</v>
@@ -5865,7 +6081,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5899,7 +6115,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -5923,7 +6139,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -5931,7 +6147,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -5969,7 +6185,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>348</v>
+        <v>320</v>
       </c>
       <c r="D13" s="25">
         <v>1975000</v>
@@ -5989,7 +6205,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D14" s="25">
         <v>1160236</v>
@@ -6009,7 +6225,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="D15" s="25">
         <v>789764</v>
@@ -6029,7 +6245,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="D16" s="25">
         <v>864756</v>
@@ -6049,7 +6265,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D17" s="25">
         <v>231645</v>
@@ -6069,7 +6285,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6107,7 +6323,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D21" s="24">
         <v>0.3998803072577175</v>
@@ -6127,7 +6343,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="D22" s="42">
         <v>24.92</v>
@@ -6167,7 +6383,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D24" s="22">
         <v>100</v>
@@ -6187,7 +6403,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7484,18 +7700,23 @@
         <v>195</v>
       </c>
       <c r="B12" s="26">
+        <f>SUM(B5:B11)</f>
         <v>1975000</v>
       </c>
       <c r="C12" s="26">
+        <f>SUM(C5:C11)</f>
         <v>2621350</v>
       </c>
       <c r="D12" s="26">
+        <f>SUM(D5:D11)</f>
         <v>3304704</v>
       </c>
       <c r="E12" s="26">
+        <f>SUM(E5:E11)</f>
         <v>3922890</v>
       </c>
       <c r="F12" s="26">
+        <f>SUM(F5:F11)</f>
         <v>4361347</v>
       </c>
     </row>
@@ -7879,18 +8100,23 @@
         <v>204</v>
       </c>
       <c r="B6" s="30">
+        <f>SUM(B5:B5)</f>
         <v>60000</v>
       </c>
       <c r="C6" s="30">
+        <f>SUM(C5:C5)</f>
         <v>80340</v>
       </c>
       <c r="D6" s="30">
+        <f>SUM(D5:D5)</f>
         <v>101846</v>
       </c>
       <c r="E6" s="30">
+        <f>SUM(E5:E5)</f>
         <v>121293</v>
       </c>
       <c r="F6" s="30">
+        <f>SUM(F5:F5)</f>
         <v>135061</v>
       </c>
     </row>
@@ -7929,18 +8155,23 @@
         <v>206</v>
       </c>
       <c r="B9" s="30">
+        <f>SUM(B8:B8)</f>
         <v>40000</v>
       </c>
       <c r="C9" s="30">
+        <f>SUM(C8:C8)</f>
         <v>53560</v>
       </c>
       <c r="D9" s="30">
+        <f>SUM(D8:D8)</f>
         <v>67898</v>
       </c>
       <c r="E9" s="30">
+        <f>SUM(E8:E8)</f>
         <v>80862</v>
       </c>
       <c r="F9" s="30">
+        <f>SUM(F8:F8)</f>
         <v>90041</v>
       </c>
     </row>
@@ -8039,18 +8270,23 @@
         <v>211</v>
       </c>
       <c r="B15" s="30">
+        <f>SUM(B11:B14)</f>
         <v>136400</v>
       </c>
       <c r="C15" s="30">
+        <f>SUM(C11:C14)</f>
         <v>140492</v>
       </c>
       <c r="D15" s="30">
+        <f>SUM(D11:D14)</f>
         <v>144707</v>
       </c>
       <c r="E15" s="30">
+        <f>SUM(E11:E14)</f>
         <v>149048</v>
       </c>
       <c r="F15" s="30">
+        <f>SUM(F11:F14)</f>
         <v>153519</v>
       </c>
     </row>
@@ -8129,18 +8365,23 @@
         <v>215</v>
       </c>
       <c r="B20" s="30">
+        <f>SUM(B17:B19)</f>
         <v>35000</v>
       </c>
       <c r="C20" s="30">
+        <f>SUM(C17:C19)</f>
         <v>36050</v>
       </c>
       <c r="D20" s="30">
+        <f>SUM(D17:D19)</f>
         <v>37132</v>
       </c>
       <c r="E20" s="30">
+        <f>SUM(E17:E19)</f>
         <v>38245</v>
       </c>
       <c r="F20" s="30">
+        <f>SUM(F17:F19)</f>
         <v>39393</v>
       </c>
     </row>
@@ -8149,18 +8390,23 @@
         <v>216</v>
       </c>
       <c r="B22" s="26">
+        <f>B6+B9+B15+B20</f>
         <v>271400</v>
       </c>
       <c r="C22" s="26">
+        <f>C6+C9+C15+C20</f>
         <v>310442</v>
       </c>
       <c r="D22" s="26">
+        <f>D6+D9+D15+D20</f>
         <v>351582</v>
       </c>
       <c r="E22" s="26">
+        <f>E6+E9+E15+E20</f>
         <v>389448</v>
       </c>
       <c r="F22" s="26">
+        <f>F6+F9+F15+F20</f>
         <v>418014</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -216,7 +216,7 @@
     <t>Underwriting Snapshot</t>
   </si>
   <si>
-    <t>CONFIDENTIAL — Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
+    <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
     <t>How to Use This Workbook</t>
@@ -225,10 +225,10 @@
     <t>Color Legend</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs — change these to update your model.</t>
-  </si>
-  <si>
-    <t>Gray cells contain formulas — do not edit.</t>
+    <t>Yellow cells are editable inputs - change these to update your model.</t>
+  </si>
+  <si>
+    <t>Gray cells contain formulas - do not edit.</t>
   </si>
   <si>
     <t>Green cells are key outputs and summary metrics.</t>
@@ -240,7 +240,7 @@
     <t>Navigation</t>
   </si>
   <si>
-    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
+    <t>The Assumptions tab is the central control panel - all other tabs reference it.</t>
   </si>
   <si>
     <t>Structure</t>
@@ -279,7 +279,7 @@
     <t>user-provided assumptions and should be independently verified.</t>
   </si>
   <si>
-    <t>Heritage Academy — Assumptions</t>
+    <t>Heritage Academy - Assumptions</t>
   </si>
   <si>
     <t>Yellow cells are editable inputs. All other cells are formulas.</t>
@@ -588,7 +588,7 @@
     <t>Enrollment Growth Rate</t>
   </si>
   <si>
-    <t>—</t>
+    <t>-</t>
   </si>
   <si>
     <t>Tuition &amp; Funding Drivers</t>
@@ -744,7 +744,7 @@
     <t>TOTAL PERSONNEL</t>
   </si>
   <si>
-    <t>Heritage Academy — Budget Detail</t>
+    <t>Heritage Academy - Budget Detail</t>
   </si>
   <si>
     <t>REVENUE</t>
@@ -825,7 +825,7 @@
     <t>Total Capital &amp; Debt</t>
   </si>
   <si>
-    <t>Heritage Academy — Budget Summary</t>
+    <t>Heritage Academy - Budget Summary</t>
   </si>
   <si>
     <t>Total Capital &amp; Debt Service</t>
@@ -849,7 +849,7 @@
     <t>Cost per Student</t>
   </si>
   <si>
-    <t>Heritage Academy — Year 1 Monthly Cash Flow</t>
+    <t>Heritage Academy - Year 1 Monthly Cash Flow</t>
   </si>
   <si>
     <t>July</t>
@@ -921,7 +921,7 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
-    <t>Heritage Academy — 5-Year Operating Statement</t>
+    <t>Heritage Academy - 5-Year Operating Statement</t>
   </si>
   <si>
     <t>Capital &amp; Debt Service</t>
@@ -945,7 +945,7 @@
     <t>Ending Balance</t>
   </si>
   <si>
-    <t>Heritage Academy — Balance Sheet</t>
+    <t>Heritage Academy - Balance Sheet</t>
   </si>
   <si>
     <t>ASSETS</t>
@@ -1098,7 +1098,7 @@
     <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +10%</t>
   </si>
   <si>
-    <t>Underwriting Snapshot — Loan Committee Summary</t>
+    <t>Underwriting Snapshot - Loan Committee Summary</t>
   </si>
   <si>
     <t>Entity</t>
@@ -1125,7 +1125,7 @@
     <t>Enrollment</t>
   </si>
   <si>
-    <t>Prepared by SchoolStack Budget — budget.schoolstack.ai</t>
+    <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -1083,19 +1083,19 @@
     <t>BASE CASE</t>
   </si>
   <si>
-    <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +0%</t>
+    <t>Enrollment: +0%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>LOW ENROLLMENT</t>
   </si>
   <si>
-    <t>Enrollment: -15%  |  Revenue: +0%  |  Expenses: +0%</t>
+    <t>Enrollment: -15%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +0%</t>
   </si>
   <si>
     <t>HIGH COSTS</t>
   </si>
   <si>
-    <t>Enrollment: +0%  |  Revenue: +0%  |  Expenses: +10%</t>
+    <t>Enrollment: +0%  |  Revenue: +0%  |  Staffing: +0%  |  Facility: +0%  |  Expenses: +10%</t>
   </si>
   <si>
     <t>Underwriting Snapshot - Loan Committee Summary</t>
@@ -5783,19 +5783,19 @@
         <v>320</v>
       </c>
       <c r="B16" s="25">
-        <v>1975000</v>
+        <v>1678750</v>
       </c>
       <c r="C16" s="25">
-        <v>2621350</v>
+        <v>2228148</v>
       </c>
       <c r="D16" s="25">
-        <v>3304704</v>
+        <v>2808998</v>
       </c>
       <c r="E16" s="25">
-        <v>3922890</v>
+        <v>3334456</v>
       </c>
       <c r="F16" s="25">
-        <v>4361347</v>
+        <v>3707145</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5823,19 +5823,19 @@
         <v>268</v>
       </c>
       <c r="B18" s="26">
-        <v>814764</v>
+        <v>518514</v>
       </c>
       <c r="C18" s="26">
-        <v>1396428</v>
+        <v>1003226</v>
       </c>
       <c r="D18" s="26">
-        <v>2012229</v>
+        <v>1516524</v>
       </c>
       <c r="E18" s="26">
-        <v>2565345</v>
+        <v>1976912</v>
       </c>
       <c r="F18" s="26">
-        <v>2947215</v>
+        <v>2293013</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5843,19 +5843,19 @@
         <v>269</v>
       </c>
       <c r="B19" s="24">
-        <v>0.4125385351058188</v>
+        <v>0.308868864830375</v>
       </c>
       <c r="C19" s="24">
-        <v>0.5327134670433142</v>
+        <v>0.45025113769801683</v>
       </c>
       <c r="D19" s="24">
-        <v>0.6088985689741885</v>
+        <v>0.5398806693813982</v>
       </c>
       <c r="E19" s="24">
-        <v>0.6539426893351535</v>
+        <v>0.5928737521590041</v>
       </c>
       <c r="F19" s="24">
-        <v>0.6757579942908114</v>
+        <v>0.6185388168127194</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5863,19 +5863,19 @@
         <v>322</v>
       </c>
       <c r="B20" s="42">
-        <v>24.92</v>
+        <v>16.22</v>
       </c>
       <c r="C20" s="42">
-        <v>41.99</v>
+        <v>30.45</v>
       </c>
       <c r="D20" s="42">
-        <v>60.07</v>
+        <v>45.52</v>
       </c>
       <c r="E20" s="42">
-        <v>76.31</v>
+        <v>59.03</v>
       </c>
       <c r="F20" s="42">
-        <v>87.52</v>
+        <v>68.31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -5883,19 +5883,19 @@
         <v>330</v>
       </c>
       <c r="B21" s="22">
-        <v>45</v>
+        <v>54</v>
       </c>
       <c r="C21" s="22">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D21" s="22">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="E21" s="22">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="F21" s="22">
-        <v>43</v>
+        <v>52</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -5654,13 +5654,13 @@
         <v>1224922</v>
       </c>
       <c r="D7" s="25">
-        <v>1292474</v>
+        <v>1292490</v>
       </c>
       <c r="E7" s="25">
-        <v>1357545</v>
+        <v>1357593</v>
       </c>
       <c r="F7" s="25">
-        <v>1414132</v>
+        <v>1414023</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5674,13 +5674,13 @@
         <v>1396428</v>
       </c>
       <c r="D8" s="26">
-        <v>2012229</v>
+        <v>2012214</v>
       </c>
       <c r="E8" s="26">
-        <v>2565345</v>
+        <v>2565297</v>
       </c>
       <c r="F8" s="26">
-        <v>2947215</v>
+        <v>2947324</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5694,13 +5694,13 @@
         <v>0.5327134670433142</v>
       </c>
       <c r="D9" s="24">
-        <v>0.6088985689741885</v>
+        <v>0.6088938665856081</v>
       </c>
       <c r="E9" s="24">
-        <v>0.6539426893351535</v>
+        <v>0.6539303894233892</v>
       </c>
       <c r="F9" s="24">
-        <v>0.6757579942908114</v>
+        <v>0.6757830034045176</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5809,13 +5809,13 @@
         <v>1224922</v>
       </c>
       <c r="D17" s="25">
-        <v>1292474</v>
+        <v>1292490</v>
       </c>
       <c r="E17" s="25">
-        <v>1357545</v>
+        <v>1357593</v>
       </c>
       <c r="F17" s="25">
-        <v>1414132</v>
+        <v>1414023</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5829,13 +5829,13 @@
         <v>1003226</v>
       </c>
       <c r="D18" s="26">
-        <v>1516524</v>
+        <v>1516508</v>
       </c>
       <c r="E18" s="26">
-        <v>1976912</v>
+        <v>1976863</v>
       </c>
       <c r="F18" s="26">
-        <v>2293013</v>
+        <v>2293122</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5849,13 +5849,13 @@
         <v>0.45025113769801683</v>
       </c>
       <c r="D19" s="24">
-        <v>0.5398806693813982</v>
+        <v>0.5398751371595389</v>
       </c>
       <c r="E19" s="24">
-        <v>0.5928737521590041</v>
+        <v>0.5928592816745755</v>
       </c>
       <c r="F19" s="24">
-        <v>0.6185388168127194</v>
+        <v>0.6185682392994323</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -5875,7 +5875,7 @@
         <v>59.03</v>
       </c>
       <c r="F20" s="42">
-        <v>68.31</v>
+        <v>68.32</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -5958,19 +5958,19 @@
         <v>266</v>
       </c>
       <c r="B27" s="25">
-        <v>1187376</v>
+        <v>1173736</v>
       </c>
       <c r="C27" s="25">
-        <v>1255966</v>
+        <v>1241917</v>
       </c>
       <c r="D27" s="25">
-        <v>1327632</v>
+        <v>1313179</v>
       </c>
       <c r="E27" s="25">
-        <v>1396490</v>
+        <v>1381638</v>
       </c>
       <c r="F27" s="25">
-        <v>1455933</v>
+        <v>1440462</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
@@ -5978,19 +5978,19 @@
         <v>268</v>
       </c>
       <c r="B28" s="26">
-        <v>787624</v>
+        <v>801264</v>
       </c>
       <c r="C28" s="26">
-        <v>1365384</v>
+        <v>1379433</v>
       </c>
       <c r="D28" s="26">
-        <v>1977071</v>
+        <v>1991524</v>
       </c>
       <c r="E28" s="26">
-        <v>2526400</v>
+        <v>2541252</v>
       </c>
       <c r="F28" s="26">
-        <v>2905413</v>
+        <v>2920885</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -5998,19 +5998,19 @@
         <v>269</v>
       </c>
       <c r="B29" s="24">
-        <v>0.39879676295392</v>
+        <v>0.4057030920678441</v>
       </c>
       <c r="C29" s="24">
-        <v>0.5208706379666935</v>
+        <v>0.5262301664539233</v>
       </c>
       <c r="D29" s="24">
-        <v>0.5982597246724228</v>
+        <v>0.6026333351945166</v>
       </c>
       <c r="E29" s="24">
-        <v>0.6440151127334821</v>
+        <v>0.6478009541272017</v>
       </c>
       <c r="F29" s="24">
-        <v>0.6661734781617792</v>
+        <v>0.6697208161513672</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -6018,19 +6018,19 @@
         <v>322</v>
       </c>
       <c r="B30" s="42">
-        <v>24.12</v>
+        <v>24.52</v>
       </c>
       <c r="C30" s="42">
-        <v>41.08</v>
+        <v>41.49</v>
       </c>
       <c r="D30" s="42">
-        <v>59.04</v>
+        <v>59.46</v>
       </c>
       <c r="E30" s="42">
-        <v>75.17</v>
+        <v>75.6</v>
       </c>
       <c r="F30" s="42">
-        <v>86.29</v>
+        <v>86.75</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -6038,10 +6038,10 @@
         <v>330</v>
       </c>
       <c r="B31" s="22">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C31" s="22">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D31" s="22">
         <v>52</v>
@@ -6050,7 +6050,7 @@
         <v>52</v>
       </c>
       <c r="F31" s="22">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="680" uniqueCount="365">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="366">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -505,6 +505,9 @@
   </si>
   <si>
     <t>Salary Escalation Rate</t>
+  </si>
+  <si>
+    <t>Derived from tuition escalation rate</t>
   </si>
   <si>
     <t>Cost Inflation Rate</t>
@@ -1139,7 +1142,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1207,6 +1210,12 @@
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF808080"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1293,7 +1302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1322,6 +1331,7 @@
     <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1337,14 +1347,14 @@
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2010,7 +2020,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2042,25 +2052,25 @@
       <c r="A4" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="20">
+      <c r="B4" s="21">
         <v>100</v>
       </c>
-      <c r="C4" s="20">
+      <c r="C4" s="21">
         <v>130</v>
       </c>
-      <c r="D4" s="20">
+      <c r="D4" s="21">
         <v>160</v>
       </c>
-      <c r="E4" s="20">
+      <c r="E4" s="21">
         <v>185</v>
       </c>
-      <c r="F4" s="20">
+      <c r="F4" s="21">
         <v>200</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2072,19 +2082,19 @@
       <c r="A7" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="25">
+      <c r="B7" s="26">
         <v>1050000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>1405950</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>1782312</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>2122622</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>2363569</v>
       </c>
     </row>
@@ -2092,19 +2102,19 @@
       <c r="A8" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="26">
         <v>35000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>46865</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>59410</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>70754</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>78786</v>
       </c>
     </row>
@@ -2112,19 +2122,19 @@
       <c r="A9" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="26">
         <v>105000</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>140595</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>178231</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>212262</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>236357</v>
       </c>
     </row>
@@ -2132,19 +2142,19 @@
       <c r="A10" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="26">
         <v>870000</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>1164930</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>1476773</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>1758744</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>1958385</v>
       </c>
     </row>
@@ -2152,19 +2162,19 @@
       <c r="A11" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="26">
         <v>50000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>51500</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>53045</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>54636</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>56275</v>
       </c>
     </row>
@@ -2172,19 +2182,19 @@
       <c r="A12" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="26">
         <v>25000</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <v>25750</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <v>26523</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <v>27318</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <v>28138</v>
       </c>
     </row>
@@ -2192,64 +2202,64 @@
       <c r="A13" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="26">
         <v>50000</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>66950</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>84872</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>101077</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>112551</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B14" s="26">
+        <v>196</v>
+      </c>
+      <c r="B14" s="27">
         <f>SUM(B7:B13)</f>
         <v>1975000</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>SUM(C7:C13)</f>
         <v>2621350</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>SUM(D7:D13)</f>
         <v>3304704</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>SUM(E7:E13)</f>
         <v>3922890</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>SUM(F7:F13)</f>
         <v>4361347</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B16" s="25">
+        <v>225</v>
+      </c>
+      <c r="B16" s="26">
         <v>19750</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <v>20164</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <v>20654</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>21205</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>21807</v>
       </c>
     </row>
@@ -2279,7 +2289,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2319,65 +2329,65 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B5" s="25">
+        <v>227</v>
+      </c>
+      <c r="B5" s="26">
         <v>382032</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>393493</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>405298</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>417457</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>429980</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B6" s="25">
+        <v>228</v>
+      </c>
+      <c r="B6" s="26">
         <v>122544</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>126220</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>130007</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>133907</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>137924</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="B7" s="30">
+        <v>229</v>
+      </c>
+      <c r="B7" s="31">
         <f>SUM(B5:B6)</f>
         <v>504576</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <f>SUM(C5:C6)</f>
         <v>519713</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <f>SUM(D5:D6)</f>
         <v>535305</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <f>SUM(E5:E6)</f>
         <v>551364</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <f>SUM(F5:F6)</f>
         <v>567905</v>
       </c>
@@ -2394,65 +2404,65 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B9" s="25">
+        <v>230</v>
+      </c>
+      <c r="B9" s="26">
         <v>126018</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>129798</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>133692</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>137703</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>141834</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B10" s="25">
+        <v>231</v>
+      </c>
+      <c r="B10" s="26">
         <v>99488</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>102472</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>105546</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>108713</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>111974</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="B11" s="30">
+        <v>232</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
         <v>225505</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUM(C9:C10)</f>
         <v>232270</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUM(D9:D10)</f>
         <v>239238</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUM(E9:E10)</f>
         <v>246415</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>SUM(F9:F10)</f>
         <v>253808</v>
       </c>
@@ -2469,45 +2479,45 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B13" s="25">
+        <v>233</v>
+      </c>
+      <c r="B13" s="26">
         <v>68978</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>71047</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>73179</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>75374</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>77635</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="B14" s="30">
+        <v>234</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
         <v>68978</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <f>SUM(C13:C13)</f>
         <v>71047</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <f>SUM(D13:D13)</f>
         <v>73179</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <f>SUM(E13:E13)</f>
         <v>75374</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <f>SUM(F13:F13)</f>
         <v>77635</v>
       </c>
@@ -2524,70 +2534,70 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B16" s="25">
+        <v>235</v>
+      </c>
+      <c r="B16" s="26">
         <v>55713</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <v>57384</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <v>59106</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>60879</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>62705</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="B17" s="30">
+        <v>236</v>
+      </c>
+      <c r="B17" s="31">
         <f>SUM(B16:B16)</f>
         <v>55713</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <f>SUM(C16:C16)</f>
         <v>57384</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <f>SUM(D16:D16)</f>
         <v>59106</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <f>SUM(E16:E16)</f>
         <v>60879</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <f>SUM(F16:F16)</f>
         <v>62705</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>236</v>
-      </c>
-      <c r="B19" s="26">
+        <v>237</v>
+      </c>
+      <c r="B19" s="27">
         <f>B7+B11+B14+B17</f>
         <v>854772</v>
       </c>
-      <c r="C19" s="26">
+      <c r="C19" s="27">
         <f>C7+C11+C14+C17</f>
         <v>880415</v>
       </c>
-      <c r="D19" s="26">
+      <c r="D19" s="27">
         <f>D7+D11+D14+D17</f>
         <v>906828</v>
       </c>
-      <c r="E19" s="26">
+      <c r="E19" s="27">
         <f>E7+E11+E14+E17</f>
         <v>934032</v>
       </c>
-      <c r="F19" s="26">
+      <c r="F19" s="27">
         <f>F7+F11+F14+F17</f>
         <v>962053</v>
       </c>
@@ -2618,7 +2628,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2648,7 +2658,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2658,172 +2668,172 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="25">
+        <v>240</v>
+      </c>
+      <c r="B5" s="26">
         <v>1050000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>1405950</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>1782312</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>2122622</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>2363569</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>240</v>
-      </c>
-      <c r="B6" s="25">
+        <v>241</v>
+      </c>
+      <c r="B6" s="26">
         <v>35000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>46865</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>59410</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>70754</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>78786</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="B7" s="25">
+        <v>242</v>
+      </c>
+      <c r="B7" s="26">
         <v>105000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>140595</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>178231</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>212262</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>236357</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="B8" s="25">
+        <v>243</v>
+      </c>
+      <c r="B8" s="26">
         <v>870000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>1164930</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>1476773</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>1758744</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>1958385</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="B9" s="25">
+        <v>244</v>
+      </c>
+      <c r="B9" s="26">
         <v>50000</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>51500</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>53045</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>54636</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>56275</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B10" s="25">
+        <v>245</v>
+      </c>
+      <c r="B10" s="26">
         <v>25000</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>25750</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>26523</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>27318</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>28138</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>245</v>
-      </c>
-      <c r="B11" s="25">
+        <v>246</v>
+      </c>
+      <c r="B11" s="26">
         <v>50000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>66950</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>84872</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>101077</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>112551</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B12" s="30">
+        <v>247</v>
+      </c>
+      <c r="B12" s="31">
         <f>SUM(B5:B11)</f>
         <v>1975000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <f>SUM(C5:C11)</f>
         <v>2621350</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <f>SUM(D5:D11)</f>
         <v>3304704</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <f>SUM(E5:E11)</f>
         <v>3922890</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <f>SUM(F5:F11)</f>
         <v>4361347</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2833,145 +2843,145 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B15" s="25">
+        <v>230</v>
+      </c>
+      <c r="B15" s="26">
         <v>126018</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <v>129798</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <v>133692</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <v>137703</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <v>141834</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="B16" s="25">
+        <v>231</v>
+      </c>
+      <c r="B16" s="26">
         <v>99488</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <v>102472</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <v>105546</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>108713</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>111974</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="B17" s="25">
+        <v>227</v>
+      </c>
+      <c r="B17" s="26">
         <v>382032</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>393493</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <v>405298</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>417457</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>429980</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>227</v>
-      </c>
-      <c r="B18" s="25">
+        <v>228</v>
+      </c>
+      <c r="B18" s="26">
         <v>122544</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <v>126220</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <v>130007</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <v>133907</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <v>137924</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B19" s="25">
+        <v>235</v>
+      </c>
+      <c r="B19" s="26">
         <v>55713</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <v>57384</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <v>59106</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <v>60879</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <v>62705</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="B20" s="25">
+        <v>233</v>
+      </c>
+      <c r="B20" s="26">
         <v>68978</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <v>71047</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <v>73179</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <v>75374</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <v>77635</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B21" s="30">
+        <v>200</v>
+      </c>
+      <c r="B21" s="31">
         <f>SUM(B15:B20)</f>
         <v>854772</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <f>SUM(C15:C20)</f>
         <v>880415</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <f>SUM(D15:D20)</f>
         <v>906828</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <f>SUM(E15:E20)</f>
         <v>934032</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <f>SUM(F15:F20)</f>
         <v>962053</v>
       </c>
@@ -2987,283 +2997,283 @@
       <c r="F23" s="13"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="31" t="s">
+      <c r="A24" s="32" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="B25" s="25">
+        <v>249</v>
+      </c>
+      <c r="B25" s="26">
         <v>60000</v>
       </c>
-      <c r="C25" s="25">
+      <c r="C25" s="26">
         <v>80340</v>
       </c>
-      <c r="D25" s="25">
+      <c r="D25" s="26">
         <v>101846</v>
       </c>
-      <c r="E25" s="25">
+      <c r="E25" s="26">
         <v>121293</v>
       </c>
-      <c r="F25" s="25">
+      <c r="F25" s="26">
         <v>135061</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="31" t="s">
+      <c r="A26" s="32" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>249</v>
-      </c>
-      <c r="B27" s="25">
+        <v>250</v>
+      </c>
+      <c r="B27" s="26">
         <v>40000</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="26">
         <v>53560</v>
       </c>
-      <c r="D27" s="25">
+      <c r="D27" s="26">
         <v>67898</v>
       </c>
-      <c r="E27" s="25">
+      <c r="E27" s="26">
         <v>80862</v>
       </c>
-      <c r="F27" s="25">
+      <c r="F27" s="26">
         <v>90041</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="31" t="s">
+      <c r="A28" s="32" t="s">
         <v>136</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B29" s="25">
+        <v>251</v>
+      </c>
+      <c r="B29" s="26">
         <v>102000</v>
       </c>
-      <c r="C29" s="25">
+      <c r="C29" s="26">
         <v>105060</v>
       </c>
-      <c r="D29" s="25">
+      <c r="D29" s="26">
         <v>108212</v>
       </c>
-      <c r="E29" s="25">
+      <c r="E29" s="26">
         <v>111458</v>
       </c>
-      <c r="F29" s="25">
+      <c r="F29" s="26">
         <v>114802</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="B30" s="25">
+        <v>252</v>
+      </c>
+      <c r="B30" s="26">
         <v>14400</v>
       </c>
-      <c r="C30" s="25">
+      <c r="C30" s="26">
         <v>14832</v>
       </c>
-      <c r="D30" s="25">
+      <c r="D30" s="26">
         <v>15277</v>
       </c>
-      <c r="E30" s="25">
+      <c r="E30" s="26">
         <v>15735</v>
       </c>
-      <c r="F30" s="25">
+      <c r="F30" s="26">
         <v>16207</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>252</v>
-      </c>
-      <c r="B31" s="25">
+        <v>253</v>
+      </c>
+      <c r="B31" s="26">
         <v>12000</v>
       </c>
-      <c r="C31" s="25">
+      <c r="C31" s="26">
         <v>12360</v>
       </c>
-      <c r="D31" s="25">
+      <c r="D31" s="26">
         <v>12731</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="26">
         <v>13113</v>
       </c>
-      <c r="F31" s="25">
+      <c r="F31" s="26">
         <v>13506</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="B32" s="25">
+        <v>254</v>
+      </c>
+      <c r="B32" s="26">
         <v>8000</v>
       </c>
-      <c r="C32" s="25">
+      <c r="C32" s="26">
         <v>8240</v>
       </c>
-      <c r="D32" s="25">
+      <c r="D32" s="26">
         <v>8487</v>
       </c>
-      <c r="E32" s="25">
+      <c r="E32" s="26">
         <v>8742</v>
       </c>
-      <c r="F32" s="25">
+      <c r="F32" s="26">
         <v>9004</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B33" s="30">
+        <v>255</v>
+      </c>
+      <c r="B33" s="31">
         <f>SUM(B29:B32)</f>
         <v>136400</v>
       </c>
-      <c r="C33" s="30">
+      <c r="C33" s="31">
         <f>SUM(C29:C32)</f>
         <v>140492</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33" s="31">
         <f>SUM(D29:D32)</f>
         <v>144707</v>
       </c>
-      <c r="E33" s="30">
+      <c r="E33" s="31">
         <f>SUM(E29:E32)</f>
         <v>149048</v>
       </c>
-      <c r="F33" s="30">
+      <c r="F33" s="31">
         <f>SUM(F29:F32)</f>
         <v>153519</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="31" t="s">
+      <c r="A34" s="32" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="B35" s="25">
+        <v>256</v>
+      </c>
+      <c r="B35" s="26">
         <v>15000</v>
       </c>
-      <c r="C35" s="25">
+      <c r="C35" s="26">
         <v>15450</v>
       </c>
-      <c r="D35" s="25">
+      <c r="D35" s="26">
         <v>15914</v>
       </c>
-      <c r="E35" s="25">
+      <c r="E35" s="26">
         <v>16391</v>
       </c>
-      <c r="F35" s="25">
+      <c r="F35" s="26">
         <v>16883</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="B36" s="25">
+        <v>257</v>
+      </c>
+      <c r="B36" s="26">
         <v>8000</v>
       </c>
-      <c r="C36" s="25">
+      <c r="C36" s="26">
         <v>8240</v>
       </c>
-      <c r="D36" s="25">
+      <c r="D36" s="26">
         <v>8487</v>
       </c>
-      <c r="E36" s="25">
+      <c r="E36" s="26">
         <v>8742</v>
       </c>
-      <c r="F36" s="25">
+      <c r="F36" s="26">
         <v>9004</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="B37" s="25">
+        <v>258</v>
+      </c>
+      <c r="B37" s="26">
         <v>12000</v>
       </c>
-      <c r="C37" s="25">
+      <c r="C37" s="26">
         <v>12360</v>
       </c>
-      <c r="D37" s="25">
+      <c r="D37" s="26">
         <v>12731</v>
       </c>
-      <c r="E37" s="25">
+      <c r="E37" s="26">
         <v>13113</v>
       </c>
-      <c r="F37" s="25">
+      <c r="F37" s="26">
         <v>13506</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B38" s="30">
+        <v>259</v>
+      </c>
+      <c r="B38" s="31">
         <f>SUM(B35:B37)</f>
         <v>35000</v>
       </c>
-      <c r="C38" s="30">
+      <c r="C38" s="31">
         <f>SUM(C35:C37)</f>
         <v>36050</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38" s="31">
         <f>SUM(D35:D37)</f>
         <v>37132</v>
       </c>
-      <c r="E38" s="30">
+      <c r="E38" s="31">
         <f>SUM(E35:E37)</f>
         <v>38245</v>
       </c>
-      <c r="F38" s="30">
+      <c r="F38" s="31">
         <f>SUM(F35:F37)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B39" s="30">
+        <v>260</v>
+      </c>
+      <c r="B39" s="31">
         <f>B25+B27+B33+B38</f>
         <v>271400</v>
       </c>
-      <c r="C39" s="30">
+      <c r="C39" s="31">
         <f>C25+C27+C33+C38</f>
         <v>310442</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39" s="31">
         <f>D25+D27+D33+D38</f>
         <v>351582</v>
       </c>
-      <c r="E39" s="30">
+      <c r="E39" s="31">
         <f>E25+E27+E33+E38</f>
         <v>389448</v>
       </c>
-      <c r="F39" s="30">
+      <c r="F39" s="31">
         <f>F25+F27+F33+F38</f>
         <v>418014</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -3273,65 +3283,65 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>261</v>
-      </c>
-      <c r="B42" s="25">
+        <v>262</v>
+      </c>
+      <c r="B42" s="26">
         <v>34064</v>
       </c>
-      <c r="C42" s="25">
+      <c r="C42" s="26">
         <v>34064</v>
       </c>
-      <c r="D42" s="25">
+      <c r="D42" s="26">
         <v>34064</v>
       </c>
-      <c r="E42" s="25">
+      <c r="E42" s="26">
         <v>34064</v>
       </c>
-      <c r="F42" s="25">
+      <c r="F42" s="26">
         <v>34064</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B43" s="25">
+        <v>263</v>
+      </c>
+      <c r="B43" s="26">
         <v>25000</v>
       </c>
-      <c r="C43" s="25">
+      <c r="C43" s="26">
         <v>10000</v>
       </c>
-      <c r="D43" s="25">
+      <c r="D43" s="26">
         <v>10000</v>
       </c>
-      <c r="E43" s="25">
+      <c r="E43" s="26">
         <v>5000</v>
       </c>
-      <c r="F43" s="25">
+      <c r="F43" s="26">
         <v>5000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="B44" s="30">
+        <v>264</v>
+      </c>
+      <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
         <v>59064</v>
       </c>
-      <c r="C44" s="30">
+      <c r="C44" s="31">
         <f>SUM(C42:C43)</f>
         <v>44064</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44" s="31">
         <f>SUM(D42:D43)</f>
         <v>44064</v>
       </c>
-      <c r="E44" s="30">
+      <c r="E44" s="31">
         <f>SUM(E42:E43)</f>
         <v>39064</v>
       </c>
-      <c r="F44" s="30">
+      <c r="F44" s="31">
         <f>SUM(F42:F43)</f>
         <v>39064</v>
       </c>
@@ -3362,7 +3372,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3392,132 +3402,132 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="28">
+        <v>247</v>
+      </c>
+      <c r="B4" s="29">
         <f>'Budget Detail'!B12</f>
         <v>1975000</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="29">
         <f>'Budget Detail'!C12</f>
         <v>2621350</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="29">
         <f>'Budget Detail'!D12</f>
         <v>3304704</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="29">
         <f>'Budget Detail'!E12</f>
         <v>3922890</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <f>'Budget Detail'!F12</f>
         <v>4361347</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B5" s="28">
+        <v>200</v>
+      </c>
+      <c r="B5" s="29">
         <f>'Budget Detail'!B21</f>
         <v>854772</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="29">
         <f>'Budget Detail'!C21</f>
         <v>880415</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="29">
         <f>'Budget Detail'!D21</f>
         <v>906828</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="29">
         <f>'Budget Detail'!E21</f>
         <v>934032</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <f>'Budget Detail'!F21</f>
         <v>962053</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="B6" s="28">
+        <v>260</v>
+      </c>
+      <c r="B6" s="29">
         <f>'Budget Detail'!B39</f>
         <v>271400</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="29">
         <f>'Budget Detail'!C39</f>
         <v>310442</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="29">
         <f>'Budget Detail'!D39</f>
         <v>351582</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="29">
         <f>'Budget Detail'!E39</f>
         <v>389448</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="29">
         <f>'Budget Detail'!F39</f>
         <v>418014</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="B7" s="28">
+        <v>266</v>
+      </c>
+      <c r="B7" s="29">
         <f>'Budget Detail'!B44</f>
         <v>59064</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="29">
         <f>'Budget Detail'!C44</f>
         <v>44064</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="29">
         <f>'Budget Detail'!D44</f>
         <v>44064</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="29">
         <f>'Budget Detail'!E44</f>
         <v>39064</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="29">
         <f>'Budget Detail'!F44</f>
         <v>39064</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B8" s="30">
+        <v>267</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>1185236</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>1234922</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>1302474</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>1362545</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3527,111 +3537,111 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B11" s="26">
+        <v>269</v>
+      </c>
+      <c r="B11" s="27">
         <f>B4-B8</f>
         <v>789764</v>
       </c>
-      <c r="C11" s="26">
+      <c r="C11" s="27">
         <f>C4-C8</f>
         <v>1386428</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="27">
         <f>D4-D8</f>
         <v>2002229</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="27">
         <f>E4-E8</f>
         <v>2560345</v>
       </c>
-      <c r="F11" s="26">
+      <c r="F11" s="27">
         <f>F4-F8</f>
         <v>2942215</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B12" s="24">
+        <v>270</v>
+      </c>
+      <c r="B12" s="25">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.39988031</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="25">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.52889864</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="25">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.60587258</v>
       </c>
-      <c r="E12" s="24">
+      <c r="E12" s="25">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.65266812</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="25">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.67461156</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>270</v>
-      </c>
-      <c r="B13" s="25">
+        <v>271</v>
+      </c>
+      <c r="B13" s="26">
         <v>789764</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>2176192</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>4178421</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>6738766</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>9680981</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B14" s="25">
+        <v>225</v>
+      </c>
+      <c r="B14" s="26">
         <v>19750</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <v>20164</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <v>20654</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>21205</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>21807</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>271</v>
-      </c>
-      <c r="B15" s="25">
+        <v>272</v>
+      </c>
+      <c r="B15" s="26">
         <v>11852</v>
       </c>
-      <c r="C15" s="25">
+      <c r="C15" s="26">
         <v>9499</v>
       </c>
-      <c r="D15" s="25">
+      <c r="D15" s="26">
         <v>8140</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <v>7365</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <v>7096</v>
       </c>
     </row>
@@ -3662,7 +3672,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3683,48 +3693,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3742,51 +3752,51 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="B4" s="30">
+        <v>247</v>
+      </c>
+      <c r="B4" s="31">
         <v>85833</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="31">
         <v>180333</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>180333</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>180333</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="31">
         <v>180333</v>
       </c>
-      <c r="G4" s="30">
+      <c r="G4" s="31">
         <v>180333</v>
       </c>
-      <c r="H4" s="30">
+      <c r="H4" s="31">
         <v>180333</v>
       </c>
-      <c r="I4" s="30">
+      <c r="I4" s="31">
         <v>180333</v>
       </c>
-      <c r="J4" s="30">
+      <c r="J4" s="31">
         <v>180333</v>
       </c>
-      <c r="K4" s="30">
+      <c r="K4" s="31">
         <v>180333</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="31">
         <v>180333</v>
       </c>
-      <c r="M4" s="30">
+      <c r="M4" s="31">
         <v>85833</v>
       </c>
-      <c r="N4" s="30">
+      <c r="N4" s="31">
         <v>1974996</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3804,139 +3814,139 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B7" s="25">
+        <v>288</v>
+      </c>
+      <c r="B7" s="26">
         <v>71231</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>71231</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>71231</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>71231</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>71231</v>
       </c>
-      <c r="G7" s="25">
+      <c r="G7" s="26">
         <v>71231</v>
       </c>
-      <c r="H7" s="25">
+      <c r="H7" s="26">
         <v>71231</v>
       </c>
-      <c r="I7" s="25">
+      <c r="I7" s="26">
         <v>71231</v>
       </c>
-      <c r="J7" s="25">
+      <c r="J7" s="26">
         <v>71231</v>
       </c>
-      <c r="K7" s="25">
+      <c r="K7" s="26">
         <v>71231</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="26">
         <v>71231</v>
       </c>
-      <c r="M7" s="25">
+      <c r="M7" s="26">
         <v>71231</v>
       </c>
-      <c r="N7" s="25">
+      <c r="N7" s="26">
         <v>854772</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B8" s="25">
+        <v>289</v>
+      </c>
+      <c r="B8" s="26">
         <v>22617</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>22617</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>22617</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>22617</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>22617</v>
       </c>
-      <c r="G8" s="25">
+      <c r="G8" s="26">
         <v>22617</v>
       </c>
-      <c r="H8" s="25">
+      <c r="H8" s="26">
         <v>22617</v>
       </c>
-      <c r="I8" s="25">
+      <c r="I8" s="26">
         <v>22617</v>
       </c>
-      <c r="J8" s="25">
+      <c r="J8" s="26">
         <v>22617</v>
       </c>
-      <c r="K8" s="25">
+      <c r="K8" s="26">
         <v>22617</v>
       </c>
-      <c r="L8" s="25">
+      <c r="L8" s="26">
         <v>22617</v>
       </c>
-      <c r="M8" s="25">
+      <c r="M8" s="26">
         <v>22617</v>
       </c>
-      <c r="N8" s="25">
+      <c r="N8" s="26">
         <v>271400</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="25">
+        <v>290</v>
+      </c>
+      <c r="B9" s="26">
         <v>4922</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>4922</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>4922</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>4922</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>4922</v>
       </c>
-      <c r="G9" s="25">
+      <c r="G9" s="26">
         <v>4922</v>
       </c>
-      <c r="H9" s="25">
+      <c r="H9" s="26">
         <v>4922</v>
       </c>
-      <c r="I9" s="25">
+      <c r="I9" s="26">
         <v>4922</v>
       </c>
-      <c r="J9" s="25">
+      <c r="J9" s="26">
         <v>4922</v>
       </c>
-      <c r="K9" s="25">
+      <c r="K9" s="26">
         <v>4922</v>
       </c>
-      <c r="L9" s="25">
+      <c r="L9" s="26">
         <v>4922</v>
       </c>
-      <c r="M9" s="25">
+      <c r="M9" s="26">
         <v>4922</v>
       </c>
-      <c r="N9" s="25">
+      <c r="N9" s="26">
         <v>59064</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3954,164 +3964,164 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="B12" s="28">
+        <v>267</v>
+      </c>
+      <c r="B12" s="29">
         <v>98770</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="29">
         <v>98770</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="29">
         <v>98770</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="29">
         <v>98770</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="29">
         <v>98770</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="29">
         <v>98770</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="29">
         <v>98770</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="29">
         <v>98770</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="29">
         <v>98770</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="29">
         <v>98770</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="29">
         <v>98770</v>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="29">
         <v>98770</v>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="29">
         <v>1185240</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="B13" s="28">
+        <v>292</v>
+      </c>
+      <c r="B13" s="29">
         <v>-12937</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="29">
         <v>81563</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="29">
         <v>81563</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <v>81563</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="29">
         <v>81563</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="29">
         <v>81563</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="29">
         <v>81563</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="29">
         <v>81563</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="29">
         <v>81563</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="29">
         <v>81563</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="29">
         <v>81563</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="29">
         <v>-12937</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="29">
         <v>789756</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="B14" s="32">
+        <v>293</v>
+      </c>
+      <c r="B14" s="33">
         <v>62063</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <v>143626</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <v>225189</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <v>306752</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <v>388315</v>
       </c>
-      <c r="G14" s="32">
+      <c r="G14" s="33">
         <v>469878</v>
       </c>
-      <c r="H14" s="32">
+      <c r="H14" s="33">
         <v>551441</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="33">
         <v>633004</v>
       </c>
-      <c r="J14" s="32">
+      <c r="J14" s="33">
         <v>714567</v>
       </c>
-      <c r="K14" s="32">
+      <c r="K14" s="33">
         <v>796130</v>
       </c>
-      <c r="L14" s="32">
+      <c r="L14" s="33">
         <v>877693</v>
       </c>
-      <c r="M14" s="32">
+      <c r="M14" s="33">
         <v>864756</v>
       </c>
-      <c r="N14" s="26">
+      <c r="N14" s="27">
         <v>864756</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="B17" s="25">
+        <v>161</v>
+      </c>
+      <c r="B17" s="26">
         <v>75000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="B18" s="32">
+        <v>295</v>
+      </c>
+      <c r="B18" s="33">
         <v>864756</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>295</v>
-      </c>
-      <c r="B19" s="25">
+        <v>296</v>
+      </c>
+      <c r="B19" s="26">
         <v>62063</v>
       </c>
     </row>
@@ -4141,7 +4151,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4171,7 +4181,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4180,28 +4190,28 @@
       <c r="F4" s="13"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
-        <v>246</v>
-      </c>
-      <c r="B5" s="30">
+      <c r="A5" s="34" t="s">
+        <v>247</v>
+      </c>
+      <c r="B5" s="31">
         <v>1975000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>2621350</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>3304704</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>3922890</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>4361347</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4211,92 +4221,92 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="B8" s="28">
+        <v>288</v>
+      </c>
+      <c r="B8" s="29">
         <v>854772</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <v>880415</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>906828</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <v>934032</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <v>962053</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="B9" s="28">
+        <v>289</v>
+      </c>
+      <c r="B9" s="29">
         <v>271400</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="29">
         <v>310442</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="29">
         <v>351582</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="29">
         <v>389448</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="29">
         <v>418014</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="B10" s="28">
+        <v>298</v>
+      </c>
+      <c r="B10" s="29">
         <v>59064</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="29">
         <v>44064</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="29">
         <v>44064</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="29">
         <v>39064</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="29">
         <v>39064</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="B11" s="30">
+      <c r="A11" s="34" t="s">
+        <v>267</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
         <v>1185236</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>SUM(C8:C10)</f>
         <v>1234922</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>SUM(D8:D10)</f>
         <v>1302474</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>SUM(E8:E10)</f>
         <v>1362545</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>SUM(F8:F10)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4305,51 +4315,51 @@
       <c r="F13" s="13"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="B14" s="26">
+      <c r="A14" s="34" t="s">
+        <v>269</v>
+      </c>
+      <c r="B14" s="27">
         <f>B5-B11</f>
         <v>789764</v>
       </c>
-      <c r="C14" s="26">
+      <c r="C14" s="27">
         <f>C5-C11</f>
         <v>1386428</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="27">
         <f>D5-D11</f>
         <v>2002229</v>
       </c>
-      <c r="E14" s="26">
+      <c r="E14" s="27">
         <f>E5-E11</f>
         <v>2560345</v>
       </c>
-      <c r="F14" s="26">
+      <c r="F14" s="27">
         <f>F5-F11</f>
         <v>2942215</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B15" s="24">
+        <v>270</v>
+      </c>
+      <c r="B15" s="25">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.39988031</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="25">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.52889864</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="25">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.60587258</v>
       </c>
-      <c r="E15" s="24">
+      <c r="E15" s="25">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.65266812</v>
       </c>
-      <c r="F15" s="24">
+      <c r="F15" s="25">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.67461156</v>
       </c>
@@ -4420,101 +4430,101 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>299</v>
-      </c>
-      <c r="B5" s="25">
+        <v>300</v>
+      </c>
+      <c r="B5" s="26">
         <v>250000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>231645</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>212061</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>191165</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>168870</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="B6" s="25">
+        <v>301</v>
+      </c>
+      <c r="B6" s="26">
         <v>15710</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>14480</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>13169</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>11769</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>10276</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" s="25">
+        <v>302</v>
+      </c>
+      <c r="B7" s="26">
         <v>18355</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>19584</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>20896</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>22295</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>23788</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="B8" s="28">
+        <v>303</v>
+      </c>
+      <c r="B8" s="29">
         <v>34064</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <v>34064</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>34064</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <v>34064</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <v>34064</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B9" s="32">
+        <v>304</v>
+      </c>
+      <c r="B9" s="33">
         <v>231645</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <v>212061</v>
       </c>
-      <c r="D9" s="32">
+      <c r="D9" s="33">
         <v>191165</v>
       </c>
-      <c r="E9" s="32">
+      <c r="E9" s="33">
         <v>168870</v>
       </c>
-      <c r="F9" s="32">
+      <c r="F9" s="33">
         <v>145082</v>
       </c>
     </row>
@@ -4544,7 +4554,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4574,7 +4584,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4584,107 +4594,107 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>306</v>
-      </c>
-      <c r="B5" s="34">
+        <v>307</v>
+      </c>
+      <c r="B5" s="35">
         <v>864756</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="35">
         <v>2251184</v>
       </c>
-      <c r="D5" s="34">
+      <c r="D5" s="35">
         <v>4253414</v>
       </c>
-      <c r="E5" s="34">
+      <c r="E5" s="35">
         <v>6813759</v>
       </c>
-      <c r="F5" s="34">
+      <c r="F5" s="35">
         <v>9755974</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>307</v>
-      </c>
-      <c r="B6" s="25">
+        <v>308</v>
+      </c>
+      <c r="B6" s="26">
         <v>12000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>12000</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>12000</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>12000</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>12000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B7" s="25">
+        <v>309</v>
+      </c>
+      <c r="B7" s="26">
         <v>180000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>180000</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>180000</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>180000</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>180000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="B8" s="25">
+        <v>310</v>
+      </c>
+      <c r="B8" s="26">
         <v>5000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>5000</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>5000</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>5000</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>5000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B9" s="30">
+        <v>311</v>
+      </c>
+      <c r="B9" s="31">
         <v>1061756</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>2448184</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>4450414</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>7010759</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>9952974</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4694,67 +4704,67 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>312</v>
-      </c>
-      <c r="B12" s="25">
+        <v>313</v>
+      </c>
+      <c r="B12" s="26">
         <v>8000</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <v>8000</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <v>8000</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <v>8000</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <v>8000</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>313</v>
-      </c>
-      <c r="B13" s="25">
+        <v>314</v>
+      </c>
+      <c r="B13" s="26">
         <v>231645</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>212061</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>191165</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>168870</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>145082</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="B14" s="30">
+        <v>315</v>
+      </c>
+      <c r="B14" s="31">
         <v>239645</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>220061</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>199165</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>176870</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>153082</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4764,41 +4774,41 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="B17" s="26">
+        <v>317</v>
+      </c>
+      <c r="B17" s="27">
         <v>822111</v>
       </c>
-      <c r="C17" s="26">
+      <c r="C17" s="27">
         <v>2228123</v>
       </c>
-      <c r="D17" s="26">
+      <c r="D17" s="27">
         <v>4251248</v>
       </c>
-      <c r="E17" s="26">
+      <c r="E17" s="27">
         <v>6833888</v>
       </c>
-      <c r="F17" s="26">
+      <c r="F17" s="27">
         <v>9799892</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="B19" s="35">
+        <v>318</v>
+      </c>
+      <c r="B19" s="36">
         <v>0</v>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="36">
         <v>0</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="37">
         <v>1</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="37">
         <v>1</v>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="36">
         <v>0</v>
       </c>
     </row>
@@ -4828,7 +4838,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4858,7 +4868,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4868,137 +4878,137 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B5" s="25">
+        <v>321</v>
+      </c>
+      <c r="B5" s="26">
         <v>1975000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>2621350</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>3304704</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>3922890</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>4361347</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>287</v>
-      </c>
-      <c r="B6" s="25">
+        <v>288</v>
+      </c>
+      <c r="B6" s="26">
         <v>854772</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>880415</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>906828</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>934032</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>962053</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>288</v>
-      </c>
-      <c r="B7" s="25">
+        <v>289</v>
+      </c>
+      <c r="B7" s="26">
         <v>271400</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>310442</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>351582</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>389448</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>418014</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B8" s="28">
+        <v>322</v>
+      </c>
+      <c r="B8" s="29">
         <f>B5-B6-B7</f>
         <v>848828</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="29">
         <f>C5-C6-C7</f>
         <v>1430493</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <f>D5-D6-D7</f>
         <v>2046294</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>E5-E6-E7</f>
         <v>2599410</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>F5-F6-F7</f>
         <v>2981279</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="B9" s="25">
+        <v>290</v>
+      </c>
+      <c r="B9" s="26">
         <v>34064</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>34064</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>34064</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>34064</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>34064</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="B10" s="37">
+        <v>323</v>
+      </c>
+      <c r="B10" s="38">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>24.92</v>
       </c>
-      <c r="C10" s="37">
+      <c r="C10" s="38">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>41.99</v>
       </c>
-      <c r="D10" s="37">
+      <c r="D10" s="38">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>60.07</v>
       </c>
-      <c r="E10" s="37">
+      <c r="E10" s="38">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>76.31</v>
       </c>
-      <c r="F10" s="37">
+      <c r="F10" s="38">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>87.52</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5008,97 +5018,97 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B13" s="25">
+        <v>325</v>
+      </c>
+      <c r="B13" s="26">
         <v>864756</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>2251184</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>4253414</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>6813759</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>9755974</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>325</v>
-      </c>
-      <c r="B14" s="22">
+        <v>326</v>
+      </c>
+      <c r="B14" s="23">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>272</v>
       </c>
-      <c r="C14" s="22">
+      <c r="C14" s="23">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>671</v>
       </c>
-      <c r="D14" s="22">
+      <c r="D14" s="23">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>1201</v>
       </c>
-      <c r="E14" s="22">
+      <c r="E14" s="23">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1832</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="23">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>2518</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>326</v>
-      </c>
-      <c r="B15" s="29">
+        <v>327</v>
+      </c>
+      <c r="B15" s="30">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>8.9</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>22.1</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>39.5</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>60.2</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>82.8</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="24">
+        <v>184</v>
+      </c>
+      <c r="B16" s="25">
         <v>0.5</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="25">
         <v>0.65</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="25">
         <v>0.8</v>
       </c>
-      <c r="E16" s="24">
+      <c r="E16" s="25">
         <v>0.925</v>
       </c>
-      <c r="F16" s="24">
+      <c r="F16" s="25">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5108,87 +5118,87 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="B19" s="25">
+        <v>225</v>
+      </c>
+      <c r="B19" s="26">
         <v>19750</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <v>20164</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <v>20654</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <v>21205</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <v>21807</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>328</v>
-      </c>
-      <c r="B20" s="25">
+        <v>329</v>
+      </c>
+      <c r="B20" s="26">
         <v>888836</v>
       </c>
-      <c r="C20" s="25">
+      <c r="C20" s="26">
         <v>914480</v>
       </c>
-      <c r="D20" s="25">
+      <c r="D20" s="26">
         <v>940892</v>
       </c>
-      <c r="E20" s="25">
+      <c r="E20" s="26">
         <v>968097</v>
       </c>
-      <c r="F20" s="25">
+      <c r="F20" s="26">
         <v>996118</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="B21" s="25">
+        <v>330</v>
+      </c>
+      <c r="B21" s="26">
         <v>2714</v>
       </c>
-      <c r="C21" s="25">
+      <c r="C21" s="26">
         <v>2388</v>
       </c>
-      <c r="D21" s="25">
+      <c r="D21" s="26">
         <v>2197</v>
       </c>
-      <c r="E21" s="25">
+      <c r="E21" s="26">
         <v>2105</v>
       </c>
-      <c r="F21" s="25">
+      <c r="F21" s="26">
         <v>2090</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B22" s="38">
+        <v>331</v>
+      </c>
+      <c r="B22" s="39">
         <v>53</v>
       </c>
-      <c r="C22" s="38">
+      <c r="C22" s="39">
         <v>52</v>
       </c>
-      <c r="D22" s="38">
+      <c r="D22" s="39">
         <v>51</v>
       </c>
-      <c r="E22" s="38">
+      <c r="E22" s="39">
         <v>51</v>
       </c>
-      <c r="F22" s="38">
+      <c r="F22" s="39">
         <v>51</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5198,102 +5208,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="B25" s="39" t="s">
         <v>333</v>
       </c>
-      <c r="C25" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E25" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="F25" s="39" t="s">
-        <v>333</v>
+      <c r="B25" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="D25" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="E25" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="F25" s="40" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>335</v>
+      </c>
+      <c r="B26" s="40" t="s">
         <v>334</v>
       </c>
-      <c r="B26" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="D26" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E26" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="F26" s="39" t="s">
-        <v>333</v>
+      <c r="C26" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="B27" s="40" t="s">
         <v>336</v>
       </c>
-      <c r="C27" s="40" t="s">
-        <v>336</v>
-      </c>
-      <c r="D27" s="40" t="s">
-        <v>336</v>
-      </c>
-      <c r="E27" s="40" t="s">
-        <v>336</v>
-      </c>
-      <c r="F27" s="40" t="s">
-        <v>336</v>
+      <c r="B27" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="C27" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="D27" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>337</v>
+      </c>
+      <c r="F27" s="41" t="s">
+        <v>337</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B28" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="D28" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E28" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="F28" s="39" t="s">
-        <v>333</v>
+        <v>338</v>
+      </c>
+      <c r="B28" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="E28" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>334</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="B29" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="D29" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="E29" s="39" t="s">
-        <v>333</v>
-      </c>
-      <c r="F29" s="39" t="s">
-        <v>333</v>
+        <v>339</v>
+      </c>
+      <c r="B29" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="D29" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="E29" s="40" t="s">
+        <v>334</v>
+      </c>
+      <c r="F29" s="40" t="s">
+        <v>334</v>
       </c>
     </row>
   </sheetData>
@@ -5333,16 +5343,16 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="41" t="s">
-        <v>339</v>
-      </c>
-      <c r="B3" s="41" t="s">
+      <c r="A3" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="B3" s="42" t="s">
         <v>100</v>
       </c>
-      <c r="D3" s="41" t="s">
-        <v>340</v>
-      </c>
-      <c r="E3" s="41" t="s">
+      <c r="D3" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="E3" s="42" t="s">
         <v>100</v>
       </c>
     </row>
@@ -5350,13 +5360,13 @@
       <c r="A4" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <v>250000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>341</v>
-      </c>
-      <c r="E4" s="25">
+        <v>342</v>
+      </c>
+      <c r="E4" s="26">
         <v>200000</v>
       </c>
     </row>
@@ -5364,57 +5374,57 @@
       <c r="A5" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="25">
+      <c r="B5" s="26">
         <v>50000</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>50000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="B6" s="25">
+        <v>343</v>
+      </c>
+      <c r="B6" s="26">
         <v>75000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="E6" s="25">
+        <v>344</v>
+      </c>
+      <c r="E6" s="26">
         <v>75000</v>
       </c>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>344</v>
-      </c>
-      <c r="E7" s="25">
+        <v>345</v>
+      </c>
+      <c r="E7" s="26">
         <v>50000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B9" s="26">
+        <v>346</v>
+      </c>
+      <c r="B9" s="27">
         <v>375000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E9" s="26">
+        <v>347</v>
+      </c>
+      <c r="E9" s="27">
         <v>375000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B10" s="35">
+        <v>348</v>
+      </c>
+      <c r="B10" s="36">
         <v>0</v>
       </c>
     </row>
@@ -5580,7 +5590,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5590,7 +5600,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5600,7 +5610,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5625,127 +5635,127 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B6" s="25">
+        <v>321</v>
+      </c>
+      <c r="B6" s="26">
         <v>1975000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>2621350</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>3304704</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>3922890</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>4361347</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B7" s="25">
+        <v>267</v>
+      </c>
+      <c r="B7" s="26">
         <v>1160236</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>1224922</v>
       </c>
-      <c r="D7" s="25">
-        <v>1292490</v>
-      </c>
-      <c r="E7" s="25">
-        <v>1357593</v>
-      </c>
-      <c r="F7" s="25">
-        <v>1414023</v>
+      <c r="D7" s="26">
+        <v>1292474</v>
+      </c>
+      <c r="E7" s="26">
+        <v>1357545</v>
+      </c>
+      <c r="F7" s="26">
+        <v>1414132</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B8" s="26">
+        <v>269</v>
+      </c>
+      <c r="B8" s="27">
         <v>814764</v>
       </c>
-      <c r="C8" s="26">
+      <c r="C8" s="27">
         <v>1396428</v>
       </c>
-      <c r="D8" s="26">
-        <v>2012214</v>
-      </c>
-      <c r="E8" s="26">
-        <v>2565297</v>
-      </c>
-      <c r="F8" s="26">
-        <v>2947324</v>
+      <c r="D8" s="27">
+        <v>2012229</v>
+      </c>
+      <c r="E8" s="27">
+        <v>2565345</v>
+      </c>
+      <c r="F8" s="27">
+        <v>2947215</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B9" s="24">
+        <v>270</v>
+      </c>
+      <c r="B9" s="25">
         <v>0.4125385351058188</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="25">
         <v>0.5327134670433142</v>
       </c>
-      <c r="D9" s="24">
-        <v>0.6088938665856081</v>
-      </c>
-      <c r="E9" s="24">
-        <v>0.6539303894233892</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.6757830034045176</v>
+      <c r="D9" s="25">
+        <v>0.6088985689741885</v>
+      </c>
+      <c r="E9" s="25">
+        <v>0.6539426893351535</v>
+      </c>
+      <c r="F9" s="25">
+        <v>0.6757579942908114</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B10" s="42">
+        <v>323</v>
+      </c>
+      <c r="B10" s="43">
         <v>24.92</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="43">
         <v>41.99</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="43">
         <v>60.07</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="43">
         <v>76.31</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="43">
         <v>87.52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B11" s="22">
+        <v>331</v>
+      </c>
+      <c r="B11" s="23">
         <v>53</v>
       </c>
-      <c r="C11" s="22">
+      <c r="C11" s="23">
         <v>52</v>
       </c>
-      <c r="D11" s="22">
+      <c r="D11" s="23">
         <v>51</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="23">
         <v>51</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="23">
         <v>51</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5755,7 +5765,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5780,127 +5790,127 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B16" s="25">
+        <v>321</v>
+      </c>
+      <c r="B16" s="26">
         <v>1678750</v>
       </c>
-      <c r="C16" s="25">
+      <c r="C16" s="26">
         <v>2228148</v>
       </c>
-      <c r="D16" s="25">
+      <c r="D16" s="26">
         <v>2808998</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>3334456</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>3707145</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B17" s="25">
+        <v>267</v>
+      </c>
+      <c r="B17" s="26">
         <v>1160236</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>1224922</v>
       </c>
-      <c r="D17" s="25">
-        <v>1292490</v>
-      </c>
-      <c r="E17" s="25">
-        <v>1357593</v>
-      </c>
-      <c r="F17" s="25">
-        <v>1414023</v>
+      <c r="D17" s="26">
+        <v>1292474</v>
+      </c>
+      <c r="E17" s="26">
+        <v>1357545</v>
+      </c>
+      <c r="F17" s="26">
+        <v>1414132</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B18" s="26">
+        <v>269</v>
+      </c>
+      <c r="B18" s="27">
         <v>518514</v>
       </c>
-      <c r="C18" s="26">
+      <c r="C18" s="27">
         <v>1003226</v>
       </c>
-      <c r="D18" s="26">
-        <v>1516508</v>
-      </c>
-      <c r="E18" s="26">
-        <v>1976863</v>
-      </c>
-      <c r="F18" s="26">
-        <v>2293122</v>
+      <c r="D18" s="27">
+        <v>1516524</v>
+      </c>
+      <c r="E18" s="27">
+        <v>1976912</v>
+      </c>
+      <c r="F18" s="27">
+        <v>2293013</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B19" s="24">
+        <v>270</v>
+      </c>
+      <c r="B19" s="25">
         <v>0.308868864830375</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="25">
         <v>0.45025113769801683</v>
       </c>
-      <c r="D19" s="24">
-        <v>0.5398751371595389</v>
-      </c>
-      <c r="E19" s="24">
-        <v>0.5928592816745755</v>
-      </c>
-      <c r="F19" s="24">
-        <v>0.6185682392994323</v>
+      <c r="D19" s="25">
+        <v>0.5398806693813982</v>
+      </c>
+      <c r="E19" s="25">
+        <v>0.5928737521590041</v>
+      </c>
+      <c r="F19" s="25">
+        <v>0.6185388168127194</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B20" s="42">
+        <v>323</v>
+      </c>
+      <c r="B20" s="43">
         <v>16.22</v>
       </c>
-      <c r="C20" s="42">
+      <c r="C20" s="43">
         <v>30.45</v>
       </c>
-      <c r="D20" s="42">
+      <c r="D20" s="43">
         <v>45.52</v>
       </c>
-      <c r="E20" s="42">
+      <c r="E20" s="43">
         <v>59.03</v>
       </c>
-      <c r="F20" s="42">
-        <v>68.32</v>
+      <c r="F20" s="43">
+        <v>68.31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B21" s="22">
+        <v>331</v>
+      </c>
+      <c r="B21" s="23">
         <v>54</v>
       </c>
-      <c r="C21" s="22">
+      <c r="C21" s="23">
         <v>53</v>
       </c>
-      <c r="D21" s="22">
+      <c r="D21" s="23">
         <v>53</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <v>52</v>
       </c>
-      <c r="F21" s="22">
+      <c r="F21" s="23">
         <v>52</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5910,7 +5920,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5935,121 +5945,121 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="B26" s="25">
+        <v>321</v>
+      </c>
+      <c r="B26" s="26">
         <v>1975000</v>
       </c>
-      <c r="C26" s="25">
+      <c r="C26" s="26">
         <v>2621350</v>
       </c>
-      <c r="D26" s="25">
+      <c r="D26" s="26">
         <v>3304704</v>
       </c>
-      <c r="E26" s="25">
+      <c r="E26" s="26">
         <v>3922890</v>
       </c>
-      <c r="F26" s="25">
+      <c r="F26" s="26">
         <v>4361347</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="B27" s="25">
+        <v>267</v>
+      </c>
+      <c r="B27" s="26">
         <v>1173736</v>
       </c>
-      <c r="C27" s="25">
+      <c r="C27" s="26">
         <v>1241917</v>
       </c>
-      <c r="D27" s="25">
-        <v>1313179</v>
-      </c>
-      <c r="E27" s="25">
-        <v>1381638</v>
-      </c>
-      <c r="F27" s="25">
-        <v>1440462</v>
+      <c r="D27" s="26">
+        <v>1313162</v>
+      </c>
+      <c r="E27" s="26">
+        <v>1381585</v>
+      </c>
+      <c r="F27" s="26">
+        <v>1440581</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B28" s="26">
+        <v>269</v>
+      </c>
+      <c r="B28" s="27">
         <v>801264</v>
       </c>
-      <c r="C28" s="26">
+      <c r="C28" s="27">
         <v>1379433</v>
       </c>
-      <c r="D28" s="26">
-        <v>1991524</v>
-      </c>
-      <c r="E28" s="26">
-        <v>2541252</v>
-      </c>
-      <c r="F28" s="26">
-        <v>2920885</v>
+      <c r="D28" s="27">
+        <v>1991542</v>
+      </c>
+      <c r="E28" s="27">
+        <v>2541305</v>
+      </c>
+      <c r="F28" s="27">
+        <v>2920765</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="B29" s="24">
+        <v>270</v>
+      </c>
+      <c r="B29" s="25">
         <v>0.4057030920678441</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="25">
         <v>0.5262301664539233</v>
       </c>
-      <c r="D29" s="24">
-        <v>0.6026333351945166</v>
-      </c>
-      <c r="E29" s="24">
-        <v>0.6478009541272017</v>
-      </c>
-      <c r="F29" s="24">
-        <v>0.6697208161513672</v>
+      <c r="D29" s="25">
+        <v>0.6026385368714597</v>
+      </c>
+      <c r="E29" s="25">
+        <v>0.6478145556304181</v>
+      </c>
+      <c r="F29" s="25">
+        <v>0.6696934781617792</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="B30" s="42">
+        <v>323</v>
+      </c>
+      <c r="B30" s="43">
         <v>24.52</v>
       </c>
-      <c r="C30" s="42">
+      <c r="C30" s="43">
         <v>41.49</v>
       </c>
-      <c r="D30" s="42">
+      <c r="D30" s="43">
         <v>59.46</v>
       </c>
-      <c r="E30" s="42">
+      <c r="E30" s="43">
         <v>75.6</v>
       </c>
-      <c r="F30" s="42">
-        <v>86.75</v>
+      <c r="F30" s="43">
+        <v>86.74</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>330</v>
-      </c>
-      <c r="B31" s="22">
+        <v>331</v>
+      </c>
+      <c r="B31" s="23">
         <v>53</v>
       </c>
-      <c r="C31" s="22">
+      <c r="C31" s="23">
         <v>52</v>
       </c>
-      <c r="D31" s="22">
+      <c r="D31" s="23">
         <v>52</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <v>52</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <v>51</v>
       </c>
     </row>
@@ -6081,7 +6091,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6115,7 +6125,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6139,7 +6149,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6147,7 +6157,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6167,125 +6177,125 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F12" s="43" t="s">
+      <c r="F12" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H12" s="43" t="s">
+      <c r="H12" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>320</v>
-      </c>
-      <c r="D13" s="25">
+        <v>321</v>
+      </c>
+      <c r="D13" s="26">
         <v>1975000</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>2621350</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>3304704</v>
       </c>
-      <c r="G13" s="25">
+      <c r="G13" s="26">
         <v>3922890</v>
       </c>
-      <c r="H13" s="25">
+      <c r="H13" s="26">
         <v>4361347</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>266</v>
-      </c>
-      <c r="D14" s="25">
+        <v>267</v>
+      </c>
+      <c r="D14" s="26">
         <v>1160236</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>1224922</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>1292474</v>
       </c>
-      <c r="G14" s="25">
+      <c r="G14" s="26">
         <v>1357545</v>
       </c>
-      <c r="H14" s="25">
+      <c r="H14" s="26">
         <v>1414132</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="D15" s="25">
+        <v>269</v>
+      </c>
+      <c r="D15" s="26">
         <v>789764</v>
       </c>
-      <c r="E15" s="25">
+      <c r="E15" s="26">
         <v>1386428</v>
       </c>
-      <c r="F15" s="25">
+      <c r="F15" s="26">
         <v>2002229</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="26">
         <v>2560345</v>
       </c>
-      <c r="H15" s="25">
+      <c r="H15" s="26">
         <v>2942215</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>359</v>
-      </c>
-      <c r="D16" s="25">
+        <v>360</v>
+      </c>
+      <c r="D16" s="26">
         <v>864756</v>
       </c>
-      <c r="E16" s="25">
+      <c r="E16" s="26">
         <v>2251184</v>
       </c>
-      <c r="F16" s="25">
+      <c r="F16" s="26">
         <v>4253414</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="26">
         <v>6813759</v>
       </c>
-      <c r="H16" s="25">
+      <c r="H16" s="26">
         <v>9755974</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>360</v>
-      </c>
-      <c r="D17" s="25">
+        <v>361</v>
+      </c>
+      <c r="D17" s="26">
         <v>231645</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>212061</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>191165</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="26">
         <v>168870</v>
       </c>
-      <c r="H17" s="25">
+      <c r="H17" s="26">
         <v>145082</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6305,105 +6315,105 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="43" t="s">
+      <c r="D20" s="44" t="s">
         <v>90</v>
       </c>
-      <c r="E20" s="43" t="s">
+      <c r="E20" s="44" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="43" t="s">
+      <c r="F20" s="44" t="s">
         <v>92</v>
       </c>
-      <c r="G20" s="43" t="s">
+      <c r="G20" s="44" t="s">
         <v>93</v>
       </c>
-      <c r="H20" s="43" t="s">
+      <c r="H20" s="44" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="D21" s="24">
+        <v>363</v>
+      </c>
+      <c r="D21" s="25">
         <v>0.3998803072577175</v>
       </c>
-      <c r="E21" s="24">
+      <c r="E21" s="25">
         <v>0.5288986388059557</v>
       </c>
-      <c r="F21" s="24">
+      <c r="F21" s="25">
         <v>0.6058725788967125</v>
       </c>
-      <c r="G21" s="24">
+      <c r="G21" s="25">
         <v>0.6526681187789514</v>
       </c>
-      <c r="H21" s="24">
+      <c r="H21" s="25">
         <v>0.6746115593902751</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>322</v>
-      </c>
-      <c r="D22" s="42">
+        <v>323</v>
+      </c>
+      <c r="D22" s="43">
         <v>24.92</v>
       </c>
-      <c r="E22" s="42">
+      <c r="E22" s="43">
         <v>41.99</v>
       </c>
-      <c r="F22" s="42">
+      <c r="F22" s="43">
         <v>60.07</v>
       </c>
-      <c r="G22" s="42">
+      <c r="G22" s="43">
         <v>76.31</v>
       </c>
-      <c r="H22" s="42">
+      <c r="H22" s="43">
         <v>87.52</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D23" s="24">
+        <v>184</v>
+      </c>
+      <c r="D23" s="25">
         <v>0.5</v>
       </c>
-      <c r="E23" s="24">
+      <c r="E23" s="25">
         <v>0.65</v>
       </c>
-      <c r="F23" s="24">
+      <c r="F23" s="25">
         <v>0.8</v>
       </c>
-      <c r="G23" s="24">
+      <c r="G23" s="25">
         <v>0.925</v>
       </c>
-      <c r="H23" s="24">
+      <c r="H23" s="25">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>363</v>
-      </c>
-      <c r="D24" s="22">
+        <v>364</v>
+      </c>
+      <c r="D24" s="23">
         <v>100</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="23">
         <v>130</v>
       </c>
-      <c r="F24" s="22">
+      <c r="F24" s="23">
         <v>160</v>
       </c>
-      <c r="G24" s="22">
+      <c r="G24" s="23">
         <v>185</v>
       </c>
-      <c r="H24" s="22">
+      <c r="H24" s="23">
         <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7162,25 +7172,31 @@
       <c r="F55" s="13"/>
       <c r="G55" s="13"/>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
         <v>157</v>
       </c>
       <c r="B56" s="18">
         <v>0.03</v>
       </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C56" s="20" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B57" s="18">
         <v>0.03</v>
       </c>
+      <c r="C57" s="20" t="s">
+        <v>158</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B58" s="19">
         <v>1</v>
@@ -7188,7 +7204,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B59" s="17">
         <v>75000</v>
@@ -7196,10 +7212,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
   </sheetData>
@@ -7234,10 +7250,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7258,10 +7274,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7274,7 +7290,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7285,31 +7301,31 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7317,31 +7333,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -7384,10 +7400,10 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>90</v>
@@ -7407,7 +7423,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7421,25 +7437,25 @@
       <c r="A6" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="B6" s="20">
+      <c r="B6" s="21">
         <v>85</v>
       </c>
-      <c r="C6" s="20">
+      <c r="C6" s="21">
         <v>0</v>
       </c>
-      <c r="D6" s="21">
+      <c r="D6" s="22">
         <v>100</v>
       </c>
-      <c r="E6" s="21">
+      <c r="E6" s="22">
         <v>130</v>
       </c>
-      <c r="F6" s="21">
+      <c r="F6" s="22">
         <v>160</v>
       </c>
-      <c r="G6" s="21">
+      <c r="G6" s="22">
         <v>185</v>
       </c>
-      <c r="H6" s="21">
+      <c r="H6" s="22">
         <v>200</v>
       </c>
     </row>
@@ -7447,47 +7463,47 @@
       <c r="A7" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="23">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="D8" s="23">
+        <v>184</v>
+      </c>
+      <c r="D8" s="24">
         <v>0.5</v>
       </c>
-      <c r="E8" s="23">
+      <c r="E8" s="24">
         <v>0.65</v>
       </c>
-      <c r="F8" s="23">
+      <c r="F8" s="24">
         <v>0.8</v>
       </c>
-      <c r="G8" s="23">
+      <c r="G8" s="24">
         <v>0.925</v>
       </c>
-      <c r="H8" s="23">
+      <c r="H8" s="24">
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="E10" s="24">
+        <v>186</v>
+      </c>
+      <c r="E10" s="25">
         <v>0.3</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="25">
         <v>0.23076923076923078</v>
       </c>
-      <c r="G10" s="24">
+      <c r="G10" s="25">
         <v>0.15625</v>
       </c>
-      <c r="H10" s="24">
+      <c r="H10" s="25">
         <v>0.08108108108108109</v>
       </c>
     </row>
@@ -7517,7 +7533,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7547,7 +7563,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7557,165 +7573,165 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>188</v>
-      </c>
-      <c r="B5" s="25">
+        <v>189</v>
+      </c>
+      <c r="B5" s="26">
         <v>1050000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>1405950</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>1782312</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>2122622</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>2363569</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="B6" s="25">
+        <v>190</v>
+      </c>
+      <c r="B6" s="26">
         <v>35000</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>46865</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>59410</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="26">
         <v>70754</v>
       </c>
-      <c r="F6" s="25">
+      <c r="F6" s="26">
         <v>78786</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="B7" s="25">
+        <v>191</v>
+      </c>
+      <c r="B7" s="26">
         <v>105000</v>
       </c>
-      <c r="C7" s="25">
+      <c r="C7" s="26">
         <v>140595</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>178231</v>
       </c>
-      <c r="E7" s="25">
+      <c r="E7" s="26">
         <v>212262</v>
       </c>
-      <c r="F7" s="25">
+      <c r="F7" s="26">
         <v>236357</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="B8" s="25">
+        <v>192</v>
+      </c>
+      <c r="B8" s="26">
         <v>870000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>1164930</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>1476773</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>1758744</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>1958385</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B9" s="25">
+        <v>193</v>
+      </c>
+      <c r="B9" s="26">
         <v>50000</v>
       </c>
-      <c r="C9" s="25">
+      <c r="C9" s="26">
         <v>51500</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>53045</v>
       </c>
-      <c r="E9" s="25">
+      <c r="E9" s="26">
         <v>54636</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="26">
         <v>56275</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>193</v>
-      </c>
-      <c r="B10" s="25">
+        <v>194</v>
+      </c>
+      <c r="B10" s="26">
         <v>25000</v>
       </c>
-      <c r="C10" s="25">
+      <c r="C10" s="26">
         <v>25750</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D10" s="26">
         <v>26523</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E10" s="26">
         <v>27318</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F10" s="26">
         <v>28138</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>194</v>
-      </c>
-      <c r="B11" s="25">
+        <v>195</v>
+      </c>
+      <c r="B11" s="26">
         <v>50000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>66950</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>84872</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>101077</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>112551</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="B12" s="26">
+        <v>196</v>
+      </c>
+      <c r="B12" s="27">
         <f>SUM(B5:B11)</f>
         <v>1975000</v>
       </c>
-      <c r="C12" s="26">
+      <c r="C12" s="27">
         <f>SUM(C5:C11)</f>
         <v>2621350</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="27">
         <f>SUM(D5:D11)</f>
         <v>3304704</v>
       </c>
-      <c r="E12" s="26">
+      <c r="E12" s="27">
         <f>SUM(E5:E11)</f>
         <v>3922890</v>
       </c>
-      <c r="F12" s="26">
+      <c r="F12" s="27">
         <f>SUM(F5:F11)</f>
         <v>4361347</v>
       </c>
@@ -7770,7 +7786,7 @@
         <v>119</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>121</v>
@@ -7779,7 +7795,7 @@
         <v>122</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7789,19 +7805,19 @@
       <c r="B4" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="27">
+      <c r="C4" s="28">
         <v>1</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <v>95000</v>
       </c>
-      <c r="E4" s="24">
+      <c r="E4" s="25">
         <v>0.25</v>
       </c>
-      <c r="F4" s="24">
+      <c r="F4" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="29">
         <v>126018</v>
       </c>
     </row>
@@ -7812,19 +7828,19 @@
       <c r="B5" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C5" s="27">
+      <c r="C5" s="28">
         <v>1</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>75000</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="25">
         <v>0.25</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="29">
         <v>99488</v>
       </c>
     </row>
@@ -7835,19 +7851,19 @@
       <c r="B6" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="27">
+      <c r="C6" s="28">
         <v>6</v>
       </c>
-      <c r="D6" s="25">
+      <c r="D6" s="26">
         <v>48000</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="25">
         <v>0.25</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="29">
         <v>382032</v>
       </c>
     </row>
@@ -7858,19 +7874,19 @@
       <c r="B7" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C7" s="27">
+      <c r="C7" s="28">
         <v>3</v>
       </c>
-      <c r="D7" s="25">
+      <c r="D7" s="26">
         <v>32000</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="25">
         <v>0.2</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="29">
         <v>122544</v>
       </c>
     </row>
@@ -7881,19 +7897,19 @@
       <c r="B8" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="C8" s="27">
+      <c r="C8" s="28">
         <v>1</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>42000</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="25">
         <v>0.25</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <v>55713</v>
       </c>
     </row>
@@ -7904,25 +7920,25 @@
       <c r="B9" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="C9" s="27">
+      <c r="C9" s="28">
         <v>1</v>
       </c>
-      <c r="D9" s="25">
+      <c r="D9" s="26">
         <v>52000</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="25">
         <v>0.25</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="25">
         <v>0.0765</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="29">
         <v>68978</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -7953,61 +7969,61 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B13" s="26">
+        <v>200</v>
+      </c>
+      <c r="B13" s="27">
         <v>854772</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="27">
         <v>880415</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="27">
         <v>906828</v>
       </c>
-      <c r="E13" s="26">
+      <c r="E13" s="27">
         <v>934032</v>
       </c>
-      <c r="F13" s="26">
+      <c r="F13" s="27">
         <v>962053</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="B14" s="24">
+        <v>201</v>
+      </c>
+      <c r="B14" s="25">
         <v>0.4327959493670886</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="25">
         <v>0.3358632612966601</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <v>0.2744051364365971</v>
       </c>
-      <c r="E14" s="24">
+      <c r="E14" s="25">
         <v>0.23809805013927576</v>
       </c>
-      <c r="F14" s="24">
+      <c r="F14" s="25">
         <v>0.22058632258064514</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="B15" s="29">
+        <v>202</v>
+      </c>
+      <c r="B15" s="30">
         <v>7.7</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <v>10</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <v>12.3</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <v>14.2</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <v>15.4</v>
       </c>
     </row>
@@ -8037,7 +8053,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8077,45 +8093,45 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="25">
+        <v>204</v>
+      </c>
+      <c r="B5" s="26">
         <v>60000</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="26">
         <v>80340</v>
       </c>
-      <c r="D5" s="25">
+      <c r="D5" s="26">
         <v>101846</v>
       </c>
-      <c r="E5" s="25">
+      <c r="E5" s="26">
         <v>121293</v>
       </c>
-      <c r="F5" s="25">
+      <c r="F5" s="26">
         <v>135061</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="B6" s="30">
+        <v>205</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
         <v>60000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <f>SUM(C5:C5)</f>
         <v>80340</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <f>SUM(D5:D5)</f>
         <v>101846</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>SUM(E5:E5)</f>
         <v>121293</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <f>SUM(F5:F5)</f>
         <v>135061</v>
       </c>
@@ -8132,45 +8148,45 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>205</v>
-      </c>
-      <c r="B8" s="25">
+        <v>206</v>
+      </c>
+      <c r="B8" s="26">
         <v>40000</v>
       </c>
-      <c r="C8" s="25">
+      <c r="C8" s="26">
         <v>53560</v>
       </c>
-      <c r="D8" s="25">
+      <c r="D8" s="26">
         <v>67898</v>
       </c>
-      <c r="E8" s="25">
+      <c r="E8" s="26">
         <v>80862</v>
       </c>
-      <c r="F8" s="25">
+      <c r="F8" s="26">
         <v>90041</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="B9" s="30">
+        <v>207</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
         <v>40000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>SUM(C8:C8)</f>
         <v>53560</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>SUM(D8:D8)</f>
         <v>67898</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>SUM(E8:E8)</f>
         <v>80862</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>SUM(F8:F8)</f>
         <v>90041</v>
       </c>
@@ -8187,105 +8203,105 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>207</v>
-      </c>
-      <c r="B11" s="25">
+        <v>208</v>
+      </c>
+      <c r="B11" s="26">
         <v>102000</v>
       </c>
-      <c r="C11" s="25">
+      <c r="C11" s="26">
         <v>105060</v>
       </c>
-      <c r="D11" s="25">
+      <c r="D11" s="26">
         <v>108212</v>
       </c>
-      <c r="E11" s="25">
+      <c r="E11" s="26">
         <v>111458</v>
       </c>
-      <c r="F11" s="25">
+      <c r="F11" s="26">
         <v>114802</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="25">
+        <v>209</v>
+      </c>
+      <c r="B12" s="26">
         <v>14400</v>
       </c>
-      <c r="C12" s="25">
+      <c r="C12" s="26">
         <v>14832</v>
       </c>
-      <c r="D12" s="25">
+      <c r="D12" s="26">
         <v>15277</v>
       </c>
-      <c r="E12" s="25">
+      <c r="E12" s="26">
         <v>15735</v>
       </c>
-      <c r="F12" s="25">
+      <c r="F12" s="26">
         <v>16207</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="B13" s="25">
+        <v>210</v>
+      </c>
+      <c r="B13" s="26">
         <v>12000</v>
       </c>
-      <c r="C13" s="25">
+      <c r="C13" s="26">
         <v>12360</v>
       </c>
-      <c r="D13" s="25">
+      <c r="D13" s="26">
         <v>12731</v>
       </c>
-      <c r="E13" s="25">
+      <c r="E13" s="26">
         <v>13113</v>
       </c>
-      <c r="F13" s="25">
+      <c r="F13" s="26">
         <v>13506</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="B14" s="25">
+        <v>211</v>
+      </c>
+      <c r="B14" s="26">
         <v>8000</v>
       </c>
-      <c r="C14" s="25">
+      <c r="C14" s="26">
         <v>8240</v>
       </c>
-      <c r="D14" s="25">
+      <c r="D14" s="26">
         <v>8487</v>
       </c>
-      <c r="E14" s="25">
+      <c r="E14" s="26">
         <v>8742</v>
       </c>
-      <c r="F14" s="25">
+      <c r="F14" s="26">
         <v>9004</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B15" s="30">
+        <v>212</v>
+      </c>
+      <c r="B15" s="31">
         <f>SUM(B11:B14)</f>
         <v>136400</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <f>SUM(C11:C14)</f>
         <v>140492</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <f>SUM(D11:D14)</f>
         <v>144707</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <f>SUM(E11:E14)</f>
         <v>149048</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <f>SUM(F11:F14)</f>
         <v>153519</v>
       </c>
@@ -8302,110 +8318,110 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>212</v>
-      </c>
-      <c r="B17" s="25">
+        <v>213</v>
+      </c>
+      <c r="B17" s="26">
         <v>15000</v>
       </c>
-      <c r="C17" s="25">
+      <c r="C17" s="26">
         <v>15450</v>
       </c>
-      <c r="D17" s="25">
+      <c r="D17" s="26">
         <v>15914</v>
       </c>
-      <c r="E17" s="25">
+      <c r="E17" s="26">
         <v>16391</v>
       </c>
-      <c r="F17" s="25">
+      <c r="F17" s="26">
         <v>16883</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>213</v>
-      </c>
-      <c r="B18" s="25">
+        <v>214</v>
+      </c>
+      <c r="B18" s="26">
         <v>8000</v>
       </c>
-      <c r="C18" s="25">
+      <c r="C18" s="26">
         <v>8240</v>
       </c>
-      <c r="D18" s="25">
+      <c r="D18" s="26">
         <v>8487</v>
       </c>
-      <c r="E18" s="25">
+      <c r="E18" s="26">
         <v>8742</v>
       </c>
-      <c r="F18" s="25">
+      <c r="F18" s="26">
         <v>9004</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="B19" s="25">
+        <v>215</v>
+      </c>
+      <c r="B19" s="26">
         <v>12000</v>
       </c>
-      <c r="C19" s="25">
+      <c r="C19" s="26">
         <v>12360</v>
       </c>
-      <c r="D19" s="25">
+      <c r="D19" s="26">
         <v>12731</v>
       </c>
-      <c r="E19" s="25">
+      <c r="E19" s="26">
         <v>13113</v>
       </c>
-      <c r="F19" s="25">
+      <c r="F19" s="26">
         <v>13506</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B20" s="30">
+        <v>216</v>
+      </c>
+      <c r="B20" s="31">
         <f>SUM(B17:B19)</f>
         <v>35000</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <f>SUM(C17:C19)</f>
         <v>36050</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <f>SUM(D17:D19)</f>
         <v>37132</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <f>SUM(E17:E19)</f>
         <v>38245</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <f>SUM(F17:F19)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>216</v>
-      </c>
-      <c r="B22" s="26">
+        <v>217</v>
+      </c>
+      <c r="B22" s="27">
         <f>B6+B9+B15+B20</f>
         <v>271400</v>
       </c>
-      <c r="C22" s="26">
+      <c r="C22" s="27">
         <f>C6+C9+C15+C20</f>
         <v>310442</v>
       </c>
-      <c r="D22" s="26">
+      <c r="D22" s="27">
         <f>D6+D9+D15+D20</f>
         <v>351582</v>
       </c>
-      <c r="E22" s="26">
+      <c r="E22" s="27">
         <f>E6+E9+E15+E20</f>
         <v>389448</v>
       </c>
-      <c r="F22" s="26">
+      <c r="F22" s="27">
         <f>F6+F9+F15+F20</f>
         <v>418014</v>
       </c>
@@ -8437,7 +8453,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8462,7 +8478,7 @@
         <v>151</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -8475,13 +8491,13 @@
       <c r="C4" s="17">
         <v>250000</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="25">
         <v>0.065</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="23">
         <v>10</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="29">
         <v>34064</v>
       </c>
     </row>
@@ -8490,34 +8506,34 @@
         <v>154</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C5" s="17">
         <v>25000</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="25">
         <v>0</v>
       </c>
-      <c r="E5" s="22">
+      <c r="E5" s="23">
         <v>0</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="29">
         <v>25000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="F7" s="26">
+        <v>221</v>
+      </c>
+      <c r="F7" s="27">
         <v>34064</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="F8" s="30">
+        <v>222</v>
+      </c>
+      <c r="F8" s="31">
         <v>250000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="366">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="367">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -507,10 +507,13 @@
     <t>Salary Escalation Rate</t>
   </si>
   <si>
-    <t>Derived from tuition escalation rate</t>
+    <t>Salary input or tuition escalation fallback</t>
   </si>
   <si>
     <t>Cost Inflation Rate</t>
+  </si>
+  <si>
+    <t>Cost inflation input or tuition escalation fallback</t>
   </si>
   <si>
     <t>Year 1 Proration Factor</t>
@@ -2020,7 +2023,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2070,7 +2073,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2220,7 +2223,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B14" s="27">
         <f>SUM(B7:B13)</f>
@@ -2245,7 +2248,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B16" s="26">
         <v>19750</v>
@@ -2289,7 +2292,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2329,7 +2332,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B5" s="26">
         <v>382032</v>
@@ -2349,7 +2352,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B6" s="26">
         <v>122544</v>
@@ -2369,7 +2372,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B7" s="31">
         <f>SUM(B5:B6)</f>
@@ -2404,7 +2407,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B9" s="26">
         <v>126018</v>
@@ -2424,7 +2427,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B10" s="26">
         <v>99488</v>
@@ -2444,7 +2447,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
@@ -2479,7 +2482,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B13" s="26">
         <v>68978</v>
@@ -2499,7 +2502,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
@@ -2534,7 +2537,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B16" s="26">
         <v>55713</v>
@@ -2554,7 +2557,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B17" s="31">
         <f>SUM(B16:B16)</f>
@@ -2579,7 +2582,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B19" s="27">
         <f>B7+B11+B14+B17</f>
@@ -2628,7 +2631,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2658,7 +2661,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2668,7 +2671,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B5" s="26">
         <v>1050000</v>
@@ -2688,7 +2691,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B6" s="26">
         <v>35000</v>
@@ -2708,7 +2711,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B7" s="26">
         <v>105000</v>
@@ -2728,7 +2731,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B8" s="26">
         <v>870000</v>
@@ -2748,7 +2751,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B9" s="26">
         <v>50000</v>
@@ -2768,7 +2771,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B10" s="26">
         <v>25000</v>
@@ -2788,7 +2791,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B11" s="26">
         <v>50000</v>
@@ -2808,7 +2811,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B5:B11)</f>
@@ -2833,7 +2836,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2843,7 +2846,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B15" s="26">
         <v>126018</v>
@@ -2863,7 +2866,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B16" s="26">
         <v>99488</v>
@@ -2883,7 +2886,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B17" s="26">
         <v>382032</v>
@@ -2903,7 +2906,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B18" s="26">
         <v>122544</v>
@@ -2923,7 +2926,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B19" s="26">
         <v>55713</v>
@@ -2943,7 +2946,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B20" s="26">
         <v>68978</v>
@@ -2963,7 +2966,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B21" s="31">
         <f>SUM(B15:B20)</f>
@@ -3003,7 +3006,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B25" s="26">
         <v>60000</v>
@@ -3028,7 +3031,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B27" s="26">
         <v>40000</v>
@@ -3053,7 +3056,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B29" s="26">
         <v>102000</v>
@@ -3073,7 +3076,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B30" s="26">
         <v>14400</v>
@@ -3093,7 +3096,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B31" s="26">
         <v>12000</v>
@@ -3113,7 +3116,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B32" s="26">
         <v>8000</v>
@@ -3133,7 +3136,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B33" s="31">
         <f>SUM(B29:B32)</f>
@@ -3163,7 +3166,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B35" s="26">
         <v>15000</v>
@@ -3183,7 +3186,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B36" s="26">
         <v>8000</v>
@@ -3203,7 +3206,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B37" s="26">
         <v>12000</v>
@@ -3223,7 +3226,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B38" s="31">
         <f>SUM(B35:B37)</f>
@@ -3248,7 +3251,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B39" s="31">
         <f>B25+B27+B33+B38</f>
@@ -3273,7 +3276,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -3283,7 +3286,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B42" s="26">
         <v>34064</v>
@@ -3303,7 +3306,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B43" s="26">
         <v>25000</v>
@@ -3323,7 +3326,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
@@ -3372,7 +3375,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3402,7 +3405,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B4" s="29">
         <f>'Budget Detail'!B12</f>
@@ -3427,7 +3430,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B5" s="29">
         <f>'Budget Detail'!B21</f>
@@ -3452,7 +3455,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B6" s="29">
         <f>'Budget Detail'!B39</f>
@@ -3477,7 +3480,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B7" s="29">
         <f>'Budget Detail'!B44</f>
@@ -3502,7 +3505,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -3527,7 +3530,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3537,7 +3540,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B11" s="27">
         <f>B4-B8</f>
@@ -3562,7 +3565,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B12" s="25">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3587,7 +3590,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B13" s="26">
         <v>789764</v>
@@ -3607,7 +3610,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B14" s="26">
         <v>19750</v>
@@ -3627,7 +3630,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B15" s="26">
         <v>11852</v>
@@ -3672,7 +3675,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3693,48 +3696,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3752,7 +3755,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B4" s="31">
         <v>85833</v>
@@ -3796,7 +3799,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3814,7 +3817,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B7" s="26">
         <v>71231</v>
@@ -3858,7 +3861,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B8" s="26">
         <v>22617</v>
@@ -3902,7 +3905,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B9" s="26">
         <v>4922</v>
@@ -3946,7 +3949,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3964,7 +3967,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B12" s="29">
         <v>98770</v>
@@ -4008,7 +4011,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B13" s="29">
         <v>-12937</v>
@@ -4052,7 +4055,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B14" s="33">
         <v>62063</v>
@@ -4096,14 +4099,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B17" s="26">
         <v>75000</v>
@@ -4111,7 +4114,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B18" s="33">
         <v>864756</v>
@@ -4119,7 +4122,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B19" s="26">
         <v>62063</v>
@@ -4151,7 +4154,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4181,7 +4184,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4191,7 +4194,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B5" s="31">
         <v>1975000</v>
@@ -4211,7 +4214,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4221,7 +4224,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B8" s="29">
         <v>854772</v>
@@ -4241,7 +4244,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B9" s="29">
         <v>271400</v>
@@ -4261,7 +4264,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B10" s="29">
         <v>59064</v>
@@ -4281,7 +4284,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
@@ -4306,7 +4309,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4316,7 +4319,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B14" s="27">
         <f>B5-B11</f>
@@ -4341,7 +4344,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B15" s="25">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4430,7 +4433,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B5" s="26">
         <v>250000</v>
@@ -4450,7 +4453,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B6" s="26">
         <v>15710</v>
@@ -4470,7 +4473,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B7" s="26">
         <v>18355</v>
@@ -4490,7 +4493,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B8" s="29">
         <v>34064</v>
@@ -4510,7 +4513,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B9" s="33">
         <v>231645</v>
@@ -4554,7 +4557,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4584,7 +4587,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4594,7 +4597,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B5" s="35">
         <v>864756</v>
@@ -4614,7 +4617,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B6" s="26">
         <v>12000</v>
@@ -4634,7 +4637,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B7" s="26">
         <v>180000</v>
@@ -4654,7 +4657,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B8" s="26">
         <v>5000</v>
@@ -4674,7 +4677,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B9" s="31">
         <v>1061756</v>
@@ -4694,7 +4697,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4704,7 +4707,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B12" s="26">
         <v>8000</v>
@@ -4724,7 +4727,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B13" s="26">
         <v>231645</v>
@@ -4744,7 +4747,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B14" s="31">
         <v>239645</v>
@@ -4764,7 +4767,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4774,7 +4777,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B17" s="27">
         <v>822111</v>
@@ -4794,7 +4797,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B19" s="36">
         <v>0</v>
@@ -4838,7 +4841,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4868,7 +4871,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4878,7 +4881,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B5" s="26">
         <v>1975000</v>
@@ -4898,7 +4901,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B6" s="26">
         <v>854772</v>
@@ -4918,7 +4921,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B7" s="26">
         <v>271400</v>
@@ -4938,7 +4941,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="B8" s="29">
         <f>B5-B6-B7</f>
@@ -4963,7 +4966,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B9" s="26">
         <v>34064</v>
@@ -4983,7 +4986,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B10" s="38">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5008,7 +5011,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5018,7 +5021,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B13" s="26">
         <v>864756</v>
@@ -5038,7 +5041,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B14" s="23">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5063,7 +5066,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B15" s="30">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5088,7 +5091,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B16" s="25">
         <v>0.5</v>
@@ -5108,7 +5111,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5118,7 +5121,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B19" s="26">
         <v>19750</v>
@@ -5138,7 +5141,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B20" s="26">
         <v>888836</v>
@@ -5158,7 +5161,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B21" s="26">
         <v>2714</v>
@@ -5178,7 +5181,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B22" s="39">
         <v>53</v>
@@ -5198,7 +5201,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5208,102 +5211,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B25" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D25" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E25" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F25" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="B26" s="40" t="s">
         <v>335</v>
       </c>
-      <c r="B26" s="40" t="s">
-        <v>334</v>
-      </c>
       <c r="C26" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D26" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E26" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F26" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B27" s="41" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C27" s="41" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D27" s="41" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E27" s="41" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F27" s="41" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B28" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D28" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E28" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F28" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B29" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D29" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E29" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="F29" s="40" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
   </sheetData>
@@ -5344,13 +5347,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="42" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B3" s="42" t="s">
         <v>100</v>
       </c>
       <c r="D3" s="42" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="E3" s="42" t="s">
         <v>100</v>
@@ -5364,7 +5367,7 @@
         <v>250000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="E4" s="26">
         <v>200000</v>
@@ -5386,13 +5389,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B6" s="26">
         <v>75000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="E6" s="26">
         <v>75000</v>
@@ -5400,7 +5403,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="E7" s="26">
         <v>50000</v>
@@ -5408,13 +5411,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B9" s="27">
         <v>375000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="E9" s="27">
         <v>375000</v>
@@ -5422,7 +5425,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B10" s="36">
         <v>0</v>
@@ -5590,7 +5593,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5600,7 +5603,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5610,7 +5613,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5635,7 +5638,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B6" s="26">
         <v>1975000</v>
@@ -5655,7 +5658,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B7" s="26">
         <v>1160236</v>
@@ -5675,7 +5678,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B8" s="27">
         <v>814764</v>
@@ -5695,7 +5698,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B9" s="25">
         <v>0.4125385351058188</v>
@@ -5715,7 +5718,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B10" s="43">
         <v>24.92</v>
@@ -5735,7 +5738,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B11" s="23">
         <v>53</v>
@@ -5755,7 +5758,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5765,7 +5768,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5790,7 +5793,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B16" s="26">
         <v>1678750</v>
@@ -5810,7 +5813,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B17" s="26">
         <v>1160236</v>
@@ -5830,7 +5833,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B18" s="27">
         <v>518514</v>
@@ -5850,7 +5853,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B19" s="25">
         <v>0.308868864830375</v>
@@ -5870,7 +5873,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B20" s="43">
         <v>16.22</v>
@@ -5890,7 +5893,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B21" s="23">
         <v>54</v>
@@ -5910,7 +5913,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5920,7 +5923,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5945,7 +5948,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B26" s="26">
         <v>1975000</v>
@@ -5965,7 +5968,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B27" s="26">
         <v>1173736</v>
@@ -5985,7 +5988,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B28" s="27">
         <v>801264</v>
@@ -6005,7 +6008,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B29" s="25">
         <v>0.4057030920678441</v>
@@ -6025,7 +6028,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B30" s="43">
         <v>24.52</v>
@@ -6045,7 +6048,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B31" s="23">
         <v>53</v>
@@ -6091,7 +6094,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6125,7 +6128,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6149,7 +6152,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6157,7 +6160,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6195,7 +6198,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D13" s="26">
         <v>1975000</v>
@@ -6215,7 +6218,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="D14" s="26">
         <v>1160236</v>
@@ -6235,7 +6238,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="D15" s="26">
         <v>789764</v>
@@ -6255,7 +6258,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D16" s="26">
         <v>864756</v>
@@ -6275,7 +6278,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D17" s="26">
         <v>231645</v>
@@ -6295,7 +6298,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6333,7 +6336,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D21" s="25">
         <v>0.3998803072577175</v>
@@ -6353,7 +6356,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="D22" s="43">
         <v>24.92</v>
@@ -6373,7 +6376,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D23" s="25">
         <v>0.5</v>
@@ -6393,7 +6396,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D24" s="23">
         <v>100</v>
@@ -6413,7 +6416,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -7191,12 +7194,12 @@
         <v>0.03</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B58" s="19">
         <v>1</v>
@@ -7204,7 +7207,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B59" s="17">
         <v>75000</v>
@@ -7212,10 +7215,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -7250,10 +7253,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7274,10 +7277,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7290,7 +7293,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7301,31 +7304,31 @@
         <v>87</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
@@ -7333,31 +7336,31 @@
         <v>88</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -7400,10 +7403,10 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="D3" s="15" t="s">
         <v>90</v>
@@ -7423,7 +7426,7 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7469,7 +7472,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D8" s="24">
         <v>0.5</v>
@@ -7489,10 +7492,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E10" s="25">
         <v>0.3</v>
@@ -7533,7 +7536,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7563,7 +7566,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7573,7 +7576,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B5" s="26">
         <v>1050000</v>
@@ -7593,7 +7596,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B6" s="26">
         <v>35000</v>
@@ -7613,7 +7616,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B7" s="26">
         <v>105000</v>
@@ -7633,7 +7636,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B8" s="26">
         <v>870000</v>
@@ -7653,7 +7656,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B9" s="26">
         <v>50000</v>
@@ -7673,7 +7676,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="B10" s="26">
         <v>25000</v>
@@ -7693,7 +7696,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B11" s="26">
         <v>50000</v>
@@ -7713,7 +7716,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B12" s="27">
         <f>SUM(B5:B11)</f>
@@ -7786,7 +7789,7 @@
         <v>119</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E3" s="15" t="s">
         <v>121</v>
@@ -7795,7 +7798,7 @@
         <v>122</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -7938,7 +7941,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -7969,7 +7972,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B13" s="27">
         <v>854772</v>
@@ -7989,7 +7992,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B14" s="25">
         <v>0.4327959493670886</v>
@@ -8009,7 +8012,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="B15" s="30">
         <v>7.7</v>
@@ -8053,7 +8056,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8093,7 +8096,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="B5" s="26">
         <v>60000</v>
@@ -8113,7 +8116,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
@@ -8148,7 +8151,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="B8" s="26">
         <v>40000</v>
@@ -8168,7 +8171,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -8203,7 +8206,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B11" s="26">
         <v>102000</v>
@@ -8223,7 +8226,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B12" s="26">
         <v>14400</v>
@@ -8243,7 +8246,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B13" s="26">
         <v>12000</v>
@@ -8263,7 +8266,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B14" s="26">
         <v>8000</v>
@@ -8283,7 +8286,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B11:B14)</f>
@@ -8318,7 +8321,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B17" s="26">
         <v>15000</v>
@@ -8338,7 +8341,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B18" s="26">
         <v>8000</v>
@@ -8358,7 +8361,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B19" s="26">
         <v>12000</v>
@@ -8378,7 +8381,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B20" s="31">
         <f>SUM(B17:B19)</f>
@@ -8403,7 +8406,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B22" s="27">
         <f>B6+B9+B15+B20</f>
@@ -8453,7 +8456,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8478,7 +8481,7 @@
         <v>151</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -8506,7 +8509,7 @@
         <v>154</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="C5" s="17">
         <v>25000</v>
@@ -8523,7 +8526,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F7" s="27">
         <v>34064</v>
@@ -8531,7 +8534,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F8" s="31">
         <v>250000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -26,7 +26,7 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -72,7 +72,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 17, 2026</t>
+    <t>March 18, 2026</t>
   </si>
   <si>
     <t>Stage</t>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="682" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="378">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -222,13 +222,13 @@
     <t>How to Use This Workbook</t>
   </si>
   <si>
-    <t>Color Legend</t>
-  </si>
-  <si>
-    <t>Yellow cells are editable inputs - change these to update your model.</t>
-  </si>
-  <si>
-    <t>Gray cells contain formulas - do not edit.</t>
+    <t>Cell Color Legend</t>
+  </si>
+  <si>
+    <t>Yellow cells are editable inputs — change these to update your model.</t>
+  </si>
+  <si>
+    <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
   </si>
   <si>
     <t>Green cells are key outputs and summary metrics.</t>
@@ -240,7 +240,7 @@
     <t>Navigation</t>
   </si>
   <si>
-    <t>The Assumptions tab is the central control panel - all other tabs reference it.</t>
+    <t>The Assumptions tab is the central control panel — all other tabs reference it.</t>
   </si>
   <si>
     <t>Structure</t>
@@ -258,6 +258,24 @@
     <t>Tabs 18-21: Analysis &amp; underwriting</t>
   </si>
   <si>
+    <t>Debt Service Convention</t>
+  </si>
+  <si>
+    <t>operating expense on the 5-Year Operating Statement. This is a standard</t>
+  </si>
+  <si>
+    <t>simplification used in school financial underwriting that ensures internal</t>
+  </si>
+  <si>
+    <t>consistency across all tabs: the Cash Flow, Balance Sheet, and DSCR</t>
+  </si>
+  <si>
+    <t>schedules all reference the same debt service figures. The Debt Schedule</t>
+  </si>
+  <si>
+    <t>tab breaks out interest and principal separately for detailed analysis.</t>
+  </si>
+  <si>
     <t>Tips</t>
   </si>
   <si>
@@ -934,6 +952,21 @@
   </si>
   <si>
     <t>BOTTOM LINE</t>
+  </si>
+  <si>
+    <t>LOAN TERMS</t>
+  </si>
+  <si>
+    <t>Loan Name</t>
+  </si>
+  <si>
+    <t>Annual Rate</t>
+  </si>
+  <si>
+    <t>Term (Years)</t>
+  </si>
+  <si>
+    <t>AMORTIZATION: Facility Buildout Loan</t>
   </si>
   <si>
     <t>Beginning Balance</t>
@@ -1305,7 +1338,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1349,6 +1382,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -2023,7 +2059,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2036,24 +2072,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B4" s="21">
         <v>100</v>
@@ -2073,7 +2109,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2083,7 +2119,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B7" s="26">
         <v>1050000</v>
@@ -2103,7 +2139,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B8" s="26">
         <v>35000</v>
@@ -2123,7 +2159,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B9" s="26">
         <v>105000</v>
@@ -2143,7 +2179,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B10" s="26">
         <v>870000</v>
@@ -2163,7 +2199,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B11" s="26">
         <v>50000</v>
@@ -2183,7 +2219,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B12" s="26">
         <v>25000</v>
@@ -2203,7 +2239,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B13" s="26">
         <v>50000</v>
@@ -2223,7 +2259,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B14" s="27">
         <f>SUM(B7:B13)</f>
@@ -2248,7 +2284,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B16" s="26">
         <v>19750</v>
@@ -2292,7 +2328,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2305,24 +2341,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2332,7 +2368,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B5" s="26">
         <v>382032</v>
@@ -2352,7 +2388,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B6" s="26">
         <v>122544</v>
@@ -2372,7 +2408,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="B7" s="31">
         <f>SUM(B5:B6)</f>
@@ -2397,7 +2433,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2407,7 +2443,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B9" s="26">
         <v>126018</v>
@@ -2427,7 +2463,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B10" s="26">
         <v>99488</v>
@@ -2447,7 +2483,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
@@ -2472,7 +2508,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2482,7 +2518,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B13" s="26">
         <v>68978</v>
@@ -2502,7 +2538,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
@@ -2527,7 +2563,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2537,7 +2573,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B16" s="26">
         <v>55713</v>
@@ -2557,7 +2593,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B17" s="31">
         <f>SUM(B16:B16)</f>
@@ -2582,7 +2618,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B19" s="27">
         <f>B7+B11+B14+B17</f>
@@ -2631,7 +2667,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2644,24 +2680,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2671,7 +2707,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B5" s="26">
         <v>1050000</v>
@@ -2691,7 +2727,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B6" s="26">
         <v>35000</v>
@@ -2711,7 +2747,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B7" s="26">
         <v>105000</v>
@@ -2731,7 +2767,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="B8" s="26">
         <v>870000</v>
@@ -2751,7 +2787,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B9" s="26">
         <v>50000</v>
@@ -2771,7 +2807,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B10" s="26">
         <v>25000</v>
@@ -2791,7 +2827,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B11" s="26">
         <v>50000</v>
@@ -2811,7 +2847,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B5:B11)</f>
@@ -2836,7 +2872,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2846,7 +2882,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B15" s="26">
         <v>126018</v>
@@ -2866,7 +2902,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B16" s="26">
         <v>99488</v>
@@ -2886,7 +2922,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="B17" s="26">
         <v>382032</v>
@@ -2906,7 +2942,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B18" s="26">
         <v>122544</v>
@@ -2926,7 +2962,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B19" s="26">
         <v>55713</v>
@@ -2946,7 +2982,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="B20" s="26">
         <v>68978</v>
@@ -2966,7 +3002,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B21" s="31">
         <f>SUM(B15:B20)</f>
@@ -2991,7 +3027,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3001,12 +3037,12 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="32" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="B25" s="26">
         <v>60000</v>
@@ -3026,12 +3062,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B27" s="26">
         <v>40000</v>
@@ -3051,12 +3087,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B29" s="26">
         <v>102000</v>
@@ -3076,7 +3112,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B30" s="26">
         <v>14400</v>
@@ -3096,7 +3132,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B31" s="26">
         <v>12000</v>
@@ -3116,7 +3152,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B32" s="26">
         <v>8000</v>
@@ -3136,7 +3172,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B33" s="31">
         <f>SUM(B29:B32)</f>
@@ -3161,12 +3197,12 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="32" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="B35" s="26">
         <v>15000</v>
@@ -3186,7 +3222,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B36" s="26">
         <v>8000</v>
@@ -3206,7 +3242,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B37" s="26">
         <v>12000</v>
@@ -3226,7 +3262,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="B38" s="31">
         <f>SUM(B35:B37)</f>
@@ -3251,7 +3287,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B39" s="31">
         <f>B25+B27+B33+B38</f>
@@ -3276,7 +3312,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -3286,7 +3322,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B42" s="26">
         <v>34064</v>
@@ -3306,7 +3342,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="B43" s="26">
         <v>25000</v>
@@ -3326,7 +3362,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
@@ -3375,7 +3411,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3388,24 +3424,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B4" s="29">
         <f>'Budget Detail'!B12</f>
@@ -3430,7 +3466,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B5" s="29">
         <f>'Budget Detail'!B21</f>
@@ -3455,7 +3491,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B6" s="29">
         <f>'Budget Detail'!B39</f>
@@ -3480,7 +3516,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B7" s="29">
         <f>'Budget Detail'!B44</f>
@@ -3505,7 +3541,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -3530,7 +3566,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3540,7 +3576,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B11" s="27">
         <f>B4-B8</f>
@@ -3565,7 +3601,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B12" s="25">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3590,7 +3626,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B13" s="26">
         <v>789764</v>
@@ -3610,7 +3646,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B14" s="26">
         <v>19750</v>
@@ -3630,7 +3666,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B15" s="26">
         <v>11852</v>
@@ -3675,7 +3711,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3696,48 +3732,48 @@
         <v>67</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E2" s="15" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="G2" s="15" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="H2" s="15" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="I2" s="15" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="J2" s="15" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="K2" s="15" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="L2" s="15" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="M2" s="15" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="N2" s="15" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3755,7 +3791,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B4" s="31">
         <v>85833</v>
@@ -3799,7 +3835,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3817,7 +3853,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B7" s="26">
         <v>71231</v>
@@ -3861,7 +3897,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B8" s="26">
         <v>22617</v>
@@ -3905,7 +3941,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B9" s="26">
         <v>4922</v>
@@ -3949,7 +3985,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -3967,7 +4003,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B12" s="29">
         <v>98770</v>
@@ -4011,7 +4047,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B13" s="29">
         <v>-12937</v>
@@ -4055,7 +4091,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B14" s="33">
         <v>62063</v>
@@ -4099,14 +4135,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B17" s="26">
         <v>75000</v>
@@ -4114,7 +4150,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B18" s="33">
         <v>864756</v>
@@ -4122,7 +4158,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="B19" s="26">
         <v>62063</v>
@@ -4154,7 +4190,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4167,24 +4203,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4194,7 +4230,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B5" s="31">
         <v>1975000</v>
@@ -4214,7 +4250,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4224,7 +4260,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B8" s="29">
         <v>854772</v>
@@ -4244,7 +4280,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B9" s="29">
         <v>271400</v>
@@ -4264,7 +4300,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B10" s="29">
         <v>59064</v>
@@ -4284,7 +4320,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
@@ -4309,7 +4345,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4319,7 +4355,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B14" s="27">
         <f>B5-B11</f>
@@ -4344,7 +4380,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B15" s="25">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4384,7 +4420,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4406,24 +4442,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>152</v>
+        <v>307</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4431,103 +4467,173 @@
       <c r="E4" s="13"/>
       <c r="F4" s="13"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
-        <v>301</v>
-      </c>
-      <c r="B5" s="26">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="35" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>156</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>309</v>
+      </c>
+      <c r="D5" s="35" t="s">
+        <v>310</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="B6" s="17">
         <v>250000</v>
       </c>
-      <c r="C5" s="26">
+      <c r="C6" s="18">
+        <v>0.065</v>
+      </c>
+      <c r="D6" s="14">
+        <v>10</v>
+      </c>
+      <c r="E6" s="26">
+        <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
+        <v>34064</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="13" t="s">
+        <v>311</v>
+      </c>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>312</v>
+      </c>
+      <c r="B9" s="26">
+        <f>B6</f>
+        <v>250000</v>
+      </c>
+      <c r="C9" s="26">
+        <f>B13</f>
         <v>231645</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D9" s="26">
+        <f>C13</f>
         <v>212061</v>
       </c>
-      <c r="E5" s="26">
+      <c r="E9" s="26">
+        <f>D13</f>
         <v>191165</v>
       </c>
-      <c r="F5" s="26">
+      <c r="F9" s="26">
+        <f>E13</f>
         <v>168870</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="B6" s="26">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>313</v>
+      </c>
+      <c r="B10" s="26">
+        <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>15710</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C10" s="26">
+        <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>14480</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D10" s="26">
+        <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>13169</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E10" s="26">
+        <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>11769</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F10" s="26">
+        <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>10276</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
-        <v>303</v>
-      </c>
-      <c r="B7" s="26">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>314</v>
+      </c>
+      <c r="B11" s="26">
+        <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>18355</v>
       </c>
-      <c r="C7" s="26">
+      <c r="C11" s="26">
+        <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>19584</v>
       </c>
-      <c r="D7" s="26">
+      <c r="D11" s="26">
+        <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>20896</v>
       </c>
-      <c r="E7" s="26">
+      <c r="E11" s="26">
+        <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>22295</v>
       </c>
-      <c r="F7" s="26">
+      <c r="F11" s="26">
+        <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>23788</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="B8" s="29">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="B12" s="29">
+        <f>B10+B11</f>
         <v>34064</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C12" s="29">
+        <f>C10+C11</f>
         <v>34064</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D12" s="29">
+        <f>D10+D11</f>
         <v>34064</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E12" s="29">
+        <f>E10+E11</f>
         <v>34064</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F12" s="29">
+        <f>F10+F11</f>
         <v>34064</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="B9" s="33">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B13" s="33">
+        <f>MAX(0,B9-B11)</f>
         <v>231645</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C13" s="33">
+        <f>MAX(0,C9-C11)</f>
         <v>212061</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D13" s="33">
+        <f>MAX(0,D9-D11)</f>
         <v>191165</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E13" s="33">
+        <f>MAX(0,E9-E11)</f>
         <v>168870</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F13" s="33">
+        <f>MAX(0,F9-F11)</f>
         <v>145082</v>
       </c>
     </row>
@@ -4557,7 +4663,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4570,24 +4676,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4597,27 +4703,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="B5" s="35">
+        <v>319</v>
+      </c>
+      <c r="B5" s="38">
         <v>864756</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="38">
         <v>2251184</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="38">
         <v>4253414</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="38">
         <v>6813759</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="38">
         <v>9755974</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="B6" s="26">
         <v>12000</v>
@@ -4637,7 +4743,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="B7" s="26">
         <v>180000</v>
@@ -4657,7 +4763,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="B8" s="26">
         <v>5000</v>
@@ -4677,7 +4783,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="B9" s="31">
         <v>1061756</v>
@@ -4697,7 +4803,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4707,7 +4813,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="B12" s="26">
         <v>8000</v>
@@ -4727,7 +4833,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="B13" s="26">
         <v>231645</v>
@@ -4747,7 +4853,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
       <c r="B14" s="31">
         <v>239645</v>
@@ -4767,7 +4873,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4777,7 +4883,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="B17" s="27">
         <v>822111</v>
@@ -4797,21 +4903,21 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="B19" s="36">
+        <v>330</v>
+      </c>
+      <c r="B19" s="39">
         <v>0</v>
       </c>
-      <c r="C19" s="36">
+      <c r="C19" s="39">
         <v>0</v>
       </c>
-      <c r="D19" s="37">
+      <c r="D19" s="40">
         <v>1</v>
       </c>
-      <c r="E19" s="37">
+      <c r="E19" s="40">
         <v>1</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="39">
         <v>0</v>
       </c>
     </row>
@@ -4841,7 +4947,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4854,24 +4960,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4881,7 +4987,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B5" s="26">
         <v>1975000</v>
@@ -4901,7 +5007,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B6" s="26">
         <v>854772</v>
@@ -4921,7 +5027,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B7" s="26">
         <v>271400</v>
@@ -4941,7 +5047,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="B8" s="29">
         <f>B5-B6-B7</f>
@@ -4966,7 +5072,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B9" s="26">
         <v>34064</v>
@@ -4986,32 +5092,32 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B10" s="38">
+        <v>335</v>
+      </c>
+      <c r="B10" s="41">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>24.92</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="41">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>41.99</v>
       </c>
-      <c r="D10" s="38">
+      <c r="D10" s="41">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>60.07</v>
       </c>
-      <c r="E10" s="38">
+      <c r="E10" s="41">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>76.31</v>
       </c>
-      <c r="F10" s="38">
+      <c r="F10" s="41">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>87.52</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5021,7 +5127,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B13" s="26">
         <v>864756</v>
@@ -5041,7 +5147,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="B14" s="23">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5066,7 +5172,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="B15" s="30">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5091,7 +5197,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="B16" s="25">
         <v>0.5</v>
@@ -5111,7 +5217,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5121,7 +5227,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="B19" s="26">
         <v>19750</v>
@@ -5141,7 +5247,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B20" s="26">
         <v>888836</v>
@@ -5161,7 +5267,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="B21" s="26">
         <v>2714</v>
@@ -5181,27 +5287,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B22" s="39">
+        <v>343</v>
+      </c>
+      <c r="B22" s="42">
         <v>53</v>
       </c>
-      <c r="C22" s="39">
+      <c r="C22" s="42">
         <v>52</v>
       </c>
-      <c r="D22" s="39">
+      <c r="D22" s="42">
         <v>51</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="42">
         <v>51</v>
       </c>
-      <c r="F22" s="39">
+      <c r="F22" s="42">
         <v>51</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5211,102 +5317,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>334</v>
-      </c>
-      <c r="B25" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="E25" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="F25" s="40" t="s">
-        <v>335</v>
+        <v>345</v>
+      </c>
+      <c r="B25" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="C25" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="D25" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="F25" s="43" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="B26" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="E26" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="F26" s="40" t="s">
-        <v>335</v>
+        <v>347</v>
+      </c>
+      <c r="B26" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="C26" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="D26" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="E26" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="F26" s="43" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>337</v>
-      </c>
-      <c r="B27" s="41" t="s">
-        <v>338</v>
-      </c>
-      <c r="C27" s="41" t="s">
-        <v>338</v>
-      </c>
-      <c r="D27" s="41" t="s">
-        <v>338</v>
-      </c>
-      <c r="E27" s="41" t="s">
-        <v>338</v>
-      </c>
-      <c r="F27" s="41" t="s">
-        <v>338</v>
+        <v>348</v>
+      </c>
+      <c r="B27" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="E27" s="44" t="s">
+        <v>349</v>
+      </c>
+      <c r="F27" s="44" t="s">
+        <v>349</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>339</v>
-      </c>
-      <c r="B28" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="D28" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="E28" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="F28" s="40" t="s">
-        <v>335</v>
+        <v>350</v>
+      </c>
+      <c r="B28" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="C28" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="D28" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="F28" s="43" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>340</v>
-      </c>
-      <c r="B29" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="D29" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="E29" s="40" t="s">
-        <v>335</v>
-      </c>
-      <c r="F29" s="40" t="s">
-        <v>335</v>
+        <v>351</v>
+      </c>
+      <c r="B29" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="C29" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="D29" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>346</v>
+      </c>
+      <c r="F29" s="43" t="s">
+        <v>346</v>
       </c>
     </row>
   </sheetData>
@@ -5346,28 +5452,28 @@
       <c r="E1" s="11"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
-        <v>341</v>
-      </c>
-      <c r="B3" s="42" t="s">
-        <v>100</v>
-      </c>
-      <c r="D3" s="42" t="s">
-        <v>342</v>
-      </c>
-      <c r="E3" s="42" t="s">
-        <v>100</v>
+      <c r="A3" s="45" t="s">
+        <v>352</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="45" t="s">
+        <v>353</v>
+      </c>
+      <c r="E3" s="45" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B4" s="26">
         <v>250000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="E4" s="26">
         <v>200000</v>
@@ -5375,13 +5481,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B5" s="26">
         <v>50000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E5" s="26">
         <v>50000</v>
@@ -5389,13 +5495,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="B6" s="26">
         <v>75000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="E6" s="26">
         <v>75000</v>
@@ -5403,7 +5509,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="E7" s="26">
         <v>50000</v>
@@ -5411,13 +5517,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="B9" s="27">
         <v>375000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="E9" s="27">
         <v>375000</v>
@@ -5425,9 +5531,9 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B10" s="36">
+        <v>360</v>
+      </c>
+      <c r="B10" s="39">
         <v>0</v>
       </c>
     </row>
@@ -5448,7 +5554,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B25"/>
+  <dimension ref="B2:B32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5552,22 +5658,57 @@
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>67</v>
+        <v>79</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>79</v>
+      <c r="B23" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="10" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="26" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="27" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="28" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B29" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B30" s="10" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B31" s="6" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B32" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -5593,7 +5734,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5603,7 +5744,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5613,7 +5754,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5621,24 +5762,24 @@
         <v>67</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E5" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B6" s="26">
         <v>1975000</v>
@@ -5658,7 +5799,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B7" s="26">
         <v>1160236</v>
@@ -5678,7 +5819,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B8" s="27">
         <v>814764</v>
@@ -5698,7 +5839,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B9" s="25">
         <v>0.4125385351058188</v>
@@ -5718,27 +5859,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B10" s="43">
+        <v>335</v>
+      </c>
+      <c r="B10" s="46">
         <v>24.92</v>
       </c>
-      <c r="C10" s="43">
+      <c r="C10" s="46">
         <v>41.99</v>
       </c>
-      <c r="D10" s="43">
+      <c r="D10" s="46">
         <v>60.07</v>
       </c>
-      <c r="E10" s="43">
+      <c r="E10" s="46">
         <v>76.31</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="46">
         <v>87.52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B11" s="23">
         <v>53</v>
@@ -5758,7 +5899,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5768,7 +5909,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5776,24 +5917,24 @@
         <v>67</v>
       </c>
       <c r="B15" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C15" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F15" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B16" s="26">
         <v>1678750</v>
@@ -5813,7 +5954,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B17" s="26">
         <v>1160236</v>
@@ -5833,7 +5974,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B18" s="27">
         <v>518514</v>
@@ -5853,7 +5994,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B19" s="25">
         <v>0.308868864830375</v>
@@ -5873,27 +6014,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B20" s="43">
+        <v>335</v>
+      </c>
+      <c r="B20" s="46">
         <v>16.22</v>
       </c>
-      <c r="C20" s="43">
+      <c r="C20" s="46">
         <v>30.45</v>
       </c>
-      <c r="D20" s="43">
+      <c r="D20" s="46">
         <v>45.52</v>
       </c>
-      <c r="E20" s="43">
+      <c r="E20" s="46">
         <v>59.03</v>
       </c>
-      <c r="F20" s="43">
+      <c r="F20" s="46">
         <v>68.31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B21" s="23">
         <v>54</v>
@@ -5913,7 +6054,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -5923,7 +6064,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5931,24 +6072,24 @@
         <v>67</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F25" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B26" s="26">
         <v>1975000</v>
@@ -5968,7 +6109,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B27" s="26">
         <v>1173736</v>
@@ -5988,7 +6129,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B28" s="27">
         <v>801264</v>
@@ -6008,7 +6149,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B29" s="25">
         <v>0.4057030920678441</v>
@@ -6028,27 +6169,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="B30" s="43">
+        <v>335</v>
+      </c>
+      <c r="B30" s="46">
         <v>24.52</v>
       </c>
-      <c r="C30" s="43">
+      <c r="C30" s="46">
         <v>41.49</v>
       </c>
-      <c r="D30" s="43">
+      <c r="D30" s="46">
         <v>59.46</v>
       </c>
-      <c r="E30" s="43">
+      <c r="E30" s="46">
         <v>75.6</v>
       </c>
-      <c r="F30" s="43">
+      <c r="F30" s="46">
         <v>86.74</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="B31" s="23">
         <v>53</v>
@@ -6094,7 +6235,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6106,7 +6247,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B3" s="13"/>
     </row>
@@ -6120,7 +6261,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -6128,7 +6269,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6152,7 +6293,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6160,7 +6301,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6180,25 +6321,25 @@
       <c r="C12" t="s">
         <v>67</v>
       </c>
-      <c r="D12" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E12" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F12" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G12" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H12" s="44" t="s">
-        <v>94</v>
+      <c r="D12" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="E12" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F12" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="H12" s="47" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="D13" s="26">
         <v>1975000</v>
@@ -6218,7 +6359,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D14" s="26">
         <v>1160236</v>
@@ -6238,7 +6379,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D15" s="26">
         <v>789764</v>
@@ -6258,7 +6399,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D16" s="26">
         <v>864756</v>
@@ -6278,7 +6419,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="D17" s="26">
         <v>231645</v>
@@ -6298,7 +6439,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6318,25 +6459,25 @@
       <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="D20" s="44" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F20" s="44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="44" t="s">
-        <v>93</v>
-      </c>
-      <c r="H20" s="44" t="s">
-        <v>94</v>
+      <c r="D20" s="47" t="s">
+        <v>96</v>
+      </c>
+      <c r="E20" s="47" t="s">
+        <v>97</v>
+      </c>
+      <c r="F20" s="47" t="s">
+        <v>98</v>
+      </c>
+      <c r="G20" s="47" t="s">
+        <v>99</v>
+      </c>
+      <c r="H20" s="47" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="D21" s="25">
         <v>0.3998803072577175</v>
@@ -6356,27 +6497,27 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="D22" s="43">
+        <v>335</v>
+      </c>
+      <c r="D22" s="46">
         <v>24.92</v>
       </c>
-      <c r="E22" s="43">
+      <c r="E22" s="46">
         <v>41.99</v>
       </c>
-      <c r="F22" s="43">
+      <c r="F22" s="46">
         <v>60.07</v>
       </c>
-      <c r="G22" s="43">
+      <c r="G22" s="46">
         <v>76.31</v>
       </c>
-      <c r="H22" s="43">
+      <c r="H22" s="46">
         <v>87.52</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D23" s="25">
         <v>0.5</v>
@@ -6396,7 +6537,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D24" s="23">
         <v>100</v>
@@ -6416,7 +6557,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6454,7 +6595,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6465,12 +6606,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6513,10 +6654,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B9" s="14" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6537,7 +6678,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -6545,7 +6686,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B13" s="14">
         <v>200</v>
@@ -6553,7 +6694,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6567,24 +6708,24 @@
         <v>67</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B17" s="16">
         <v>100</v>
@@ -6604,7 +6745,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>96</v>
+        <v>102</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6615,30 +6756,30 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D21" s="17">
         <v>10500</v>
@@ -6649,13 +6790,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D22" s="17">
         <v>350</v>
@@ -6666,13 +6807,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D23" s="17">
         <v>-1050</v>
@@ -6683,13 +6824,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D24" s="17">
         <v>8700</v>
@@ -6700,13 +6841,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D25" s="17">
         <v>50000</v>
@@ -6717,13 +6858,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D26" s="17">
         <v>25000</v>
@@ -6734,13 +6875,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D27" s="17">
         <v>500</v>
@@ -6751,7 +6892,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -6762,36 +6903,36 @@
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C30" s="15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="D30" s="15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E30" s="15" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="G30" s="15" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D31" s="19">
         <v>1</v>
@@ -6808,13 +6949,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D32" s="19">
         <v>1</v>
@@ -6831,13 +6972,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D33" s="19">
         <v>6</v>
@@ -6854,13 +6995,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D34" s="19">
         <v>3</v>
@@ -6877,13 +7018,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B35" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>131</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>125</v>
       </c>
       <c r="D35" s="19">
         <v>1</v>
@@ -6900,13 +7041,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="D36" s="19">
         <v>1</v>
@@ -6923,7 +7064,7 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -6934,30 +7075,30 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C39" s="15" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="D39" s="15" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="E39" s="15" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D40" s="17">
         <v>8500</v>
@@ -6968,13 +7109,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="D41" s="17">
         <v>1200</v>
@@ -6985,13 +7126,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D42" s="17">
         <v>12000</v>
@@ -7002,13 +7143,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D43" s="17">
         <v>8000</v>
@@ -7019,13 +7160,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D44" s="17">
         <v>600</v>
@@ -7036,13 +7177,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="D45" s="17">
         <v>400</v>
@@ -7053,13 +7194,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D46" s="17">
         <v>15000</v>
@@ -7070,13 +7211,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D47" s="17">
         <v>8000</v>
@@ -7087,13 +7228,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="D48" s="17">
         <v>12000</v>
@@ -7104,7 +7245,7 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -7115,27 +7256,27 @@
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D51" s="15" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E51" s="15" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C52" s="17">
         <v>250000</v>
@@ -7149,10 +7290,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C53" s="17">
         <v>25000</v>
@@ -7166,7 +7307,7 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -7177,29 +7318,29 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B56" s="18">
         <v>0.03</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B57" s="18">
         <v>0.03</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="B58" s="19">
         <v>1</v>
@@ -7207,7 +7348,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B59" s="17">
         <v>75000</v>
@@ -7215,10 +7356,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7253,10 +7394,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7277,10 +7418,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7293,7 +7434,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7301,66 +7442,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -7403,30 +7544,30 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="H3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7438,7 +7579,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="B6" s="21">
         <v>85</v>
@@ -7464,7 +7605,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B7" s="23">
         <v>200</v>
@@ -7472,7 +7613,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="D8" s="24">
         <v>0.5</v>
@@ -7492,10 +7633,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E10" s="25">
         <v>0.3</v>
@@ -7536,7 +7677,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7549,24 +7690,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7576,7 +7717,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="B5" s="26">
         <v>1050000</v>
@@ -7596,7 +7737,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B6" s="26">
         <v>35000</v>
@@ -7616,7 +7757,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="B7" s="26">
         <v>105000</v>
@@ -7636,7 +7777,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B8" s="26">
         <v>870000</v>
@@ -7656,7 +7797,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B9" s="26">
         <v>50000</v>
@@ -7676,7 +7817,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="B10" s="26">
         <v>25000</v>
@@ -7696,7 +7837,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B11" s="26">
         <v>50000</v>
@@ -7716,7 +7857,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="B12" s="27">
         <f>SUM(B5:B11)</f>
@@ -7780,33 +7921,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G3" s="15" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C4" s="28">
         <v>1</v>
@@ -7826,10 +7967,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="C5" s="28">
         <v>1</v>
@@ -7849,10 +7990,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C6" s="28">
         <v>6</v>
@@ -7872,10 +8013,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="C7" s="28">
         <v>3</v>
@@ -7895,10 +8036,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="C8" s="28">
         <v>1</v>
@@ -7918,10 +8059,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="C9" s="28">
         <v>1</v>
@@ -7941,7 +8082,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -7955,24 +8096,24 @@
         <v>67</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C12" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D12" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B13" s="27">
         <v>854772</v>
@@ -7992,7 +8133,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="B14" s="25">
         <v>0.4327959493670886</v>
@@ -8012,7 +8153,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B15" s="30">
         <v>7.7</v>
@@ -8056,7 +8197,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8069,24 +8210,24 @@
         <v>67</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8096,7 +8237,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B5" s="26">
         <v>60000</v>
@@ -8116,7 +8257,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
@@ -8141,7 +8282,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -8151,7 +8292,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B8" s="26">
         <v>40000</v>
@@ -8171,7 +8312,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -8196,7 +8337,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -8206,7 +8347,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B11" s="26">
         <v>102000</v>
@@ -8226,7 +8367,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="B12" s="26">
         <v>14400</v>
@@ -8246,7 +8387,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B13" s="26">
         <v>12000</v>
@@ -8266,7 +8407,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="B14" s="26">
         <v>8000</v>
@@ -8286,7 +8427,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B11:B14)</f>
@@ -8311,7 +8452,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -8321,7 +8462,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="B17" s="26">
         <v>15000</v>
@@ -8341,7 +8482,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B18" s="26">
         <v>8000</v>
@@ -8361,7 +8502,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="B19" s="26">
         <v>12000</v>
@@ -8381,7 +8522,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B20" s="31">
         <f>SUM(B17:B19)</f>
@@ -8406,7 +8547,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="B22" s="27">
         <f>B6+B9+B15+B20</f>
@@ -8456,7 +8597,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8466,30 +8607,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E3" s="15" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="F3" s="15" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="C4" s="17">
         <v>250000</v>
@@ -8506,10 +8647,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="C5" s="17">
         <v>25000</v>
@@ -8526,7 +8667,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F7" s="27">
         <v>34064</v>
@@ -8534,7 +8675,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="F8" s="31">
         <v>250000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -3830,6 +3830,7 @@
         <v>85833</v>
       </c>
       <c r="N4" s="31">
+        <f>SUM(B4:M4)</f>
         <v>1974996</v>
       </c>
     </row>
@@ -3892,6 +3893,7 @@
         <v>71231</v>
       </c>
       <c r="N7" s="26">
+        <f>SUM(B7:M7)</f>
         <v>854772</v>
       </c>
     </row>
@@ -3936,6 +3938,7 @@
         <v>22617</v>
       </c>
       <c r="N8" s="26">
+        <f>SUM(B8:M8)</f>
         <v>271400</v>
       </c>
     </row>
@@ -3980,6 +3983,7 @@
         <v>4922</v>
       </c>
       <c r="N9" s="26">
+        <f>SUM(B9:M9)</f>
         <v>59064</v>
       </c>
     </row>
@@ -4006,42 +4010,55 @@
         <v>274</v>
       </c>
       <c r="B12" s="29">
+        <f>B7+B8+B9</f>
         <v>98770</v>
       </c>
       <c r="C12" s="29">
+        <f>C7+C8+C9</f>
         <v>98770</v>
       </c>
       <c r="D12" s="29">
+        <f>D7+D8+D9</f>
         <v>98770</v>
       </c>
       <c r="E12" s="29">
+        <f>E7+E8+E9</f>
         <v>98770</v>
       </c>
       <c r="F12" s="29">
+        <f>F7+F8+F9</f>
         <v>98770</v>
       </c>
       <c r="G12" s="29">
+        <f>G7+G8+G9</f>
         <v>98770</v>
       </c>
       <c r="H12" s="29">
+        <f>H7+H8+H9</f>
         <v>98770</v>
       </c>
       <c r="I12" s="29">
+        <f>I7+I8+I9</f>
         <v>98770</v>
       </c>
       <c r="J12" s="29">
+        <f>J7+J8+J9</f>
         <v>98770</v>
       </c>
       <c r="K12" s="29">
+        <f>K7+K8+K9</f>
         <v>98770</v>
       </c>
       <c r="L12" s="29">
+        <f>L7+L8+L9</f>
         <v>98770</v>
       </c>
       <c r="M12" s="29">
+        <f>M7+M8+M9</f>
         <v>98770</v>
       </c>
       <c r="N12" s="29">
+        <f>SUM(B12:M12)</f>
         <v>1185240</v>
       </c>
     </row>
@@ -4050,42 +4067,55 @@
         <v>299</v>
       </c>
       <c r="B13" s="29">
+        <f>B4-B12</f>
         <v>-12937</v>
       </c>
       <c r="C13" s="29">
+        <f>C4-C12</f>
         <v>81563</v>
       </c>
       <c r="D13" s="29">
+        <f>D4-D12</f>
         <v>81563</v>
       </c>
       <c r="E13" s="29">
+        <f>E4-E12</f>
         <v>81563</v>
       </c>
       <c r="F13" s="29">
+        <f>F4-F12</f>
         <v>81563</v>
       </c>
       <c r="G13" s="29">
+        <f>G4-G12</f>
         <v>81563</v>
       </c>
       <c r="H13" s="29">
+        <f>H4-H12</f>
         <v>81563</v>
       </c>
       <c r="I13" s="29">
+        <f>I4-I12</f>
         <v>81563</v>
       </c>
       <c r="J13" s="29">
+        <f>J4-J12</f>
         <v>81563</v>
       </c>
       <c r="K13" s="29">
+        <f>K4-K12</f>
         <v>81563</v>
       </c>
       <c r="L13" s="29">
+        <f>L4-L12</f>
         <v>81563</v>
       </c>
       <c r="M13" s="29">
+        <f>M4-M12</f>
         <v>-12937</v>
       </c>
       <c r="N13" s="29">
+        <f>SUM(B13:M13)</f>
         <v>789756</v>
       </c>
     </row>
@@ -4094,42 +4124,55 @@
         <v>300</v>
       </c>
       <c r="B14" s="33">
+        <f>B17+B13</f>
         <v>62063</v>
       </c>
       <c r="C14" s="33">
+        <f>B14+C13</f>
         <v>143626</v>
       </c>
       <c r="D14" s="33">
+        <f>C14+D13</f>
         <v>225189</v>
       </c>
       <c r="E14" s="33">
+        <f>D14+E13</f>
         <v>306752</v>
       </c>
       <c r="F14" s="33">
+        <f>E14+F13</f>
         <v>388315</v>
       </c>
       <c r="G14" s="33">
+        <f>F14+G13</f>
         <v>469878</v>
       </c>
       <c r="H14" s="33">
+        <f>G14+H13</f>
         <v>551441</v>
       </c>
       <c r="I14" s="33">
+        <f>H14+I13</f>
         <v>633004</v>
       </c>
       <c r="J14" s="33">
+        <f>I14+J13</f>
         <v>714567</v>
       </c>
       <c r="K14" s="33">
+        <f>J14+K13</f>
         <v>796130</v>
       </c>
       <c r="L14" s="33">
+        <f>K14+L13</f>
         <v>877693</v>
       </c>
       <c r="M14" s="33">
+        <f>L14+M13</f>
         <v>864756</v>
       </c>
       <c r="N14" s="27">
+        <f>M14</f>
         <v>864756</v>
       </c>
     </row>
@@ -4144,7 +4187,7 @@
       <c r="A17" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B17" s="26">
+      <c r="B17" s="17">
         <v>75000</v>
       </c>
     </row>
@@ -4153,6 +4196,7 @@
         <v>302</v>
       </c>
       <c r="B18" s="33">
+        <f>M14</f>
         <v>864756</v>
       </c>
     </row>
@@ -4161,6 +4205,7 @@
         <v>303</v>
       </c>
       <c r="B19" s="26">
+        <f>MIN(B14:M14)</f>
         <v>62063</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -4751,18 +4751,23 @@
         <v>319</v>
       </c>
       <c r="B5" s="38">
+        <f>'Monthly Cash Flow Y1'!M14</f>
         <v>864756</v>
       </c>
       <c r="C5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>2251184</v>
       </c>
       <c r="D5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>4253414</v>
       </c>
       <c r="E5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>6813759</v>
       </c>
       <c r="F5" s="38">
+        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>9755974</v>
       </c>
     </row>
@@ -4831,18 +4836,23 @@
         <v>323</v>
       </c>
       <c r="B9" s="31">
+        <f>SUM(B5:B8)</f>
         <v>1061756</v>
       </c>
       <c r="C9" s="31">
+        <f>SUM(C5:C8)</f>
         <v>2448184</v>
       </c>
       <c r="D9" s="31">
+        <f>SUM(D5:D8)</f>
         <v>4450414</v>
       </c>
       <c r="E9" s="31">
+        <f>SUM(E5:E8)</f>
         <v>7010759</v>
       </c>
       <c r="F9" s="31">
+        <f>SUM(F5:F8)</f>
         <v>9952974</v>
       </c>
     </row>
@@ -4881,18 +4891,23 @@
         <v>326</v>
       </c>
       <c r="B13" s="26">
+        <f>'Debt Schedule'!B13</f>
         <v>231645</v>
       </c>
       <c r="C13" s="26">
+        <f>'Debt Schedule'!C13</f>
         <v>212061</v>
       </c>
       <c r="D13" s="26">
+        <f>'Debt Schedule'!D13</f>
         <v>191165</v>
       </c>
       <c r="E13" s="26">
+        <f>'Debt Schedule'!E13</f>
         <v>168870</v>
       </c>
       <c r="F13" s="26">
+        <f>'Debt Schedule'!F13</f>
         <v>145082</v>
       </c>
     </row>
@@ -4901,18 +4916,23 @@
         <v>327</v>
       </c>
       <c r="B14" s="31">
+        <f>SUM(B12:B13)</f>
         <v>239645</v>
       </c>
       <c r="C14" s="31">
+        <f>SUM(C12:C13)</f>
         <v>220061</v>
       </c>
       <c r="D14" s="31">
+        <f>SUM(D12:D13)</f>
         <v>199165</v>
       </c>
       <c r="E14" s="31">
+        <f>SUM(E12:E13)</f>
         <v>176870</v>
       </c>
       <c r="F14" s="31">
+        <f>SUM(F12:F13)</f>
         <v>153082</v>
       </c>
     </row>
@@ -4931,18 +4951,23 @@
         <v>329</v>
       </c>
       <c r="B17" s="27">
+        <f>B9-B14</f>
         <v>822111</v>
       </c>
       <c r="C17" s="27">
+        <f>C9-C14</f>
         <v>2228123</v>
       </c>
       <c r="D17" s="27">
+        <f>D9-D14</f>
         <v>4251248</v>
       </c>
       <c r="E17" s="27">
+        <f>E9-E14</f>
         <v>6833888</v>
       </c>
       <c r="F17" s="27">
+        <f>F9-F14</f>
         <v>9799892</v>
       </c>
     </row>
@@ -4950,19 +4975,24 @@
       <c r="A19" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B19" s="39">
+      <c r="B19" s="39" t="str">
+        <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="39">
+      <c r="C19" s="39" t="str">
+        <f>C9-C14-C17</f>
         <v>0</v>
       </c>
       <c r="D19" s="40">
+        <f>D9-D14-D17</f>
         <v>1</v>
       </c>
       <c r="E19" s="40">
+        <f>E9-E14-E17</f>
         <v>1</v>
       </c>
-      <c r="F19" s="39">
+      <c r="F19" s="39" t="str">
+        <f>F9-F14-F17</f>
         <v>0</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -25,13 +25,14 @@
     <sheet sheetId="19" name="Sources &amp; Uses" state="visible" r:id="rId22"/>
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
+    <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="415">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -72,7 +73,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 18, 2026</t>
+    <t>March 26, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -216,6 +217,12 @@
     <t>Underwriting Snapshot</t>
   </si>
   <si>
+    <t>22.</t>
+  </si>
+  <si>
+    <t>Financial Health</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -225,7 +232,7 @@
     <t>Cell Color Legend</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs — change these to update your model.</t>
+    <t>Blue cells are editable inputs — change these to update your model.</t>
   </si>
   <si>
     <t>White cells contain formulas — do not edit (they recalculate automatically).</t>
@@ -255,37 +262,28 @@
     <t>Tabs 14-17: Financial statements</t>
   </si>
   <si>
-    <t>Tabs 18-21: Analysis &amp; underwriting</t>
+    <t>Tabs 18-22: Analysis, underwriting &amp; dashboard</t>
   </si>
   <si>
     <t>Debt Service Convention</t>
   </si>
   <si>
-    <t>operating expense on the 5-Year Operating Statement. This is a standard</t>
+    <t>operating expense on the Operating Statement. This is a standard</t>
   </si>
   <si>
     <t>simplification used in school financial underwriting that ensures internal</t>
   </si>
   <si>
-    <t>consistency across all tabs: the Cash Flow, Balance Sheet, and DSCR</t>
-  </si>
-  <si>
-    <t>schedules all reference the same debt service figures. The Debt Schedule</t>
-  </si>
-  <si>
-    <t>tab breaks out interest and principal separately for detailed analysis.</t>
+    <t>consistency across all tabs.</t>
   </si>
   <si>
     <t>Tips</t>
   </si>
   <si>
-    <t>Review the Budget Summary for a high-level view.</t>
-  </si>
-  <si>
-    <t>Check DSCR &amp; Covenants for lender readiness.</t>
-  </si>
-  <si>
-    <t>The Underwriting Snapshot provides a one-page summary.</t>
+    <t>Check the Financial Health dashboard for an at-a-glance assessment.</t>
+  </si>
+  <si>
+    <t>Review key metrics: net margin, cash runway, and DSCR.</t>
   </si>
   <si>
     <t>Disclaimer</t>
@@ -300,7 +298,7 @@
     <t>Heritage Academy - Assumptions</t>
   </si>
   <si>
-    <t>Yellow cells are editable inputs. All other cells are formulas.</t>
+    <t>Blue cells are editable inputs. All other cells are formulas.</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1165,6 +1163,120 @@
   </si>
   <si>
     <t>Prepared by SchoolStack Budget - budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Heritage Academy — Financial Health Dashboard</t>
+  </si>
+  <si>
+    <t>Generated March 26, 2026</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Year 1</t>
+  </si>
+  <si>
+    <t>Year 2</t>
+  </si>
+  <si>
+    <t>Year 3</t>
+  </si>
+  <si>
+    <t>Year 4</t>
+  </si>
+  <si>
+    <t>Year 5</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>FINANCIAL HEALTH SIGNALS</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Assessment</t>
+  </si>
+  <si>
+    <t>Watch Item</t>
+  </si>
+  <si>
+    <t>Viability</t>
+  </si>
+  <si>
+    <t>● Healthy</t>
+  </si>
+  <si>
+    <t>The model reaches net income early and sustains strong margins through Year 5.</t>
+  </si>
+  <si>
+    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+  </si>
+  <si>
+    <t>Liquidity</t>
+  </si>
+  <si>
+    <t>Cash stays positive throughout the projection and reserves exceed 3 months of expenses.</t>
+  </si>
+  <si>
+    <t>Maintain reserves as a buffer against seasonal revenue dips.</t>
+  </si>
+  <si>
+    <t>Staffing Burden</t>
+  </si>
+  <si>
+    <t>Staffing at 22% of revenue leaves room for facilities, programs, and reserves.</t>
+  </si>
+  <si>
+    <t>As you add staff, ensure staffing stays below 60% of revenue.</t>
+  </si>
+  <si>
+    <t>Facility Burden</t>
+  </si>
+  <si>
+    <t>Facility costs at 3% of revenue are well-managed and leave budget for programs.</t>
+  </si>
+  <si>
+    <t>Watch for rent escalation clauses that could push this higher over time.</t>
+  </si>
+  <si>
+    <t>Debt Affordability</t>
+  </si>
+  <si>
+    <t>DSCR of 87.52x provides comfortable coverage of debt payments with room to spare.</t>
+  </si>
+  <si>
+    <t>Maintain this ratio as you take on any additional debt.</t>
+  </si>
+  <si>
+    <t>Revenue Concentration</t>
+  </si>
+  <si>
+    <t>Revenue is anchored to enrollment-driven income — the strongest foundation for a school model. A focused revenue stream is a strength when backed by dependable demand.</t>
+  </si>
+  <si>
+    <t>Continue to pressure-test enrollment assumptions: recruitment pipeline, waitlist depth, retention rates, and collection reliability.</t>
+  </si>
+  <si>
+    <t>Reserve Strength</t>
+  </si>
+  <si>
+    <t>82.8 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+  </si>
+  <si>
+    <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
+  </si>
+  <si>
+    <t>Summary</t>
+  </si>
+  <si>
+    <t>7 Healthy  |  0 Watch  |  0 Needs Attention</t>
+  </si>
+  <si>
+    <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
   </si>
 </sst>
 </file>
@@ -1178,7 +1290,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1244,6 +1356,11 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF1E3A5F"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="11"/>
@@ -1267,6 +1384,24 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1282,7 +1417,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFDE8"/>
+        <fgColor rgb="FFDBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -1338,7 +1473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1359,15 +1494,15 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="4" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="11" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1386,19 +1521,47 @@
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1743,7 +1906,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C42"/>
+  <dimension ref="B3:C43"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2001,18 +2164,26 @@
         <v>60</v>
       </c>
     </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B42" s="8" t="s">
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="C42" s="8"/>
+      <c r="C40" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C43" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B42:C42"/>
+    <mergeCell ref="B43:C43"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Cover'!A1"/>
@@ -2036,6 +2207,7 @@
     <hyperlink ref="C37" r:id="rId19" location="#'Sources &amp; Uses'!A1"/>
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
+    <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -2059,7 +2231,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2069,27 +2241,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B4" s="21">
         <v>100</v>
@@ -2109,7 +2281,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -2119,7 +2291,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B7" s="26">
         <v>1050000</v>
@@ -2139,7 +2311,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B8" s="26">
         <v>35000</v>
@@ -2159,7 +2331,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B9" s="26">
         <v>105000</v>
@@ -2179,7 +2351,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B10" s="26">
         <v>870000</v>
@@ -2199,7 +2371,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B11" s="26">
         <v>50000</v>
@@ -2219,7 +2391,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B12" s="26">
         <v>25000</v>
@@ -2239,7 +2411,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B13" s="26">
         <v>50000</v>
@@ -2259,7 +2431,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B14" s="27">
         <f>SUM(B7:B13)</f>
@@ -2284,7 +2456,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B16" s="26">
         <v>19750</v>
@@ -2328,7 +2500,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2338,27 +2510,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2368,7 +2540,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B5" s="26">
         <v>382032</v>
@@ -2388,7 +2560,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B6" s="26">
         <v>122544</v>
@@ -2408,7 +2580,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B7" s="31">
         <f>SUM(B5:B6)</f>
@@ -2433,7 +2605,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -2443,7 +2615,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B9" s="26">
         <v>126018</v>
@@ -2463,7 +2635,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B10" s="26">
         <v>99488</v>
@@ -2483,7 +2655,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
@@ -2508,7 +2680,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -2518,7 +2690,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B13" s="26">
         <v>68978</v>
@@ -2538,7 +2710,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
@@ -2563,7 +2735,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -2573,7 +2745,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B16" s="26">
         <v>55713</v>
@@ -2593,7 +2765,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B17" s="31">
         <f>SUM(B16:B16)</f>
@@ -2618,7 +2790,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="B19" s="27">
         <f>B7+B11+B14+B17</f>
@@ -2667,7 +2839,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -2677,27 +2849,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -2707,7 +2879,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B5" s="26">
         <v>1050000</v>
@@ -2727,7 +2899,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B6" s="26">
         <v>35000</v>
@@ -2747,7 +2919,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="B7" s="26">
         <v>105000</v>
@@ -2767,7 +2939,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B8" s="26">
         <v>870000</v>
@@ -2787,7 +2959,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="B9" s="26">
         <v>50000</v>
@@ -2807,7 +2979,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B10" s="26">
         <v>25000</v>
@@ -2827,7 +2999,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B11" s="26">
         <v>50000</v>
@@ -2847,7 +3019,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B12" s="31">
         <f>SUM(B5:B11)</f>
@@ -2872,7 +3044,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B14" s="13"/>
       <c r="C14" s="13"/>
@@ -2882,7 +3054,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="B15" s="26">
         <v>126018</v>
@@ -2902,7 +3074,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="B16" s="26">
         <v>99488</v>
@@ -2922,7 +3094,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="B17" s="26">
         <v>382032</v>
@@ -2942,7 +3114,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B18" s="26">
         <v>122544</v>
@@ -2962,7 +3134,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B19" s="26">
         <v>55713</v>
@@ -2982,7 +3154,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B20" s="26">
         <v>68978</v>
@@ -3002,7 +3174,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B21" s="31">
         <f>SUM(B15:B20)</f>
@@ -3027,7 +3199,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -3037,12 +3209,12 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="32" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B25" s="26">
         <v>60000</v>
@@ -3062,12 +3234,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="32" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="B27" s="26">
         <v>40000</v>
@@ -3087,12 +3259,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="32" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="B29" s="26">
         <v>102000</v>
@@ -3112,7 +3284,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B30" s="26">
         <v>14400</v>
@@ -3132,7 +3304,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B31" s="26">
         <v>12000</v>
@@ -3152,7 +3324,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B32" s="26">
         <v>8000</v>
@@ -3172,7 +3344,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B33" s="31">
         <f>SUM(B29:B32)</f>
@@ -3197,12 +3369,12 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="32" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="B35" s="26">
         <v>15000</v>
@@ -3222,7 +3394,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="B36" s="26">
         <v>8000</v>
@@ -3242,7 +3414,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="B37" s="26">
         <v>12000</v>
@@ -3262,7 +3434,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B38" s="31">
         <f>SUM(B35:B37)</f>
@@ -3287,7 +3459,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B39" s="31">
         <f>B25+B27+B33+B38</f>
@@ -3312,7 +3484,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B41" s="13"/>
       <c r="C41" s="13"/>
@@ -3322,7 +3494,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B42" s="26">
         <v>34064</v>
@@ -3342,7 +3514,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="B43" s="26">
         <v>25000</v>
@@ -3362,7 +3534,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
@@ -3411,7 +3583,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3421,27 +3593,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4" s="29">
         <f>'Budget Detail'!B12</f>
@@ -3466,7 +3638,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B5" s="29">
         <f>'Budget Detail'!B21</f>
@@ -3491,7 +3663,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="B6" s="29">
         <f>'Budget Detail'!B39</f>
@@ -3516,7 +3688,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B7" s="29">
         <f>'Budget Detail'!B44</f>
@@ -3541,7 +3713,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
@@ -3566,7 +3738,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -3576,7 +3748,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B11" s="27">
         <f>B4-B8</f>
@@ -3601,7 +3773,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B12" s="25">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -3626,7 +3798,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="B13" s="26">
         <v>789764</v>
@@ -3646,7 +3818,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B14" s="26">
         <v>19750</v>
@@ -3666,7 +3838,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B15" s="26">
         <v>11852</v>
@@ -3711,7 +3883,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -3729,51 +3901,51 @@
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B2" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="C2" s="15" t="s">
         <v>281</v>
       </c>
-      <c r="C2" s="15" t="s">
+      <c r="D2" s="15" t="s">
         <v>282</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="E2" s="15" t="s">
         <v>283</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="F2" s="15" t="s">
         <v>284</v>
       </c>
-      <c r="F2" s="15" t="s">
+      <c r="G2" s="15" t="s">
         <v>285</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="H2" s="15" t="s">
         <v>286</v>
       </c>
-      <c r="H2" s="15" t="s">
+      <c r="I2" s="15" t="s">
         <v>287</v>
       </c>
-      <c r="I2" s="15" t="s">
+      <c r="J2" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="J2" s="15" t="s">
+      <c r="K2" s="15" t="s">
         <v>289</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="L2" s="15" t="s">
         <v>290</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="M2" s="15" t="s">
         <v>291</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="N2" s="15" t="s">
         <v>292</v>
-      </c>
-      <c r="N2" s="15" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -3791,7 +3963,7 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B4" s="31">
         <v>85833</v>
@@ -3836,7 +4008,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B6" s="13"/>
       <c r="C6" s="13"/>
@@ -3854,7 +4026,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B7" s="26">
         <v>71231</v>
@@ -3899,7 +4071,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B8" s="26">
         <v>22617</v>
@@ -3944,7 +4116,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B9" s="26">
         <v>4922</v>
@@ -3989,7 +4161,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4007,7 +4179,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B12" s="29">
         <f>B7+B8+B9</f>
@@ -4064,7 +4236,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B13" s="29">
         <f>B4-B12</f>
@@ -4121,7 +4293,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B14" s="33">
         <f>B17+B13</f>
@@ -4178,14 +4350,14 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B17" s="17">
         <v>75000</v>
@@ -4193,7 +4365,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B18" s="33">
         <f>M14</f>
@@ -4202,7 +4374,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B19" s="26">
         <f>MIN(B14:M14)</f>
@@ -4235,7 +4407,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4245,27 +4417,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4275,7 +4447,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="34" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="B5" s="31">
         <v>1975000</v>
@@ -4295,7 +4467,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -4305,7 +4477,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B8" s="29">
         <v>854772</v>
@@ -4325,7 +4497,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B9" s="29">
         <v>271400</v>
@@ -4345,7 +4517,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B10" s="29">
         <v>59064</v>
@@ -4365,7 +4537,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="34" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
@@ -4390,7 +4562,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -4400,7 +4572,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="34" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B14" s="27">
         <f>B5-B11</f>
@@ -4425,7 +4597,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B15" s="25">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4484,27 +4656,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4514,24 +4686,24 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="35" t="s">
+        <v>307</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>155</v>
+      </c>
+      <c r="C5" s="37" t="s">
         <v>308</v>
       </c>
-      <c r="B5" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="C5" s="37" t="s">
+      <c r="D5" s="35" t="s">
         <v>309</v>
       </c>
-      <c r="D5" s="35" t="s">
-        <v>310</v>
-      </c>
       <c r="E5" s="36" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="14" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B6" s="17">
         <v>250000</v>
@@ -4549,7 +4721,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B8" s="13"/>
       <c r="C8" s="13"/>
@@ -4559,7 +4731,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B9" s="26">
         <f>B6</f>
@@ -4584,7 +4756,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B10" s="26">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -4609,7 +4781,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B11" s="26">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -4634,7 +4806,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B12" s="29">
         <f>B10+B11</f>
@@ -4659,7 +4831,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B13" s="33">
         <f>MAX(0,B9-B11)</f>
@@ -4708,7 +4880,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -4718,27 +4890,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -4748,7 +4920,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B5" s="38">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -4773,7 +4945,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B6" s="26">
         <v>12000</v>
@@ -4793,7 +4965,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B7" s="26">
         <v>180000</v>
@@ -4813,7 +4985,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B8" s="26">
         <v>5000</v>
@@ -4833,7 +5005,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
@@ -4858,7 +5030,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -4868,7 +5040,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B12" s="26">
         <v>8000</v>
@@ -4888,7 +5060,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B13" s="26">
         <f>'Debt Schedule'!B13</f>
@@ -4913,7 +5085,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B14" s="31">
         <f>SUM(B12:B13)</f>
@@ -4938,7 +5110,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -4948,7 +5120,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B17" s="27">
         <f>B9-B14</f>
@@ -4973,7 +5145,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B19" s="39" t="str">
         <f>B9-B14-B17</f>
@@ -5022,7 +5194,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5032,27 +5204,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -5062,7 +5234,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B5" s="26">
         <v>1975000</v>
@@ -5082,7 +5254,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B6" s="26">
         <v>854772</v>
@@ -5102,7 +5274,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B7" s="26">
         <v>271400</v>
@@ -5122,7 +5294,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B8" s="29">
         <f>B5-B6-B7</f>
@@ -5147,7 +5319,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B9" s="26">
         <v>34064</v>
@@ -5167,7 +5339,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B10" s="41">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5192,7 +5364,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="B12" s="13"/>
       <c r="C12" s="13"/>
@@ -5202,7 +5374,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="B13" s="26">
         <v>864756</v>
@@ -5222,7 +5394,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="B14" s="23">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5247,7 +5419,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="B15" s="30">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5272,7 +5444,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B16" s="25">
         <v>0.5</v>
@@ -5292,7 +5464,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="B18" s="13"/>
       <c r="C18" s="13"/>
@@ -5302,7 +5474,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B19" s="26">
         <v>19750</v>
@@ -5322,7 +5494,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="B20" s="26">
         <v>888836</v>
@@ -5342,7 +5514,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B21" s="26">
         <v>2714</v>
@@ -5362,7 +5534,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B22" s="42">
         <v>53</v>
@@ -5382,7 +5554,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="13" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="B24" s="13"/>
       <c r="C24" s="13"/>
@@ -5392,102 +5564,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="B25" s="43" t="s">
         <v>345</v>
       </c>
-      <c r="B25" s="43" t="s">
-        <v>346</v>
-      </c>
       <c r="C25" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D25" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E25" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F25" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B26" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C26" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D26" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E26" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F26" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="B27" s="44" t="s">
         <v>348</v>
       </c>
-      <c r="B27" s="44" t="s">
-        <v>349</v>
-      </c>
       <c r="C27" s="44" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D27" s="44" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="E27" s="44" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F27" s="44" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B28" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C28" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D28" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E28" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F28" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="B29" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C29" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D29" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="E29" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="F29" s="43" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
   </sheetData>
@@ -5528,27 +5700,27 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="45" t="s">
+        <v>351</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>105</v>
+      </c>
+      <c r="D3" s="45" t="s">
         <v>352</v>
       </c>
-      <c r="B3" s="45" t="s">
-        <v>106</v>
-      </c>
-      <c r="D3" s="45" t="s">
-        <v>353</v>
-      </c>
       <c r="E3" s="45" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B4" s="26">
         <v>250000</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E4" s="26">
         <v>200000</v>
@@ -5556,13 +5728,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B5" s="26">
         <v>50000</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="E5" s="26">
         <v>50000</v>
@@ -5570,13 +5742,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B6" s="26">
         <v>75000</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E6" s="26">
         <v>75000</v>
@@ -5584,7 +5756,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E7" s="26">
         <v>50000</v>
@@ -5592,13 +5764,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B9" s="27">
         <v>375000</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E9" s="27">
         <v>375000</v>
@@ -5606,7 +5778,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B10" s="39">
         <v>0</v>
@@ -5629,7 +5801,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B32"/>
+  <dimension ref="B2:B29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -5638,152 +5810,137 @@
   <sheetData>
     <row r="2" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B4" s="10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="9" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B9" s="10" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="10" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="11" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B14" s="6" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B15" s="6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B16" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
     </row>
     <row r="19" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B23" s="6" t="s">
-        <v>80</v>
+      <c r="B23" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="24" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
     </row>
     <row r="25" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
-        <v>81</v>
+      <c r="B25" s="6" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="26" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B26" s="6" t="s">
-        <v>82</v>
+        <v>69</v>
       </c>
     </row>
     <row r="27" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B27" s="6" t="s">
-        <v>83</v>
+      <c r="B27" s="10" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="28" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B28" s="6" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B29" s="6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B30" s="10" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B31" s="6" t="s">
         <v>86</v>
-      </c>
-    </row>
-    <row r="32" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B32" s="6" t="s">
-        <v>87</v>
       </c>
     </row>
   </sheetData>
@@ -5809,7 +5966,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -5819,7 +5976,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B3" s="13"/>
       <c r="C3" s="13"/>
@@ -5829,32 +5986,32 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B5" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C5" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="D5" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="E5" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="F5" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F5" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B6" s="26">
         <v>1975000</v>
@@ -5874,7 +6031,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B7" s="26">
         <v>1160236</v>
@@ -5894,7 +6051,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B8" s="27">
         <v>814764</v>
@@ -5914,7 +6071,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B9" s="25">
         <v>0.4125385351058188</v>
@@ -5934,7 +6091,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B10" s="46">
         <v>24.92</v>
@@ -5954,7 +6111,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B11" s="23">
         <v>53</v>
@@ -5974,7 +6131,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -5984,32 +6141,32 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B15" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C15" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F15" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B16" s="26">
         <v>1678750</v>
@@ -6029,7 +6186,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B17" s="26">
         <v>1160236</v>
@@ -6049,7 +6206,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B18" s="27">
         <v>518514</v>
@@ -6069,7 +6226,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B19" s="25">
         <v>0.308868864830375</v>
@@ -6089,7 +6246,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B20" s="46">
         <v>16.22</v>
@@ -6109,7 +6266,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B21" s="23">
         <v>54</v>
@@ -6129,7 +6286,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -6139,32 +6296,32 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="12" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C25" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="D25" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="E25" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="F25" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="B26" s="26">
         <v>1975000</v>
@@ -6184,7 +6341,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B27" s="26">
         <v>1173736</v>
@@ -6204,7 +6361,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B28" s="27">
         <v>801264</v>
@@ -6224,7 +6381,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B29" s="25">
         <v>0.4057030920678441</v>
@@ -6244,7 +6401,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="B30" s="46">
         <v>24.52</v>
@@ -6264,7 +6421,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="B31" s="23">
         <v>53</v>
@@ -6310,7 +6467,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6322,7 +6479,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B3" s="13"/>
     </row>
@@ -6336,7 +6493,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>5</v>
@@ -6344,7 +6501,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>7</v>
@@ -6368,7 +6525,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>17</v>
@@ -6376,7 +6533,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -6388,33 +6545,33 @@
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D12" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="F12" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="F12" s="47" t="s">
+      <c r="G12" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="H12" s="47" t="s">
         <v>99</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D13" s="26">
         <v>1975000</v>
@@ -6434,7 +6591,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D14" s="26">
         <v>1160236</v>
@@ -6454,7 +6611,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D15" s="26">
         <v>789764</v>
@@ -6474,7 +6631,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D16" s="26">
         <v>864756</v>
@@ -6494,7 +6651,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D17" s="26">
         <v>231645</v>
@@ -6514,7 +6671,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6526,33 +6683,33 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D20" s="47" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="47" t="s">
         <v>96</v>
       </c>
-      <c r="E20" s="47" t="s">
+      <c r="F20" s="47" t="s">
         <v>97</v>
       </c>
-      <c r="F20" s="47" t="s">
+      <c r="G20" s="47" t="s">
         <v>98</v>
       </c>
-      <c r="G20" s="47" t="s">
+      <c r="H20" s="47" t="s">
         <v>99</v>
-      </c>
-      <c r="H20" s="47" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D21" s="25">
         <v>0.3998803072577175</v>
@@ -6572,7 +6729,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D22" s="46">
         <v>24.92</v>
@@ -6592,7 +6749,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D23" s="25">
         <v>0.5</v>
@@ -6612,7 +6769,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D24" s="23">
         <v>100</v>
@@ -6632,7 +6789,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B26" s="8"/>
       <c r="C26" s="8"/>
@@ -6646,6 +6803,399 @@
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A26:H26"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B2:G26"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="40" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>377</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="48" t="s">
+        <v>378</v>
+      </c>
+      <c r="C3" s="48"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="48"/>
+    </row>
+    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="13" t="s">
+        <v>379</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>380</v>
+      </c>
+      <c r="D5" s="49" t="s">
+        <v>381</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>382</v>
+      </c>
+      <c r="F5" s="49" t="s">
+        <v>383</v>
+      </c>
+      <c r="G5" s="49" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="C6" s="50">
+        <v>100</v>
+      </c>
+      <c r="D6" s="50">
+        <v>130</v>
+      </c>
+      <c r="E6" s="50">
+        <v>160</v>
+      </c>
+      <c r="F6" s="50">
+        <v>185</v>
+      </c>
+      <c r="G6" s="50">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="C7" s="51">
+        <v>1975000</v>
+      </c>
+      <c r="D7" s="51">
+        <v>2621350</v>
+      </c>
+      <c r="E7" s="51">
+        <v>3304703.5</v>
+      </c>
+      <c r="F7" s="51">
+        <v>3922889.9299999997</v>
+      </c>
+      <c r="G7" s="51">
+        <v>4361346.638750001</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
+        <v>294</v>
+      </c>
+      <c r="C8" s="51">
+        <v>854772</v>
+      </c>
+      <c r="D8" s="51">
+        <v>880415.16</v>
+      </c>
+      <c r="E8" s="51">
+        <v>906827.6148</v>
+      </c>
+      <c r="F8" s="51">
+        <v>934032.443244</v>
+      </c>
+      <c r="G8" s="51">
+        <v>962053.4165413202</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>295</v>
+      </c>
+      <c r="C9" s="51">
+        <v>271400</v>
+      </c>
+      <c r="D9" s="51">
+        <v>310442</v>
+      </c>
+      <c r="E9" s="51">
+        <v>351582.25999999995</v>
+      </c>
+      <c r="F9" s="51">
+        <v>389447.9028</v>
+      </c>
+      <c r="G9" s="51">
+        <v>418013.9720340001</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="C10" s="51">
+        <v>34064.39316600799</v>
+      </c>
+      <c r="D10" s="51">
+        <v>34064.39316600799</v>
+      </c>
+      <c r="E10" s="51">
+        <v>34064.39316600799</v>
+      </c>
+      <c r="F10" s="51">
+        <v>34064.39316600799</v>
+      </c>
+      <c r="G10" s="51">
+        <v>34064.39316600799</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C11" s="52">
+        <v>789763.6068339921</v>
+      </c>
+      <c r="D11" s="52">
+        <v>1386428.446833992</v>
+      </c>
+      <c r="E11" s="52">
+        <v>2002229.2320339922</v>
+      </c>
+      <c r="F11" s="52">
+        <v>2560345.190789992</v>
+      </c>
+      <c r="G11" s="52">
+        <v>2942214.857008673</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="C12" s="52">
+        <v>864756</v>
+      </c>
+      <c r="D12" s="52">
+        <v>2251184.446833992</v>
+      </c>
+      <c r="E12" s="52">
+        <v>4253413.678867985</v>
+      </c>
+      <c r="F12" s="52">
+        <v>6813758.869657977</v>
+      </c>
+      <c r="G12" s="52">
+        <v>9755973.72666665</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="C13" s="53">
+        <v>0.3998803072577175</v>
+      </c>
+      <c r="D13" s="53">
+        <v>0.5288986388059557</v>
+      </c>
+      <c r="E13" s="53">
+        <v>0.6058725788967125</v>
+      </c>
+      <c r="F13" s="53">
+        <v>0.6526681187789514</v>
+      </c>
+      <c r="G13" s="53">
+        <v>0.6746115593902751</v>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="13" t="s">
+        <v>386</v>
+      </c>
+      <c r="C15" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>388</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="G15" s="13"/>
+    </row>
+    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="35" t="s">
+        <v>390</v>
+      </c>
+      <c r="C16" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="D16" s="55" t="s">
+        <v>392</v>
+      </c>
+      <c r="E16" s="55"/>
+      <c r="F16" s="56" t="s">
+        <v>393</v>
+      </c>
+      <c r="G16" s="56"/>
+    </row>
+    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="35" t="s">
+        <v>394</v>
+      </c>
+      <c r="C17" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="D17" s="55" t="s">
+        <v>395</v>
+      </c>
+      <c r="E17" s="55"/>
+      <c r="F17" s="56" t="s">
+        <v>396</v>
+      </c>
+      <c r="G17" s="56"/>
+    </row>
+    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="35" t="s">
+        <v>397</v>
+      </c>
+      <c r="C18" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="D18" s="55" t="s">
+        <v>398</v>
+      </c>
+      <c r="E18" s="55"/>
+      <c r="F18" s="56" t="s">
+        <v>399</v>
+      </c>
+      <c r="G18" s="56"/>
+    </row>
+    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="35" t="s">
+        <v>400</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="D19" s="55" t="s">
+        <v>401</v>
+      </c>
+      <c r="E19" s="55"/>
+      <c r="F19" s="56" t="s">
+        <v>402</v>
+      </c>
+      <c r="G19" s="56"/>
+    </row>
+    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="35" t="s">
+        <v>403</v>
+      </c>
+      <c r="C20" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="D20" s="55" t="s">
+        <v>404</v>
+      </c>
+      <c r="E20" s="55"/>
+      <c r="F20" s="56" t="s">
+        <v>405</v>
+      </c>
+      <c r="G20" s="56"/>
+    </row>
+    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B21" s="35" t="s">
+        <v>406</v>
+      </c>
+      <c r="C21" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="D21" s="55" t="s">
+        <v>407</v>
+      </c>
+      <c r="E21" s="55"/>
+      <c r="F21" s="56" t="s">
+        <v>408</v>
+      </c>
+      <c r="G21" s="56"/>
+    </row>
+    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="35" t="s">
+        <v>409</v>
+      </c>
+      <c r="C22" s="54" t="s">
+        <v>391</v>
+      </c>
+      <c r="D22" s="55" t="s">
+        <v>410</v>
+      </c>
+      <c r="E22" s="55"/>
+      <c r="F22" s="56" t="s">
+        <v>411</v>
+      </c>
+      <c r="G22" s="56"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24" s="35" t="s">
+        <v>412</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="57" t="s">
+        <v>414</v>
+      </c>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+    </row>
+  </sheetData>
+  <mergeCells count="20">
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F16:G16"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="D21:E21"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="B26:G26"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6670,7 +7220,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -6681,12 +7231,12 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="12" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -6729,10 +7279,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>91</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -6753,7 +7303,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B12" s="14">
         <v>7</v>
@@ -6761,7 +7311,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="14">
         <v>200</v>
@@ -6769,7 +7319,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -6780,27 +7330,27 @@
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B16" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F16" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B17" s="16">
         <v>100</v>
@@ -6820,7 +7370,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -6831,30 +7381,30 @@
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B20" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B20" s="15" t="s">
+      <c r="C20" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="D20" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="E20" s="15" t="s">
         <v>106</v>
-      </c>
-      <c r="E20" s="15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C21" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D21" s="17">
         <v>10500</v>
@@ -6865,13 +7415,13 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B22" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>109</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>110</v>
       </c>
       <c r="D22" s="17">
         <v>350</v>
@@ -6882,13 +7432,13 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="C23" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D23" s="17">
         <v>-1050</v>
@@ -6899,13 +7449,13 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="C24" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D24" s="17">
         <v>8700</v>
@@ -6916,13 +7466,13 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="D25" s="17">
         <v>50000</v>
@@ -6933,13 +7483,13 @@
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="C26" s="4" t="s">
         <v>117</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>118</v>
       </c>
       <c r="D26" s="17">
         <v>25000</v>
@@ -6950,13 +7500,13 @@
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B27" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="C27" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D27" s="17">
         <v>500</v>
@@ -6967,7 +7517,7 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B29" s="13"/>
       <c r="C29" s="13"/>
@@ -6978,36 +7528,36 @@
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C30" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="B30" s="15" t="s">
-        <v>104</v>
-      </c>
-      <c r="C30" s="15" t="s">
+      <c r="D30" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="E30" s="15" t="s">
         <v>125</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="F30" s="15" t="s">
         <v>126</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="G30" s="15" t="s">
         <v>127</v>
-      </c>
-      <c r="G30" s="15" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B31" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="C31" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="D31" s="19">
         <v>1</v>
@@ -7024,13 +7574,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>131</v>
       </c>
       <c r="D32" s="19">
         <v>1</v>
@@ -7047,13 +7597,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B33" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="B33" s="4" t="s">
-        <v>134</v>
-      </c>
       <c r="C33" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D33" s="19">
         <v>6</v>
@@ -7070,13 +7620,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D34" s="19">
         <v>3</v>
@@ -7093,13 +7643,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="C35" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D35" s="19">
         <v>1</v>
@@ -7116,13 +7666,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B36" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B36" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="C36" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D36" s="19">
         <v>1</v>
@@ -7139,7 +7689,7 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B38" s="13"/>
       <c r="C38" s="13"/>
@@ -7150,30 +7700,30 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B39" s="15" t="s">
         <v>103</v>
       </c>
-      <c r="B39" s="15" t="s">
+      <c r="C39" s="15" t="s">
         <v>104</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="D39" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="E39" s="15" t="s">
         <v>106</v>
-      </c>
-      <c r="E39" s="15" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="B40" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="C40" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="D40" s="17">
         <v>8500</v>
@@ -7184,13 +7734,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>142</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>143</v>
       </c>
       <c r="D41" s="17">
         <v>1200</v>
@@ -7201,13 +7751,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="4" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D42" s="17">
         <v>12000</v>
@@ -7218,13 +7768,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D43" s="17">
         <v>8000</v>
@@ -7235,13 +7785,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="B44" s="4" t="s">
-        <v>148</v>
-      </c>
       <c r="C44" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D44" s="17">
         <v>600</v>
@@ -7252,13 +7802,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D45" s="17">
         <v>400</v>
@@ -7269,13 +7819,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="B46" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B46" s="4" t="s">
-        <v>151</v>
-      </c>
       <c r="C46" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D46" s="17">
         <v>15000</v>
@@ -7286,13 +7836,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D47" s="17">
         <v>8000</v>
@@ -7303,13 +7853,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="4" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D48" s="17">
         <v>12000</v>
@@ -7320,7 +7870,7 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B50" s="13"/>
       <c r="C50" s="13"/>
@@ -7331,27 +7881,27 @@
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C51" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B51" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C51" s="15" t="s">
+      <c r="D51" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E51" s="15" t="s">
         <v>156</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E51" s="15" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B52" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="C52" s="17">
         <v>250000</v>
@@ -7365,10 +7915,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B53" s="4" t="s">
         <v>160</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>161</v>
       </c>
       <c r="C53" s="17">
         <v>25000</v>
@@ -7382,7 +7932,7 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -7393,29 +7943,29 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="4" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B56" s="18">
         <v>0.03</v>
       </c>
       <c r="C56" s="20" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B57" s="18">
         <v>0.03</v>
       </c>
       <c r="C57" s="20" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B58" s="19">
         <v>1</v>
@@ -7423,7 +7973,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B59" s="17">
         <v>75000</v>
@@ -7431,10 +7981,10 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="B60" s="14" t="s">
         <v>169</v>
-      </c>
-      <c r="B60" s="14" t="s">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
@@ -7469,10 +8019,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>171</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -7493,10 +8043,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>173</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>174</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -7509,7 +8059,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>17</v>
@@ -7517,66 +8067,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="B10" s="4" t="s">
         <v>177</v>
-      </c>
-      <c r="B10" s="4" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B11" s="4" t="s">
         <v>179</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="4" t="s">
         <v>169</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>170</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B15" s="4" t="s">
         <v>184</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>185</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -7616,33 +8166,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>187</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>188</v>
       </c>
-      <c r="C3" s="15" t="s">
-        <v>189</v>
-      </c>
       <c r="D3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="F3" s="15" t="s">
+      <c r="G3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="H3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="H3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B5" s="13"/>
       <c r="C5" s="13"/>
@@ -7654,7 +8204,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B6" s="21">
         <v>85</v>
@@ -7680,7 +8230,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B7" s="23">
         <v>200</v>
@@ -7688,7 +8238,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D8" s="24">
         <v>0.5</v>
@@ -7708,10 +8258,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>192</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>193</v>
       </c>
       <c r="E10" s="25">
         <v>0.3</v>
@@ -7752,7 +8302,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -7762,27 +8312,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -7792,7 +8342,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B5" s="26">
         <v>1050000</v>
@@ -7812,7 +8362,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="B6" s="26">
         <v>35000</v>
@@ -7832,7 +8382,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B7" s="26">
         <v>105000</v>
@@ -7852,7 +8402,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B8" s="26">
         <v>870000</v>
@@ -7872,7 +8422,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B9" s="26">
         <v>50000</v>
@@ -7892,7 +8442,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B10" s="26">
         <v>25000</v>
@@ -7912,7 +8462,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="B11" s="26">
         <v>50000</v>
@@ -7932,7 +8482,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="B12" s="27">
         <f>SUM(B5:B11)</f>
@@ -7996,33 +8546,33 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D3" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="E3" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="F3" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>204</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>129</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>130</v>
       </c>
       <c r="C4" s="28">
         <v>1</v>
@@ -8042,10 +8592,10 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C5" s="28">
         <v>1</v>
@@ -8065,10 +8615,10 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B6" s="4" t="s">
         <v>133</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>134</v>
       </c>
       <c r="C6" s="28">
         <v>6</v>
@@ -8088,10 +8638,10 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C7" s="28">
         <v>3</v>
@@ -8111,10 +8661,10 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>136</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>137</v>
       </c>
       <c r="C8" s="28">
         <v>1</v>
@@ -8134,10 +8684,10 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="4" t="s">
         <v>138</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>139</v>
       </c>
       <c r="C9" s="28">
         <v>1</v>
@@ -8157,7 +8707,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -8168,27 +8718,27 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B12" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C12" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="D12" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="E12" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="F12" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F12" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B13" s="27">
         <v>854772</v>
@@ -8208,7 +8758,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B14" s="25">
         <v>0.4327959493670886</v>
@@ -8228,7 +8778,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="B15" s="30">
         <v>7.7</v>
@@ -8272,7 +8822,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8282,27 +8832,27 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B3" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="E3" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="F3" s="15" t="s">
         <v>99</v>
-      </c>
-      <c r="F3" s="15" t="s">
-        <v>100</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B4" s="13"/>
       <c r="C4" s="13"/>
@@ -8312,7 +8862,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B5" s="26">
         <v>60000</v>
@@ -8332,7 +8882,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
@@ -8357,7 +8907,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B7" s="13"/>
       <c r="C7" s="13"/>
@@ -8367,7 +8917,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="4" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B8" s="26">
         <v>40000</v>
@@ -8387,7 +8937,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
@@ -8412,7 +8962,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B10" s="13"/>
       <c r="C10" s="13"/>
@@ -8422,7 +8972,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B11" s="26">
         <v>102000</v>
@@ -8442,7 +8992,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B12" s="26">
         <v>14400</v>
@@ -8462,7 +9012,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B13" s="26">
         <v>12000</v>
@@ -8482,7 +9032,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="B14" s="26">
         <v>8000</v>
@@ -8502,7 +9052,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B15" s="31">
         <f>SUM(B11:B14)</f>
@@ -8527,7 +9077,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B16" s="13"/>
       <c r="C16" s="13"/>
@@ -8537,7 +9087,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B17" s="26">
         <v>15000</v>
@@ -8557,7 +9107,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="B18" s="26">
         <v>8000</v>
@@ -8577,7 +9127,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="4" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B19" s="26">
         <v>12000</v>
@@ -8597,7 +9147,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B20" s="31">
         <f>SUM(B17:B19)</f>
@@ -8622,7 +9172,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="B22" s="27">
         <f>B6+B9+B15+B20</f>
@@ -8672,7 +9222,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B1" s="11"/>
       <c r="C1" s="11"/>
@@ -8682,30 +9232,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
+        <v>154</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>155</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="D3" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>156</v>
       </c>
-      <c r="D3" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>157</v>
-      </c>
       <c r="F3" s="15" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B4" s="4" t="s">
         <v>158</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>159</v>
       </c>
       <c r="C4" s="17">
         <v>250000</v>
@@ -8722,10 +9272,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C5" s="17">
         <v>25000</v>
@@ -8742,7 +9292,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F7" s="27">
         <v>34064</v>
@@ -8750,7 +9300,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F8" s="31">
         <v>250000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="746" uniqueCount="415">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="421">
   <si>
     <t>SchoolStack Budget</t>
   </si>
@@ -1190,6 +1190,24 @@
   </si>
   <si>
     <t>Net Income</t>
+  </si>
+  <si>
+    <t>Payroll %</t>
+  </si>
+  <si>
+    <t>Facility %</t>
+  </si>
+  <si>
+    <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>Break-even Year</t>
+  </si>
+  <si>
+    <t>Cash Runway</t>
+  </si>
+  <si>
+    <t>60+ months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1473,7 +1491,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1552,6 +1570,10 @@
     <xf numFmtId="166" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="168" fontId="3" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -6817,7 +6839,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G26"/>
+  <dimension ref="B2:G33"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7026,176 +7048,302 @@
         <v>0.6746115593902751</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="13" t="s">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="C14" s="51">
+        <v>19750</v>
+      </c>
+      <c r="D14" s="51">
+        <v>20164.23076923077</v>
+      </c>
+      <c r="E14" s="51">
+        <v>20654.396875</v>
+      </c>
+      <c r="F14" s="51">
+        <v>21204.81043243243</v>
+      </c>
+      <c r="G14" s="51">
+        <v>21806.733193750006</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C15" s="13" t="s">
+      <c r="C15" s="53">
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="D15" s="53">
+        <v>0.3358632612966601</v>
+      </c>
+      <c r="E15" s="53">
+        <v>0.2744051364365971</v>
+      </c>
+      <c r="F15" s="53">
+        <v>0.23809805013927576</v>
+      </c>
+      <c r="G15" s="53">
+        <v>0.22058632258064514</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="C16" s="53">
+        <v>0.0412253164556962</v>
+      </c>
+      <c r="D16" s="53">
+        <v>0.035528487229862474</v>
+      </c>
+      <c r="E16" s="53">
+        <v>0.031916532905296946</v>
+      </c>
+      <c r="F16" s="53">
+        <v>0.029782729805013928</v>
+      </c>
+      <c r="G16" s="53">
+        <v>0.028753548387096775</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13" t="s">
+      <c r="C17" s="53">
+        <v>0.42978632911392406</v>
+      </c>
+      <c r="D17" s="53">
+        <v>0.5457084479371316</v>
+      </c>
+      <c r="E17" s="53">
+        <v>0.6192064205457464</v>
+      </c>
+      <c r="F17" s="53">
+        <v>0.6626261838440112</v>
+      </c>
+      <c r="G17" s="53">
+        <v>0.6835685161290322</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B18" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="C18" s="54">
+        <v>24.918336160088252</v>
+      </c>
+      <c r="D18" s="54">
+        <v>41.993786092965045</v>
+      </c>
+      <c r="E18" s="54">
+        <v>60.071336519270375</v>
+      </c>
+      <c r="F18" s="54">
+        <v>76.3087007388667</v>
+      </c>
+      <c r="G18" s="54">
+        <v>87.51893026967599</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="G15" s="13"/>
-    </row>
-    <row r="16" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="35" t="s">
+      <c r="C19" s="55" t="s">
+        <v>380</v>
+      </c>
+      <c r="D19" s="55"/>
+      <c r="E19" s="55"/>
+      <c r="F19" s="55"/>
+      <c r="G19" s="55"/>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="C16" s="54" t="s">
+      <c r="C20" s="55" t="s">
         <v>391</v>
       </c>
-      <c r="D16" s="55" t="s">
+      <c r="D20" s="55"/>
+      <c r="E20" s="55"/>
+      <c r="F20" s="55"/>
+      <c r="G20" s="55"/>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="13" t="s">
         <v>392</v>
       </c>
-      <c r="E16" s="55"/>
-      <c r="F16" s="56" t="s">
+      <c r="C22" s="13" t="s">
         <v>393</v>
       </c>
-      <c r="G16" s="56"/>
-    </row>
-    <row r="17" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="35" t="s">
+      <c r="D22" s="13" t="s">
         <v>394</v>
       </c>
-      <c r="C17" s="54" t="s">
-        <v>391</v>
-      </c>
-      <c r="D17" s="55" t="s">
+      <c r="E22" s="13"/>
+      <c r="F22" s="13" t="s">
         <v>395</v>
       </c>
-      <c r="E17" s="55"/>
-      <c r="F17" s="56" t="s">
+      <c r="G22" s="13"/>
+    </row>
+    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="35" t="s">
         <v>396</v>
       </c>
-      <c r="G17" s="56"/>
-    </row>
-    <row r="18" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="35" t="s">
+      <c r="C23" s="56" t="s">
         <v>397</v>
       </c>
-      <c r="C18" s="54" t="s">
-        <v>391</v>
-      </c>
-      <c r="D18" s="55" t="s">
+      <c r="D23" s="57" t="s">
         <v>398</v>
       </c>
-      <c r="E18" s="55"/>
-      <c r="F18" s="56" t="s">
+      <c r="E23" s="57"/>
+      <c r="F23" s="58" t="s">
         <v>399</v>
       </c>
-      <c r="G18" s="56"/>
-    </row>
-    <row r="19" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="35" t="s">
+      <c r="G23" s="58"/>
+    </row>
+    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B24" s="35" t="s">
         <v>400</v>
       </c>
-      <c r="C19" s="54" t="s">
-        <v>391</v>
-      </c>
-      <c r="D19" s="55" t="s">
+      <c r="C24" s="56" t="s">
+        <v>397</v>
+      </c>
+      <c r="D24" s="57" t="s">
         <v>401</v>
       </c>
-      <c r="E19" s="55"/>
-      <c r="F19" s="56" t="s">
+      <c r="E24" s="57"/>
+      <c r="F24" s="58" t="s">
         <v>402</v>
       </c>
-      <c r="G19" s="56"/>
-    </row>
-    <row r="20" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="35" t="s">
+      <c r="G24" s="58"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B25" s="35" t="s">
         <v>403</v>
       </c>
-      <c r="C20" s="54" t="s">
-        <v>391</v>
-      </c>
-      <c r="D20" s="55" t="s">
+      <c r="C25" s="56" t="s">
+        <v>397</v>
+      </c>
+      <c r="D25" s="57" t="s">
         <v>404</v>
       </c>
-      <c r="E20" s="55"/>
-      <c r="F20" s="56" t="s">
+      <c r="E25" s="57"/>
+      <c r="F25" s="58" t="s">
         <v>405</v>
       </c>
-      <c r="G20" s="56"/>
-    </row>
-    <row r="21" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="35" t="s">
+      <c r="G25" s="58"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="35" t="s">
         <v>406</v>
       </c>
-      <c r="C21" s="54" t="s">
-        <v>391</v>
-      </c>
-      <c r="D21" s="55" t="s">
+      <c r="C26" s="56" t="s">
+        <v>397</v>
+      </c>
+      <c r="D26" s="57" t="s">
         <v>407</v>
       </c>
-      <c r="E21" s="55"/>
-      <c r="F21" s="56" t="s">
+      <c r="E26" s="57"/>
+      <c r="F26" s="58" t="s">
         <v>408</v>
       </c>
-      <c r="G21" s="56"/>
-    </row>
-    <row r="22" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="35" t="s">
+      <c r="G26" s="58"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B27" s="35" t="s">
         <v>409</v>
       </c>
-      <c r="C22" s="54" t="s">
-        <v>391</v>
-      </c>
-      <c r="D22" s="55" t="s">
+      <c r="C27" s="56" t="s">
+        <v>397</v>
+      </c>
+      <c r="D27" s="57" t="s">
         <v>410</v>
       </c>
-      <c r="E22" s="55"/>
-      <c r="F22" s="56" t="s">
+      <c r="E27" s="57"/>
+      <c r="F27" s="58" t="s">
         <v>411</v>
       </c>
-      <c r="G22" s="56"/>
-    </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B24" s="35" t="s">
+      <c r="G27" s="58"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B28" s="35" t="s">
         <v>412</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C28" s="56" t="s">
+        <v>397</v>
+      </c>
+      <c r="D28" s="57" t="s">
         <v>413</v>
       </c>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-    </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="57" t="s">
+      <c r="E28" s="57"/>
+      <c r="F28" s="58" t="s">
         <v>414</v>
       </c>
-      <c r="C26" s="57"/>
-      <c r="D26" s="57"/>
-      <c r="E26" s="57"/>
-      <c r="F26" s="57"/>
-      <c r="G26" s="57"/>
+      <c r="G28" s="58"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B29" s="35" t="s">
+        <v>415</v>
+      </c>
+      <c r="C29" s="56" t="s">
+        <v>397</v>
+      </c>
+      <c r="D29" s="57" t="s">
+        <v>416</v>
+      </c>
+      <c r="E29" s="57"/>
+      <c r="F29" s="58" t="s">
+        <v>417</v>
+      </c>
+      <c r="G29" s="58"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31" s="35" t="s">
+        <v>418</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+    </row>
+    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B33" s="59" t="s">
+        <v>420</v>
+      </c>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="22">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B3:G3"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="D16:E16"/>
-    <mergeCell ref="F16:G16"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="D22:E22"/>
     <mergeCell ref="F22:G22"/>
-    <mergeCell ref="C24:E24"/>
-    <mergeCell ref="B26:G26"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:G29"/>
+    <mergeCell ref="C31:E31"/>
+    <mergeCell ref="B33:G33"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="427">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1520,7 +1520,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1543,6 +1543,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2324,22 +2325,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -2347,49 +2348,49 @@
       <c r="A4" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B4" s="25">
+      <c r="B4" s="26">
         <v>100</v>
       </c>
-      <c r="C4" s="25">
+      <c r="C4" s="26">
         <v>130</v>
       </c>
-      <c r="D4" s="25">
+      <c r="D4" s="26">
         <v>160</v>
       </c>
-      <c r="E4" s="25">
+      <c r="E4" s="26">
         <v>185</v>
       </c>
-      <c r="F4" s="25">
+      <c r="F4" s="26">
         <v>200</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>1050000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>1405950</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>1782312</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>2122622</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>2363569</v>
       </c>
     </row>
@@ -2397,19 +2398,19 @@
       <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>35000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>46865</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>59410</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>70754</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>78786</v>
       </c>
     </row>
@@ -2417,19 +2418,19 @@
       <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>105000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>140595</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>178231</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>212262</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>236357</v>
       </c>
     </row>
@@ -2437,19 +2438,19 @@
       <c r="A10" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>870000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>1164930</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>1476773</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>1758744</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>1958385</v>
       </c>
     </row>
@@ -2457,19 +2458,19 @@
       <c r="A11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>50000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>51500</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>53045</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>54636</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>56275</v>
       </c>
     </row>
@@ -2477,19 +2478,19 @@
       <c r="A12" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>25000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>25750</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>26523</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>27318</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>28138</v>
       </c>
     </row>
@@ -2497,43 +2498,43 @@
       <c r="A13" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>50000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>66950</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>84872</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>101077</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>112551</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>SUM(B7:B13)</f>
         <v>1975000</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C7:C13)</f>
         <v>2621350</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D7:D13)</f>
         <v>3304704</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E7:E13)</f>
         <v>3922890</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F7:F13)</f>
         <v>4361347</v>
       </c>
@@ -2542,19 +2543,19 @@
       <c r="A16" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>19750</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>20164</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>20654</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>21205</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>21807</v>
       </c>
     </row>
@@ -2593,52 +2594,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>382032</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>393493</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>405298</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>417457</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>429980</v>
       </c>
     </row>
@@ -2646,19 +2647,19 @@
       <c r="A6" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>122544</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>126220</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>130007</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>133907</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>137924</v>
       </c>
     </row>
@@ -2666,54 +2667,54 @@
       <c r="A7" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B7" s="35">
+      <c r="B7" s="36">
         <f>SUM(B5:B6)</f>
         <v>504576</v>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="36">
         <f>SUM(C5:C6)</f>
         <v>519713</v>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="36">
         <f>SUM(D5:D6)</f>
         <v>535305</v>
       </c>
-      <c r="E7" s="35">
+      <c r="E7" s="36">
         <f>SUM(E5:E6)</f>
         <v>551364</v>
       </c>
-      <c r="F7" s="35">
+      <c r="F7" s="36">
         <f>SUM(F5:F6)</f>
         <v>567905</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>135</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>126018</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>129798</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>133692</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>137703</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>141834</v>
       </c>
     </row>
@@ -2721,19 +2722,19 @@
       <c r="A10" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>99488</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>102472</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>105546</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>108713</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>111974</v>
       </c>
     </row>
@@ -2741,54 +2742,54 @@
       <c r="A11" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>SUM(B9:B10)</f>
         <v>225505</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <f>SUM(C9:C10)</f>
         <v>232270</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="36">
         <f>SUM(D9:D10)</f>
         <v>239238</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="36">
         <f>SUM(E9:E10)</f>
         <v>246415</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <f>SUM(F9:F10)</f>
         <v>253808</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>68978</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>71047</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>73179</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>75374</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>77635</v>
       </c>
     </row>
@@ -2796,54 +2797,54 @@
       <c r="A14" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="36">
         <f>SUM(B13:B13)</f>
         <v>68978</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>SUM(C13:C13)</f>
         <v>71047</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="36">
         <f>SUM(D13:D13)</f>
         <v>73179</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>SUM(E13:E13)</f>
         <v>75374</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="36">
         <f>SUM(F13:F13)</f>
         <v>77635</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>55713</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>57384</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>59106</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>60879</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>62705</v>
       </c>
     </row>
@@ -2851,48 +2852,48 @@
       <c r="A17" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="B17" s="35">
+      <c r="B17" s="36">
         <f>SUM(B16:B16)</f>
         <v>55713</v>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="36">
         <f>SUM(C16:C16)</f>
         <v>57384</v>
       </c>
-      <c r="D17" s="35">
+      <c r="D17" s="36">
         <f>SUM(D16:D16)</f>
         <v>59106</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="36">
         <f>SUM(E16:E16)</f>
         <v>60879</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="36">
         <f>SUM(F16:F16)</f>
         <v>62705</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>249</v>
       </c>
-      <c r="B19" s="31">
+      <c r="B19" s="32">
         <f>B7+B11+B14+B17</f>
         <v>854772</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="32">
         <f>C7+C11+C14+C17</f>
         <v>880415</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="32">
         <f>D7+D11+D14+D17</f>
         <v>906828</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="32">
         <f>E7+E11+E14+E17</f>
         <v>934032</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="32">
         <f>F7+F11+F14+F17</f>
         <v>962053</v>
       </c>
@@ -2932,52 +2933,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>252</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>1050000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>1405950</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>1782312</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>2122622</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>2363569</v>
       </c>
     </row>
@@ -2985,19 +2986,19 @@
       <c r="A6" s="11" t="s">
         <v>253</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>35000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>46865</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>59410</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>70754</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>78786</v>
       </c>
     </row>
@@ -3005,19 +3006,19 @@
       <c r="A7" s="11" t="s">
         <v>254</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>105000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>140595</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>178231</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>212262</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>236357</v>
       </c>
     </row>
@@ -3025,19 +3026,19 @@
       <c r="A8" s="11" t="s">
         <v>255</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>870000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>1164930</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>1476773</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>1758744</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>1958385</v>
       </c>
     </row>
@@ -3045,19 +3046,19 @@
       <c r="A9" s="11" t="s">
         <v>256</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>50000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>51500</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>53045</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>54636</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>56275</v>
       </c>
     </row>
@@ -3065,19 +3066,19 @@
       <c r="A10" s="11" t="s">
         <v>257</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>25000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>25750</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>26523</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>27318</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>28138</v>
       </c>
     </row>
@@ -3085,19 +3086,19 @@
       <c r="A11" s="11" t="s">
         <v>258</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>50000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>66950</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>84872</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>101077</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>112551</v>
       </c>
     </row>
@@ -3105,54 +3106,54 @@
       <c r="A12" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B12" s="35">
+      <c r="B12" s="36">
         <f>SUM(B5:B11)</f>
         <v>1975000</v>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="36">
         <f>SUM(C5:C11)</f>
         <v>2621350</v>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="36">
         <f>SUM(D5:D11)</f>
         <v>3304704</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="36">
         <f>SUM(E5:E11)</f>
         <v>3922890</v>
       </c>
-      <c r="F12" s="35">
+      <c r="F12" s="36">
         <f>SUM(F5:F11)</f>
         <v>4361347</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>260</v>
       </c>
-      <c r="B14" s="17"/>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>242</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <v>126018</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>129798</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>133692</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>137703</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>141834</v>
       </c>
     </row>
@@ -3160,19 +3161,19 @@
       <c r="A16" s="11" t="s">
         <v>243</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>99488</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>102472</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>105546</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>108713</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>111974</v>
       </c>
     </row>
@@ -3180,19 +3181,19 @@
       <c r="A17" s="11" t="s">
         <v>239</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <v>382032</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>393493</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>405298</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>417457</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>429980</v>
       </c>
     </row>
@@ -3200,19 +3201,19 @@
       <c r="A18" s="11" t="s">
         <v>240</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <v>122544</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>126220</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>130007</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>133907</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>137924</v>
       </c>
     </row>
@@ -3220,19 +3221,19 @@
       <c r="A19" s="11" t="s">
         <v>247</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <v>55713</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>57384</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>59106</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>60879</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>62705</v>
       </c>
     </row>
@@ -3240,19 +3241,19 @@
       <c r="A20" s="11" t="s">
         <v>245</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <v>68978</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>71047</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>73179</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>75374</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>77635</v>
       </c>
     </row>
@@ -3260,39 +3261,39 @@
       <c r="A21" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="36">
         <f>SUM(B15:B20)</f>
         <v>854772</v>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="36">
         <f>SUM(C15:C20)</f>
         <v>880415</v>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="36">
         <f>SUM(D15:D20)</f>
         <v>906828</v>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="36">
         <f>SUM(E15:E20)</f>
         <v>934032</v>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="36">
         <f>SUM(F15:F20)</f>
         <v>962053</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="36" t="s">
+      <c r="A24" s="37" t="s">
         <v>153</v>
       </c>
     </row>
@@ -3300,24 +3301,24 @@
       <c r="A25" s="11" t="s">
         <v>261</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="31">
         <v>60000</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>80340</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>101846</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>121293</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>135061</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="36" t="s">
+      <c r="A26" s="37" t="s">
         <v>154</v>
       </c>
     </row>
@@ -3325,24 +3326,24 @@
       <c r="A27" s="11" t="s">
         <v>262</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <v>40000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>53560</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>67898</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>80862</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>90041</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="36" t="s">
+      <c r="A28" s="37" t="s">
         <v>147</v>
       </c>
     </row>
@@ -3350,19 +3351,19 @@
       <c r="A29" s="11" t="s">
         <v>263</v>
       </c>
-      <c r="B29" s="30">
+      <c r="B29" s="31">
         <v>102000</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <v>105060</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="31">
         <v>108212</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="31">
         <v>111458</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="31">
         <v>114802</v>
       </c>
     </row>
@@ -3370,19 +3371,19 @@
       <c r="A30" s="11" t="s">
         <v>264</v>
       </c>
-      <c r="B30" s="30">
+      <c r="B30" s="31">
         <v>14400</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <v>14832</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="31">
         <v>15277</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="31">
         <v>15735</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="31">
         <v>16207</v>
       </c>
     </row>
@@ -3390,19 +3391,19 @@
       <c r="A31" s="11" t="s">
         <v>265</v>
       </c>
-      <c r="B31" s="30">
+      <c r="B31" s="31">
         <v>12000</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <v>12360</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="31">
         <v>12731</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="31">
         <v>13113</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="31">
         <v>13506</v>
       </c>
     </row>
@@ -3410,19 +3411,19 @@
       <c r="A32" s="11" t="s">
         <v>266</v>
       </c>
-      <c r="B32" s="30">
+      <c r="B32" s="31">
         <v>8000</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <v>8240</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="31">
         <v>8487</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="31">
         <v>8742</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="31">
         <v>9004</v>
       </c>
     </row>
@@ -3430,29 +3431,29 @@
       <c r="A33" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="36">
         <f>SUM(B29:B32)</f>
         <v>136400</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <f>SUM(C29:C32)</f>
         <v>140492</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <f>SUM(D29:D32)</f>
         <v>144707</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <f>SUM(E29:E32)</f>
         <v>149048</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <f>SUM(F29:F32)</f>
         <v>153519</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="36" t="s">
+      <c r="A34" s="37" t="s">
         <v>156</v>
       </c>
     </row>
@@ -3460,19 +3461,19 @@
       <c r="A35" s="11" t="s">
         <v>268</v>
       </c>
-      <c r="B35" s="30">
+      <c r="B35" s="31">
         <v>15000</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <v>15450</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="31">
         <v>15914</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="31">
         <v>16391</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="31">
         <v>16883</v>
       </c>
     </row>
@@ -3480,19 +3481,19 @@
       <c r="A36" s="11" t="s">
         <v>269</v>
       </c>
-      <c r="B36" s="30">
+      <c r="B36" s="31">
         <v>8000</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <v>8240</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="31">
         <v>8487</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="31">
         <v>8742</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="31">
         <v>9004</v>
       </c>
     </row>
@@ -3500,19 +3501,19 @@
       <c r="A37" s="11" t="s">
         <v>270</v>
       </c>
-      <c r="B37" s="30">
+      <c r="B37" s="31">
         <v>12000</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <v>12360</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="31">
         <v>12731</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="31">
         <v>13113</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="31">
         <v>13506</v>
       </c>
     </row>
@@ -3520,23 +3521,23 @@
       <c r="A38" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B38" s="35">
+      <c r="B38" s="36">
         <f>SUM(B35:B37)</f>
         <v>35000</v>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="36">
         <f>SUM(C35:C37)</f>
         <v>36050</v>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="36">
         <f>SUM(D35:D37)</f>
         <v>37132</v>
       </c>
-      <c r="E38" s="35">
+      <c r="E38" s="36">
         <f>SUM(E35:E37)</f>
         <v>38245</v>
       </c>
-      <c r="F38" s="35">
+      <c r="F38" s="36">
         <f>SUM(F35:F37)</f>
         <v>39393</v>
       </c>
@@ -3545,54 +3546,54 @@
       <c r="A39" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B39" s="35">
+      <c r="B39" s="36">
         <f>B25+B27+B33+B38</f>
         <v>271400</v>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="36">
         <f>C25+C27+C33+C38</f>
         <v>310442</v>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="36">
         <f>D25+D27+D33+D38</f>
         <v>351582</v>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="36">
         <f>E25+E27+E33+E38</f>
         <v>389448</v>
       </c>
-      <c r="F39" s="35">
+      <c r="F39" s="36">
         <f>F25+F27+F33+F38</f>
         <v>418014</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>273</v>
       </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="17"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>274</v>
       </c>
-      <c r="B42" s="30">
+      <c r="B42" s="31">
         <v>34064</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <v>34064</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <v>34064</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="31">
         <v>34064</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="31">
         <v>34064</v>
       </c>
     </row>
@@ -3600,19 +3601,19 @@
       <c r="A43" s="11" t="s">
         <v>275</v>
       </c>
-      <c r="B43" s="30">
+      <c r="B43" s="31">
         <v>25000</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <v>10000</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="31">
         <v>10000</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <v>5000</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <v>5000</v>
       </c>
     </row>
@@ -3620,23 +3621,23 @@
       <c r="A44" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B44" s="35">
+      <c r="B44" s="36">
         <f>SUM(B42:B43)</f>
         <v>59064</v>
       </c>
-      <c r="C44" s="35">
+      <c r="C44" s="36">
         <f>SUM(C42:C43)</f>
         <v>44064</v>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="36">
         <f>SUM(D42:D43)</f>
         <v>44064</v>
       </c>
-      <c r="E44" s="35">
+      <c r="E44" s="36">
         <f>SUM(E42:E43)</f>
         <v>39064</v>
       </c>
-      <c r="F44" s="35">
+      <c r="F44" s="36">
         <f>SUM(F42:F43)</f>
         <v>39064</v>
       </c>
@@ -3676,22 +3677,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -3699,23 +3700,23 @@
       <c r="A4" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="33">
+      <c r="B4" s="34">
         <f>'Budget Detail'!B12</f>
         <v>1975000</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="34">
         <f>'Budget Detail'!C12</f>
         <v>2621350</v>
       </c>
-      <c r="D4" s="33">
+      <c r="D4" s="34">
         <f>'Budget Detail'!D12</f>
         <v>3304704</v>
       </c>
-      <c r="E4" s="33">
+      <c r="E4" s="34">
         <f>'Budget Detail'!E12</f>
         <v>3922890</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="34">
         <f>'Budget Detail'!F12</f>
         <v>4361347</v>
       </c>
@@ -3724,23 +3725,23 @@
       <c r="A5" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B5" s="33">
+      <c r="B5" s="34">
         <f>'Budget Detail'!B21</f>
         <v>854772</v>
       </c>
-      <c r="C5" s="33">
+      <c r="C5" s="34">
         <f>'Budget Detail'!C21</f>
         <v>880415</v>
       </c>
-      <c r="D5" s="33">
+      <c r="D5" s="34">
         <f>'Budget Detail'!D21</f>
         <v>906828</v>
       </c>
-      <c r="E5" s="33">
+      <c r="E5" s="34">
         <f>'Budget Detail'!E21</f>
         <v>934032</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <f>'Budget Detail'!F21</f>
         <v>962053</v>
       </c>
@@ -3749,23 +3750,23 @@
       <c r="A6" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="B6" s="33">
+      <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
         <v>271400</v>
       </c>
-      <c r="C6" s="33">
+      <c r="C6" s="34">
         <f>'Budget Detail'!C39</f>
         <v>310442</v>
       </c>
-      <c r="D6" s="33">
+      <c r="D6" s="34">
         <f>'Budget Detail'!D39</f>
         <v>351582</v>
       </c>
-      <c r="E6" s="33">
+      <c r="E6" s="34">
         <f>'Budget Detail'!E39</f>
         <v>389448</v>
       </c>
-      <c r="F6" s="33">
+      <c r="F6" s="34">
         <f>'Budget Detail'!F39</f>
         <v>418014</v>
       </c>
@@ -3774,23 +3775,23 @@
       <c r="A7" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B7" s="33">
+      <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
         <v>59064</v>
       </c>
-      <c r="C7" s="33">
+      <c r="C7" s="34">
         <f>'Budget Detail'!C44</f>
         <v>44064</v>
       </c>
-      <c r="D7" s="33">
+      <c r="D7" s="34">
         <f>'Budget Detail'!D44</f>
         <v>44064</v>
       </c>
-      <c r="E7" s="33">
+      <c r="E7" s="34">
         <f>'Budget Detail'!E44</f>
         <v>39064</v>
       </c>
-      <c r="F7" s="33">
+      <c r="F7" s="34">
         <f>'Budget Detail'!F44</f>
         <v>39064</v>
       </c>
@@ -3799,58 +3800,58 @@
       <c r="A8" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B8" s="35">
+      <c r="B8" s="36">
         <f>SUM(B5:B7)</f>
         <v>1185236</v>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="36">
         <f>SUM(C5:C7)</f>
         <v>1234922</v>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="36">
         <f>SUM(D5:D7)</f>
         <v>1302474</v>
       </c>
-      <c r="E8" s="35">
+      <c r="E8" s="36">
         <f>SUM(E5:E7)</f>
         <v>1362545</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="36">
         <f>SUM(F5:F7)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>280</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="32">
         <f>B4-B8</f>
         <v>789764</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>C4-C8</f>
         <v>1386428</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>D4-D8</f>
         <v>2002229</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>E4-E8</f>
         <v>2560345</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>F4-F8</f>
         <v>2942215</v>
       </c>
@@ -3859,23 +3860,23 @@
       <c r="A12" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B12" s="29">
+      <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.39988031</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.52889864</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.60587258</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.65266812</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.67461156</v>
       </c>
@@ -3884,19 +3885,19 @@
       <c r="A13" s="11" t="s">
         <v>283</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>789764</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>2176192</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>4178421</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>6738766</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>9680981</v>
       </c>
     </row>
@@ -3904,19 +3905,19 @@
       <c r="A14" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <v>19750</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>20164</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>20654</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>21205</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>21807</v>
       </c>
     </row>
@@ -3924,19 +3925,19 @@
       <c r="A15" s="11" t="s">
         <v>284</v>
       </c>
-      <c r="B15" s="30">
+      <c r="B15" s="31">
         <v>11852</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>9499</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>8140</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>7365</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>7096</v>
       </c>
     </row>
@@ -3984,171 +3985,171 @@
       <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="20" t="s">
         <v>286</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="D2" s="20" t="s">
         <v>288</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="E2" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="F2" s="20" t="s">
         <v>290</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="G2" s="20" t="s">
         <v>291</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="20" t="s">
         <v>292</v>
       </c>
-      <c r="I2" s="19" t="s">
+      <c r="I2" s="20" t="s">
         <v>293</v>
       </c>
-      <c r="J2" s="19" t="s">
+      <c r="J2" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="K2" s="19" t="s">
+      <c r="K2" s="20" t="s">
         <v>295</v>
       </c>
-      <c r="L2" s="19" t="s">
+      <c r="L2" s="20" t="s">
         <v>296</v>
       </c>
-      <c r="M2" s="19" t="s">
+      <c r="M2" s="20" t="s">
         <v>297</v>
       </c>
-      <c r="N2" s="19" t="s">
+      <c r="N2" s="20" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
+      <c r="L3" s="18"/>
+      <c r="M3" s="18"/>
+      <c r="N3" s="18"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="B4" s="35">
+      <c r="B4" s="36">
         <v>85833</v>
       </c>
-      <c r="C4" s="35">
+      <c r="C4" s="36">
         <v>180333</v>
       </c>
-      <c r="D4" s="35">
+      <c r="D4" s="36">
         <v>180333</v>
       </c>
-      <c r="E4" s="35">
+      <c r="E4" s="36">
         <v>180333</v>
       </c>
-      <c r="F4" s="35">
+      <c r="F4" s="36">
         <v>180333</v>
       </c>
-      <c r="G4" s="35">
+      <c r="G4" s="36">
         <v>180333</v>
       </c>
-      <c r="H4" s="35">
+      <c r="H4" s="36">
         <v>180333</v>
       </c>
-      <c r="I4" s="35">
+      <c r="I4" s="36">
         <v>180333</v>
       </c>
-      <c r="J4" s="35">
+      <c r="J4" s="36">
         <v>180333</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="36">
         <v>180333</v>
       </c>
-      <c r="L4" s="35">
+      <c r="L4" s="36">
         <v>180333</v>
       </c>
-      <c r="M4" s="35">
+      <c r="M4" s="36">
         <v>85833</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="36">
         <f>SUM(B4:M4)</f>
         <v>1974996</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="18"/>
+      <c r="M6" s="18"/>
+      <c r="N6" s="18"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>71231</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>71231</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>71231</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>71231</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>71231</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>71231</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <v>71231</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <v>71231</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="31">
         <v>71231</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="31">
         <v>71231</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="31">
         <v>71231</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="31">
         <v>71231</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="31">
         <f>SUM(B7:M7)</f>
         <v>854772</v>
       </c>
@@ -4157,43 +4158,43 @@
       <c r="A8" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>22617</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>22617</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>22617</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>22617</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>22617</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>22617</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <v>22617</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <v>22617</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="31">
         <v>22617</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="31">
         <v>22617</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="31">
         <v>22617</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="31">
         <v>22617</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="31">
         <f>SUM(B8:M8)</f>
         <v>271400</v>
       </c>
@@ -4202,118 +4203,118 @@
       <c r="A9" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>4922</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>4922</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>4922</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>4922</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>4922</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>4922</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <v>4922</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <v>4922</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="31">
         <v>4922</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="31">
         <v>4922</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="31">
         <v>4922</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="31">
         <v>4922</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="31">
         <f>SUM(B9:M9)</f>
         <v>59064</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>303</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="17"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="17"/>
-      <c r="L11" s="17"/>
-      <c r="M11" s="17"/>
-      <c r="N11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="18"/>
+      <c r="M11" s="18"/>
+      <c r="N11" s="18"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>B7+B8+B9</f>
         <v>98770</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>C7+C8+C9</f>
         <v>98770</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>D7+D8+D9</f>
         <v>98770</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>E7+E8+E9</f>
         <v>98770</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>F7+F8+F9</f>
         <v>98770</v>
       </c>
-      <c r="G12" s="33">
+      <c r="G12" s="34">
         <f>G7+G8+G9</f>
         <v>98770</v>
       </c>
-      <c r="H12" s="33">
+      <c r="H12" s="34">
         <f>H7+H8+H9</f>
         <v>98770</v>
       </c>
-      <c r="I12" s="33">
+      <c r="I12" s="34">
         <f>I7+I8+I9</f>
         <v>98770</v>
       </c>
-      <c r="J12" s="33">
+      <c r="J12" s="34">
         <f>J7+J8+J9</f>
         <v>98770</v>
       </c>
-      <c r="K12" s="33">
+      <c r="K12" s="34">
         <f>K7+K8+K9</f>
         <v>98770</v>
       </c>
-      <c r="L12" s="33">
+      <c r="L12" s="34">
         <f>L7+L8+L9</f>
         <v>98770</v>
       </c>
-      <c r="M12" s="33">
+      <c r="M12" s="34">
         <f>M7+M8+M9</f>
         <v>98770</v>
       </c>
-      <c r="N12" s="33">
+      <c r="N12" s="34">
         <f>SUM(B12:M12)</f>
         <v>1185240</v>
       </c>
@@ -4322,55 +4323,55 @@
       <c r="A13" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B13" s="33">
+      <c r="B13" s="34">
         <f>B4-B12</f>
         <v>-12937</v>
       </c>
-      <c r="C13" s="33">
+      <c r="C13" s="34">
         <f>C4-C12</f>
         <v>81563</v>
       </c>
-      <c r="D13" s="33">
+      <c r="D13" s="34">
         <f>D4-D12</f>
         <v>81563</v>
       </c>
-      <c r="E13" s="33">
+      <c r="E13" s="34">
         <f>E4-E12</f>
         <v>81563</v>
       </c>
-      <c r="F13" s="33">
+      <c r="F13" s="34">
         <f>F4-F12</f>
         <v>81563</v>
       </c>
-      <c r="G13" s="33">
+      <c r="G13" s="34">
         <f>G4-G12</f>
         <v>81563</v>
       </c>
-      <c r="H13" s="33">
+      <c r="H13" s="34">
         <f>H4-H12</f>
         <v>81563</v>
       </c>
-      <c r="I13" s="33">
+      <c r="I13" s="34">
         <f>I4-I12</f>
         <v>81563</v>
       </c>
-      <c r="J13" s="33">
+      <c r="J13" s="34">
         <f>J4-J12</f>
         <v>81563</v>
       </c>
-      <c r="K13" s="33">
+      <c r="K13" s="34">
         <f>K4-K12</f>
         <v>81563</v>
       </c>
-      <c r="L13" s="33">
+      <c r="L13" s="34">
         <f>L4-L12</f>
         <v>81563</v>
       </c>
-      <c r="M13" s="33">
+      <c r="M13" s="34">
         <f>M4-M12</f>
         <v>-12937</v>
       </c>
-      <c r="N13" s="33">
+      <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
         <v>789756</v>
       </c>
@@ -4379,71 +4380,71 @@
       <c r="A14" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="B14" s="37">
+      <c r="B14" s="38">
         <f>B17+B13</f>
         <v>62063</v>
       </c>
-      <c r="C14" s="37">
+      <c r="C14" s="38">
         <f>B14+C13</f>
         <v>143626</v>
       </c>
-      <c r="D14" s="37">
+      <c r="D14" s="38">
         <f>C14+D13</f>
         <v>225189</v>
       </c>
-      <c r="E14" s="37">
+      <c r="E14" s="38">
         <f>D14+E13</f>
         <v>306752</v>
       </c>
-      <c r="F14" s="37">
+      <c r="F14" s="38">
         <f>E14+F13</f>
         <v>388315</v>
       </c>
-      <c r="G14" s="37">
+      <c r="G14" s="38">
         <f>F14+G13</f>
         <v>469878</v>
       </c>
-      <c r="H14" s="37">
+      <c r="H14" s="38">
         <f>G14+H13</f>
         <v>551441</v>
       </c>
-      <c r="I14" s="37">
+      <c r="I14" s="38">
         <f>H14+I13</f>
         <v>633004</v>
       </c>
-      <c r="J14" s="37">
+      <c r="J14" s="38">
         <f>I14+J13</f>
         <v>714567</v>
       </c>
-      <c r="K14" s="37">
+      <c r="K14" s="38">
         <f>J14+K13</f>
         <v>796130</v>
       </c>
-      <c r="L14" s="37">
+      <c r="L14" s="38">
         <f>K14+L13</f>
         <v>877693</v>
       </c>
-      <c r="M14" s="37">
+      <c r="M14" s="38">
         <f>L14+M13</f>
         <v>864756</v>
       </c>
-      <c r="N14" s="31">
+      <c r="N14" s="32">
         <f>M14</f>
         <v>864756</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>306</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B17" s="21">
+      <c r="B17" s="22">
         <v>75000</v>
       </c>
     </row>
@@ -4451,7 +4452,7 @@
       <c r="A18" s="11" t="s">
         <v>307</v>
       </c>
-      <c r="B18" s="37">
+      <c r="B18" s="38">
         <f>M14</f>
         <v>864756</v>
       </c>
@@ -4460,7 +4461,7 @@
       <c r="A19" s="11" t="s">
         <v>308</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
         <v>62063</v>
       </c>
@@ -4500,82 +4501,82 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>251</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="38" t="s">
+      <c r="A5" s="39" t="s">
         <v>259</v>
       </c>
-      <c r="B5" s="35">
+      <c r="B5" s="36">
         <v>1975000</v>
       </c>
-      <c r="C5" s="35">
+      <c r="C5" s="36">
         <v>2621350</v>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="36">
         <v>3304704</v>
       </c>
-      <c r="E5" s="35">
+      <c r="E5" s="36">
         <v>3922890</v>
       </c>
-      <c r="F5" s="35">
+      <c r="F5" s="36">
         <v>4361347</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="34">
         <v>854772</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <v>880415</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <v>906828</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <v>934032</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <v>962053</v>
       </c>
     </row>
@@ -4583,19 +4584,19 @@
       <c r="A9" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="B9" s="33">
+      <c r="B9" s="34">
         <v>271400</v>
       </c>
-      <c r="C9" s="33">
+      <c r="C9" s="34">
         <v>310442</v>
       </c>
-      <c r="D9" s="33">
+      <c r="D9" s="34">
         <v>351582</v>
       </c>
-      <c r="E9" s="33">
+      <c r="E9" s="34">
         <v>389448</v>
       </c>
-      <c r="F9" s="33">
+      <c r="F9" s="34">
         <v>418014</v>
       </c>
     </row>
@@ -4603,78 +4604,78 @@
       <c r="A10" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B10" s="33">
+      <c r="B10" s="34">
         <v>59064</v>
       </c>
-      <c r="C10" s="33">
+      <c r="C10" s="34">
         <v>44064</v>
       </c>
-      <c r="D10" s="33">
+      <c r="D10" s="34">
         <v>44064</v>
       </c>
-      <c r="E10" s="33">
+      <c r="E10" s="34">
         <v>39064</v>
       </c>
-      <c r="F10" s="33">
+      <c r="F10" s="34">
         <v>39064</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="B11" s="35">
+      <c r="B11" s="36">
         <f>SUM(B8:B10)</f>
         <v>1185236</v>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="36">
         <f>SUM(C8:C10)</f>
         <v>1234922</v>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="36">
         <f>SUM(D8:D10)</f>
         <v>1302474</v>
       </c>
-      <c r="E11" s="35">
+      <c r="E11" s="36">
         <f>SUM(E8:E10)</f>
         <v>1362545</v>
       </c>
-      <c r="F11" s="35">
+      <c r="F11" s="36">
         <f>SUM(F8:F10)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>311</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="38" t="s">
+      <c r="A14" s="39" t="s">
         <v>281</v>
       </c>
-      <c r="B14" s="31">
+      <c r="B14" s="32">
         <f>B5-B11</f>
         <v>789764</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>C5-C11</f>
         <v>1386428</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>D5-D11</f>
         <v>2002229</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>E5-E11</f>
         <v>2560345</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>F5-F11</f>
         <v>2942215</v>
       </c>
@@ -4683,23 +4684,23 @@
       <c r="A15" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B15" s="29">
+      <c r="B15" s="30">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.39988031</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.52889864</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.60587258</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.65266812</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.67461156</v>
       </c>
@@ -4739,101 +4740,101 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>312</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
+      <c r="A5" s="40" t="s">
         <v>313</v>
       </c>
-      <c r="B5" s="40" t="s">
+      <c r="B5" s="41" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="41" t="s">
+      <c r="C5" s="42" t="s">
         <v>314</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="40" t="s">
         <v>315</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="41" t="s">
         <v>231</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="B6" s="21">
+      <c r="B6" s="22">
         <v>250000</v>
       </c>
-      <c r="C6" s="22">
+      <c r="C6" s="23">
         <v>0.065</v>
       </c>
-      <c r="D6" s="18">
+      <c r="D6" s="19">
         <v>10</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>34064</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="18" t="s">
         <v>316</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <f>B6</f>
         <v>250000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>B13</f>
         <v>231645</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>C13</f>
         <v>212061</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>D13</f>
         <v>191165</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>E13</f>
         <v>168870</v>
       </c>
@@ -4842,23 +4843,23 @@
       <c r="A10" s="11" t="s">
         <v>318</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>15710</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>14480</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>13169</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>11769</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>10276</v>
       </c>
@@ -4867,23 +4868,23 @@
       <c r="A11" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>18355</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>19584</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>20896</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>22295</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>23788</v>
       </c>
@@ -4892,23 +4893,23 @@
       <c r="A12" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="B12" s="33">
+      <c r="B12" s="34">
         <f>B10+B11</f>
         <v>34064</v>
       </c>
-      <c r="C12" s="33">
+      <c r="C12" s="34">
         <f>C10+C11</f>
         <v>34064</v>
       </c>
-      <c r="D12" s="33">
+      <c r="D12" s="34">
         <f>D10+D11</f>
         <v>34064</v>
       </c>
-      <c r="E12" s="33">
+      <c r="E12" s="34">
         <f>E10+E11</f>
         <v>34064</v>
       </c>
-      <c r="F12" s="33">
+      <c r="F12" s="34">
         <f>F10+F11</f>
         <v>34064</v>
       </c>
@@ -4917,23 +4918,23 @@
       <c r="A13" s="10" t="s">
         <v>321</v>
       </c>
-      <c r="B13" s="37">
+      <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
         <v>231645</v>
       </c>
-      <c r="C13" s="37">
+      <c r="C13" s="38">
         <f>MAX(0,C9-C11)</f>
         <v>212061</v>
       </c>
-      <c r="D13" s="37">
+      <c r="D13" s="38">
         <f>MAX(0,D9-D11)</f>
         <v>191165</v>
       </c>
-      <c r="E13" s="37">
+      <c r="E13" s="38">
         <f>MAX(0,E9-E11)</f>
         <v>168870</v>
       </c>
-      <c r="F13" s="37">
+      <c r="F13" s="38">
         <f>MAX(0,F9-F11)</f>
         <v>145082</v>
       </c>
@@ -4973,56 +4974,56 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>324</v>
       </c>
-      <c r="B5" s="42">
+      <c r="B5" s="43">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>864756</v>
       </c>
-      <c r="C5" s="42">
+      <c r="C5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>2251184</v>
       </c>
-      <c r="D5" s="42">
+      <c r="D5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>4253414</v>
       </c>
-      <c r="E5" s="42">
+      <c r="E5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>6813759</v>
       </c>
-      <c r="F5" s="42">
+      <c r="F5" s="43">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>9755974</v>
       </c>
@@ -5031,19 +5032,19 @@
       <c r="A6" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>12000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>12000</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>12000</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>12000</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>12000</v>
       </c>
     </row>
@@ -5051,19 +5052,19 @@
       <c r="A7" s="11" t="s">
         <v>326</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>180000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>180000</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>180000</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>180000</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>180000</v>
       </c>
     </row>
@@ -5071,19 +5072,19 @@
       <c r="A8" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>5000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>5000</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>5000</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>5000</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>5000</v>
       </c>
     </row>
@@ -5091,54 +5092,54 @@
       <c r="A9" s="10" t="s">
         <v>328</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>SUM(B5:B8)</f>
         <v>1061756</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <f>SUM(C5:C8)</f>
         <v>2448184</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="36">
         <f>SUM(D5:D8)</f>
         <v>4450414</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="36">
         <f>SUM(E5:E8)</f>
         <v>7010759</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="36">
         <f>SUM(F5:F8)</f>
         <v>9952974</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>329</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>8000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>8000</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>8000</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>8000</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>8000</v>
       </c>
     </row>
@@ -5146,23 +5147,23 @@
       <c r="A13" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
         <v>231645</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>'Debt Schedule'!C13</f>
         <v>212061</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>'Debt Schedule'!D13</f>
         <v>191165</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>'Debt Schedule'!E13</f>
         <v>168870</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>'Debt Schedule'!F13</f>
         <v>145082</v>
       </c>
@@ -5171,58 +5172,58 @@
       <c r="A14" s="10" t="s">
         <v>332</v>
       </c>
-      <c r="B14" s="35">
+      <c r="B14" s="36">
         <f>SUM(B12:B13)</f>
         <v>239645</v>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="36">
         <f>SUM(C12:C13)</f>
         <v>220061</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="36">
         <f>SUM(D12:D13)</f>
         <v>199165</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="36">
         <f>SUM(E12:E13)</f>
         <v>176870</v>
       </c>
-      <c r="F14" s="35">
+      <c r="F14" s="36">
         <f>SUM(F12:F13)</f>
         <v>153082</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>334</v>
       </c>
-      <c r="B17" s="31">
+      <c r="B17" s="32">
         <f>B9-B14</f>
         <v>822111</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>C9-C14</f>
         <v>2228123</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>D9-D14</f>
         <v>4251248</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>E9-E14</f>
         <v>6833888</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>F9-F14</f>
         <v>9799892</v>
       </c>
@@ -5231,23 +5232,23 @@
       <c r="A19" s="10" t="s">
         <v>335</v>
       </c>
-      <c r="B19" s="43" t="str">
+      <c r="B19" s="44" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="43" t="str">
+      <c r="C19" s="44" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="44">
+      <c r="D19" s="45">
         <f>D9-D14-D17</f>
         <v>1</v>
       </c>
-      <c r="E19" s="44">
+      <c r="E19" s="45">
         <f>E9-E14-E17</f>
         <v>1</v>
       </c>
-      <c r="F19" s="43" t="str">
+      <c r="F19" s="44" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -5287,52 +5288,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>1975000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>2621350</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>3304704</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>3922890</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>4361347</v>
       </c>
     </row>
@@ -5340,19 +5341,19 @@
       <c r="A6" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>854772</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>880415</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>906828</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>934032</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>962053</v>
       </c>
     </row>
@@ -5360,19 +5361,19 @@
       <c r="A7" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>271400</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>310442</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>351582</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>389448</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>418014</v>
       </c>
     </row>
@@ -5380,23 +5381,23 @@
       <c r="A8" s="10" t="s">
         <v>339</v>
       </c>
-      <c r="B8" s="33">
+      <c r="B8" s="34">
         <f>B5-B6-B7</f>
         <v>848828</v>
       </c>
-      <c r="C8" s="33">
+      <c r="C8" s="34">
         <f>C5-C6-C7</f>
         <v>1430493</v>
       </c>
-      <c r="D8" s="33">
+      <c r="D8" s="34">
         <f>D5-D6-D7</f>
         <v>2046294</v>
       </c>
-      <c r="E8" s="33">
+      <c r="E8" s="34">
         <f>E5-E6-E7</f>
         <v>2599410</v>
       </c>
-      <c r="F8" s="33">
+      <c r="F8" s="34">
         <f>F5-F6-F7</f>
         <v>2981279</v>
       </c>
@@ -5405,19 +5406,19 @@
       <c r="A9" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>34064</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>34064</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>34064</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>34064</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>34064</v>
       </c>
     </row>
@@ -5425,54 +5426,54 @@
       <c r="A10" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="B10" s="45">
+      <c r="B10" s="46">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>24.92</v>
       </c>
-      <c r="C10" s="45">
+      <c r="C10" s="46">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>41.99</v>
       </c>
-      <c r="D10" s="45">
+      <c r="D10" s="46">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>60.07</v>
       </c>
-      <c r="E10" s="45">
+      <c r="E10" s="46">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>76.31</v>
       </c>
-      <c r="F10" s="45">
+      <c r="F10" s="46">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>87.52</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>341</v>
       </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>864756</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>2251184</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>4253414</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>6813759</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>9755974</v>
       </c>
     </row>
@@ -5480,23 +5481,23 @@
       <c r="A14" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="28">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>272</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="28">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>671</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="28">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>1201</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="28">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1832</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="28">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>2518</v>
       </c>
@@ -5505,23 +5506,23 @@
       <c r="A15" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
         <v>8.9</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
         <v>22.1</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
         <v>39.5</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
         <v>60.2</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
         <v>82.8</v>
       </c>
@@ -5530,49 +5531,49 @@
       <c r="A16" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B16" s="29">
+      <c r="B16" s="30">
         <v>0.5</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>0.65</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>0.8</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>0.925</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="18" t="s">
         <v>345</v>
       </c>
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>237</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <v>19750</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>20164</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>20654</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>21205</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>21807</v>
       </c>
     </row>
@@ -5580,19 +5581,19 @@
       <c r="A20" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="B20" s="30">
+      <c r="B20" s="31">
         <v>888836</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>914480</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>940892</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>968097</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>996118</v>
       </c>
     </row>
@@ -5600,19 +5601,19 @@
       <c r="A21" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="31">
         <v>2714</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>2388</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>2197</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>2105</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>2090</v>
       </c>
     </row>
@@ -5620,49 +5621,49 @@
       <c r="A22" s="10" t="s">
         <v>348</v>
       </c>
-      <c r="B22" s="46">
+      <c r="B22" s="47">
         <v>53</v>
       </c>
-      <c r="C22" s="46">
+      <c r="C22" s="47">
         <v>52</v>
       </c>
-      <c r="D22" s="46">
+      <c r="D22" s="47">
         <v>51</v>
       </c>
-      <c r="E22" s="46">
+      <c r="E22" s="47">
         <v>51</v>
       </c>
-      <c r="F22" s="46">
+      <c r="F22" s="47">
         <v>51</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="17" t="s">
+      <c r="A24" s="18" t="s">
         <v>349</v>
       </c>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
+      <c r="B24" s="18"/>
+      <c r="C24" s="18"/>
+      <c r="D24" s="18"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="18"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="B25" s="47" t="s">
+      <c r="B25" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="C25" s="47" t="s">
+      <c r="C25" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="D25" s="47" t="s">
+      <c r="D25" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="E25" s="47" t="s">
+      <c r="E25" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="F25" s="47" t="s">
+      <c r="F25" s="48" t="s">
         <v>351</v>
       </c>
     </row>
@@ -5670,19 +5671,19 @@
       <c r="A26" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="B26" s="47" t="s">
+      <c r="B26" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="C26" s="47" t="s">
+      <c r="C26" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="D26" s="47" t="s">
+      <c r="D26" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="E26" s="47" t="s">
+      <c r="E26" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="F26" s="47" t="s">
+      <c r="F26" s="48" t="s">
         <v>351</v>
       </c>
     </row>
@@ -5690,19 +5691,19 @@
       <c r="A27" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="B27" s="48" t="s">
+      <c r="B27" s="49" t="s">
         <v>354</v>
       </c>
-      <c r="C27" s="48" t="s">
+      <c r="C27" s="49" t="s">
         <v>354</v>
       </c>
-      <c r="D27" s="48" t="s">
+      <c r="D27" s="49" t="s">
         <v>354</v>
       </c>
-      <c r="E27" s="48" t="s">
+      <c r="E27" s="49" t="s">
         <v>354</v>
       </c>
-      <c r="F27" s="48" t="s">
+      <c r="F27" s="49" t="s">
         <v>354</v>
       </c>
     </row>
@@ -5710,19 +5711,19 @@
       <c r="A28" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="B28" s="47" t="s">
+      <c r="B28" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="C28" s="47" t="s">
+      <c r="C28" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="D28" s="47" t="s">
+      <c r="D28" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="E28" s="47" t="s">
+      <c r="E28" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="F28" s="47" t="s">
+      <c r="F28" s="48" t="s">
         <v>351</v>
       </c>
     </row>
@@ -5730,19 +5731,19 @@
       <c r="A29" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="B29" s="47" t="s">
+      <c r="B29" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="C29" s="47" t="s">
+      <c r="C29" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="D29" s="47" t="s">
+      <c r="D29" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="E29" s="47" t="s">
+      <c r="E29" s="48" t="s">
         <v>351</v>
       </c>
-      <c r="F29" s="47" t="s">
+      <c r="F29" s="48" t="s">
         <v>351</v>
       </c>
     </row>
@@ -5783,16 +5784,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="49" t="s">
+      <c r="A3" s="50" t="s">
         <v>357</v>
       </c>
-      <c r="B3" s="49" t="s">
+      <c r="B3" s="50" t="s">
         <v>111</v>
       </c>
-      <c r="D3" s="49" t="s">
+      <c r="D3" s="50" t="s">
         <v>358</v>
       </c>
-      <c r="E3" s="49" t="s">
+      <c r="E3" s="50" t="s">
         <v>111</v>
       </c>
     </row>
@@ -5800,13 +5801,13 @@
       <c r="A4" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="30">
+      <c r="B4" s="31">
         <v>250000</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="31">
         <v>200000</v>
       </c>
     </row>
@@ -5814,13 +5815,13 @@
       <c r="A5" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>50000</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>50000</v>
       </c>
     </row>
@@ -5828,13 +5829,13 @@
       <c r="A6" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>75000</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>75000</v>
       </c>
     </row>
@@ -5842,7 +5843,7 @@
       <c r="D7" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>50000</v>
       </c>
     </row>
@@ -5850,13 +5851,13 @@
       <c r="A9" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="32">
         <v>375000</v>
       </c>
       <c r="D9" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <v>375000</v>
       </c>
     </row>
@@ -5864,7 +5865,7 @@
       <c r="A10" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="B10" s="43">
+      <c r="B10" s="44">
         <v>0</v>
       </c>
     </row>
@@ -6219,37 +6220,37 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="A4" s="17" t="s">
         <v>368</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="19" t="s">
+      <c r="A5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C5" s="19" t="s">
+      <c r="C5" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6257,19 +6258,19 @@
       <c r="A6" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>1975000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>2621350</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>3304704</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>3922890</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>4361347</v>
       </c>
     </row>
@@ -6277,19 +6278,19 @@
       <c r="A7" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>1160236</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>1224922</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>1292474</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>1357545</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>1414132</v>
       </c>
     </row>
@@ -6297,19 +6298,19 @@
       <c r="A8" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="32">
         <v>814764</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <v>1396428</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <v>2012229</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <v>2565345</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <v>2947215</v>
       </c>
     </row>
@@ -6317,19 +6318,19 @@
       <c r="A9" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B9" s="29">
+      <c r="B9" s="30">
         <v>0.4125385351058188</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>0.5327134670433142</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>0.6088985689741885</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>0.6539426893351535</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>0.6757579942908114</v>
       </c>
     </row>
@@ -6337,19 +6338,19 @@
       <c r="A10" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="B10" s="50">
+      <c r="B10" s="51">
         <v>24.92</v>
       </c>
-      <c r="C10" s="50">
+      <c r="C10" s="51">
         <v>41.99</v>
       </c>
-      <c r="D10" s="50">
+      <c r="D10" s="51">
         <v>60.07</v>
       </c>
-      <c r="E10" s="50">
+      <c r="E10" s="51">
         <v>76.31</v>
       </c>
-      <c r="F10" s="50">
+      <c r="F10" s="51">
         <v>87.52</v>
       </c>
     </row>
@@ -6357,54 +6358,54 @@
       <c r="A11" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="28">
         <v>53</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="28">
         <v>52</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="28">
         <v>51</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="28">
         <v>51</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="28">
         <v>51</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>369</v>
       </c>
-      <c r="B13" s="17"/>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
+      <c r="B13" s="18"/>
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="17" t="s">
         <v>370</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="C15" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6412,19 +6413,19 @@
       <c r="A16" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="31">
         <v>1678750</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>2228148</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>2808998</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>3334456</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>3707145</v>
       </c>
     </row>
@@ -6432,19 +6433,19 @@
       <c r="A17" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <v>1160236</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>1224922</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>1292474</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>1357545</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>1414132</v>
       </c>
     </row>
@@ -6452,19 +6453,19 @@
       <c r="A18" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B18" s="31">
+      <c r="B18" s="32">
         <v>518514</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="32">
         <v>1003226</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="32">
         <v>1516524</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="32">
         <v>1976912</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="32">
         <v>2293013</v>
       </c>
     </row>
@@ -6472,19 +6473,19 @@
       <c r="A19" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B19" s="29">
+      <c r="B19" s="30">
         <v>0.308868864830375</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>0.45025113769801683</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>0.5398806693813982</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>0.5928737521590041</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>0.6185388168127194</v>
       </c>
     </row>
@@ -6492,19 +6493,19 @@
       <c r="A20" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="B20" s="50">
+      <c r="B20" s="51">
         <v>16.22</v>
       </c>
-      <c r="C20" s="50">
+      <c r="C20" s="51">
         <v>30.45</v>
       </c>
-      <c r="D20" s="50">
+      <c r="D20" s="51">
         <v>45.52</v>
       </c>
-      <c r="E20" s="50">
+      <c r="E20" s="51">
         <v>59.03</v>
       </c>
-      <c r="F20" s="50">
+      <c r="F20" s="51">
         <v>68.31</v>
       </c>
     </row>
@@ -6512,54 +6513,54 @@
       <c r="A21" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="B21" s="27">
+      <c r="B21" s="28">
         <v>54</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="28">
         <v>53</v>
       </c>
-      <c r="D21" s="27">
+      <c r="D21" s="28">
         <v>53</v>
       </c>
-      <c r="E21" s="27">
+      <c r="E21" s="28">
         <v>52</v>
       </c>
-      <c r="F21" s="27">
+      <c r="F21" s="28">
         <v>52</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>371</v>
       </c>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="F23" s="17"/>
+      <c r="B23" s="18"/>
+      <c r="C23" s="18"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="18"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="17" t="s">
         <v>372</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="19" t="s">
+      <c r="A25" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="19" t="s">
+      <c r="B25" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C25" s="19" t="s">
+      <c r="C25" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="19" t="s">
+      <c r="D25" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="19" t="s">
+      <c r="F25" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6567,19 +6568,19 @@
       <c r="A26" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="B26" s="30">
+      <c r="B26" s="31">
         <v>1975000</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <v>2621350</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <v>3304704</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="31">
         <v>3922890</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="31">
         <v>4361347</v>
       </c>
     </row>
@@ -6587,19 +6588,19 @@
       <c r="A27" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="B27" s="30">
+      <c r="B27" s="31">
         <v>1173736</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>1241917</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>1313162</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>1381585</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>1440581</v>
       </c>
     </row>
@@ -6607,19 +6608,19 @@
       <c r="A28" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <v>801264</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>1379433</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>1991542</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>2541305</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>2920765</v>
       </c>
     </row>
@@ -6627,19 +6628,19 @@
       <c r="A29" s="11" t="s">
         <v>282</v>
       </c>
-      <c r="B29" s="29">
+      <c r="B29" s="30">
         <v>0.4057030920678441</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>0.5262301664539233</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>0.6026385368714597</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>0.6478145556304181</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>0.6696934781617792</v>
       </c>
     </row>
@@ -6647,19 +6648,19 @@
       <c r="A30" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="B30" s="50">
+      <c r="B30" s="51">
         <v>24.52</v>
       </c>
-      <c r="C30" s="50">
+      <c r="C30" s="51">
         <v>41.49</v>
       </c>
-      <c r="D30" s="50">
+      <c r="D30" s="51">
         <v>59.46</v>
       </c>
-      <c r="E30" s="50">
+      <c r="E30" s="51">
         <v>75.6</v>
       </c>
-      <c r="F30" s="50">
+      <c r="F30" s="51">
         <v>86.74</v>
       </c>
     </row>
@@ -6667,19 +6668,19 @@
       <c r="A31" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="B31" s="27">
+      <c r="B31" s="28">
         <v>53</v>
       </c>
-      <c r="C31" s="27">
+      <c r="C31" s="28">
         <v>52</v>
       </c>
-      <c r="D31" s="27">
+      <c r="D31" s="28">
         <v>52</v>
       </c>
-      <c r="E31" s="27">
+      <c r="E31" s="28">
         <v>52</v>
       </c>
-      <c r="F31" s="27">
+      <c r="F31" s="28">
         <v>51</v>
       </c>
     </row>
@@ -6722,10 +6723,10 @@
       <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="17" t="s">
+      <c r="A3" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B3" s="17"/>
+      <c r="B3" s="18"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -6776,16 +6777,16 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
-      <c r="H11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -6797,19 +6798,19 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="51" t="s">
+      <c r="D12" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="E12" s="51" t="s">
+      <c r="E12" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="F12" s="51" t="s">
+      <c r="F12" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="G12" s="51" t="s">
+      <c r="G12" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="H12" s="51" t="s">
+      <c r="H12" s="52" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6817,19 +6818,19 @@
       <c r="A13" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>1975000</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>2621350</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>3304704</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <v>3922890</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <v>4361347</v>
       </c>
     </row>
@@ -6837,19 +6838,19 @@
       <c r="A14" s="11" t="s">
         <v>279</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>1160236</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>1224922</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>1292474</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <v>1357545</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <v>1414132</v>
       </c>
     </row>
@@ -6857,19 +6858,19 @@
       <c r="A15" s="11" t="s">
         <v>281</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>789764</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>1386428</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>2002229</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <v>2560345</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <v>2942215</v>
       </c>
     </row>
@@ -6877,19 +6878,19 @@
       <c r="A16" s="11" t="s">
         <v>377</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>864756</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>2251184</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>4253414</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <v>6813759</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <v>9755974</v>
       </c>
     </row>
@@ -6897,33 +6898,33 @@
       <c r="A17" s="11" t="s">
         <v>378</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>231645</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>212061</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>191165</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <v>168870</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <v>145082</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>379</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -6935,19 +6936,19 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="51" t="s">
+      <c r="D20" s="52" t="s">
         <v>101</v>
       </c>
-      <c r="E20" s="51" t="s">
+      <c r="E20" s="52" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="51" t="s">
+      <c r="F20" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="G20" s="51" t="s">
+      <c r="G20" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="H20" s="51" t="s">
+      <c r="H20" s="52" t="s">
         <v>105</v>
       </c>
     </row>
@@ -6955,19 +6956,19 @@
       <c r="A21" s="11" t="s">
         <v>380</v>
       </c>
-      <c r="D21" s="29">
+      <c r="D21" s="30">
         <v>0.3998803072577175</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>0.5288986388059557</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>0.6058725788967125</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>0.6526681187789514</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>0.6746115593902751</v>
       </c>
     </row>
@@ -6975,19 +6976,19 @@
       <c r="A22" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="D22" s="50">
+      <c r="D22" s="51">
         <v>24.92</v>
       </c>
-      <c r="E22" s="50">
+      <c r="E22" s="51">
         <v>41.99</v>
       </c>
-      <c r="F22" s="50">
+      <c r="F22" s="51">
         <v>60.07</v>
       </c>
-      <c r="G22" s="50">
+      <c r="G22" s="51">
         <v>76.31</v>
       </c>
-      <c r="H22" s="50">
+      <c r="H22" s="51">
         <v>87.52</v>
       </c>
     </row>
@@ -6995,19 +6996,19 @@
       <c r="A23" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="29">
+      <c r="D23" s="30">
         <v>0.5</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>0.65</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>0.8</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <v>0.925</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <v>1</v>
       </c>
     </row>
@@ -7015,19 +7016,19 @@
       <c r="A24" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="D24" s="27">
+      <c r="D24" s="28">
         <v>100</v>
       </c>
-      <c r="E24" s="27">
+      <c r="E24" s="28">
         <v>130</v>
       </c>
-      <c r="F24" s="27">
+      <c r="F24" s="28">
         <v>160</v>
       </c>
-      <c r="G24" s="27">
+      <c r="G24" s="28">
         <v>185</v>
       </c>
-      <c r="H24" s="27">
+      <c r="H24" s="28">
         <v>200</v>
       </c>
     </row>
@@ -7082,32 +7083,32 @@
       <c r="G2" s="1"/>
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B3" s="52" t="s">
+      <c r="B3" s="53" t="s">
         <v>384</v>
       </c>
-      <c r="C3" s="52"/>
-      <c r="D3" s="52"/>
-      <c r="E3" s="52"/>
-      <c r="F3" s="52"/>
-      <c r="G3" s="52"/>
+      <c r="C3" s="53"/>
+      <c r="D3" s="53"/>
+      <c r="E3" s="53"/>
+      <c r="F3" s="53"/>
+      <c r="G3" s="53"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="18" t="s">
         <v>385</v>
       </c>
-      <c r="C5" s="53" t="s">
+      <c r="C5" s="54" t="s">
         <v>386</v>
       </c>
-      <c r="D5" s="53" t="s">
+      <c r="D5" s="54" t="s">
         <v>387</v>
       </c>
-      <c r="E5" s="53" t="s">
+      <c r="E5" s="54" t="s">
         <v>388</v>
       </c>
-      <c r="F5" s="53" t="s">
+      <c r="F5" s="54" t="s">
         <v>389</v>
       </c>
-      <c r="G5" s="53" t="s">
+      <c r="G5" s="54" t="s">
         <v>390</v>
       </c>
     </row>
@@ -7115,19 +7116,19 @@
       <c r="B6" s="11" t="s">
         <v>381</v>
       </c>
-      <c r="C6" s="54">
+      <c r="C6" s="55">
         <v>100</v>
       </c>
-      <c r="D6" s="54">
+      <c r="D6" s="55">
         <v>130</v>
       </c>
-      <c r="E6" s="54">
+      <c r="E6" s="55">
         <v>160</v>
       </c>
-      <c r="F6" s="54">
+      <c r="F6" s="55">
         <v>185</v>
       </c>
-      <c r="G6" s="54">
+      <c r="G6" s="55">
         <v>200</v>
       </c>
     </row>
@@ -7135,19 +7136,19 @@
       <c r="B7" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="C7" s="55">
+      <c r="C7" s="56">
         <v>1975000</v>
       </c>
-      <c r="D7" s="55">
+      <c r="D7" s="56">
         <v>2621350</v>
       </c>
-      <c r="E7" s="55">
+      <c r="E7" s="56">
         <v>3304703.5</v>
       </c>
-      <c r="F7" s="55">
+      <c r="F7" s="56">
         <v>3922889.9299999997</v>
       </c>
-      <c r="G7" s="55">
+      <c r="G7" s="56">
         <v>4361346.638750001</v>
       </c>
     </row>
@@ -7155,19 +7156,19 @@
       <c r="B8" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="C8" s="55">
+      <c r="C8" s="56">
         <v>854772</v>
       </c>
-      <c r="D8" s="55">
+      <c r="D8" s="56">
         <v>880415.16</v>
       </c>
-      <c r="E8" s="55">
+      <c r="E8" s="56">
         <v>906827.6148</v>
       </c>
-      <c r="F8" s="55">
+      <c r="F8" s="56">
         <v>934032.443244</v>
       </c>
-      <c r="G8" s="55">
+      <c r="G8" s="56">
         <v>962053.4165413202</v>
       </c>
     </row>
@@ -7175,19 +7176,19 @@
       <c r="B9" s="11" t="s">
         <v>301</v>
       </c>
-      <c r="C9" s="55">
+      <c r="C9" s="56">
         <v>271400</v>
       </c>
-      <c r="D9" s="55">
+      <c r="D9" s="56">
         <v>310442</v>
       </c>
-      <c r="E9" s="55">
+      <c r="E9" s="56">
         <v>351582.25999999995</v>
       </c>
-      <c r="F9" s="55">
+      <c r="F9" s="56">
         <v>389447.9028</v>
       </c>
-      <c r="G9" s="55">
+      <c r="G9" s="56">
         <v>418013.9720340001</v>
       </c>
     </row>
@@ -7195,19 +7196,19 @@
       <c r="B10" s="11" t="s">
         <v>302</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="56">
         <v>34064.39316600799</v>
       </c>
-      <c r="D10" s="55">
+      <c r="D10" s="56">
         <v>34064.39316600799</v>
       </c>
-      <c r="E10" s="55">
+      <c r="E10" s="56">
         <v>34064.39316600799</v>
       </c>
-      <c r="F10" s="55">
+      <c r="F10" s="56">
         <v>34064.39316600799</v>
       </c>
-      <c r="G10" s="55">
+      <c r="G10" s="56">
         <v>34064.39316600799</v>
       </c>
     </row>
@@ -7215,19 +7216,19 @@
       <c r="B11" s="10" t="s">
         <v>391</v>
       </c>
-      <c r="C11" s="56">
+      <c r="C11" s="57">
         <v>789763.6068339921</v>
       </c>
-      <c r="D11" s="56">
+      <c r="D11" s="57">
         <v>1386428.446833992</v>
       </c>
-      <c r="E11" s="56">
+      <c r="E11" s="57">
         <v>2002229.2320339922</v>
       </c>
-      <c r="F11" s="56">
+      <c r="F11" s="57">
         <v>2560345.190789992</v>
       </c>
-      <c r="G11" s="56">
+      <c r="G11" s="57">
         <v>2942214.857008673</v>
       </c>
     </row>
@@ -7235,19 +7236,19 @@
       <c r="B12" s="10" t="s">
         <v>342</v>
       </c>
-      <c r="C12" s="56">
+      <c r="C12" s="57">
         <v>864756</v>
       </c>
-      <c r="D12" s="56">
+      <c r="D12" s="57">
         <v>2251184.446833992</v>
       </c>
-      <c r="E12" s="56">
+      <c r="E12" s="57">
         <v>4253413.678867985</v>
       </c>
-      <c r="F12" s="56">
+      <c r="F12" s="57">
         <v>6813758.869657977</v>
       </c>
-      <c r="G12" s="56">
+      <c r="G12" s="57">
         <v>9755973.72666665</v>
       </c>
     </row>
@@ -7255,19 +7256,19 @@
       <c r="B13" s="10" t="s">
         <v>380</v>
       </c>
-      <c r="C13" s="57">
+      <c r="C13" s="58">
         <v>0.3998803072577175</v>
       </c>
-      <c r="D13" s="57">
+      <c r="D13" s="58">
         <v>0.5288986388059557</v>
       </c>
-      <c r="E13" s="57">
+      <c r="E13" s="58">
         <v>0.6058725788967125</v>
       </c>
-      <c r="F13" s="57">
+      <c r="F13" s="58">
         <v>0.6526681187789514</v>
       </c>
-      <c r="G13" s="57">
+      <c r="G13" s="58">
         <v>0.6746115593902751</v>
       </c>
     </row>
@@ -7275,19 +7276,19 @@
       <c r="B14" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="C14" s="55">
+      <c r="C14" s="56">
         <v>19750</v>
       </c>
-      <c r="D14" s="55">
+      <c r="D14" s="56">
         <v>20164.23076923077</v>
       </c>
-      <c r="E14" s="55">
+      <c r="E14" s="56">
         <v>20654.396875</v>
       </c>
-      <c r="F14" s="55">
+      <c r="F14" s="56">
         <v>21204.81043243243</v>
       </c>
-      <c r="G14" s="55">
+      <c r="G14" s="56">
         <v>21806.733193750006</v>
       </c>
     </row>
@@ -7295,19 +7296,19 @@
       <c r="B15" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="C15" s="57">
+      <c r="C15" s="58">
         <v>0.4327959493670886</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="58">
         <v>0.3358632612966601</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="58">
         <v>0.2744051364365971</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="58">
         <v>0.23809805013927576</v>
       </c>
-      <c r="G15" s="57">
+      <c r="G15" s="58">
         <v>0.22058632258064514</v>
       </c>
     </row>
@@ -7315,19 +7316,19 @@
       <c r="B16" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C16" s="57">
+      <c r="C16" s="58">
         <v>0.0412253164556962</v>
       </c>
-      <c r="D16" s="57">
+      <c r="D16" s="58">
         <v>0.035528487229862474</v>
       </c>
-      <c r="E16" s="57">
+      <c r="E16" s="58">
         <v>0.031916532905296946</v>
       </c>
-      <c r="F16" s="57">
+      <c r="F16" s="58">
         <v>0.029782729805013928</v>
       </c>
-      <c r="G16" s="57">
+      <c r="G16" s="58">
         <v>0.028753548387096775</v>
       </c>
     </row>
@@ -7335,19 +7336,19 @@
       <c r="B17" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="C17" s="57">
+      <c r="C17" s="58">
         <v>0.42978632911392406</v>
       </c>
-      <c r="D17" s="57">
+      <c r="D17" s="58">
         <v>0.5457084479371316</v>
       </c>
-      <c r="E17" s="57">
+      <c r="E17" s="58">
         <v>0.6192064205457464</v>
       </c>
-      <c r="F17" s="57">
+      <c r="F17" s="58">
         <v>0.6626261838440112</v>
       </c>
-      <c r="G17" s="57">
+      <c r="G17" s="58">
         <v>0.6835685161290322</v>
       </c>
     </row>
@@ -7355,19 +7356,19 @@
       <c r="B18" s="10" t="s">
         <v>340</v>
       </c>
-      <c r="C18" s="58">
+      <c r="C18" s="59">
         <v>24.918336160088252</v>
       </c>
-      <c r="D18" s="58">
+      <c r="D18" s="59">
         <v>41.993786092965045</v>
       </c>
-      <c r="E18" s="58">
+      <c r="E18" s="59">
         <v>60.071336519270375</v>
       </c>
-      <c r="F18" s="58">
+      <c r="F18" s="59">
         <v>76.3087007388667</v>
       </c>
-      <c r="G18" s="58">
+      <c r="G18" s="59">
         <v>87.51893026967599</v>
       </c>
     </row>
@@ -7375,156 +7376,156 @@
       <c r="B19" s="10" t="s">
         <v>395</v>
       </c>
-      <c r="C19" s="59" t="s">
+      <c r="C19" s="60" t="s">
         <v>386</v>
       </c>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
         <v>396</v>
       </c>
-      <c r="C20" s="59" t="s">
+      <c r="C20" s="60" t="s">
         <v>397</v>
       </c>
-      <c r="D20" s="59"/>
-      <c r="E20" s="59"/>
-      <c r="F20" s="59"/>
-      <c r="G20" s="59"/>
+      <c r="D20" s="60"/>
+      <c r="E20" s="60"/>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="17" t="s">
+      <c r="B22" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="C22" s="17" t="s">
+      <c r="C22" s="18" t="s">
         <v>399</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="18" t="s">
         <v>400</v>
       </c>
-      <c r="E22" s="17"/>
-      <c r="F22" s="17" t="s">
+      <c r="E22" s="18"/>
+      <c r="F22" s="18" t="s">
         <v>401</v>
       </c>
-      <c r="G22" s="17"/>
+      <c r="G22" s="18"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="39" t="s">
+      <c r="B23" s="40" t="s">
         <v>402</v>
       </c>
-      <c r="C23" s="60" t="s">
+      <c r="C23" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="D23" s="61" t="s">
+      <c r="D23" s="62" t="s">
         <v>404</v>
       </c>
-      <c r="E23" s="61"/>
-      <c r="F23" s="62" t="s">
+      <c r="E23" s="62"/>
+      <c r="F23" s="63" t="s">
         <v>405</v>
       </c>
-      <c r="G23" s="62"/>
+      <c r="G23" s="63"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="39" t="s">
+      <c r="B24" s="40" t="s">
         <v>406</v>
       </c>
-      <c r="C24" s="60" t="s">
+      <c r="C24" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="D24" s="61" t="s">
+      <c r="D24" s="62" t="s">
         <v>407</v>
       </c>
-      <c r="E24" s="61"/>
-      <c r="F24" s="62" t="s">
+      <c r="E24" s="62"/>
+      <c r="F24" s="63" t="s">
         <v>408</v>
       </c>
-      <c r="G24" s="62"/>
+      <c r="G24" s="63"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B25" s="39" t="s">
+      <c r="B25" s="40" t="s">
         <v>409</v>
       </c>
-      <c r="C25" s="60" t="s">
+      <c r="C25" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="D25" s="61" t="s">
+      <c r="D25" s="62" t="s">
         <v>410</v>
       </c>
-      <c r="E25" s="61"/>
-      <c r="F25" s="62" t="s">
+      <c r="E25" s="62"/>
+      <c r="F25" s="63" t="s">
         <v>411</v>
       </c>
-      <c r="G25" s="62"/>
+      <c r="G25" s="63"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B26" s="39" t="s">
+      <c r="B26" s="40" t="s">
         <v>412</v>
       </c>
-      <c r="C26" s="60" t="s">
+      <c r="C26" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="D26" s="61" t="s">
+      <c r="D26" s="62" t="s">
         <v>413</v>
       </c>
-      <c r="E26" s="61"/>
-      <c r="F26" s="62" t="s">
+      <c r="E26" s="62"/>
+      <c r="F26" s="63" t="s">
         <v>414</v>
       </c>
-      <c r="G26" s="62"/>
+      <c r="G26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B27" s="39" t="s">
+      <c r="B27" s="40" t="s">
         <v>415</v>
       </c>
-      <c r="C27" s="60" t="s">
+      <c r="C27" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="D27" s="61" t="s">
+      <c r="D27" s="62" t="s">
         <v>416</v>
       </c>
-      <c r="E27" s="61"/>
-      <c r="F27" s="62" t="s">
+      <c r="E27" s="62"/>
+      <c r="F27" s="63" t="s">
         <v>417</v>
       </c>
-      <c r="G27" s="62"/>
+      <c r="G27" s="63"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B28" s="39" t="s">
+      <c r="B28" s="40" t="s">
         <v>418</v>
       </c>
-      <c r="C28" s="60" t="s">
+      <c r="C28" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="D28" s="61" t="s">
+      <c r="D28" s="62" t="s">
         <v>419</v>
       </c>
-      <c r="E28" s="61"/>
-      <c r="F28" s="62" t="s">
+      <c r="E28" s="62"/>
+      <c r="F28" s="63" t="s">
         <v>420</v>
       </c>
-      <c r="G28" s="62"/>
+      <c r="G28" s="63"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B29" s="39" t="s">
+      <c r="B29" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="C29" s="60" t="s">
+      <c r="C29" s="61" t="s">
         <v>403</v>
       </c>
-      <c r="D29" s="61" t="s">
+      <c r="D29" s="62" t="s">
         <v>422</v>
       </c>
-      <c r="E29" s="61"/>
-      <c r="F29" s="62" t="s">
+      <c r="E29" s="62"/>
+      <c r="F29" s="63" t="s">
         <v>423</v>
       </c>
-      <c r="G29" s="62"/>
+      <c r="G29" s="63"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B31" s="39" t="s">
+      <c r="B31" s="40" t="s">
         <v>424</v>
       </c>
       <c r="C31" s="10" t="s">
@@ -7534,14 +7535,14 @@
       <c r="E31" s="10"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="64" t="s">
         <v>426</v>
       </c>
-      <c r="C33" s="63"/>
-      <c r="D33" s="63"/>
-      <c r="E33" s="63"/>
-      <c r="F33" s="63"/>
-      <c r="G33" s="63"/>
+      <c r="C33" s="64"/>
+      <c r="D33" s="64"/>
+      <c r="E33" s="64"/>
+      <c r="F33" s="64"/>
+      <c r="G33" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -7677,27 +7678,30 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
-      <c r="G4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="18" t="s">
+      <c r="B5" s="19" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7705,7 +7709,7 @@
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="18" t="s">
+      <c r="B6" s="19" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7713,7 +7717,7 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="18" t="s">
+      <c r="B7" s="19" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7721,7 +7725,7 @@
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="19" t="s">
         <v>38</v>
       </c>
     </row>
@@ -7729,7 +7733,7 @@
       <c r="A9" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B9" s="18" t="s">
+      <c r="B9" s="19" t="s">
         <v>97</v>
       </c>
     </row>
@@ -7737,7 +7741,7 @@
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="B10" s="19" t="s">
         <v>44</v>
       </c>
     </row>
@@ -7745,7 +7749,7 @@
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="19" t="s">
         <v>46</v>
       </c>
     </row>
@@ -7753,7 +7757,7 @@
       <c r="A12" s="11" t="s">
         <v>98</v>
       </c>
-      <c r="B12" s="18">
+      <c r="B12" s="19">
         <v>7</v>
       </c>
     </row>
@@ -7761,38 +7765,38 @@
       <c r="A13" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>200</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="B15" s="17"/>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="19" t="s">
+      <c r="A16" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="19" t="s">
+      <c r="B16" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C16" s="19" t="s">
+      <c r="C16" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -7800,47 +7804,47 @@
       <c r="A17" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="B17" s="20">
+      <c r="B17" s="21">
         <v>100</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="21">
         <v>130</v>
       </c>
-      <c r="D17" s="20">
+      <c r="D17" s="21">
         <v>160</v>
       </c>
-      <c r="E17" s="20">
+      <c r="E17" s="21">
         <v>185</v>
       </c>
-      <c r="F17" s="20">
+      <c r="F17" s="21">
         <v>200</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>107</v>
       </c>
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
+      <c r="B19" s="18"/>
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="19" t="s">
+      <c r="A20" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B20" s="19" t="s">
+      <c r="B20" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="19" t="s">
+      <c r="C20" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="19" t="s">
+      <c r="D20" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="19" t="s">
+      <c r="E20" s="20" t="s">
         <v>112</v>
       </c>
     </row>
@@ -7854,10 +7858,10 @@
       <c r="C21" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D21" s="21">
+      <c r="D21" s="22">
         <v>10500</v>
       </c>
-      <c r="E21" s="22">
+      <c r="E21" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7871,10 +7875,10 @@
       <c r="C22" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D22" s="21">
+      <c r="D22" s="22">
         <v>350</v>
       </c>
-      <c r="E22" s="22">
+      <c r="E22" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7888,10 +7892,10 @@
       <c r="C23" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="21">
+      <c r="D23" s="22">
         <v>-1050</v>
       </c>
-      <c r="E23" s="22">
+      <c r="E23" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7905,10 +7909,10 @@
       <c r="C24" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D24" s="21">
+      <c r="D24" s="22">
         <v>8700</v>
       </c>
-      <c r="E24" s="22">
+      <c r="E24" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7922,10 +7926,10 @@
       <c r="C25" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D25" s="21">
+      <c r="D25" s="22">
         <v>50000</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E25" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7939,10 +7943,10 @@
       <c r="C26" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D26" s="21">
+      <c r="D26" s="22">
         <v>25000</v>
       </c>
-      <c r="E26" s="22">
+      <c r="E26" s="23">
         <v>0</v>
       </c>
     </row>
@@ -7956,44 +7960,44 @@
       <c r="C27" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D27" s="21">
+      <c r="D27" s="22">
         <v>500</v>
       </c>
-      <c r="E27" s="22">
+      <c r="E27" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>127</v>
       </c>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="17"/>
-      <c r="G29" s="17"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="19" t="s">
+      <c r="B30" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C30" s="19" t="s">
+      <c r="C30" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="D30" s="19" t="s">
+      <c r="D30" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="F30" s="19" t="s">
+      <c r="F30" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="G30" s="19" t="s">
+      <c r="G30" s="20" t="s">
         <v>133</v>
       </c>
     </row>
@@ -8007,16 +8011,16 @@
       <c r="C31" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D31" s="23">
+      <c r="D31" s="24">
         <v>1</v>
       </c>
-      <c r="E31" s="21">
+      <c r="E31" s="22">
         <v>95000</v>
       </c>
-      <c r="F31" s="22">
+      <c r="F31" s="23">
         <v>0.25</v>
       </c>
-      <c r="G31" s="22">
+      <c r="G31" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8030,16 +8034,16 @@
       <c r="C32" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D32" s="23">
+      <c r="D32" s="24">
         <v>1</v>
       </c>
-      <c r="E32" s="21">
+      <c r="E32" s="22">
         <v>75000</v>
       </c>
-      <c r="F32" s="22">
+      <c r="F32" s="23">
         <v>0.25</v>
       </c>
-      <c r="G32" s="22">
+      <c r="G32" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8053,16 +8057,16 @@
       <c r="C33" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D33" s="23">
+      <c r="D33" s="24">
         <v>6</v>
       </c>
-      <c r="E33" s="21">
+      <c r="E33" s="22">
         <v>48000</v>
       </c>
-      <c r="F33" s="22">
+      <c r="F33" s="23">
         <v>0.25</v>
       </c>
-      <c r="G33" s="22">
+      <c r="G33" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8076,16 +8080,16 @@
       <c r="C34" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="24">
         <v>3</v>
       </c>
-      <c r="E34" s="21">
+      <c r="E34" s="22">
         <v>32000</v>
       </c>
-      <c r="F34" s="22">
+      <c r="F34" s="23">
         <v>0.2</v>
       </c>
-      <c r="G34" s="22">
+      <c r="G34" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8099,16 +8103,16 @@
       <c r="C35" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="24">
         <v>1</v>
       </c>
-      <c r="E35" s="21">
+      <c r="E35" s="22">
         <v>42000</v>
       </c>
-      <c r="F35" s="22">
+      <c r="F35" s="23">
         <v>0.25</v>
       </c>
-      <c r="G35" s="22">
+      <c r="G35" s="23">
         <v>0.0765</v>
       </c>
     </row>
@@ -8122,44 +8126,44 @@
       <c r="C36" s="11" t="s">
         <v>136</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="24">
         <v>1</v>
       </c>
-      <c r="E36" s="21">
+      <c r="E36" s="22">
         <v>52000</v>
       </c>
-      <c r="F36" s="22">
+      <c r="F36" s="23">
         <v>0.25</v>
       </c>
-      <c r="G36" s="22">
+      <c r="G36" s="23">
         <v>0.0765</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="17" t="s">
+      <c r="A38" s="18" t="s">
         <v>145</v>
       </c>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="17"/>
-      <c r="F38" s="17"/>
-      <c r="G38" s="17"/>
+      <c r="B38" s="18"/>
+      <c r="C38" s="18"/>
+      <c r="D38" s="18"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="18"/>
+      <c r="G38" s="18"/>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="19" t="s">
+      <c r="A39" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="B39" s="19" t="s">
+      <c r="B39" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="19" t="s">
+      <c r="C39" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="19" t="s">
+      <c r="D39" s="20" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="19" t="s">
+      <c r="E39" s="20" t="s">
         <v>112</v>
       </c>
     </row>
@@ -8173,10 +8177,10 @@
       <c r="C40" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D40" s="21">
+      <c r="D40" s="22">
         <v>8500</v>
       </c>
-      <c r="E40" s="22">
+      <c r="E40" s="23">
         <v>0.03</v>
       </c>
     </row>
@@ -8190,10 +8194,10 @@
       <c r="C41" s="11" t="s">
         <v>148</v>
       </c>
-      <c r="D41" s="21">
+      <c r="D41" s="22">
         <v>1200</v>
       </c>
-      <c r="E41" s="22">
+      <c r="E41" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8207,10 +8211,10 @@
       <c r="C42" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D42" s="21">
+      <c r="D42" s="22">
         <v>12000</v>
       </c>
-      <c r="E42" s="22">
+      <c r="E42" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8224,10 +8228,10 @@
       <c r="C43" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D43" s="21">
+      <c r="D43" s="22">
         <v>8000</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8241,10 +8245,10 @@
       <c r="C44" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D44" s="21">
+      <c r="D44" s="22">
         <v>600</v>
       </c>
-      <c r="E44" s="22">
+      <c r="E44" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8258,10 +8262,10 @@
       <c r="C45" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="D45" s="21">
+      <c r="D45" s="22">
         <v>400</v>
       </c>
-      <c r="E45" s="22">
+      <c r="E45" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8275,10 +8279,10 @@
       <c r="C46" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D46" s="21">
+      <c r="D46" s="22">
         <v>15000</v>
       </c>
-      <c r="E46" s="22">
+      <c r="E46" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8292,10 +8296,10 @@
       <c r="C47" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D47" s="21">
+      <c r="D47" s="22">
         <v>8000</v>
       </c>
-      <c r="E47" s="22">
+      <c r="E47" s="23">
         <v>0</v>
       </c>
     </row>
@@ -8309,38 +8313,38 @@
       <c r="C48" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="D48" s="21">
+      <c r="D48" s="22">
         <v>12000</v>
       </c>
-      <c r="E48" s="22">
+      <c r="E48" s="23">
         <v>0</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="17" t="s">
+      <c r="A50" s="18" t="s">
         <v>159</v>
       </c>
-      <c r="B50" s="17"/>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
+      <c r="B50" s="18"/>
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="B51" s="19" t="s">
+      <c r="B51" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C51" s="19" t="s">
+      <c r="C51" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="D51" s="19" t="s">
+      <c r="D51" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E51" s="19" t="s">
+      <c r="E51" s="20" t="s">
         <v>162</v>
       </c>
     </row>
@@ -8351,13 +8355,13 @@
       <c r="B52" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C52" s="21">
+      <c r="C52" s="22">
         <v>250000</v>
       </c>
-      <c r="D52" s="22">
+      <c r="D52" s="23">
         <v>0.065</v>
       </c>
-      <c r="E52" s="20">
+      <c r="E52" s="21">
         <v>10</v>
       </c>
     </row>
@@ -8368,35 +8372,35 @@
       <c r="B53" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="C53" s="21">
+      <c r="C53" s="22">
         <v>25000</v>
       </c>
-      <c r="D53" s="22">
+      <c r="D53" s="23">
         <v>0</v>
       </c>
-      <c r="E53" s="20">
+      <c r="E53" s="21">
         <v>0</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="17" t="s">
+      <c r="A55" s="18" t="s">
         <v>167</v>
       </c>
-      <c r="B55" s="17"/>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
+      <c r="B55" s="18"/>
+      <c r="C55" s="18"/>
+      <c r="D55" s="18"/>
+      <c r="E55" s="18"/>
+      <c r="F55" s="18"/>
+      <c r="G55" s="18"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>168</v>
       </c>
-      <c r="B56" s="22">
+      <c r="B56" s="23">
         <v>0.03</v>
       </c>
-      <c r="C56" s="24" t="s">
+      <c r="C56" s="25" t="s">
         <v>169</v>
       </c>
     </row>
@@ -8404,10 +8408,10 @@
       <c r="A57" s="11" t="s">
         <v>170</v>
       </c>
-      <c r="B57" s="22">
+      <c r="B57" s="23">
         <v>0.03</v>
       </c>
-      <c r="C57" s="24" t="s">
+      <c r="C57" s="25" t="s">
         <v>171</v>
       </c>
     </row>
@@ -8415,7 +8419,7 @@
       <c r="A58" s="11" t="s">
         <v>172</v>
       </c>
-      <c r="B58" s="23">
+      <c r="B58" s="24">
         <v>1</v>
       </c>
     </row>
@@ -8423,7 +8427,7 @@
       <c r="A59" s="11" t="s">
         <v>173</v>
       </c>
-      <c r="B59" s="21">
+      <c r="B59" s="22">
         <v>75000</v>
       </c>
     </row>
@@ -8431,7 +8435,7 @@
       <c r="A60" s="11" t="s">
         <v>174</v>
       </c>
-      <c r="B60" s="18" t="s">
+      <c r="B60" s="19" t="s">
         <v>175</v>
       </c>
     </row>
@@ -8613,66 +8617,66 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>193</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>194</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="17" t="s">
+      <c r="A5" s="18" t="s">
         <v>195</v>
       </c>
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="17"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="B6" s="25">
+      <c r="B6" s="26">
         <v>85</v>
       </c>
-      <c r="C6" s="25">
+      <c r="C6" s="26">
         <v>0</v>
       </c>
-      <c r="D6" s="26">
+      <c r="D6" s="27">
         <v>100</v>
       </c>
-      <c r="E6" s="26">
+      <c r="E6" s="27">
         <v>130</v>
       </c>
-      <c r="F6" s="26">
+      <c r="F6" s="27">
         <v>160</v>
       </c>
-      <c r="G6" s="26">
+      <c r="G6" s="27">
         <v>185</v>
       </c>
-      <c r="H6" s="26">
+      <c r="H6" s="27">
         <v>200</v>
       </c>
     </row>
@@ -8680,7 +8684,7 @@
       <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="28">
         <v>200</v>
       </c>
     </row>
@@ -8688,19 +8692,19 @@
       <c r="A8" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="29">
         <v>0.5</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <v>0.65</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <v>0.8</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <v>0.925</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="29">
         <v>1</v>
       </c>
     </row>
@@ -8711,16 +8715,16 @@
       <c r="D10" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E10" s="29">
+      <c r="E10" s="30">
         <v>0.3</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <v>0.23076923076923078</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <v>0.15625</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <v>0.08108108108108109</v>
       </c>
     </row>
@@ -8759,52 +8763,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>201</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>1050000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>1405950</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>1782312</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>2122622</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>2363569</v>
       </c>
     </row>
@@ -8812,19 +8816,19 @@
       <c r="A6" s="11" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="30">
+      <c r="B6" s="31">
         <v>35000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>46865</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>59410</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>70754</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>78786</v>
       </c>
     </row>
@@ -8832,19 +8836,19 @@
       <c r="A7" s="11" t="s">
         <v>203</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="31">
         <v>105000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>140595</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>178231</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>212262</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>236357</v>
       </c>
     </row>
@@ -8852,19 +8856,19 @@
       <c r="A8" s="11" t="s">
         <v>204</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>870000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>1164930</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>1476773</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>1758744</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>1958385</v>
       </c>
     </row>
@@ -8872,19 +8876,19 @@
       <c r="A9" s="11" t="s">
         <v>205</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="31">
         <v>50000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>51500</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>53045</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>54636</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>56275</v>
       </c>
     </row>
@@ -8892,19 +8896,19 @@
       <c r="A10" s="11" t="s">
         <v>206</v>
       </c>
-      <c r="B10" s="30">
+      <c r="B10" s="31">
         <v>25000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>25750</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>26523</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>27318</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>28138</v>
       </c>
     </row>
@@ -8912,43 +8916,43 @@
       <c r="A11" s="11" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>50000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>66950</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>84872</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>101077</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>112551</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="18" t="s">
         <v>208</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="32">
         <f>SUM(B5:B11)</f>
         <v>1975000</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>SUM(C5:C11)</f>
         <v>2621350</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>SUM(D5:D11)</f>
         <v>3304704</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>SUM(E5:E11)</f>
         <v>3922890</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>SUM(F5:F11)</f>
         <v>4361347</v>
       </c>
@@ -8993,25 +8997,25 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>130</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>209</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>132</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="19" t="s">
+      <c r="G3" s="20" t="s">
         <v>210</v>
       </c>
     </row>
@@ -9022,19 +9026,19 @@
       <c r="B4" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C4" s="32">
+      <c r="C4" s="33">
         <v>1</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="31">
         <v>95000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="30">
         <v>0.25</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G4" s="33">
+      <c r="G4" s="34">
         <v>126018</v>
       </c>
     </row>
@@ -9045,19 +9049,19 @@
       <c r="B5" s="11" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="32">
+      <c r="C5" s="33">
         <v>1</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>75000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="30">
         <v>0.25</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G5" s="33">
+      <c r="G5" s="34">
         <v>99488</v>
       </c>
     </row>
@@ -9068,19 +9072,19 @@
       <c r="B6" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C6" s="32">
+      <c r="C6" s="33">
         <v>6</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>48000</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="30">
         <v>0.25</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G6" s="33">
+      <c r="G6" s="34">
         <v>382032</v>
       </c>
     </row>
@@ -9091,19 +9095,19 @@
       <c r="B7" s="11" t="s">
         <v>139</v>
       </c>
-      <c r="C7" s="32">
+      <c r="C7" s="33">
         <v>3</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>32000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>0.2</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G7" s="33">
+      <c r="G7" s="34">
         <v>122544</v>
       </c>
     </row>
@@ -9114,19 +9118,19 @@
       <c r="B8" s="11" t="s">
         <v>142</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>1</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>42000</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>0.25</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G8" s="33">
+      <c r="G8" s="34">
         <v>55713</v>
       </c>
     </row>
@@ -9137,50 +9141,50 @@
       <c r="B9" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="C9" s="32">
+      <c r="C9" s="33">
         <v>1</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>52000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>0.25</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>0.0765</v>
       </c>
-      <c r="G9" s="33">
+      <c r="G9" s="34">
         <v>68978</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="17" t="s">
+      <c r="A11" s="18" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="17"/>
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="19" t="s">
+      <c r="B12" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C12" s="19" t="s">
+      <c r="C12" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="D12" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="19" t="s">
+      <c r="E12" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="19" t="s">
+      <c r="F12" s="20" t="s">
         <v>105</v>
       </c>
     </row>
@@ -9188,19 +9192,19 @@
       <c r="A13" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="32">
         <v>854772</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <v>880415</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <v>906828</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <v>934032</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <v>962053</v>
       </c>
     </row>
@@ -9208,19 +9212,19 @@
       <c r="A14" s="11" t="s">
         <v>213</v>
       </c>
-      <c r="B14" s="29">
+      <c r="B14" s="30">
         <v>0.4327959493670886</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>0.3358632612966601</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>0.2744051364365971</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>0.23809805013927576</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>0.22058632258064514</v>
       </c>
     </row>
@@ -9228,19 +9232,19 @@
       <c r="A15" s="11" t="s">
         <v>214</v>
       </c>
-      <c r="B15" s="34">
+      <c r="B15" s="35">
         <v>7.7</v>
       </c>
-      <c r="C15" s="34">
+      <c r="C15" s="35">
         <v>10</v>
       </c>
-      <c r="D15" s="34">
+      <c r="D15" s="35">
         <v>12.3</v>
       </c>
-      <c r="E15" s="34">
+      <c r="E15" s="35">
         <v>14.2</v>
       </c>
-      <c r="F15" s="34">
+      <c r="F15" s="35">
         <v>15.4</v>
       </c>
     </row>
@@ -9279,52 +9283,52 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>101</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>153</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="17"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="B5" s="30">
+      <c r="B5" s="31">
         <v>60000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>80340</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>101846</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>121293</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>135061</v>
       </c>
     </row>
@@ -9332,54 +9336,54 @@
       <c r="A6" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="B6" s="35">
+      <c r="B6" s="36">
         <f>SUM(B5:B5)</f>
         <v>60000</v>
       </c>
-      <c r="C6" s="35">
+      <c r="C6" s="36">
         <f>SUM(C5:C5)</f>
         <v>80340</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="36">
         <f>SUM(D5:D5)</f>
         <v>101846</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="36">
         <f>SUM(E5:E5)</f>
         <v>121293</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="36">
         <f>SUM(F5:F5)</f>
         <v>135061</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="17" t="s">
+      <c r="A7" s="18" t="s">
         <v>154</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="18"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="18"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
         <v>218</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="31">
         <v>40000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>53560</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>67898</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>80862</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>90041</v>
       </c>
     </row>
@@ -9387,54 +9391,54 @@
       <c r="A9" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="B9" s="35">
+      <c r="B9" s="36">
         <f>SUM(B8:B8)</f>
         <v>40000</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="36">
         <f>SUM(C8:C8)</f>
         <v>53560</v>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="36">
         <f>SUM(D8:D8)</f>
         <v>67898</v>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="36">
         <f>SUM(E8:E8)</f>
         <v>80862</v>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="36">
         <f>SUM(F8:F8)</f>
         <v>90041</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="18" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="17"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17"/>
-      <c r="F10" s="17"/>
+      <c r="B10" s="18"/>
+      <c r="C10" s="18"/>
+      <c r="D10" s="18"/>
+      <c r="E10" s="18"/>
+      <c r="F10" s="18"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
         <v>220</v>
       </c>
-      <c r="B11" s="30">
+      <c r="B11" s="31">
         <v>102000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>105060</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>108212</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>111458</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>114802</v>
       </c>
     </row>
@@ -9442,19 +9446,19 @@
       <c r="A12" s="11" t="s">
         <v>221</v>
       </c>
-      <c r="B12" s="30">
+      <c r="B12" s="31">
         <v>14400</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>14832</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>15277</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>15735</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>16207</v>
       </c>
     </row>
@@ -9462,19 +9466,19 @@
       <c r="A13" s="11" t="s">
         <v>222</v>
       </c>
-      <c r="B13" s="30">
+      <c r="B13" s="31">
         <v>12000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>12360</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>12731</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>13113</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>13506</v>
       </c>
     </row>
@@ -9482,19 +9486,19 @@
       <c r="A14" s="11" t="s">
         <v>223</v>
       </c>
-      <c r="B14" s="30">
+      <c r="B14" s="31">
         <v>8000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>8240</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>8487</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>8742</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>9004</v>
       </c>
     </row>
@@ -9502,54 +9506,54 @@
       <c r="A15" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="B15" s="35">
+      <c r="B15" s="36">
         <f>SUM(B11:B14)</f>
         <v>136400</v>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="36">
         <f>SUM(C11:C14)</f>
         <v>140492</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="36">
         <f>SUM(D11:D14)</f>
         <v>144707</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="36">
         <f>SUM(E11:E14)</f>
         <v>149048</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="36">
         <f>SUM(F11:F14)</f>
         <v>153519</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>156</v>
       </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="17"/>
-      <c r="D16" s="17"/>
-      <c r="E16" s="17"/>
-      <c r="F16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+      <c r="F16" s="18"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>225</v>
       </c>
-      <c r="B17" s="30">
+      <c r="B17" s="31">
         <v>15000</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>15450</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>15914</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>16391</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>16883</v>
       </c>
     </row>
@@ -9557,19 +9561,19 @@
       <c r="A18" s="11" t="s">
         <v>226</v>
       </c>
-      <c r="B18" s="30">
+      <c r="B18" s="31">
         <v>8000</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>8240</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>8487</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>8742</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>9004</v>
       </c>
     </row>
@@ -9577,19 +9581,19 @@
       <c r="A19" s="11" t="s">
         <v>227</v>
       </c>
-      <c r="B19" s="30">
+      <c r="B19" s="31">
         <v>12000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>12360</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>12731</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>13113</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>13506</v>
       </c>
     </row>
@@ -9597,48 +9601,48 @@
       <c r="A20" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="36">
         <f>SUM(B17:B19)</f>
         <v>35000</v>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="36">
         <f>SUM(C17:C19)</f>
         <v>36050</v>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="36">
         <f>SUM(D17:D19)</f>
         <v>37132</v>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="36">
         <f>SUM(E17:E19)</f>
         <v>38245</v>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="36">
         <f>SUM(F17:F19)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>229</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <f>B6+B9+B15+B20</f>
         <v>271400</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <f>C6+C9+C15+C20</f>
         <v>310442</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <f>D6+D9+D15+D20</f>
         <v>351582</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <f>E6+E9+E15+E20</f>
         <v>389448</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <f>F6+F9+F15+F20</f>
         <v>418014</v>
       </c>
@@ -9679,22 +9683,22 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>160</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="20" t="s">
         <v>129</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="20" t="s">
         <v>161</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="20" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="20" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="20" t="s">
         <v>231</v>
       </c>
     </row>
@@ -9705,16 +9709,16 @@
       <c r="B4" s="11" t="s">
         <v>164</v>
       </c>
-      <c r="C4" s="21">
+      <c r="C4" s="22">
         <v>250000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="30">
         <v>0.065</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="28">
         <v>10</v>
       </c>
-      <c r="F4" s="33">
+      <c r="F4" s="34">
         <v>34064</v>
       </c>
     </row>
@@ -9725,16 +9729,16 @@
       <c r="B5" s="11" t="s">
         <v>232</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="22">
         <v>25000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>0</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="28">
         <v>0</v>
       </c>
-      <c r="F5" s="33">
+      <c r="F5" s="34">
         <v>25000</v>
       </c>
     </row>
@@ -9742,7 +9746,7 @@
       <c r="A7" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <v>34064</v>
       </c>
     </row>
@@ -9750,7 +9754,7 @@
       <c r="A8" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F8" s="35">
+      <c r="F8" s="36">
         <v>250000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="430">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -634,115 +634,124 @@
     <t>Tuition &amp; Funding Drivers</t>
   </si>
   <si>
-    <t>REVENUE BY LINE ITEM</t>
-  </si>
-  <si>
-    <t>Tuition (Tuition &amp; Fees)</t>
-  </si>
-  <si>
-    <t>Registration Fee (Tuition &amp; Fees)</t>
-  </si>
-  <si>
-    <t>Scholarship Discount (Tuition Offsets)</t>
-  </si>
-  <si>
-    <t>FL FTC Scholarship (School Choice)</t>
-  </si>
-  <si>
-    <t>Foundation Grant (Philanthropy)</t>
-  </si>
-  <si>
-    <t>Annual Fund (Philanthropy)</t>
-  </si>
-  <si>
-    <t>After-School Programs (Other Revenue)</t>
+    <t>TUITION &amp; FEES</t>
+  </si>
+  <si>
+    <t>Total Tuition &amp; Fees</t>
+  </si>
+  <si>
+    <t>TUITION OFFSETS</t>
+  </si>
+  <si>
+    <t>Total Tuition Offsets</t>
+  </si>
+  <si>
+    <t>SCHOOL CHOICE</t>
+  </si>
+  <si>
+    <t>Total School Choice</t>
+  </si>
+  <si>
+    <t>PHILANTHROPY</t>
+  </si>
+  <si>
+    <t>Total Philanthropy</t>
+  </si>
+  <si>
+    <t>OTHER REVENUE</t>
+  </si>
+  <si>
+    <t>Total Other Revenue</t>
+  </si>
+  <si>
+    <t>GRAND TOTAL REVENUE</t>
+  </si>
+  <si>
+    <t>Base Rate</t>
+  </si>
+  <si>
+    <t>Loaded Cost</t>
+  </si>
+  <si>
+    <t>5-YEAR TOTAL PERSONNEL COST</t>
+  </si>
+  <si>
+    <t>Total Personnel</t>
+  </si>
+  <si>
+    <t>Personnel as % of Revenue</t>
+  </si>
+  <si>
+    <t>Students per FTE</t>
+  </si>
+  <si>
+    <t>Operating Expense Drivers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Curriculum</t>
+  </si>
+  <si>
+    <t>Total Instructional / Program</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Technology</t>
+  </si>
+  <si>
+    <t>Total Technology</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Utilities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Insurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Maintenance</t>
+  </si>
+  <si>
+    <t>Total Occupancy / Facility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Marketing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Professional Development</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Accounting &amp; Legal</t>
+  </si>
+  <si>
+    <t>Total Administrative / General</t>
+  </si>
+  <si>
+    <t>TOTAL OPERATING EXPENSES</t>
+  </si>
+  <si>
+    <t>Capital Stack &amp; Loan Terms</t>
+  </si>
+  <si>
+    <t>Annual Payment</t>
+  </si>
+  <si>
+    <t>Capital Expense</t>
+  </si>
+  <si>
+    <t>Total Annual Debt Service</t>
+  </si>
+  <si>
+    <t>Total Loan Principal</t>
+  </si>
+  <si>
+    <t>Enrollment &amp; Tuition Forecast</t>
+  </si>
+  <si>
+    <t>REVENUE FORECAST</t>
   </si>
   <si>
     <t>TOTAL REVENUE</t>
-  </si>
-  <si>
-    <t>Base Rate</t>
-  </si>
-  <si>
-    <t>Loaded Cost</t>
-  </si>
-  <si>
-    <t>5-YEAR TOTAL PERSONNEL COST</t>
-  </si>
-  <si>
-    <t>Total Personnel</t>
-  </si>
-  <si>
-    <t>Personnel as % of Revenue</t>
-  </si>
-  <si>
-    <t>Students per FTE</t>
-  </si>
-  <si>
-    <t>Operating Expense Drivers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Curriculum</t>
-  </si>
-  <si>
-    <t>Total Instructional / Program</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Technology</t>
-  </si>
-  <si>
-    <t>Total Technology</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Rent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Utilities</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Insurance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Maintenance</t>
-  </si>
-  <si>
-    <t>Total Occupancy / Facility</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Marketing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Professional Development</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Accounting &amp; Legal</t>
-  </si>
-  <si>
-    <t>Total Administrative / General</t>
-  </si>
-  <si>
-    <t>TOTAL OPERATING EXPENSES</t>
-  </si>
-  <si>
-    <t>Capital Stack &amp; Loan Terms</t>
-  </si>
-  <si>
-    <t>Annual Payment</t>
-  </si>
-  <si>
-    <t>Capital Expense</t>
-  </si>
-  <si>
-    <t>Total Annual Debt Service</t>
-  </si>
-  <si>
-    <t>Total Loan Principal</t>
-  </si>
-  <si>
-    <t>Enrollment &amp; Tuition Forecast</t>
-  </si>
-  <si>
-    <t>REVENUE FORECAST</t>
   </si>
   <si>
     <t>Revenue per Student</t>
@@ -1557,15 +1566,15 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2316,7 +2325,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2366,7 +2375,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2378,19 +2387,19 @@
       <c r="A7" s="11" t="s">
         <v>113</v>
       </c>
-      <c r="B7" s="31">
+      <c r="B7" s="30">
         <v>1050000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>1405950</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>1782312</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>2122622</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>2363569</v>
       </c>
     </row>
@@ -2398,19 +2407,19 @@
       <c r="A8" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B8" s="31">
+      <c r="B8" s="30">
         <v>35000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>46865</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>59410</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>70754</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>78786</v>
       </c>
     </row>
@@ -2418,19 +2427,19 @@
       <c r="A9" s="11" t="s">
         <v>117</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B9" s="30">
         <v>105000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>140595</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>178231</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>212262</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>236357</v>
       </c>
     </row>
@@ -2438,19 +2447,19 @@
       <c r="A10" s="11" t="s">
         <v>119</v>
       </c>
-      <c r="B10" s="31">
+      <c r="B10" s="30">
         <v>870000</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>1164930</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <v>1476773</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>1758744</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <v>1958385</v>
       </c>
     </row>
@@ -2458,19 +2467,19 @@
       <c r="A11" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B11" s="30">
         <v>50000</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>51500</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <v>53045</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <v>54636</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <v>56275</v>
       </c>
     </row>
@@ -2478,19 +2487,19 @@
       <c r="A12" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B12" s="31">
+      <c r="B12" s="30">
         <v>25000</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <v>25750</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="30">
         <v>26523</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <v>27318</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>28138</v>
       </c>
     </row>
@@ -2498,25 +2507,25 @@
       <c r="A13" s="11" t="s">
         <v>125</v>
       </c>
-      <c r="B13" s="31">
+      <c r="B13" s="30">
         <v>50000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>66950</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>84872</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>101077</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>112551</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>208</v>
+        <v>239</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B7:B13)</f>
@@ -2541,21 +2550,21 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B16" s="31">
+        <v>240</v>
+      </c>
+      <c r="B16" s="30">
         <v>19750</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="30">
         <v>20164</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>20654</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>21205</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>21807</v>
       </c>
     </row>
@@ -2585,7 +2594,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2625,65 +2634,65 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B5" s="31">
+        <v>242</v>
+      </c>
+      <c r="B5" s="30">
         <v>382032</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>393493</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>405298</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>417457</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>429980</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B6" s="31">
+        <v>243</v>
+      </c>
+      <c r="B6" s="30">
         <v>122544</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>126220</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>130007</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>133907</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>137924</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="B7" s="36">
+        <v>244</v>
+      </c>
+      <c r="B7" s="31">
         <f>SUM(B5:B6)</f>
         <v>504576</v>
       </c>
-      <c r="C7" s="36">
+      <c r="C7" s="31">
         <f>SUM(C5:C6)</f>
         <v>519713</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D7" s="31">
         <f>SUM(D5:D6)</f>
         <v>535305</v>
       </c>
-      <c r="E7" s="36">
+      <c r="E7" s="31">
         <f>SUM(E5:E6)</f>
         <v>551364</v>
       </c>
-      <c r="F7" s="36">
+      <c r="F7" s="31">
         <f>SUM(F5:F6)</f>
         <v>567905</v>
       </c>
@@ -2700,65 +2709,65 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B9" s="31">
+        <v>245</v>
+      </c>
+      <c r="B9" s="30">
         <v>126018</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>129798</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>133692</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>137703</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>141834</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B10" s="31">
+        <v>246</v>
+      </c>
+      <c r="B10" s="30">
         <v>99488</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>102472</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <v>105546</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>108713</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <v>111974</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="B11" s="36">
+        <v>247</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B9:B10)</f>
         <v>225505</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="31">
         <f>SUM(C9:C10)</f>
         <v>232270</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="31">
         <f>SUM(D9:D10)</f>
         <v>239238</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="31">
         <f>SUM(E9:E10)</f>
         <v>246415</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="31">
         <f>SUM(F9:F10)</f>
         <v>253808</v>
       </c>
@@ -2775,45 +2784,45 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="B13" s="31">
+        <v>248</v>
+      </c>
+      <c r="B13" s="30">
         <v>68978</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>71047</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>73179</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>75374</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>77635</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>246</v>
-      </c>
-      <c r="B14" s="36">
+        <v>249</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B13:B13)</f>
         <v>68978</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="31">
         <f>SUM(C13:C13)</f>
         <v>71047</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="31">
         <f>SUM(D13:D13)</f>
         <v>73179</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="31">
         <f>SUM(E13:E13)</f>
         <v>75374</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="31">
         <f>SUM(F13:F13)</f>
         <v>77635</v>
       </c>
@@ -2830,52 +2839,52 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="B16" s="31">
+        <v>250</v>
+      </c>
+      <c r="B16" s="30">
         <v>55713</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="30">
         <v>57384</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>59106</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>60879</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>62705</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>248</v>
-      </c>
-      <c r="B17" s="36">
+        <v>251</v>
+      </c>
+      <c r="B17" s="31">
         <f>SUM(B16:B16)</f>
         <v>55713</v>
       </c>
-      <c r="C17" s="36">
+      <c r="C17" s="31">
         <f>SUM(C16:C16)</f>
         <v>57384</v>
       </c>
-      <c r="D17" s="36">
+      <c r="D17" s="31">
         <f>SUM(D16:D16)</f>
         <v>59106</v>
       </c>
-      <c r="E17" s="36">
+      <c r="E17" s="31">
         <f>SUM(E16:E16)</f>
         <v>60879</v>
       </c>
-      <c r="F17" s="36">
+      <c r="F17" s="31">
         <f>SUM(F16:F16)</f>
         <v>62705</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B19" s="32">
         <f>B7+B11+B14+B17</f>
@@ -2924,7 +2933,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2954,7 +2963,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -2964,172 +2973,172 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>252</v>
-      </c>
-      <c r="B5" s="31">
+        <v>255</v>
+      </c>
+      <c r="B5" s="30">
         <v>1050000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>1405950</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>1782312</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>2122622</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>2363569</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>253</v>
-      </c>
-      <c r="B6" s="31">
+        <v>256</v>
+      </c>
+      <c r="B6" s="30">
         <v>35000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>46865</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>59410</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>70754</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>78786</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>254</v>
-      </c>
-      <c r="B7" s="31">
+        <v>257</v>
+      </c>
+      <c r="B7" s="30">
         <v>105000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>140595</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>178231</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>212262</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>236357</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B8" s="31">
+        <v>258</v>
+      </c>
+      <c r="B8" s="30">
         <v>870000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>1164930</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>1476773</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>1758744</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>1958385</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B9" s="31">
+        <v>259</v>
+      </c>
+      <c r="B9" s="30">
         <v>50000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>51500</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>53045</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>54636</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>56275</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B10" s="31">
+        <v>260</v>
+      </c>
+      <c r="B10" s="30">
         <v>25000</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <v>25750</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <v>26523</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <v>27318</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <v>28138</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B11" s="31">
+        <v>261</v>
+      </c>
+      <c r="B11" s="30">
         <v>50000</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>66950</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <v>84872</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <v>101077</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <v>112551</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="B12" s="36">
+        <v>262</v>
+      </c>
+      <c r="B12" s="31">
         <f>SUM(B5:B11)</f>
         <v>1975000</v>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="31">
         <f>SUM(C5:C11)</f>
         <v>2621350</v>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="31">
         <f>SUM(D5:D11)</f>
         <v>3304704</v>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="31">
         <f>SUM(E5:E11)</f>
         <v>3922890</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="31">
         <f>SUM(F5:F11)</f>
         <v>4361347</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="18" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -3139,145 +3148,145 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B15" s="31">
+        <v>245</v>
+      </c>
+      <c r="B15" s="30">
         <v>126018</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="30">
         <v>129798</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="30">
         <v>133692</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>137703</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>141834</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B16" s="31">
+        <v>246</v>
+      </c>
+      <c r="B16" s="30">
         <v>99488</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="30">
         <v>102472</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>105546</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>108713</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>111974</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>239</v>
-      </c>
-      <c r="B17" s="31">
+        <v>242</v>
+      </c>
+      <c r="B17" s="30">
         <v>382032</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>393493</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <v>405298</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>417457</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>429980</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B18" s="31">
+        <v>243</v>
+      </c>
+      <c r="B18" s="30">
         <v>122544</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="30">
         <v>126220</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="30">
         <v>130007</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <v>133907</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <v>137924</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>247</v>
-      </c>
-      <c r="B19" s="31">
+        <v>250</v>
+      </c>
+      <c r="B19" s="30">
         <v>55713</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>57384</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="30">
         <v>59106</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="30">
         <v>60879</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="30">
         <v>62705</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="B20" s="31">
+        <v>248</v>
+      </c>
+      <c r="B20" s="30">
         <v>68978</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="30">
         <v>71047</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="30">
         <v>73179</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="30">
         <v>75374</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <v>77635</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="B21" s="36">
+        <v>214</v>
+      </c>
+      <c r="B21" s="31">
         <f>SUM(B15:B20)</f>
         <v>854772</v>
       </c>
-      <c r="C21" s="36">
+      <c r="C21" s="31">
         <f>SUM(C15:C20)</f>
         <v>880415</v>
       </c>
-      <c r="D21" s="36">
+      <c r="D21" s="31">
         <f>SUM(D15:D20)</f>
         <v>906828</v>
       </c>
-      <c r="E21" s="36">
+      <c r="E21" s="31">
         <f>SUM(E15:E20)</f>
         <v>934032</v>
       </c>
-      <c r="F21" s="36">
+      <c r="F21" s="31">
         <f>SUM(F15:F20)</f>
         <v>962053</v>
       </c>
@@ -3299,21 +3308,21 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B25" s="31">
+        <v>264</v>
+      </c>
+      <c r="B25" s="30">
         <v>60000</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="30">
         <v>80340</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="30">
         <v>101846</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="30">
         <v>121293</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="30">
         <v>135061</v>
       </c>
     </row>
@@ -3324,21 +3333,21 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>262</v>
-      </c>
-      <c r="B27" s="31">
+        <v>265</v>
+      </c>
+      <c r="B27" s="30">
         <v>40000</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="30">
         <v>53560</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="30">
         <v>67898</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="30">
         <v>80862</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="30">
         <v>90041</v>
       </c>
     </row>
@@ -3349,105 +3358,105 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>263</v>
-      </c>
-      <c r="B29" s="31">
+        <v>266</v>
+      </c>
+      <c r="B29" s="30">
         <v>102000</v>
       </c>
-      <c r="C29" s="31">
+      <c r="C29" s="30">
         <v>105060</v>
       </c>
-      <c r="D29" s="31">
+      <c r="D29" s="30">
         <v>108212</v>
       </c>
-      <c r="E29" s="31">
+      <c r="E29" s="30">
         <v>111458</v>
       </c>
-      <c r="F29" s="31">
+      <c r="F29" s="30">
         <v>114802</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="B30" s="31">
+        <v>267</v>
+      </c>
+      <c r="B30" s="30">
         <v>14400</v>
       </c>
-      <c r="C30" s="31">
+      <c r="C30" s="30">
         <v>14832</v>
       </c>
-      <c r="D30" s="31">
+      <c r="D30" s="30">
         <v>15277</v>
       </c>
-      <c r="E30" s="31">
+      <c r="E30" s="30">
         <v>15735</v>
       </c>
-      <c r="F30" s="31">
+      <c r="F30" s="30">
         <v>16207</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B31" s="31">
+        <v>268</v>
+      </c>
+      <c r="B31" s="30">
         <v>12000</v>
       </c>
-      <c r="C31" s="31">
+      <c r="C31" s="30">
         <v>12360</v>
       </c>
-      <c r="D31" s="31">
+      <c r="D31" s="30">
         <v>12731</v>
       </c>
-      <c r="E31" s="31">
+      <c r="E31" s="30">
         <v>13113</v>
       </c>
-      <c r="F31" s="31">
+      <c r="F31" s="30">
         <v>13506</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="B32" s="31">
+        <v>269</v>
+      </c>
+      <c r="B32" s="30">
         <v>8000</v>
       </c>
-      <c r="C32" s="31">
+      <c r="C32" s="30">
         <v>8240</v>
       </c>
-      <c r="D32" s="31">
+      <c r="D32" s="30">
         <v>8487</v>
       </c>
-      <c r="E32" s="31">
+      <c r="E32" s="30">
         <v>8742</v>
       </c>
-      <c r="F32" s="31">
+      <c r="F32" s="30">
         <v>9004</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>267</v>
-      </c>
-      <c r="B33" s="36">
+        <v>270</v>
+      </c>
+      <c r="B33" s="31">
         <f>SUM(B29:B32)</f>
         <v>136400</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="31">
         <f>SUM(C29:C32)</f>
         <v>140492</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="31">
         <f>SUM(D29:D32)</f>
         <v>144707</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="31">
         <f>SUM(E29:E32)</f>
         <v>149048</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="31">
         <f>SUM(F29:F32)</f>
         <v>153519</v>
       </c>
@@ -3459,117 +3468,117 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="B35" s="31">
+        <v>271</v>
+      </c>
+      <c r="B35" s="30">
         <v>15000</v>
       </c>
-      <c r="C35" s="31">
+      <c r="C35" s="30">
         <v>15450</v>
       </c>
-      <c r="D35" s="31">
+      <c r="D35" s="30">
         <v>15914</v>
       </c>
-      <c r="E35" s="31">
+      <c r="E35" s="30">
         <v>16391</v>
       </c>
-      <c r="F35" s="31">
+      <c r="F35" s="30">
         <v>16883</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B36" s="31">
+        <v>272</v>
+      </c>
+      <c r="B36" s="30">
         <v>8000</v>
       </c>
-      <c r="C36" s="31">
+      <c r="C36" s="30">
         <v>8240</v>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="30">
         <v>8487</v>
       </c>
-      <c r="E36" s="31">
+      <c r="E36" s="30">
         <v>8742</v>
       </c>
-      <c r="F36" s="31">
+      <c r="F36" s="30">
         <v>9004</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>270</v>
-      </c>
-      <c r="B37" s="31">
+        <v>273</v>
+      </c>
+      <c r="B37" s="30">
         <v>12000</v>
       </c>
-      <c r="C37" s="31">
+      <c r="C37" s="30">
         <v>12360</v>
       </c>
-      <c r="D37" s="31">
+      <c r="D37" s="30">
         <v>12731</v>
       </c>
-      <c r="E37" s="31">
+      <c r="E37" s="30">
         <v>13113</v>
       </c>
-      <c r="F37" s="31">
+      <c r="F37" s="30">
         <v>13506</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>271</v>
-      </c>
-      <c r="B38" s="36">
+        <v>274</v>
+      </c>
+      <c r="B38" s="31">
         <f>SUM(B35:B37)</f>
         <v>35000</v>
       </c>
-      <c r="C38" s="36">
+      <c r="C38" s="31">
         <f>SUM(C35:C37)</f>
         <v>36050</v>
       </c>
-      <c r="D38" s="36">
+      <c r="D38" s="31">
         <f>SUM(D35:D37)</f>
         <v>37132</v>
       </c>
-      <c r="E38" s="36">
+      <c r="E38" s="31">
         <f>SUM(E35:E37)</f>
         <v>38245</v>
       </c>
-      <c r="F38" s="36">
+      <c r="F38" s="31">
         <f>SUM(F35:F37)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>272</v>
-      </c>
-      <c r="B39" s="36">
+        <v>275</v>
+      </c>
+      <c r="B39" s="31">
         <f>B25+B27+B33+B38</f>
         <v>271400</v>
       </c>
-      <c r="C39" s="36">
+      <c r="C39" s="31">
         <f>C25+C27+C33+C38</f>
         <v>310442</v>
       </c>
-      <c r="D39" s="36">
+      <c r="D39" s="31">
         <f>D25+D27+D33+D38</f>
         <v>351582</v>
       </c>
-      <c r="E39" s="36">
+      <c r="E39" s="31">
         <f>E25+E27+E33+E38</f>
         <v>389448</v>
       </c>
-      <c r="F39" s="36">
+      <c r="F39" s="31">
         <f>F25+F27+F33+F38</f>
         <v>418014</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="18" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B41" s="18"/>
       <c r="C41" s="18"/>
@@ -3579,65 +3588,65 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>274</v>
-      </c>
-      <c r="B42" s="31">
+        <v>277</v>
+      </c>
+      <c r="B42" s="30">
         <v>34064</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="30">
         <v>34064</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="30">
         <v>34064</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="30">
         <v>34064</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="30">
         <v>34064</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="B43" s="31">
+        <v>278</v>
+      </c>
+      <c r="B43" s="30">
         <v>25000</v>
       </c>
-      <c r="C43" s="31">
+      <c r="C43" s="30">
         <v>10000</v>
       </c>
-      <c r="D43" s="31">
+      <c r="D43" s="30">
         <v>10000</v>
       </c>
-      <c r="E43" s="31">
+      <c r="E43" s="30">
         <v>5000</v>
       </c>
-      <c r="F43" s="31">
+      <c r="F43" s="30">
         <v>5000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>276</v>
-      </c>
-      <c r="B44" s="36">
+        <v>279</v>
+      </c>
+      <c r="B44" s="31">
         <f>SUM(B42:B43)</f>
         <v>59064</v>
       </c>
-      <c r="C44" s="36">
+      <c r="C44" s="31">
         <f>SUM(C42:C43)</f>
         <v>44064</v>
       </c>
-      <c r="D44" s="36">
+      <c r="D44" s="31">
         <f>SUM(D42:D43)</f>
         <v>44064</v>
       </c>
-      <c r="E44" s="36">
+      <c r="E44" s="31">
         <f>SUM(E42:E43)</f>
         <v>39064</v>
       </c>
-      <c r="F44" s="36">
+      <c r="F44" s="31">
         <f>SUM(F42:F43)</f>
         <v>39064</v>
       </c>
@@ -3668,7 +3677,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3698,7 +3707,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B4" s="34">
         <f>'Budget Detail'!B12</f>
@@ -3723,7 +3732,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B5" s="34">
         <f>'Budget Detail'!B21</f>
@@ -3748,7 +3757,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
@@ -3773,7 +3782,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
@@ -3798,32 +3807,32 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="B8" s="36">
+        <v>282</v>
+      </c>
+      <c r="B8" s="31">
         <f>SUM(B5:B7)</f>
         <v>1185236</v>
       </c>
-      <c r="C8" s="36">
+      <c r="C8" s="31">
         <f>SUM(C5:C7)</f>
         <v>1234922</v>
       </c>
-      <c r="D8" s="36">
+      <c r="D8" s="31">
         <f>SUM(D5:D7)</f>
         <v>1302474</v>
       </c>
-      <c r="E8" s="36">
+      <c r="E8" s="31">
         <f>SUM(E5:E7)</f>
         <v>1362545</v>
       </c>
-      <c r="F8" s="36">
+      <c r="F8" s="31">
         <f>SUM(F5:F7)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
@@ -3833,7 +3842,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B11" s="32">
         <f>B4-B8</f>
@@ -3858,86 +3867,86 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B12" s="30">
+        <v>285</v>
+      </c>
+      <c r="B12" s="29">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.39988031</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="29">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.52889864</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="29">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.60587258</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="29">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.65266812</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="29">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.67461156</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>283</v>
-      </c>
-      <c r="B13" s="31">
+        <v>286</v>
+      </c>
+      <c r="B13" s="30">
         <v>789764</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>2176192</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>4178421</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>6738766</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>9680981</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B14" s="31">
+        <v>240</v>
+      </c>
+      <c r="B14" s="30">
         <v>19750</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="30">
         <v>20164</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <v>20654</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <v>21205</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>21807</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="B15" s="31">
+        <v>287</v>
+      </c>
+      <c r="B15" s="30">
         <v>11852</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="30">
         <v>9499</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="30">
         <v>8140</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>7365</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>7096</v>
       </c>
     </row>
@@ -3968,7 +3977,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3989,48 +3998,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="20" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="C2" s="20" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D2" s="20" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="E2" s="20" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="G2" s="20" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="H2" s="20" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="I2" s="20" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="J2" s="20" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K2" s="20" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="L2" s="20" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="M2" s="20" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="N2" s="20" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -4048,52 +4057,52 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>259</v>
-      </c>
-      <c r="B4" s="36">
+        <v>262</v>
+      </c>
+      <c r="B4" s="31">
         <v>85833</v>
       </c>
-      <c r="C4" s="36">
+      <c r="C4" s="31">
         <v>180333</v>
       </c>
-      <c r="D4" s="36">
+      <c r="D4" s="31">
         <v>180333</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="31">
         <v>180333</v>
       </c>
-      <c r="F4" s="36">
+      <c r="F4" s="31">
         <v>180333</v>
       </c>
-      <c r="G4" s="36">
+      <c r="G4" s="31">
         <v>180333</v>
       </c>
-      <c r="H4" s="36">
+      <c r="H4" s="31">
         <v>180333</v>
       </c>
-      <c r="I4" s="36">
+      <c r="I4" s="31">
         <v>180333</v>
       </c>
-      <c r="J4" s="36">
+      <c r="J4" s="31">
         <v>180333</v>
       </c>
-      <c r="K4" s="36">
+      <c r="K4" s="31">
         <v>180333</v>
       </c>
-      <c r="L4" s="36">
+      <c r="L4" s="31">
         <v>180333</v>
       </c>
-      <c r="M4" s="36">
+      <c r="M4" s="31">
         <v>85833</v>
       </c>
-      <c r="N4" s="36">
+      <c r="N4" s="31">
         <f>SUM(B4:M4)</f>
         <v>1974996</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="18" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -4111,142 +4120,142 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="B7" s="31">
+        <v>303</v>
+      </c>
+      <c r="B7" s="30">
         <v>71231</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>71231</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>71231</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>71231</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>71231</v>
       </c>
-      <c r="G7" s="31">
+      <c r="G7" s="30">
         <v>71231</v>
       </c>
-      <c r="H7" s="31">
+      <c r="H7" s="30">
         <v>71231</v>
       </c>
-      <c r="I7" s="31">
+      <c r="I7" s="30">
         <v>71231</v>
       </c>
-      <c r="J7" s="31">
+      <c r="J7" s="30">
         <v>71231</v>
       </c>
-      <c r="K7" s="31">
+      <c r="K7" s="30">
         <v>71231</v>
       </c>
-      <c r="L7" s="31">
+      <c r="L7" s="30">
         <v>71231</v>
       </c>
-      <c r="M7" s="31">
+      <c r="M7" s="30">
         <v>71231</v>
       </c>
-      <c r="N7" s="31">
+      <c r="N7" s="30">
         <f>SUM(B7:M7)</f>
         <v>854772</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B8" s="31">
+        <v>304</v>
+      </c>
+      <c r="B8" s="30">
         <v>22617</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>22617</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>22617</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>22617</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>22617</v>
       </c>
-      <c r="G8" s="31">
+      <c r="G8" s="30">
         <v>22617</v>
       </c>
-      <c r="H8" s="31">
+      <c r="H8" s="30">
         <v>22617</v>
       </c>
-      <c r="I8" s="31">
+      <c r="I8" s="30">
         <v>22617</v>
       </c>
-      <c r="J8" s="31">
+      <c r="J8" s="30">
         <v>22617</v>
       </c>
-      <c r="K8" s="31">
+      <c r="K8" s="30">
         <v>22617</v>
       </c>
-      <c r="L8" s="31">
+      <c r="L8" s="30">
         <v>22617</v>
       </c>
-      <c r="M8" s="31">
+      <c r="M8" s="30">
         <v>22617</v>
       </c>
-      <c r="N8" s="31">
+      <c r="N8" s="30">
         <f>SUM(B8:M8)</f>
         <v>271400</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="B9" s="31">
+        <v>305</v>
+      </c>
+      <c r="B9" s="30">
         <v>4922</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>4922</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>4922</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>4922</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>4922</v>
       </c>
-      <c r="G9" s="31">
+      <c r="G9" s="30">
         <v>4922</v>
       </c>
-      <c r="H9" s="31">
+      <c r="H9" s="30">
         <v>4922</v>
       </c>
-      <c r="I9" s="31">
+      <c r="I9" s="30">
         <v>4922</v>
       </c>
-      <c r="J9" s="31">
+      <c r="J9" s="30">
         <v>4922</v>
       </c>
-      <c r="K9" s="31">
+      <c r="K9" s="30">
         <v>4922</v>
       </c>
-      <c r="L9" s="31">
+      <c r="L9" s="30">
         <v>4922</v>
       </c>
-      <c r="M9" s="31">
+      <c r="M9" s="30">
         <v>4922</v>
       </c>
-      <c r="N9" s="31">
+      <c r="N9" s="30">
         <f>SUM(B9:M9)</f>
         <v>59064</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -4264,7 +4273,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
@@ -4321,7 +4330,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
@@ -4378,7 +4387,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
@@ -4435,7 +4444,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -4450,7 +4459,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
@@ -4459,9 +4468,9 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>308</v>
-      </c>
-      <c r="B19" s="31">
+        <v>311</v>
+      </c>
+      <c r="B19" s="30">
         <f>MIN(B14:M14)</f>
         <v>62063</v>
       </c>
@@ -4492,7 +4501,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4522,7 +4531,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4532,27 +4541,27 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="B5" s="36">
+        <v>262</v>
+      </c>
+      <c r="B5" s="31">
         <v>1975000</v>
       </c>
-      <c r="C5" s="36">
+      <c r="C5" s="31">
         <v>2621350</v>
       </c>
-      <c r="D5" s="36">
+      <c r="D5" s="31">
         <v>3304704</v>
       </c>
-      <c r="E5" s="36">
+      <c r="E5" s="31">
         <v>3922890</v>
       </c>
-      <c r="F5" s="36">
+      <c r="F5" s="31">
         <v>4361347</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="18" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
@@ -4562,7 +4571,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="B8" s="34">
         <v>854772</v>
@@ -4582,7 +4591,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B9" s="34">
         <v>271400</v>
@@ -4602,7 +4611,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B10" s="34">
         <v>59064</v>
@@ -4622,32 +4631,32 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>279</v>
-      </c>
-      <c r="B11" s="36">
+        <v>282</v>
+      </c>
+      <c r="B11" s="31">
         <f>SUM(B8:B10)</f>
         <v>1185236</v>
       </c>
-      <c r="C11" s="36">
+      <c r="C11" s="31">
         <f>SUM(C8:C10)</f>
         <v>1234922</v>
       </c>
-      <c r="D11" s="36">
+      <c r="D11" s="31">
         <f>SUM(D8:D10)</f>
         <v>1302474</v>
       </c>
-      <c r="E11" s="36">
+      <c r="E11" s="31">
         <f>SUM(E8:E10)</f>
         <v>1362545</v>
       </c>
-      <c r="F11" s="36">
+      <c r="F11" s="31">
         <f>SUM(F8:F10)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -4657,7 +4666,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B14" s="32">
         <f>B5-B11</f>
@@ -4682,25 +4691,25 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B15" s="30">
+        <v>285</v>
+      </c>
+      <c r="B15" s="29">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.39988031</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="29">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.52889864</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="29">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.60587258</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="29">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.65266812</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="29">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.67461156</v>
       </c>
@@ -4761,7 +4770,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -4771,19 +4780,19 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="B5" s="41" t="s">
         <v>161</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -4799,14 +4808,14 @@
       <c r="D6" s="19">
         <v>10</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>34064</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="18" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B8" s="18"/>
       <c r="C8" s="18"/>
@@ -4816,82 +4825,82 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>317</v>
-      </c>
-      <c r="B9" s="31">
+        <v>320</v>
+      </c>
+      <c r="B9" s="30">
         <f>B6</f>
         <v>250000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <f>B13</f>
         <v>231645</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <f>C13</f>
         <v>212061</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <f>D13</f>
         <v>191165</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <f>E13</f>
         <v>168870</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>318</v>
-      </c>
-      <c r="B10" s="31">
+        <v>321</v>
+      </c>
+      <c r="B10" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>15710</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="30">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>14480</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="30">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>13169</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="30">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>11769</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="30">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>10276</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>319</v>
-      </c>
-      <c r="B11" s="31">
+        <v>322</v>
+      </c>
+      <c r="B11" s="30">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>18355</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>19584</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>20896</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>22295</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>23788</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -4916,7 +4925,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -4965,7 +4974,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4995,7 +5004,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5005,7 +5014,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B5" s="43">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -5030,92 +5039,92 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>325</v>
-      </c>
-      <c r="B6" s="31">
+        <v>328</v>
+      </c>
+      <c r="B6" s="30">
         <v>12000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>12000</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>12000</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>12000</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>12000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>326</v>
-      </c>
-      <c r="B7" s="31">
+        <v>329</v>
+      </c>
+      <c r="B7" s="30">
         <v>180000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>180000</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>180000</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>180000</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>180000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>327</v>
-      </c>
-      <c r="B8" s="31">
+        <v>330</v>
+      </c>
+      <c r="B8" s="30">
         <v>5000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>5000</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>5000</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>5000</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>5000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>328</v>
-      </c>
-      <c r="B9" s="36">
+        <v>331</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B5:B8)</f>
         <v>1061756</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="31">
         <f>SUM(C5:C8)</f>
         <v>2448184</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="31">
         <f>SUM(D5:D8)</f>
         <v>4450414</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="31">
         <f>SUM(E5:E8)</f>
         <v>7010759</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="31">
         <f>SUM(F5:F8)</f>
         <v>9952974</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -5125,77 +5134,77 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B12" s="31">
+        <v>333</v>
+      </c>
+      <c r="B12" s="30">
         <v>8000</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <v>8000</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="30">
         <v>8000</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <v>8000</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>8000</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B13" s="31">
+        <v>334</v>
+      </c>
+      <c r="B13" s="30">
         <f>'Debt Schedule'!B13</f>
         <v>231645</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <f>'Debt Schedule'!C13</f>
         <v>212061</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <f>'Debt Schedule'!D13</f>
         <v>191165</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <f>'Debt Schedule'!E13</f>
         <v>168870</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <f>'Debt Schedule'!F13</f>
         <v>145082</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>332</v>
-      </c>
-      <c r="B14" s="36">
+        <v>335</v>
+      </c>
+      <c r="B14" s="31">
         <f>SUM(B12:B13)</f>
         <v>239645</v>
       </c>
-      <c r="C14" s="36">
+      <c r="C14" s="31">
         <f>SUM(C12:C13)</f>
         <v>220061</v>
       </c>
-      <c r="D14" s="36">
+      <c r="D14" s="31">
         <f>SUM(D12:D13)</f>
         <v>199165</v>
       </c>
-      <c r="E14" s="36">
+      <c r="E14" s="31">
         <f>SUM(E12:E13)</f>
         <v>176870</v>
       </c>
-      <c r="F14" s="36">
+      <c r="F14" s="31">
         <f>SUM(F12:F13)</f>
         <v>153082</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="18" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -5205,7 +5214,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B17" s="32">
         <f>B9-B14</f>
@@ -5230,7 +5239,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B19" s="44" t="str">
         <f>B9-B14-B17</f>
@@ -5279,7 +5288,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5309,7 +5318,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="18" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B4" s="18"/>
       <c r="C4" s="18"/>
@@ -5319,67 +5328,67 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B5" s="31">
+        <v>341</v>
+      </c>
+      <c r="B5" s="30">
         <v>1975000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>2621350</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>3304704</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>3922890</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>4361347</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="B6" s="31">
+        <v>303</v>
+      </c>
+      <c r="B6" s="30">
         <v>854772</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>880415</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>906828</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>934032</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>962053</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="B7" s="31">
+        <v>304</v>
+      </c>
+      <c r="B7" s="30">
         <v>271400</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>310442</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>351582</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>389448</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>418014</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="B8" s="34">
         <f>B5-B6-B7</f>
@@ -5404,27 +5413,27 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="B9" s="31">
+        <v>305</v>
+      </c>
+      <c r="B9" s="30">
         <v>34064</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="30">
         <v>34064</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>34064</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="30">
         <v>34064</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="30">
         <v>34064</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B10" s="46">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5449,7 +5458,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="18" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -5459,52 +5468,52 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="B13" s="31">
+        <v>345</v>
+      </c>
+      <c r="B13" s="30">
         <v>864756</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>2251184</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>4253414</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>6813759</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>9755974</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="B14" s="28">
+        <v>346</v>
+      </c>
+      <c r="B14" s="36">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
         <v>272</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="36">
         <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
         <v>671</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="36">
         <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
         <v>1201</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="36">
         <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
         <v>1832</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="36">
         <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
         <v>2518</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5531,25 +5540,25 @@
       <c r="A16" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="B16" s="30">
+      <c r="B16" s="29">
         <v>0.5</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="29">
         <v>0.65</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="29">
         <v>0.8</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="29">
         <v>0.925</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="18" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
@@ -5559,67 +5568,67 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="B19" s="31">
+        <v>240</v>
+      </c>
+      <c r="B19" s="30">
         <v>19750</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>20164</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="30">
         <v>20654</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="30">
         <v>21205</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="30">
         <v>21807</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="B20" s="31">
+        <v>349</v>
+      </c>
+      <c r="B20" s="30">
         <v>888836</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="30">
         <v>914480</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="30">
         <v>940892</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="30">
         <v>968097</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="30">
         <v>996118</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="B21" s="31">
+        <v>350</v>
+      </c>
+      <c r="B21" s="30">
         <v>2714</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="30">
         <v>2388</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="30">
         <v>2197</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="30">
         <v>2105</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="30">
         <v>2090</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B22" s="47">
         <v>53</v>
@@ -5639,7 +5648,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="18" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -5649,102 +5658,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E25" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B26" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C26" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E27" s="49" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D28" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D29" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>
@@ -5785,13 +5794,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B3" s="50" t="s">
         <v>111</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E3" s="50" t="s">
         <v>111</v>
@@ -5801,13 +5810,13 @@
       <c r="A4" s="11" t="s">
         <v>163</v>
       </c>
-      <c r="B4" s="31">
+      <c r="B4" s="30">
         <v>250000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="E4" s="31">
+        <v>362</v>
+      </c>
+      <c r="E4" s="30">
         <v>200000</v>
       </c>
     </row>
@@ -5815,47 +5824,47 @@
       <c r="A5" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="B5" s="31">
+      <c r="B5" s="30">
         <v>50000</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>165</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>50000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="B6" s="31">
+        <v>363</v>
+      </c>
+      <c r="B6" s="30">
         <v>75000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="E6" s="31">
+        <v>364</v>
+      </c>
+      <c r="E6" s="30">
         <v>75000</v>
       </c>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="E7" s="31">
+        <v>365</v>
+      </c>
+      <c r="E7" s="30">
         <v>50000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B9" s="32">
         <v>375000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="E9" s="32">
         <v>375000</v>
@@ -5863,7 +5872,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="B10" s="44">
         <v>0</v>
@@ -6211,7 +6220,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6221,7 +6230,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="18" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B3" s="18"/>
       <c r="C3" s="18"/>
@@ -6231,7 +6240,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6256,47 +6265,47 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B6" s="31">
+        <v>341</v>
+      </c>
+      <c r="B6" s="30">
         <v>1975000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="30">
         <v>2621350</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>3304704</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="30">
         <v>3922890</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="30">
         <v>4361347</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="B7" s="31">
+        <v>282</v>
+      </c>
+      <c r="B7" s="30">
         <v>1160236</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="30">
         <v>1224922</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>1292474</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="30">
         <v>1357545</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="30">
         <v>1414132</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B8" s="32">
         <v>814764</v>
@@ -6316,27 +6325,27 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B9" s="30">
+        <v>285</v>
+      </c>
+      <c r="B9" s="29">
         <v>0.4125385351058188</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="29">
         <v>0.5327134670433142</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="29">
         <v>0.6088985689741885</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>0.6539426893351535</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>0.6757579942908114</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B10" s="51">
         <v>24.92</v>
@@ -6356,27 +6365,27 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="28">
+        <v>351</v>
+      </c>
+      <c r="B11" s="36">
         <v>53</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="36">
         <v>52</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="36">
         <v>51</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="36">
         <v>51</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="36">
         <v>51</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="18" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -6386,7 +6395,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6411,47 +6420,47 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B16" s="31">
+        <v>341</v>
+      </c>
+      <c r="B16" s="30">
         <v>1678750</v>
       </c>
-      <c r="C16" s="31">
+      <c r="C16" s="30">
         <v>2228148</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="30">
         <v>2808998</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>3334456</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>3707145</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="B17" s="31">
+        <v>282</v>
+      </c>
+      <c r="B17" s="30">
         <v>1160236</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>1224922</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <v>1292474</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>1357545</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>1414132</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B18" s="32">
         <v>518514</v>
@@ -6471,27 +6480,27 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B19" s="30">
+        <v>285</v>
+      </c>
+      <c r="B19" s="29">
         <v>0.308868864830375</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="29">
         <v>0.45025113769801683</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="29">
         <v>0.5398806693813982</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="29">
         <v>0.5928737521590041</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="29">
         <v>0.6185388168127194</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B20" s="51">
         <v>16.22</v>
@@ -6511,27 +6520,27 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B21" s="28">
+        <v>351</v>
+      </c>
+      <c r="B21" s="36">
         <v>54</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C21" s="36">
         <v>53</v>
       </c>
-      <c r="D21" s="28">
+      <c r="D21" s="36">
         <v>53</v>
       </c>
-      <c r="E21" s="28">
+      <c r="E21" s="36">
         <v>52</v>
       </c>
-      <c r="F21" s="28">
+      <c r="F21" s="36">
         <v>52</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="18" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -6541,7 +6550,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6566,47 +6575,47 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="B26" s="31">
+        <v>341</v>
+      </c>
+      <c r="B26" s="30">
         <v>1975000</v>
       </c>
-      <c r="C26" s="31">
+      <c r="C26" s="30">
         <v>2621350</v>
       </c>
-      <c r="D26" s="31">
+      <c r="D26" s="30">
         <v>3304704</v>
       </c>
-      <c r="E26" s="31">
+      <c r="E26" s="30">
         <v>3922890</v>
       </c>
-      <c r="F26" s="31">
+      <c r="F26" s="30">
         <v>4361347</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="B27" s="31">
+        <v>282</v>
+      </c>
+      <c r="B27" s="30">
         <v>1173736</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="30">
         <v>1241917</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="30">
         <v>1313162</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="30">
         <v>1381585</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="30">
         <v>1440581</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="B28" s="32">
         <v>801264</v>
@@ -6626,27 +6635,27 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B29" s="30">
+        <v>285</v>
+      </c>
+      <c r="B29" s="29">
         <v>0.4057030920678441</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="29">
         <v>0.5262301664539233</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="29">
         <v>0.6026385368714597</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="29">
         <v>0.6478145556304181</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="29">
         <v>0.6696934781617792</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B30" s="51">
         <v>24.52</v>
@@ -6666,21 +6675,21 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="B31" s="28">
+        <v>351</v>
+      </c>
+      <c r="B31" s="36">
         <v>53</v>
       </c>
-      <c r="C31" s="28">
+      <c r="C31" s="36">
         <v>52</v>
       </c>
-      <c r="D31" s="28">
+      <c r="D31" s="36">
         <v>52</v>
       </c>
-      <c r="E31" s="28">
+      <c r="E31" s="36">
         <v>52</v>
       </c>
-      <c r="F31" s="28">
+      <c r="F31" s="36">
         <v>51</v>
       </c>
     </row>
@@ -6712,7 +6721,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6746,7 +6755,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6770,7 +6779,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6778,7 +6787,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -6816,107 +6825,107 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="D13" s="31">
+        <v>341</v>
+      </c>
+      <c r="D13" s="30">
         <v>1975000</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>2621350</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>3304704</v>
       </c>
-      <c r="G13" s="31">
+      <c r="G13" s="30">
         <v>3922890</v>
       </c>
-      <c r="H13" s="31">
+      <c r="H13" s="30">
         <v>4361347</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>279</v>
-      </c>
-      <c r="D14" s="31">
+        <v>282</v>
+      </c>
+      <c r="D14" s="30">
         <v>1160236</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <v>1224922</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>1292474</v>
       </c>
-      <c r="G14" s="31">
+      <c r="G14" s="30">
         <v>1357545</v>
       </c>
-      <c r="H14" s="31">
+      <c r="H14" s="30">
         <v>1414132</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>281</v>
-      </c>
-      <c r="D15" s="31">
+        <v>284</v>
+      </c>
+      <c r="D15" s="30">
         <v>789764</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="30">
         <v>1386428</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="30">
         <v>2002229</v>
       </c>
-      <c r="G15" s="31">
+      <c r="G15" s="30">
         <v>2560345</v>
       </c>
-      <c r="H15" s="31">
+      <c r="H15" s="30">
         <v>2942215</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>377</v>
-      </c>
-      <c r="D16" s="31">
+        <v>380</v>
+      </c>
+      <c r="D16" s="30">
         <v>864756</v>
       </c>
-      <c r="E16" s="31">
+      <c r="E16" s="30">
         <v>2251184</v>
       </c>
-      <c r="F16" s="31">
+      <c r="F16" s="30">
         <v>4253414</v>
       </c>
-      <c r="G16" s="31">
+      <c r="G16" s="30">
         <v>6813759</v>
       </c>
-      <c r="H16" s="31">
+      <c r="H16" s="30">
         <v>9755974</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>378</v>
-      </c>
-      <c r="D17" s="31">
+        <v>381</v>
+      </c>
+      <c r="D17" s="30">
         <v>231645</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>212061</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>191165</v>
       </c>
-      <c r="G17" s="31">
+      <c r="G17" s="30">
         <v>168870</v>
       </c>
-      <c r="H17" s="31">
+      <c r="H17" s="30">
         <v>145082</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="18" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -6954,27 +6963,27 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="D21" s="30">
+        <v>383</v>
+      </c>
+      <c r="D21" s="29">
         <v>0.3998803072577175</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="29">
         <v>0.5288986388059557</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="29">
         <v>0.6058725788967125</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="29">
         <v>0.6526681187789514</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="29">
         <v>0.6746115593902751</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="D22" s="51">
         <v>24.92</v>
@@ -6996,45 +7005,45 @@
       <c r="A23" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D23" s="30">
+      <c r="D23" s="29">
         <v>0.5</v>
       </c>
-      <c r="E23" s="30">
+      <c r="E23" s="29">
         <v>0.65</v>
       </c>
-      <c r="F23" s="30">
+      <c r="F23" s="29">
         <v>0.8</v>
       </c>
-      <c r="G23" s="30">
+      <c r="G23" s="29">
         <v>0.925</v>
       </c>
-      <c r="H23" s="30">
+      <c r="H23" s="29">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="D24" s="28">
+        <v>384</v>
+      </c>
+      <c r="D24" s="36">
         <v>100</v>
       </c>
-      <c r="E24" s="28">
+      <c r="E24" s="36">
         <v>130</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="36">
         <v>160</v>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="36">
         <v>185</v>
       </c>
-      <c r="H24" s="28">
+      <c r="H24" s="36">
         <v>200</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7074,7 +7083,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7084,7 +7093,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="C3" s="53"/>
       <c r="D3" s="53"/>
@@ -7094,27 +7103,27 @@
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="18" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="C6" s="55">
         <v>100</v>
@@ -7134,7 +7143,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="C7" s="56">
         <v>1975000</v>
@@ -7154,7 +7163,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="C8" s="56">
         <v>854772</v>
@@ -7174,7 +7183,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C9" s="56">
         <v>271400</v>
@@ -7194,7 +7203,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="C10" s="56">
         <v>34064.39316600799</v>
@@ -7214,7 +7223,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C11" s="57">
         <v>789763.6068339921</v>
@@ -7234,7 +7243,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="C12" s="57">
         <v>864756</v>
@@ -7254,7 +7263,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C13" s="58">
         <v>0.3998803072577175</v>
@@ -7274,7 +7283,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C14" s="56">
         <v>19750</v>
@@ -7294,7 +7303,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="C15" s="58">
         <v>0.4327959493670886</v>
@@ -7314,7 +7323,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="C16" s="58">
         <v>0.0412253164556962</v>
@@ -7334,7 +7343,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="C17" s="58">
         <v>0.42978632911392406</v>
@@ -7354,7 +7363,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="C18" s="59">
         <v>24.918336160088252</v>
@@ -7374,10 +7383,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D19" s="60"/>
       <c r="E19" s="60"/>
@@ -7386,10 +7395,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C20" s="60" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D20" s="60"/>
       <c r="E20" s="60"/>
@@ -7398,145 +7407,145 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="18" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E22" s="18"/>
       <c r="F22" s="18" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G22" s="18"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="40" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D23" s="62" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E23" s="62"/>
       <c r="F23" s="63" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="G23" s="63"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
+        <v>409</v>
+      </c>
+      <c r="C24" s="61" t="s">
         <v>406</v>
       </c>
-      <c r="C24" s="61" t="s">
-        <v>403</v>
-      </c>
       <c r="D24" s="62" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E24" s="62"/>
       <c r="F24" s="63" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="G24" s="63"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="40" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D25" s="62" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="E25" s="62"/>
       <c r="F25" s="63" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="G25" s="63"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D26" s="62" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="E26" s="62"/>
       <c r="F26" s="63" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="G26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="40" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D27" s="62" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="E27" s="62"/>
       <c r="F27" s="63" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="G27" s="63"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="40" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D28" s="62" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="E28" s="62"/>
       <c r="F28" s="63" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G28" s="63"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="40" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="D29" s="62" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="E29" s="62"/>
       <c r="F29" s="63" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="G29" s="63"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="40" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="64" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="C33" s="64"/>
       <c r="D33" s="64"/>
@@ -8684,7 +8693,7 @@
       <c r="A7" s="11" t="s">
         <v>99</v>
       </c>
-      <c r="B7" s="28">
+      <c r="B7" s="21">
         <v>200</v>
       </c>
     </row>
@@ -8692,19 +8701,24 @@
       <c r="A8" s="11" t="s">
         <v>196</v>
       </c>
-      <c r="D8" s="29">
+      <c r="D8" s="28">
+        <f>D6/$B$7</f>
         <v>0.5</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="28">
+        <f>E6/$B$7</f>
         <v>0.65</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="28">
+        <f>F6/$B$7</f>
         <v>0.8</v>
       </c>
-      <c r="G8" s="29">
+      <c r="G8" s="28">
+        <f>G6/$B$7</f>
         <v>0.925</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="28">
+        <f>H6/$B$7</f>
         <v>1</v>
       </c>
     </row>
@@ -8715,17 +8729,21 @@
       <c r="D10" s="11" t="s">
         <v>198</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="29">
+        <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.3</v>
       </c>
-      <c r="F10" s="30">
-        <v>0.23076923076923078</v>
-      </c>
-      <c r="G10" s="30">
+      <c r="F10" s="29">
+        <f>IF(E6=0,0,(F6-E6)/E6)</f>
+        <v>0.23076923</v>
+      </c>
+      <c r="G10" s="29">
+        <f>IF(F6=0,0,(G6-F6)/F6)</f>
         <v>0.15625</v>
       </c>
-      <c r="H10" s="30">
-        <v>0.08108108108108109</v>
+      <c r="H10" s="29">
+        <f>IF(G6=0,0,(H6-G6)/G6)</f>
+        <v>0.08108108</v>
       </c>
     </row>
   </sheetData>
@@ -8745,10 +8763,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
-    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="1" max="1" width="36" customWidth="1"/>
     <col min="2" max="7" width="16" customWidth="1"/>
   </cols>
   <sheetData>
@@ -8794,166 +8812,331 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>201</v>
-      </c>
-      <c r="B5" s="31">
+        <v>113</v>
+      </c>
+      <c r="B5" s="30">
         <v>1050000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>1405950</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>1782312</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>2122622</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>2363569</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" s="30">
+        <v>35000</v>
+      </c>
+      <c r="C6" s="30">
+        <v>46865</v>
+      </c>
+      <c r="D6" s="30">
+        <v>59410</v>
+      </c>
+      <c r="E6" s="30">
+        <v>70754</v>
+      </c>
+      <c r="F6" s="30">
+        <v>78786</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" s="31">
+        <f>SUBTOTAL(9,B5:B6)</f>
+        <v>1085000</v>
+      </c>
+      <c r="C7" s="31">
+        <f>SUBTOTAL(9,C5:C6)</f>
+        <v>1452815</v>
+      </c>
+      <c r="D7" s="31">
+        <f>SUBTOTAL(9,D5:D6)</f>
+        <v>1841722</v>
+      </c>
+      <c r="E7" s="31">
+        <f>SUBTOTAL(9,E5:E6)</f>
+        <v>2193376</v>
+      </c>
+      <c r="F7" s="31">
+        <f>SUBTOTAL(9,F5:F6)</f>
+        <v>2442354</v>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="B6" s="31">
-        <v>35000</v>
-      </c>
-      <c r="C6" s="31">
-        <v>46865</v>
-      </c>
-      <c r="D6" s="31">
-        <v>59410</v>
-      </c>
-      <c r="E6" s="31">
-        <v>70754</v>
-      </c>
-      <c r="F6" s="31">
-        <v>78786</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="11" t="s">
-        <v>203</v>
-      </c>
-      <c r="B7" s="31">
-        <v>105000</v>
-      </c>
-      <c r="C7" s="31">
-        <v>140595</v>
-      </c>
-      <c r="D7" s="31">
-        <v>178231</v>
-      </c>
-      <c r="E7" s="31">
-        <v>212262</v>
-      </c>
-      <c r="F7" s="31">
-        <v>236357</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="11" t="s">
-        <v>204</v>
-      </c>
-      <c r="B8" s="31">
-        <v>870000</v>
-      </c>
-      <c r="C8" s="31">
-        <v>1164930</v>
-      </c>
-      <c r="D8" s="31">
-        <v>1476773</v>
-      </c>
-      <c r="E8" s="31">
-        <v>1758744</v>
-      </c>
-      <c r="F8" s="31">
-        <v>1958385</v>
-      </c>
+      <c r="B8" s="18"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="18"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="18"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B9" s="30">
+        <v>105000</v>
+      </c>
+      <c r="C9" s="30">
+        <v>140595</v>
+      </c>
+      <c r="D9" s="30">
+        <v>178231</v>
+      </c>
+      <c r="E9" s="30">
+        <v>212262</v>
+      </c>
+      <c r="F9" s="30">
+        <v>236357</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="B10" s="31">
+        <f>SUBTOTAL(9,B9:B9)</f>
+        <v>105000</v>
+      </c>
+      <c r="C10" s="31">
+        <f>SUBTOTAL(9,C9:C9)</f>
+        <v>140595</v>
+      </c>
+      <c r="D10" s="31">
+        <f>SUBTOTAL(9,D9:D9)</f>
+        <v>178231</v>
+      </c>
+      <c r="E10" s="31">
+        <f>SUBTOTAL(9,E9:E9)</f>
+        <v>212262</v>
+      </c>
+      <c r="F10" s="31">
+        <f>SUBTOTAL(9,F9:F9)</f>
+        <v>236357</v>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="11" t="s">
+        <v>119</v>
+      </c>
+      <c r="B12" s="30">
+        <v>870000</v>
+      </c>
+      <c r="C12" s="30">
+        <v>1164930</v>
+      </c>
+      <c r="D12" s="30">
+        <v>1476773</v>
+      </c>
+      <c r="E12" s="30">
+        <v>1758744</v>
+      </c>
+      <c r="F12" s="30">
+        <v>1958385</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B9" s="31">
+      <c r="B13" s="31">
+        <f>SUBTOTAL(9,B12:B12)</f>
+        <v>870000</v>
+      </c>
+      <c r="C13" s="31">
+        <f>SUBTOTAL(9,C12:C12)</f>
+        <v>1164930</v>
+      </c>
+      <c r="D13" s="31">
+        <f>SUBTOTAL(9,D12:D12)</f>
+        <v>1476773</v>
+      </c>
+      <c r="E13" s="31">
+        <f>SUBTOTAL(9,E12:E12)</f>
+        <v>1758744</v>
+      </c>
+      <c r="F13" s="31">
+        <f>SUBTOTAL(9,F12:F12)</f>
+        <v>1958385</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="18" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="18"/>
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="B15" s="22">
         <v>50000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C15" s="30">
         <v>51500</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D15" s="30">
         <v>53045</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E15" s="30">
         <v>54636</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F15" s="30">
         <v>56275</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="11" t="s">
-        <v>206</v>
-      </c>
-      <c r="B10" s="31">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="22">
         <v>25000</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C16" s="30">
         <v>25750</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D16" s="30">
         <v>26523</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E16" s="30">
         <v>27318</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F16" s="30">
         <v>28138</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="11" t="s">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B11" s="31">
+      <c r="B17" s="31">
+        <f>SUBTOTAL(9,B15:B16)</f>
+        <v>75000</v>
+      </c>
+      <c r="C17" s="31">
+        <f>SUBTOTAL(9,C15:C16)</f>
+        <v>77250</v>
+      </c>
+      <c r="D17" s="31">
+        <f>SUBTOTAL(9,D15:D16)</f>
+        <v>79568</v>
+      </c>
+      <c r="E17" s="31">
+        <f>SUBTOTAL(9,E15:E16)</f>
+        <v>81955</v>
+      </c>
+      <c r="F17" s="31">
+        <f>SUBTOTAL(9,F15:F16)</f>
+        <v>84413</v>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18" s="18"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B19" s="30">
         <v>50000</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C19" s="30">
         <v>66950</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D19" s="30">
         <v>84872</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E19" s="30">
         <v>101077</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F19" s="30">
         <v>112551</v>
       </c>
     </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B12" s="32">
-        <f>SUM(B5:B11)</f>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="B20" s="31">
+        <f>SUBTOTAL(9,B19:B19)</f>
+        <v>50000</v>
+      </c>
+      <c r="C20" s="31">
+        <f>SUBTOTAL(9,C19:C19)</f>
+        <v>66950</v>
+      </c>
+      <c r="D20" s="31">
+        <f>SUBTOTAL(9,D19:D19)</f>
+        <v>84872</v>
+      </c>
+      <c r="E20" s="31">
+        <f>SUBTOTAL(9,E19:E19)</f>
+        <v>101077</v>
+      </c>
+      <c r="F20" s="31">
+        <f>SUBTOTAL(9,F19:F19)</f>
+        <v>112551</v>
+      </c>
+    </row>
+    <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
+        <v>210</v>
+      </c>
+      <c r="B22" s="32">
+        <f>SUM(B7,B10,B13,B17,B20)</f>
         <v>1975000</v>
       </c>
-      <c r="C12" s="32">
-        <f>SUM(C5:C11)</f>
+      <c r="C22" s="32">
+        <f>SUM(C7,C10,C13,C17,C20)</f>
         <v>2621350</v>
       </c>
-      <c r="D12" s="32">
-        <f>SUM(D5:D11)</f>
+      <c r="D22" s="32">
+        <f>SUM(D7,D10,D13,D17,D20)</f>
         <v>3304704</v>
       </c>
-      <c r="E12" s="32">
-        <f>SUM(E5:E11)</f>
+      <c r="E22" s="32">
+        <f>SUM(E7,E10,E13,E17,E20)</f>
         <v>3922890</v>
       </c>
-      <c r="F12" s="32">
-        <f>SUM(F5:F11)</f>
+      <c r="F22" s="32">
+        <f>SUM(F7,F10,F13,F17,F20)</f>
         <v>4361347</v>
       </c>
     </row>
@@ -9007,7 +9190,7 @@
         <v>130</v>
       </c>
       <c r="D3" s="20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E3" s="20" t="s">
         <v>132</v>
@@ -9016,7 +9199,7 @@
         <v>133</v>
       </c>
       <c r="G3" s="20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
@@ -9029,13 +9212,13 @@
       <c r="C4" s="33">
         <v>1</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="30">
         <v>95000</v>
       </c>
-      <c r="E4" s="30">
+      <c r="E4" s="29">
         <v>0.25</v>
       </c>
-      <c r="F4" s="30">
+      <c r="F4" s="29">
         <v>0.0765</v>
       </c>
       <c r="G4" s="34">
@@ -9052,13 +9235,13 @@
       <c r="C5" s="33">
         <v>1</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>75000</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="29">
         <v>0.25</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="29">
         <v>0.0765</v>
       </c>
       <c r="G5" s="34">
@@ -9075,13 +9258,13 @@
       <c r="C6" s="33">
         <v>6</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="30">
         <v>48000</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="29">
         <v>0.25</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="29">
         <v>0.0765</v>
       </c>
       <c r="G6" s="34">
@@ -9098,13 +9281,13 @@
       <c r="C7" s="33">
         <v>3</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>32000</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>0.2</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>0.0765</v>
       </c>
       <c r="G7" s="34">
@@ -9121,13 +9304,13 @@
       <c r="C8" s="33">
         <v>1</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>42000</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>0.25</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>0.0765</v>
       </c>
       <c r="G8" s="34">
@@ -9144,13 +9327,13 @@
       <c r="C9" s="33">
         <v>1</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>52000</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>0.25</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>0.0765</v>
       </c>
       <c r="G9" s="34">
@@ -9159,7 +9342,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="18" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
@@ -9190,7 +9373,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B13" s="32">
         <v>854772</v>
@@ -9210,27 +9393,27 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>213</v>
-      </c>
-      <c r="B14" s="30">
+        <v>215</v>
+      </c>
+      <c r="B14" s="29">
         <v>0.4327959493670886</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="29">
         <v>0.3358632612966601</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="29">
         <v>0.2744051364365971</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="29">
         <v>0.23809805013927576</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="29">
         <v>0.22058632258064514</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="B15" s="35">
         <v>7.7</v>
@@ -9274,7 +9457,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9314,45 +9497,45 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>216</v>
-      </c>
-      <c r="B5" s="31">
+        <v>218</v>
+      </c>
+      <c r="B5" s="30">
         <v>60000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="30">
         <v>80340</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="30">
         <v>101846</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="30">
         <v>121293</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="30">
         <v>135061</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>217</v>
-      </c>
-      <c r="B6" s="36">
+        <v>219</v>
+      </c>
+      <c r="B6" s="31">
         <f>SUM(B5:B5)</f>
         <v>60000</v>
       </c>
-      <c r="C6" s="36">
+      <c r="C6" s="31">
         <f>SUM(C5:C5)</f>
         <v>80340</v>
       </c>
-      <c r="D6" s="36">
+      <c r="D6" s="31">
         <f>SUM(D5:D5)</f>
         <v>101846</v>
       </c>
-      <c r="E6" s="36">
+      <c r="E6" s="31">
         <f>SUM(E5:E5)</f>
         <v>121293</v>
       </c>
-      <c r="F6" s="36">
+      <c r="F6" s="31">
         <f>SUM(F5:F5)</f>
         <v>135061</v>
       </c>
@@ -9369,45 +9552,45 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B8" s="31">
+        <v>220</v>
+      </c>
+      <c r="B8" s="30">
         <v>40000</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="30">
         <v>53560</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>67898</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="30">
         <v>80862</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="30">
         <v>90041</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="B9" s="36">
+        <v>221</v>
+      </c>
+      <c r="B9" s="31">
         <f>SUM(B8:B8)</f>
         <v>40000</v>
       </c>
-      <c r="C9" s="36">
+      <c r="C9" s="31">
         <f>SUM(C8:C8)</f>
         <v>53560</v>
       </c>
-      <c r="D9" s="36">
+      <c r="D9" s="31">
         <f>SUM(D8:D8)</f>
         <v>67898</v>
       </c>
-      <c r="E9" s="36">
+      <c r="E9" s="31">
         <f>SUM(E8:E8)</f>
         <v>80862</v>
       </c>
-      <c r="F9" s="36">
+      <c r="F9" s="31">
         <f>SUM(F8:F8)</f>
         <v>90041</v>
       </c>
@@ -9424,105 +9607,105 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B11" s="31">
+        <v>222</v>
+      </c>
+      <c r="B11" s="30">
         <v>102000</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="30">
         <v>105060</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="30">
         <v>108212</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="30">
         <v>111458</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="30">
         <v>114802</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>221</v>
-      </c>
-      <c r="B12" s="31">
+        <v>223</v>
+      </c>
+      <c r="B12" s="30">
         <v>14400</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="30">
         <v>14832</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="30">
         <v>15277</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="30">
         <v>15735</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="30">
         <v>16207</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B13" s="31">
+        <v>224</v>
+      </c>
+      <c r="B13" s="30">
         <v>12000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="30">
         <v>12360</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="30">
         <v>12731</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="30">
         <v>13113</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="30">
         <v>13506</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B14" s="31">
+        <v>225</v>
+      </c>
+      <c r="B14" s="30">
         <v>8000</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="30">
         <v>8240</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="30">
         <v>8487</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="30">
         <v>8742</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="30">
         <v>9004</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="36">
+        <v>226</v>
+      </c>
+      <c r="B15" s="31">
         <f>SUM(B11:B14)</f>
         <v>136400</v>
       </c>
-      <c r="C15" s="36">
+      <c r="C15" s="31">
         <f>SUM(C11:C14)</f>
         <v>140492</v>
       </c>
-      <c r="D15" s="36">
+      <c r="D15" s="31">
         <f>SUM(D11:D14)</f>
         <v>144707</v>
       </c>
-      <c r="E15" s="36">
+      <c r="E15" s="31">
         <f>SUM(E11:E14)</f>
         <v>149048</v>
       </c>
-      <c r="F15" s="36">
+      <c r="F15" s="31">
         <f>SUM(F11:F14)</f>
         <v>153519</v>
       </c>
@@ -9539,92 +9722,92 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B17" s="31">
+        <v>227</v>
+      </c>
+      <c r="B17" s="30">
         <v>15000</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="30">
         <v>15450</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="30">
         <v>15914</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="30">
         <v>16391</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="30">
         <v>16883</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>226</v>
-      </c>
-      <c r="B18" s="31">
+        <v>228</v>
+      </c>
+      <c r="B18" s="30">
         <v>8000</v>
       </c>
-      <c r="C18" s="31">
+      <c r="C18" s="30">
         <v>8240</v>
       </c>
-      <c r="D18" s="31">
+      <c r="D18" s="30">
         <v>8487</v>
       </c>
-      <c r="E18" s="31">
+      <c r="E18" s="30">
         <v>8742</v>
       </c>
-      <c r="F18" s="31">
+      <c r="F18" s="30">
         <v>9004</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B19" s="31">
+        <v>229</v>
+      </c>
+      <c r="B19" s="30">
         <v>12000</v>
       </c>
-      <c r="C19" s="31">
+      <c r="C19" s="30">
         <v>12360</v>
       </c>
-      <c r="D19" s="31">
+      <c r="D19" s="30">
         <v>12731</v>
       </c>
-      <c r="E19" s="31">
+      <c r="E19" s="30">
         <v>13113</v>
       </c>
-      <c r="F19" s="31">
+      <c r="F19" s="30">
         <v>13506</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>228</v>
-      </c>
-      <c r="B20" s="36">
+        <v>230</v>
+      </c>
+      <c r="B20" s="31">
         <f>SUM(B17:B19)</f>
         <v>35000</v>
       </c>
-      <c r="C20" s="36">
+      <c r="C20" s="31">
         <f>SUM(C17:C19)</f>
         <v>36050</v>
       </c>
-      <c r="D20" s="36">
+      <c r="D20" s="31">
         <f>SUM(D17:D19)</f>
         <v>37132</v>
       </c>
-      <c r="E20" s="36">
+      <c r="E20" s="31">
         <f>SUM(E17:E19)</f>
         <v>38245</v>
       </c>
-      <c r="F20" s="36">
+      <c r="F20" s="31">
         <f>SUM(F17:F19)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="18" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B22" s="32">
         <f>B6+B9+B15+B20</f>
@@ -9674,7 +9857,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9699,7 +9882,7 @@
         <v>162</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -9712,10 +9895,10 @@
       <c r="C4" s="22">
         <v>250000</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="29">
         <v>0.065</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="36">
         <v>10</v>
       </c>
       <c r="F4" s="34">
@@ -9727,15 +9910,15 @@
         <v>165</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C5" s="22">
         <v>25000</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="29">
         <v>0</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="36">
         <v>0</v>
       </c>
       <c r="F5" s="34">
@@ -9744,7 +9927,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="F7" s="32">
         <v>34064</v>
@@ -9752,9 +9935,9 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>234</v>
-      </c>
-      <c r="F8" s="36">
+        <v>236</v>
+      </c>
+      <c r="F8" s="31">
         <v>250000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -8855,23 +8855,23 @@
         <v>201</v>
       </c>
       <c r="B7" s="31">
-        <f>SUBTOTAL(9,B5:B6)</f>
+        <f>SUM(B5,B6)</f>
         <v>1085000</v>
       </c>
       <c r="C7" s="31">
-        <f>SUBTOTAL(9,C5:C6)</f>
+        <f>SUM(C5,C6)</f>
         <v>1452815</v>
       </c>
       <c r="D7" s="31">
-        <f>SUBTOTAL(9,D5:D6)</f>
+        <f>SUM(D5,D6)</f>
         <v>1841722</v>
       </c>
       <c r="E7" s="31">
-        <f>SUBTOTAL(9,E5:E6)</f>
+        <f>SUM(E5,E6)</f>
         <v>2193376</v>
       </c>
       <c r="F7" s="31">
-        <f>SUBTOTAL(9,F5:F6)</f>
+        <f>SUM(F5,F6)</f>
         <v>2442354</v>
       </c>
     </row>
@@ -8910,23 +8910,23 @@
         <v>203</v>
       </c>
       <c r="B10" s="31">
-        <f>SUBTOTAL(9,B9:B9)</f>
+        <f>SUM(B9)</f>
         <v>105000</v>
       </c>
       <c r="C10" s="31">
-        <f>SUBTOTAL(9,C9:C9)</f>
+        <f>SUM(C9)</f>
         <v>140595</v>
       </c>
       <c r="D10" s="31">
-        <f>SUBTOTAL(9,D9:D9)</f>
+        <f>SUM(D9)</f>
         <v>178231</v>
       </c>
       <c r="E10" s="31">
-        <f>SUBTOTAL(9,E9:E9)</f>
+        <f>SUM(E9)</f>
         <v>212262</v>
       </c>
       <c r="F10" s="31">
-        <f>SUBTOTAL(9,F9:F9)</f>
+        <f>SUM(F9)</f>
         <v>236357</v>
       </c>
     </row>
@@ -8965,23 +8965,23 @@
         <v>205</v>
       </c>
       <c r="B13" s="31">
-        <f>SUBTOTAL(9,B12:B12)</f>
+        <f>SUM(B12)</f>
         <v>870000</v>
       </c>
       <c r="C13" s="31">
-        <f>SUBTOTAL(9,C12:C12)</f>
+        <f>SUM(C12)</f>
         <v>1164930</v>
       </c>
       <c r="D13" s="31">
-        <f>SUBTOTAL(9,D12:D12)</f>
+        <f>SUM(D12)</f>
         <v>1476773</v>
       </c>
       <c r="E13" s="31">
-        <f>SUBTOTAL(9,E12:E12)</f>
+        <f>SUM(E12)</f>
         <v>1758744</v>
       </c>
       <c r="F13" s="31">
-        <f>SUBTOTAL(9,F12:F12)</f>
+        <f>SUM(F12)</f>
         <v>1958385</v>
       </c>
     </row>
@@ -9040,23 +9040,23 @@
         <v>207</v>
       </c>
       <c r="B17" s="31">
-        <f>SUBTOTAL(9,B15:B16)</f>
+        <f>SUM(B15,B16)</f>
         <v>75000</v>
       </c>
       <c r="C17" s="31">
-        <f>SUBTOTAL(9,C15:C16)</f>
+        <f>SUM(C15,C16)</f>
         <v>77250</v>
       </c>
       <c r="D17" s="31">
-        <f>SUBTOTAL(9,D15:D16)</f>
+        <f>SUM(D15,D16)</f>
         <v>79568</v>
       </c>
       <c r="E17" s="31">
-        <f>SUBTOTAL(9,E15:E16)</f>
+        <f>SUM(E15,E16)</f>
         <v>81955</v>
       </c>
       <c r="F17" s="31">
-        <f>SUBTOTAL(9,F15:F16)</f>
+        <f>SUM(F15,F16)</f>
         <v>84413</v>
       </c>
     </row>
@@ -9095,23 +9095,23 @@
         <v>209</v>
       </c>
       <c r="B20" s="31">
-        <f>SUBTOTAL(9,B19:B19)</f>
+        <f>SUM(B19)</f>
         <v>50000</v>
       </c>
       <c r="C20" s="31">
-        <f>SUBTOTAL(9,C19:C19)</f>
+        <f>SUM(C19)</f>
         <v>66950</v>
       </c>
       <c r="D20" s="31">
-        <f>SUBTOTAL(9,D19:D19)</f>
+        <f>SUM(D19)</f>
         <v>84872</v>
       </c>
       <c r="E20" s="31">
-        <f>SUBTOTAL(9,E19:E19)</f>
+        <f>SUM(E19)</f>
         <v>101077</v>
       </c>
       <c r="F20" s="31">
-        <f>SUBTOTAL(9,F19:F19)</f>
+        <f>SUM(F19)</f>
         <v>112551</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="773" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="431">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -316,7 +316,10 @@
     <t>Heritage Academy - Assumptions</t>
   </si>
   <si>
-    <t>Blue cells are editable inputs. All other cells are formulas.</t>
+    <t>Editable assumption — change this value</t>
+  </si>
+  <si>
+    <t>Calculated — driven by formula</t>
   </si>
   <si>
     <t>SCHOOL PROFILE</t>
@@ -1459,7 +1462,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1478,6 +1481,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
@@ -1487,7 +1495,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -1505,6 +1513,15 @@
       <top style="thin">
         <color rgb="FFD0D0D0"/>
       </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color rgb="FFD0D0D0"/>
       </bottom>
@@ -1554,9 +1571,10 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1565,19 +1583,18 @@
     <xf numFmtId="2" fontId="5" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="167" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -1592,13 +1609,13 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1607,13 +1624,13 @@
     <xf numFmtId="165" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -2325,7 +2342,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2334,237 +2351,237 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B4" s="26">
+        <v>107</v>
+      </c>
+      <c r="B4" s="27">
         <v>100</v>
       </c>
-      <c r="C4" s="26">
+      <c r="C4" s="27">
         <v>130</v>
       </c>
-      <c r="D4" s="26">
+      <c r="D4" s="27">
         <v>160</v>
       </c>
-      <c r="E4" s="26">
+      <c r="E4" s="27">
         <v>185</v>
       </c>
-      <c r="F4" s="26">
+      <c r="F4" s="27">
         <v>200</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>238</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
+      <c r="A6" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B7" s="30">
+        <v>114</v>
+      </c>
+      <c r="B7" s="31">
         <v>1050000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>1405950</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>1782312</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>2122622</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>2363569</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B8" s="30">
+        <v>117</v>
+      </c>
+      <c r="B8" s="31">
         <v>35000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>46865</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>59410</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>70754</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>78786</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="30">
+        <v>118</v>
+      </c>
+      <c r="B9" s="31">
         <v>105000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>140595</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>178231</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>212262</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>236357</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B10" s="30">
+        <v>120</v>
+      </c>
+      <c r="B10" s="31">
         <v>870000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>1164930</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>1476773</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>1758744</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>1958385</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B11" s="30">
+        <v>122</v>
+      </c>
+      <c r="B11" s="31">
         <v>50000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>51500</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>53045</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>54636</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>56275</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B12" s="30">
+        <v>125</v>
+      </c>
+      <c r="B12" s="31">
         <v>25000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>25750</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>26523</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>27318</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>28138</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B13" s="30">
+        <v>126</v>
+      </c>
+      <c r="B13" s="31">
         <v>50000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>66950</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>84872</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>101077</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>112551</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>239</v>
-      </c>
-      <c r="B14" s="32">
+      <c r="A14" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="B14" s="33">
         <f>SUM(B7:B13)</f>
         <v>1975000</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>SUM(C7:C13)</f>
         <v>2621350</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>SUM(D7:D13)</f>
         <v>3304704</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>SUM(E7:E13)</f>
         <v>3922890</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>SUM(F7:F13)</f>
         <v>4361347</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B16" s="30">
+        <v>241</v>
+      </c>
+      <c r="B16" s="31">
         <v>19750</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>20164</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>20654</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>21205</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>21807</v>
       </c>
     </row>
@@ -2594,7 +2611,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2603,306 +2620,306 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B5" s="30">
+        <v>243</v>
+      </c>
+      <c r="B5" s="31">
         <v>382032</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>393493</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>405298</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>417457</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>429980</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B6" s="30">
+        <v>244</v>
+      </c>
+      <c r="B6" s="31">
         <v>122544</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>126220</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>130007</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>133907</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>137924</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>244</v>
-      </c>
-      <c r="B7" s="31">
+        <v>245</v>
+      </c>
+      <c r="B7" s="32">
         <f>SUM(B5:B6)</f>
         <v>504576</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>SUM(C5:C6)</f>
         <v>519713</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>SUM(D5:D6)</f>
         <v>535305</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>SUM(E5:E6)</f>
         <v>551364</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>SUM(F5:F6)</f>
         <v>567905</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>135</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="B9" s="30">
+        <v>246</v>
+      </c>
+      <c r="B9" s="31">
         <v>126018</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>129798</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>133692</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>137703</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>141834</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B10" s="30">
+        <v>247</v>
+      </c>
+      <c r="B10" s="31">
         <v>99488</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>102472</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>105546</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>108713</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>111974</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>247</v>
-      </c>
-      <c r="B11" s="31">
+        <v>248</v>
+      </c>
+      <c r="B11" s="32">
         <f>SUM(B9:B10)</f>
         <v>225505</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>SUM(C9:C10)</f>
         <v>232270</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>SUM(D9:D10)</f>
         <v>239238</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>SUM(E9:E10)</f>
         <v>246415</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>SUM(F9:F10)</f>
         <v>253808</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>144</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B13" s="30">
+        <v>249</v>
+      </c>
+      <c r="B13" s="31">
         <v>68978</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>71047</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>73179</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>75374</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>77635</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>249</v>
-      </c>
-      <c r="B14" s="31">
+        <v>250</v>
+      </c>
+      <c r="B14" s="32">
         <f>SUM(B13:B13)</f>
         <v>68978</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C13:C13)</f>
         <v>71047</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D13:D13)</f>
         <v>73179</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E13:E13)</f>
         <v>75374</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F13:F13)</f>
         <v>77635</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>142</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
+      <c r="A15" s="19" t="s">
+        <v>143</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B16" s="30">
+        <v>251</v>
+      </c>
+      <c r="B16" s="31">
         <v>55713</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>57384</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>59106</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>60879</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>62705</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>251</v>
-      </c>
-      <c r="B17" s="31">
+        <v>252</v>
+      </c>
+      <c r="B17" s="32">
         <f>SUM(B16:B16)</f>
         <v>55713</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>SUM(C16:C16)</f>
         <v>57384</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>SUM(D16:D16)</f>
         <v>59106</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>SUM(E16:E16)</f>
         <v>60879</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>SUM(F16:F16)</f>
         <v>62705</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>252</v>
-      </c>
-      <c r="B19" s="32">
+      <c r="A19" s="19" t="s">
+        <v>253</v>
+      </c>
+      <c r="B19" s="33">
         <f>B7+B11+B14+B17</f>
         <v>854772</v>
       </c>
-      <c r="C19" s="32">
+      <c r="C19" s="33">
         <f>C7+C11+C14+C17</f>
         <v>880415</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D19" s="33">
         <f>D7+D11+D14+D17</f>
         <v>906828</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E19" s="33">
         <f>E7+E11+E14+E17</f>
         <v>934032</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F19" s="33">
         <f>F7+F11+F14+F17</f>
         <v>962053</v>
       </c>
@@ -2933,7 +2950,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2942,711 +2959,711 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="B5" s="30">
+        <v>256</v>
+      </c>
+      <c r="B5" s="31">
         <v>1050000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>1405950</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>1782312</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>2122622</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>2363569</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>256</v>
-      </c>
-      <c r="B6" s="30">
+        <v>257</v>
+      </c>
+      <c r="B6" s="31">
         <v>35000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>46865</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>59410</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>70754</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>78786</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="30">
+        <v>258</v>
+      </c>
+      <c r="B7" s="31">
         <v>105000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>140595</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>178231</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>212262</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>236357</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="30">
+        <v>259</v>
+      </c>
+      <c r="B8" s="31">
         <v>870000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>1164930</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>1476773</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>1758744</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>1958385</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>259</v>
-      </c>
-      <c r="B9" s="30">
+        <v>260</v>
+      </c>
+      <c r="B9" s="31">
         <v>50000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>51500</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>53045</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>54636</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>56275</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>260</v>
-      </c>
-      <c r="B10" s="30">
+        <v>261</v>
+      </c>
+      <c r="B10" s="31">
         <v>25000</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <v>25750</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <v>26523</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <v>27318</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <v>28138</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B11" s="30">
+        <v>262</v>
+      </c>
+      <c r="B11" s="31">
         <v>50000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>66950</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>84872</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>101077</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>112551</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="B12" s="31">
+        <v>263</v>
+      </c>
+      <c r="B12" s="32">
         <f>SUM(B5:B11)</f>
         <v>1975000</v>
       </c>
-      <c r="C12" s="31">
+      <c r="C12" s="32">
         <f>SUM(C5:C11)</f>
         <v>2621350</v>
       </c>
-      <c r="D12" s="31">
+      <c r="D12" s="32">
         <f>SUM(D5:D11)</f>
         <v>3304704</v>
       </c>
-      <c r="E12" s="31">
+      <c r="E12" s="32">
         <f>SUM(E5:E11)</f>
         <v>3922890</v>
       </c>
-      <c r="F12" s="31">
+      <c r="F12" s="32">
         <f>SUM(F5:F11)</f>
         <v>4361347</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="19" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>245</v>
-      </c>
-      <c r="B15" s="30">
+        <v>246</v>
+      </c>
+      <c r="B15" s="31">
         <v>126018</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>129798</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>133692</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>137703</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>141834</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>246</v>
-      </c>
-      <c r="B16" s="30">
+        <v>247</v>
+      </c>
+      <c r="B16" s="31">
         <v>99488</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>102472</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>105546</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>108713</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>111974</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>242</v>
-      </c>
-      <c r="B17" s="30">
+        <v>243</v>
+      </c>
+      <c r="B17" s="31">
         <v>382032</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>393493</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>405298</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>417457</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>429980</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>243</v>
-      </c>
-      <c r="B18" s="30">
+        <v>244</v>
+      </c>
+      <c r="B18" s="31">
         <v>122544</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>126220</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>130007</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>133907</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>137924</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>250</v>
-      </c>
-      <c r="B19" s="30">
+        <v>251</v>
+      </c>
+      <c r="B19" s="31">
         <v>55713</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>57384</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>59106</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>60879</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>62705</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>248</v>
-      </c>
-      <c r="B20" s="30">
+        <v>249</v>
+      </c>
+      <c r="B20" s="31">
         <v>68978</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>71047</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>73179</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>75374</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>77635</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="B21" s="31">
+        <v>215</v>
+      </c>
+      <c r="B21" s="32">
         <f>SUM(B15:B20)</f>
         <v>854772</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <f>SUM(C15:C20)</f>
         <v>880415</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <f>SUM(D15:D20)</f>
         <v>906828</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <f>SUM(E15:E20)</f>
         <v>934032</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <f>SUM(F15:F20)</f>
         <v>962053</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>264</v>
-      </c>
-      <c r="B25" s="30">
+        <v>265</v>
+      </c>
+      <c r="B25" s="31">
         <v>60000</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>80340</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>101846</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>121293</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>135061</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>265</v>
-      </c>
-      <c r="B27" s="30">
+        <v>266</v>
+      </c>
+      <c r="B27" s="31">
         <v>40000</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>53560</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>67898</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>80862</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>90041</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="B29" s="30">
+        <v>267</v>
+      </c>
+      <c r="B29" s="31">
         <v>102000</v>
       </c>
-      <c r="C29" s="30">
+      <c r="C29" s="31">
         <v>105060</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29" s="31">
         <v>108212</v>
       </c>
-      <c r="E29" s="30">
+      <c r="E29" s="31">
         <v>111458</v>
       </c>
-      <c r="F29" s="30">
+      <c r="F29" s="31">
         <v>114802</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>267</v>
-      </c>
-      <c r="B30" s="30">
+        <v>268</v>
+      </c>
+      <c r="B30" s="31">
         <v>14400</v>
       </c>
-      <c r="C30" s="30">
+      <c r="C30" s="31">
         <v>14832</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30" s="31">
         <v>15277</v>
       </c>
-      <c r="E30" s="30">
+      <c r="E30" s="31">
         <v>15735</v>
       </c>
-      <c r="F30" s="30">
+      <c r="F30" s="31">
         <v>16207</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>268</v>
-      </c>
-      <c r="B31" s="30">
+        <v>269</v>
+      </c>
+      <c r="B31" s="31">
         <v>12000</v>
       </c>
-      <c r="C31" s="30">
+      <c r="C31" s="31">
         <v>12360</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31" s="31">
         <v>12731</v>
       </c>
-      <c r="E31" s="30">
+      <c r="E31" s="31">
         <v>13113</v>
       </c>
-      <c r="F31" s="30">
+      <c r="F31" s="31">
         <v>13506</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>269</v>
-      </c>
-      <c r="B32" s="30">
+        <v>270</v>
+      </c>
+      <c r="B32" s="31">
         <v>8000</v>
       </c>
-      <c r="C32" s="30">
+      <c r="C32" s="31">
         <v>8240</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32" s="31">
         <v>8487</v>
       </c>
-      <c r="E32" s="30">
+      <c r="E32" s="31">
         <v>8742</v>
       </c>
-      <c r="F32" s="30">
+      <c r="F32" s="31">
         <v>9004</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="B33" s="31">
+        <v>271</v>
+      </c>
+      <c r="B33" s="32">
         <f>SUM(B29:B32)</f>
         <v>136400</v>
       </c>
-      <c r="C33" s="31">
+      <c r="C33" s="32">
         <f>SUM(C29:C32)</f>
         <v>140492</v>
       </c>
-      <c r="D33" s="31">
+      <c r="D33" s="32">
         <f>SUM(D29:D32)</f>
         <v>144707</v>
       </c>
-      <c r="E33" s="31">
+      <c r="E33" s="32">
         <f>SUM(E29:E32)</f>
         <v>149048</v>
       </c>
-      <c r="F33" s="31">
+      <c r="F33" s="32">
         <f>SUM(F29:F32)</f>
         <v>153519</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>271</v>
-      </c>
-      <c r="B35" s="30">
+        <v>272</v>
+      </c>
+      <c r="B35" s="31">
         <v>15000</v>
       </c>
-      <c r="C35" s="30">
+      <c r="C35" s="31">
         <v>15450</v>
       </c>
-      <c r="D35" s="30">
+      <c r="D35" s="31">
         <v>15914</v>
       </c>
-      <c r="E35" s="30">
+      <c r="E35" s="31">
         <v>16391</v>
       </c>
-      <c r="F35" s="30">
+      <c r="F35" s="31">
         <v>16883</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>272</v>
-      </c>
-      <c r="B36" s="30">
+        <v>273</v>
+      </c>
+      <c r="B36" s="31">
         <v>8000</v>
       </c>
-      <c r="C36" s="30">
+      <c r="C36" s="31">
         <v>8240</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36" s="31">
         <v>8487</v>
       </c>
-      <c r="E36" s="30">
+      <c r="E36" s="31">
         <v>8742</v>
       </c>
-      <c r="F36" s="30">
+      <c r="F36" s="31">
         <v>9004</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>273</v>
-      </c>
-      <c r="B37" s="30">
+        <v>274</v>
+      </c>
+      <c r="B37" s="31">
         <v>12000</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="31">
         <v>12360</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37" s="31">
         <v>12731</v>
       </c>
-      <c r="E37" s="30">
+      <c r="E37" s="31">
         <v>13113</v>
       </c>
-      <c r="F37" s="30">
+      <c r="F37" s="31">
         <v>13506</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>274</v>
-      </c>
-      <c r="B38" s="31">
+        <v>275</v>
+      </c>
+      <c r="B38" s="32">
         <f>SUM(B35:B37)</f>
         <v>35000</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <f>SUM(C35:C37)</f>
         <v>36050</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <f>SUM(D35:D37)</f>
         <v>37132</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <f>SUM(E35:E37)</f>
         <v>38245</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <f>SUM(F35:F37)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>275</v>
-      </c>
-      <c r="B39" s="31">
+        <v>276</v>
+      </c>
+      <c r="B39" s="32">
         <f>B25+B27+B33+B38</f>
         <v>271400</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <f>C25+C27+C33+C38</f>
         <v>310442</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <f>D25+D27+D33+D38</f>
         <v>351582</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <f>E25+E27+E33+E38</f>
         <v>389448</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <f>F25+F27+F33+F38</f>
         <v>418014</v>
       </c>
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="B41" s="18"/>
-      <c r="C41" s="18"/>
-      <c r="D41" s="18"/>
-      <c r="E41" s="18"/>
-      <c r="F41" s="18"/>
+      <c r="A41" s="19" t="s">
+        <v>277</v>
+      </c>
+      <c r="B41" s="19"/>
+      <c r="C41" s="19"/>
+      <c r="D41" s="19"/>
+      <c r="E41" s="19"/>
+      <c r="F41" s="19"/>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="B42" s="30">
+        <v>278</v>
+      </c>
+      <c r="B42" s="31">
         <v>34064</v>
       </c>
-      <c r="C42" s="30">
+      <c r="C42" s="31">
         <v>34064</v>
       </c>
-      <c r="D42" s="30">
+      <c r="D42" s="31">
         <v>34064</v>
       </c>
-      <c r="E42" s="30">
+      <c r="E42" s="31">
         <v>34064</v>
       </c>
-      <c r="F42" s="30">
+      <c r="F42" s="31">
         <v>34064</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="B43" s="30">
+        <v>279</v>
+      </c>
+      <c r="B43" s="31">
         <v>25000</v>
       </c>
-      <c r="C43" s="30">
+      <c r="C43" s="31">
         <v>10000</v>
       </c>
-      <c r="D43" s="30">
+      <c r="D43" s="31">
         <v>10000</v>
       </c>
-      <c r="E43" s="30">
+      <c r="E43" s="31">
         <v>5000</v>
       </c>
-      <c r="F43" s="30">
+      <c r="F43" s="31">
         <v>5000</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>279</v>
-      </c>
-      <c r="B44" s="31">
+        <v>280</v>
+      </c>
+      <c r="B44" s="32">
         <f>SUM(B42:B43)</f>
         <v>59064</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <f>SUM(C42:C43)</f>
         <v>44064</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <f>SUM(D42:D43)</f>
         <v>44064</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <f>SUM(E42:E43)</f>
         <v>39064</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <f>SUM(F42:F43)</f>
         <v>39064</v>
       </c>
@@ -3677,7 +3694,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3686,28 +3703,28 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B4" s="34">
         <f>'Budget Detail'!B12</f>
@@ -3732,7 +3749,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="B5" s="34">
         <f>'Budget Detail'!B21</f>
@@ -3757,7 +3774,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
@@ -3782,7 +3799,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
@@ -3807,146 +3824,146 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>282</v>
-      </c>
-      <c r="B8" s="31">
+        <v>283</v>
+      </c>
+      <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
         <v>1185236</v>
       </c>
-      <c r="C8" s="31">
+      <c r="C8" s="32">
         <f>SUM(C5:C7)</f>
         <v>1234922</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="32">
         <f>SUM(D5:D7)</f>
         <v>1302474</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="32">
         <f>SUM(E5:E7)</f>
         <v>1362545</v>
       </c>
-      <c r="F8" s="31">
+      <c r="F8" s="32">
         <f>SUM(F5:F7)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19" t="s">
+        <v>284</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="B11" s="32">
+        <v>285</v>
+      </c>
+      <c r="B11" s="33">
         <f>B4-B8</f>
         <v>789764</v>
       </c>
-      <c r="C11" s="32">
+      <c r="C11" s="33">
         <f>C4-C8</f>
         <v>1386428</v>
       </c>
-      <c r="D11" s="32">
+      <c r="D11" s="33">
         <f>D4-D8</f>
         <v>2002229</v>
       </c>
-      <c r="E11" s="32">
+      <c r="E11" s="33">
         <f>E4-E8</f>
         <v>2560345</v>
       </c>
-      <c r="F11" s="32">
+      <c r="F11" s="33">
         <f>F4-F8</f>
         <v>2942215</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="B12" s="29">
+        <v>286</v>
+      </c>
+      <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
         <v>0.39988031</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="30">
         <f>IF(C4=0,0,C11/C4)</f>
         <v>0.52889864</v>
       </c>
-      <c r="D12" s="29">
+      <c r="D12" s="30">
         <f>IF(D4=0,0,D11/D4)</f>
         <v>0.60587258</v>
       </c>
-      <c r="E12" s="29">
+      <c r="E12" s="30">
         <f>IF(E4=0,0,E11/E4)</f>
         <v>0.65266812</v>
       </c>
-      <c r="F12" s="29">
+      <c r="F12" s="30">
         <f>IF(F4=0,0,F11/F4)</f>
         <v>0.67461156</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>286</v>
-      </c>
-      <c r="B13" s="30">
+        <v>287</v>
+      </c>
+      <c r="B13" s="31">
         <v>789764</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>2176192</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>4178421</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>6738766</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>9680981</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B14" s="30">
+        <v>241</v>
+      </c>
+      <c r="B14" s="31">
         <v>19750</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>20164</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>20654</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>21205</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>21807</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="B15" s="30">
+        <v>288</v>
+      </c>
+      <c r="B15" s="31">
         <v>11852</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>9499</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>8140</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>7365</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>7096</v>
       </c>
     </row>
@@ -3977,7 +3994,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3994,286 +4011,286 @@
       <c r="N1" s="15"/>
     </row>
     <row r="2" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="20" t="s">
-        <v>289</v>
-      </c>
-      <c r="C2" s="20" t="s">
+      <c r="B2" s="21" t="s">
         <v>290</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="C2" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="E2" s="20" t="s">
+      <c r="D2" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="E2" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="F2" s="21" t="s">
         <v>294</v>
       </c>
-      <c r="H2" s="20" t="s">
+      <c r="G2" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="H2" s="21" t="s">
         <v>296</v>
       </c>
-      <c r="J2" s="20" t="s">
+      <c r="I2" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="K2" s="20" t="s">
+      <c r="J2" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="L2" s="20" t="s">
+      <c r="K2" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="M2" s="20" t="s">
+      <c r="L2" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="M2" s="21" t="s">
         <v>301</v>
       </c>
+      <c r="N2" s="21" t="s">
+        <v>302</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
-      <c r="I3" s="18"/>
-      <c r="J3" s="18"/>
-      <c r="K3" s="18"/>
-      <c r="L3" s="18"/>
-      <c r="M3" s="18"/>
-      <c r="N3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>262</v>
-      </c>
-      <c r="B4" s="31">
+        <v>263</v>
+      </c>
+      <c r="B4" s="32">
         <v>85833</v>
       </c>
-      <c r="C4" s="31">
+      <c r="C4" s="32">
         <v>180333</v>
       </c>
-      <c r="D4" s="31">
+      <c r="D4" s="32">
         <v>180333</v>
       </c>
-      <c r="E4" s="31">
+      <c r="E4" s="32">
         <v>180333</v>
       </c>
-      <c r="F4" s="31">
+      <c r="F4" s="32">
         <v>180333</v>
       </c>
-      <c r="G4" s="31">
+      <c r="G4" s="32">
         <v>180333</v>
       </c>
-      <c r="H4" s="31">
+      <c r="H4" s="32">
         <v>180333</v>
       </c>
-      <c r="I4" s="31">
+      <c r="I4" s="32">
         <v>180333</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="32">
         <v>180333</v>
       </c>
-      <c r="K4" s="31">
+      <c r="K4" s="32">
         <v>180333</v>
       </c>
-      <c r="L4" s="31">
+      <c r="L4" s="32">
         <v>180333</v>
       </c>
-      <c r="M4" s="31">
+      <c r="M4" s="32">
         <v>85833</v>
       </c>
-      <c r="N4" s="31">
+      <c r="N4" s="32">
         <f>SUM(B4:M4)</f>
         <v>1974996</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="B6" s="18"/>
-      <c r="C6" s="18"/>
-      <c r="D6" s="18"/>
-      <c r="E6" s="18"/>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
-      <c r="K6" s="18"/>
-      <c r="L6" s="18"/>
-      <c r="M6" s="18"/>
-      <c r="N6" s="18"/>
+      <c r="A6" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="B6" s="19"/>
+      <c r="C6" s="19"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="19"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19"/>
+      <c r="K6" s="19"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="19"/>
+      <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="B7" s="30">
+        <v>304</v>
+      </c>
+      <c r="B7" s="31">
         <v>71231</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>71231</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>71231</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>71231</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>71231</v>
       </c>
-      <c r="G7" s="30">
+      <c r="G7" s="31">
         <v>71231</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="31">
         <v>71231</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="31">
         <v>71231</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="31">
         <v>71231</v>
       </c>
-      <c r="K7" s="30">
+      <c r="K7" s="31">
         <v>71231</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="31">
         <v>71231</v>
       </c>
-      <c r="M7" s="30">
+      <c r="M7" s="31">
         <v>71231</v>
       </c>
-      <c r="N7" s="30">
+      <c r="N7" s="31">
         <f>SUM(B7:M7)</f>
         <v>854772</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="B8" s="30">
+        <v>305</v>
+      </c>
+      <c r="B8" s="31">
         <v>22617</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>22617</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>22617</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>22617</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>22617</v>
       </c>
-      <c r="G8" s="30">
+      <c r="G8" s="31">
         <v>22617</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="31">
         <v>22617</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="31">
         <v>22617</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="31">
         <v>22617</v>
       </c>
-      <c r="K8" s="30">
+      <c r="K8" s="31">
         <v>22617</v>
       </c>
-      <c r="L8" s="30">
+      <c r="L8" s="31">
         <v>22617</v>
       </c>
-      <c r="M8" s="30">
+      <c r="M8" s="31">
         <v>22617</v>
       </c>
-      <c r="N8" s="30">
+      <c r="N8" s="31">
         <f>SUM(B8:M8)</f>
         <v>271400</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B9" s="30">
+        <v>306</v>
+      </c>
+      <c r="B9" s="31">
         <v>4922</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>4922</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>4922</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>4922</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>4922</v>
       </c>
-      <c r="G9" s="30">
+      <c r="G9" s="31">
         <v>4922</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="31">
         <v>4922</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="31">
         <v>4922</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="31">
         <v>4922</v>
       </c>
-      <c r="K9" s="30">
+      <c r="K9" s="31">
         <v>4922</v>
       </c>
-      <c r="L9" s="30">
+      <c r="L9" s="31">
         <v>4922</v>
       </c>
-      <c r="M9" s="30">
+      <c r="M9" s="31">
         <v>4922</v>
       </c>
-      <c r="N9" s="30">
+      <c r="N9" s="31">
         <f>SUM(B9:M9)</f>
         <v>59064</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>306</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="18"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>307</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="19"/>
+      <c r="M11" s="19"/>
+      <c r="N11" s="19"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
@@ -4330,7 +4347,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
@@ -4387,7 +4404,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
@@ -4437,29 +4454,29 @@
         <f>L14+M13</f>
         <v>864756</v>
       </c>
-      <c r="N14" s="32">
+      <c r="N14" s="33">
         <f>M14</f>
         <v>864756</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>309</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B17" s="22">
+        <v>174</v>
+      </c>
+      <c r="B17" s="23">
         <v>75000</v>
       </c>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
@@ -4468,9 +4485,9 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="B19" s="30">
+        <v>312</v>
+      </c>
+      <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
         <v>62063</v>
       </c>
@@ -4501,7 +4518,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4510,68 +4527,68 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="39" t="s">
-        <v>262</v>
-      </c>
-      <c r="B5" s="31">
+        <v>263</v>
+      </c>
+      <c r="B5" s="32">
         <v>1975000</v>
       </c>
-      <c r="C5" s="31">
+      <c r="C5" s="32">
         <v>2621350</v>
       </c>
-      <c r="D5" s="31">
+      <c r="D5" s="32">
         <v>3304704</v>
       </c>
-      <c r="E5" s="31">
+      <c r="E5" s="32">
         <v>3922890</v>
       </c>
-      <c r="F5" s="31">
+      <c r="F5" s="32">
         <v>4361347</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>302</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B8" s="34">
         <v>854772</v>
@@ -4591,7 +4608,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B9" s="34">
         <v>271400</v>
@@ -4611,7 +4628,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B10" s="34">
         <v>59064</v>
@@ -4631,85 +4648,85 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="B11" s="31">
+        <v>283</v>
+      </c>
+      <c r="B11" s="32">
         <f>SUM(B8:B10)</f>
         <v>1185236</v>
       </c>
-      <c r="C11" s="31">
+      <c r="C11" s="32">
         <f>SUM(C8:C10)</f>
         <v>1234922</v>
       </c>
-      <c r="D11" s="31">
+      <c r="D11" s="32">
         <f>SUM(D8:D10)</f>
         <v>1302474</v>
       </c>
-      <c r="E11" s="31">
+      <c r="E11" s="32">
         <f>SUM(E8:E10)</f>
         <v>1362545</v>
       </c>
-      <c r="F11" s="31">
+      <c r="F11" s="32">
         <f>SUM(F8:F10)</f>
         <v>1419132</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>314</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>315</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>284</v>
-      </c>
-      <c r="B14" s="32">
+        <v>285</v>
+      </c>
+      <c r="B14" s="33">
         <f>B5-B11</f>
         <v>789764</v>
       </c>
-      <c r="C14" s="32">
+      <c r="C14" s="33">
         <f>C5-C11</f>
         <v>1386428</v>
       </c>
-      <c r="D14" s="32">
+      <c r="D14" s="33">
         <f>D5-D11</f>
         <v>2002229</v>
       </c>
-      <c r="E14" s="32">
+      <c r="E14" s="33">
         <f>E5-E11</f>
         <v>2560345</v>
       </c>
-      <c r="F14" s="32">
+      <c r="F14" s="33">
         <f>F5-F11</f>
         <v>2942215</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="B15" s="29">
+        <v>286</v>
+      </c>
+      <c r="B15" s="30">
         <f>IF(B5=0,0,B14/B5)</f>
         <v>0.39988031</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="30">
         <f>IF(C5=0,0,C14/C5)</f>
         <v>0.52889864</v>
       </c>
-      <c r="D15" s="29">
+      <c r="D15" s="30">
         <f>IF(D5=0,0,D14/D5)</f>
         <v>0.60587258</v>
       </c>
-      <c r="E15" s="29">
+      <c r="E15" s="30">
         <f>IF(E5=0,0,E14/E5)</f>
         <v>0.65266812</v>
       </c>
-      <c r="F15" s="29">
+      <c r="F15" s="30">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.67461156</v>
       </c>
@@ -4749,158 +4766,158 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>315</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>316</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="40" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B5" s="41" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D5" s="40" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="E5" s="41" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="B6" s="22">
+      <c r="A6" s="20" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="23">
         <v>250000</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="24">
         <v>0.065</v>
       </c>
-      <c r="D6" s="19">
+      <c r="D6" s="20">
         <v>10</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <f>IF(OR(B6=0,D6=0),0,IF(C6=0,B6/D6,-PMT(C6/12,D6*12,B6)*12))</f>
         <v>34064</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>319</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>320</v>
-      </c>
-      <c r="B9" s="30">
+        <v>321</v>
+      </c>
+      <c r="B9" s="31">
         <f>B6</f>
         <v>250000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <f>B13</f>
         <v>231645</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <f>C13</f>
         <v>212061</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <f>D13</f>
         <v>191165</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <f>E13</f>
         <v>168870</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>321</v>
-      </c>
-      <c r="B10" s="30">
+        <v>322</v>
+      </c>
+      <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
         <v>15710</v>
       </c>
-      <c r="C10" s="30">
+      <c r="C10" s="31">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,13,24,0)))</f>
         <v>14480</v>
       </c>
-      <c r="D10" s="30">
+      <c r="D10" s="31">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,25,36,0)))</f>
         <v>13169</v>
       </c>
-      <c r="E10" s="30">
+      <c r="E10" s="31">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,37,48,0)))</f>
         <v>11769</v>
       </c>
-      <c r="F10" s="30">
+      <c r="F10" s="31">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,49,60,0)))</f>
         <v>10276</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>322</v>
-      </c>
-      <c r="B11" s="30">
+        <v>323</v>
+      </c>
+      <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
         <v>18355</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <f>IF(OR(D6=0,13&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,13,24,0)))</f>
         <v>19584</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <f>IF(OR(D6=0,25&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,25,36,0)))</f>
         <v>20896</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <f>IF(OR(D6=0,37&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,37,48,0)))</f>
         <v>22295</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <f>IF(OR(D6=0,49&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,49,60,0)))</f>
         <v>23788</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -4925,7 +4942,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -4974,7 +4991,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4983,38 +5000,38 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>326</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>327</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B5" s="43">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -5039,207 +5056,207 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B6" s="30">
+        <v>329</v>
+      </c>
+      <c r="B6" s="31">
         <v>12000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>12000</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>12000</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>12000</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>12000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>329</v>
-      </c>
-      <c r="B7" s="30">
+        <v>330</v>
+      </c>
+      <c r="B7" s="31">
         <v>180000</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>180000</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>180000</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>180000</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>180000</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>330</v>
-      </c>
-      <c r="B8" s="30">
+        <v>331</v>
+      </c>
+      <c r="B8" s="31">
         <v>5000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>5000</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>5000</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>5000</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>5000</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>331</v>
-      </c>
-      <c r="B9" s="31">
+        <v>332</v>
+      </c>
+      <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
         <v>1061756</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
         <v>2448184</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
         <v>4450414</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
         <v>7010759</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
         <v>9952974</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>332</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>333</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="B12" s="30">
+        <v>334</v>
+      </c>
+      <c r="B12" s="31">
         <v>8000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>8000</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>8000</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>8000</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>8000</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>334</v>
-      </c>
-      <c r="B13" s="30">
+        <v>335</v>
+      </c>
+      <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
         <v>231645</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <f>'Debt Schedule'!C13</f>
         <v>212061</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <f>'Debt Schedule'!D13</f>
         <v>191165</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <f>'Debt Schedule'!E13</f>
         <v>168870</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <f>'Debt Schedule'!F13</f>
         <v>145082</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>335</v>
-      </c>
-      <c r="B14" s="31">
+        <v>336</v>
+      </c>
+      <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
         <v>239645</v>
       </c>
-      <c r="C14" s="31">
+      <c r="C14" s="32">
         <f>SUM(C12:C13)</f>
         <v>220061</v>
       </c>
-      <c r="D14" s="31">
+      <c r="D14" s="32">
         <f>SUM(D12:D13)</f>
         <v>199165</v>
       </c>
-      <c r="E14" s="31">
+      <c r="E14" s="32">
         <f>SUM(E12:E13)</f>
         <v>176870</v>
       </c>
-      <c r="F14" s="31">
+      <c r="F14" s="32">
         <f>SUM(F12:F13)</f>
         <v>153082</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>336</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>337</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>337</v>
-      </c>
-      <c r="B17" s="32">
+        <v>338</v>
+      </c>
+      <c r="B17" s="33">
         <f>B9-B14</f>
         <v>822111</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="33">
         <f>C9-C14</f>
         <v>2228123</v>
       </c>
-      <c r="D17" s="32">
+      <c r="D17" s="33">
         <f>D9-D14</f>
         <v>4251248</v>
       </c>
-      <c r="E17" s="32">
+      <c r="E17" s="33">
         <f>E9-E14</f>
         <v>6833888</v>
       </c>
-      <c r="F17" s="32">
+      <c r="F17" s="33">
         <f>F9-F14</f>
         <v>9799892</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="B19" s="44" t="str">
         <f>B9-B14-B17</f>
@@ -5288,7 +5305,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5297,98 +5314,98 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>340</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>341</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="B5" s="30">
+        <v>342</v>
+      </c>
+      <c r="B5" s="31">
         <v>1975000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>2621350</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>3304704</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>3922890</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>4361347</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="B6" s="30">
+        <v>304</v>
+      </c>
+      <c r="B6" s="31">
         <v>854772</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>880415</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>906828</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>934032</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>962053</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="B7" s="30">
+        <v>305</v>
+      </c>
+      <c r="B7" s="31">
         <v>271400</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>310442</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>351582</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>389448</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>418014</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B8" s="34">
         <f>B5-B6-B7</f>
@@ -5413,27 +5430,27 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="B9" s="30">
+        <v>306</v>
+      </c>
+      <c r="B9" s="31">
         <v>34064</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>34064</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>34064</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>34064</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>34064</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B10" s="46">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5457,38 +5474,38 @@
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
+      <c r="A12" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="B13" s="30">
+        <v>346</v>
+      </c>
+      <c r="B13" s="31">
         <v>864756</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>2251184</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>4253414</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>6813759</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>9755974</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B14" s="36">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5513,7 +5530,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5538,97 +5555,97 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="B16" s="29">
+        <v>197</v>
+      </c>
+      <c r="B16" s="30">
         <v>0.5</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="30">
         <v>0.65</v>
       </c>
-      <c r="D16" s="29">
+      <c r="D16" s="30">
         <v>0.8</v>
       </c>
-      <c r="E16" s="29">
+      <c r="E16" s="30">
         <v>0.925</v>
       </c>
-      <c r="F16" s="29">
+      <c r="F16" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>348</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="19" t="s">
+        <v>349</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>240</v>
-      </c>
-      <c r="B19" s="30">
+        <v>241</v>
+      </c>
+      <c r="B19" s="31">
         <v>19750</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>20164</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>20654</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>21205</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>21807</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>349</v>
-      </c>
-      <c r="B20" s="30">
+        <v>350</v>
+      </c>
+      <c r="B20" s="31">
         <v>888836</v>
       </c>
-      <c r="C20" s="30">
+      <c r="C20" s="31">
         <v>914480</v>
       </c>
-      <c r="D20" s="30">
+      <c r="D20" s="31">
         <v>940892</v>
       </c>
-      <c r="E20" s="30">
+      <c r="E20" s="31">
         <v>968097</v>
       </c>
-      <c r="F20" s="30">
+      <c r="F20" s="31">
         <v>996118</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="B21" s="30">
+        <v>351</v>
+      </c>
+      <c r="B21" s="31">
         <v>2714</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>2388</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>2197</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>2105</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>2090</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B22" s="47">
         <v>53</v>
@@ -5647,113 +5664,113 @@
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="18" t="s">
-        <v>352</v>
-      </c>
-      <c r="B24" s="18"/>
-      <c r="C24" s="18"/>
-      <c r="D24" s="18"/>
-      <c r="E24" s="18"/>
-      <c r="F24" s="18"/>
+      <c r="A24" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B25" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C25" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D25" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E25" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="B26" s="48" t="s">
         <v>355</v>
       </c>
-      <c r="B26" s="48" t="s">
-        <v>354</v>
-      </c>
       <c r="C26" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B27" s="49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C27" s="49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="D27" s="49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="E27" s="49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F27" s="49" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B28" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C28" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D28" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B29" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C29" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="D29" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
     </row>
   </sheetData>
@@ -5794,85 +5811,85 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="50" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" s="50" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="E3" s="50" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>163</v>
-      </c>
-      <c r="B4" s="30">
+        <v>164</v>
+      </c>
+      <c r="B4" s="31">
         <v>250000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="E4" s="30">
+        <v>363</v>
+      </c>
+      <c r="E4" s="31">
         <v>200000</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="30">
+        <v>122</v>
+      </c>
+      <c r="B5" s="31">
         <v>50000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>165</v>
-      </c>
-      <c r="E5" s="30">
+        <v>166</v>
+      </c>
+      <c r="E5" s="31">
         <v>50000</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B6" s="30">
+        <v>364</v>
+      </c>
+      <c r="B6" s="31">
         <v>75000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="E6" s="30">
+        <v>365</v>
+      </c>
+      <c r="E6" s="31">
         <v>75000</v>
       </c>
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="E7" s="30">
+        <v>366</v>
+      </c>
+      <c r="E7" s="31">
         <v>50000</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>366</v>
-      </c>
-      <c r="B9" s="32">
+        <v>367</v>
+      </c>
+      <c r="B9" s="33">
         <v>375000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>367</v>
-      </c>
-      <c r="E9" s="32">
+        <v>368</v>
+      </c>
+      <c r="E9" s="33">
         <v>375000</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B10" s="44">
         <v>0</v>
@@ -6220,7 +6237,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6229,123 +6246,123 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>371</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="20" t="s">
+      <c r="A5" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="C5" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="B6" s="30">
+        <v>342</v>
+      </c>
+      <c r="B6" s="31">
         <v>1975000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>2621350</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>3304704</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>3922890</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>4361347</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B7" s="30">
+        <v>283</v>
+      </c>
+      <c r="B7" s="31">
         <v>1160236</v>
       </c>
-      <c r="C7" s="30">
+      <c r="C7" s="31">
         <v>1224922</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="31">
         <v>1292474</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="31">
         <v>1357545</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="31">
         <v>1414132</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="B8" s="32">
+        <v>285</v>
+      </c>
+      <c r="B8" s="33">
         <v>814764</v>
       </c>
-      <c r="C8" s="32">
+      <c r="C8" s="33">
         <v>1396428</v>
       </c>
-      <c r="D8" s="32">
+      <c r="D8" s="33">
         <v>2012229</v>
       </c>
-      <c r="E8" s="32">
+      <c r="E8" s="33">
         <v>2565345</v>
       </c>
-      <c r="F8" s="32">
+      <c r="F8" s="33">
         <v>2947215</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="B9" s="29">
+        <v>286</v>
+      </c>
+      <c r="B9" s="30">
         <v>0.4125385351058188</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="30">
         <v>0.5327134670433142</v>
       </c>
-      <c r="D9" s="29">
+      <c r="D9" s="30">
         <v>0.6088985689741885</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>0.6539426893351535</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>0.6757579942908114</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B10" s="51">
         <v>24.92</v>
@@ -6365,7 +6382,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B11" s="36">
         <v>53</v>
@@ -6384,123 +6401,123 @@
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="18" t="s">
-        <v>372</v>
-      </c>
-      <c r="B13" s="18"/>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
+      <c r="A13" s="19" t="s">
+        <v>373</v>
+      </c>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="20" t="s">
+      <c r="A15" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B15" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="C15" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F15" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="B16" s="30">
+        <v>342</v>
+      </c>
+      <c r="B16" s="31">
         <v>1678750</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>2228148</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>2808998</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>3334456</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>3707145</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B17" s="30">
+        <v>283</v>
+      </c>
+      <c r="B17" s="31">
         <v>1160236</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>1224922</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>1292474</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>1357545</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>1414132</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="B18" s="32">
+        <v>285</v>
+      </c>
+      <c r="B18" s="33">
         <v>518514</v>
       </c>
-      <c r="C18" s="32">
+      <c r="C18" s="33">
         <v>1003226</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D18" s="33">
         <v>1516524</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E18" s="33">
         <v>1976912</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F18" s="33">
         <v>2293013</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="B19" s="29">
+        <v>286</v>
+      </c>
+      <c r="B19" s="30">
         <v>0.308868864830375</v>
       </c>
-      <c r="C19" s="29">
+      <c r="C19" s="30">
         <v>0.45025113769801683</v>
       </c>
-      <c r="D19" s="29">
+      <c r="D19" s="30">
         <v>0.5398806693813982</v>
       </c>
-      <c r="E19" s="29">
+      <c r="E19" s="30">
         <v>0.5928737521590041</v>
       </c>
-      <c r="F19" s="29">
+      <c r="F19" s="30">
         <v>0.6185388168127194</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B20" s="51">
         <v>16.22</v>
@@ -6520,7 +6537,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B21" s="36">
         <v>54</v>
@@ -6539,123 +6556,123 @@
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="B23" s="18"/>
-      <c r="C23" s="18"/>
-      <c r="D23" s="18"/>
-      <c r="E23" s="18"/>
-      <c r="F23" s="18"/>
+      <c r="A23" s="19" t="s">
+        <v>375</v>
+      </c>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="20" t="s">
+      <c r="A25" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C25" s="20" t="s">
+      <c r="B25" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="C25" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="D25" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F25" s="20" t="s">
+      <c r="E25" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F25" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="B26" s="30">
+        <v>342</v>
+      </c>
+      <c r="B26" s="31">
         <v>1975000</v>
       </c>
-      <c r="C26" s="30">
+      <c r="C26" s="31">
         <v>2621350</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26" s="31">
         <v>3304704</v>
       </c>
-      <c r="E26" s="30">
+      <c r="E26" s="31">
         <v>3922890</v>
       </c>
-      <c r="F26" s="30">
+      <c r="F26" s="31">
         <v>4361347</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="B27" s="30">
+        <v>283</v>
+      </c>
+      <c r="B27" s="31">
         <v>1173736</v>
       </c>
-      <c r="C27" s="30">
+      <c r="C27" s="31">
         <v>1241917</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27" s="31">
         <v>1313162</v>
       </c>
-      <c r="E27" s="30">
+      <c r="E27" s="31">
         <v>1381585</v>
       </c>
-      <c r="F27" s="30">
+      <c r="F27" s="31">
         <v>1440581</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>284</v>
-      </c>
-      <c r="B28" s="32">
+        <v>285</v>
+      </c>
+      <c r="B28" s="33">
         <v>801264</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>1379433</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>1991542</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>2541305</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>2920765</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="B29" s="29">
+        <v>286</v>
+      </c>
+      <c r="B29" s="30">
         <v>0.4057030920678441</v>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <v>0.5262301664539233</v>
       </c>
-      <c r="D29" s="29">
+      <c r="D29" s="30">
         <v>0.6026385368714597</v>
       </c>
-      <c r="E29" s="29">
+      <c r="E29" s="30">
         <v>0.6478145556304181</v>
       </c>
-      <c r="F29" s="29">
+      <c r="F29" s="30">
         <v>0.6696934781617792</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B30" s="51">
         <v>24.52</v>
@@ -6675,7 +6692,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B31" s="36">
         <v>53</v>
@@ -6721,7 +6738,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6732,10 +6749,10 @@
       <c r="H1" s="15"/>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="18"/>
+      <c r="A3" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B3" s="19"/>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
@@ -6747,7 +6764,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -6755,7 +6772,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6779,23 +6796,23 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>379</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>380</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="19"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
@@ -6808,132 +6825,132 @@
         <v>7</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F12" s="52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G12" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H12" s="52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>341</v>
-      </c>
-      <c r="D13" s="30">
+        <v>342</v>
+      </c>
+      <c r="D13" s="31">
         <v>1975000</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>2621350</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>3304704</v>
       </c>
-      <c r="G13" s="30">
+      <c r="G13" s="31">
         <v>3922890</v>
       </c>
-      <c r="H13" s="30">
+      <c r="H13" s="31">
         <v>4361347</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>282</v>
-      </c>
-      <c r="D14" s="30">
+        <v>283</v>
+      </c>
+      <c r="D14" s="31">
         <v>1160236</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>1224922</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>1292474</v>
       </c>
-      <c r="G14" s="30">
+      <c r="G14" s="31">
         <v>1357545</v>
       </c>
-      <c r="H14" s="30">
+      <c r="H14" s="31">
         <v>1414132</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>284</v>
-      </c>
-      <c r="D15" s="30">
+        <v>285</v>
+      </c>
+      <c r="D15" s="31">
         <v>789764</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>1386428</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>2002229</v>
       </c>
-      <c r="G15" s="30">
+      <c r="G15" s="31">
         <v>2560345</v>
       </c>
-      <c r="H15" s="30">
+      <c r="H15" s="31">
         <v>2942215</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>380</v>
-      </c>
-      <c r="D16" s="30">
+        <v>381</v>
+      </c>
+      <c r="D16" s="31">
         <v>864756</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>2251184</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>4253414</v>
       </c>
-      <c r="G16" s="30">
+      <c r="G16" s="31">
         <v>6813759</v>
       </c>
-      <c r="H16" s="30">
+      <c r="H16" s="31">
         <v>9755974</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>381</v>
-      </c>
-      <c r="D17" s="30">
+        <v>382</v>
+      </c>
+      <c r="D17" s="31">
         <v>231645</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>212061</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>191165</v>
       </c>
-      <c r="G17" s="30">
+      <c r="G17" s="31">
         <v>168870</v>
       </c>
-      <c r="H17" s="30">
+      <c r="H17" s="31">
         <v>145082</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>382</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="A19" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
@@ -6946,44 +6963,44 @@
         <v>7</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F20" s="52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="G20" s="52" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="H20" s="52" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>383</v>
-      </c>
-      <c r="D21" s="29">
+        <v>384</v>
+      </c>
+      <c r="D21" s="30">
         <v>0.3998803072577175</v>
       </c>
-      <c r="E21" s="29">
+      <c r="E21" s="30">
         <v>0.5288986388059557</v>
       </c>
-      <c r="F21" s="29">
+      <c r="F21" s="30">
         <v>0.6058725788967125</v>
       </c>
-      <c r="G21" s="29">
+      <c r="G21" s="30">
         <v>0.6526681187789514</v>
       </c>
-      <c r="H21" s="29">
+      <c r="H21" s="30">
         <v>0.6746115593902751</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D22" s="51">
         <v>24.92</v>
@@ -7003,27 +7020,27 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D23" s="29">
+        <v>197</v>
+      </c>
+      <c r="D23" s="30">
         <v>0.5</v>
       </c>
-      <c r="E23" s="29">
+      <c r="E23" s="30">
         <v>0.65</v>
       </c>
-      <c r="F23" s="29">
+      <c r="F23" s="30">
         <v>0.8</v>
       </c>
-      <c r="G23" s="29">
+      <c r="G23" s="30">
         <v>0.925</v>
       </c>
-      <c r="H23" s="29">
+      <c r="H23" s="30">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D24" s="36">
         <v>100</v>
@@ -7043,7 +7060,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7083,7 +7100,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7093,7 +7110,7 @@
     </row>
     <row r="3" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C3" s="53"/>
       <c r="D3" s="53"/>
@@ -7102,28 +7119,28 @@
       <c r="G3" s="53"/>
     </row>
     <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>388</v>
+      <c r="B5" s="19" t="s">
+        <v>389</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D5" s="54" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E5" s="54" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F5" s="54" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="G5" s="54" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="11" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="C6" s="55">
         <v>100</v>
@@ -7143,7 +7160,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C7" s="56">
         <v>1975000</v>
@@ -7163,7 +7180,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C8" s="56">
         <v>854772</v>
@@ -7183,7 +7200,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C9" s="56">
         <v>271400</v>
@@ -7203,7 +7220,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C10" s="56">
         <v>34064.39316600799</v>
@@ -7223,7 +7240,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="10" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C11" s="57">
         <v>789763.6068339921</v>
@@ -7243,7 +7260,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C12" s="57">
         <v>864756</v>
@@ -7263,7 +7280,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="C13" s="58">
         <v>0.3998803072577175</v>
@@ -7283,7 +7300,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="C14" s="56">
         <v>19750</v>
@@ -7303,7 +7320,7 @@
     </row>
     <row r="15" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="C15" s="58">
         <v>0.4327959493670886</v>
@@ -7323,7 +7340,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C16" s="58">
         <v>0.0412253164556962</v>
@@ -7343,7 +7360,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C17" s="58">
         <v>0.42978632911392406</v>
@@ -7363,7 +7380,7 @@
     </row>
     <row r="18" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="C18" s="59">
         <v>24.918336160088252</v>
@@ -7383,10 +7400,10 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C19" s="60" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D19" s="60"/>
       <c r="E19" s="60"/>
@@ -7395,10 +7412,10 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C20" s="60" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="D20" s="60"/>
       <c r="E20" s="60"/>
@@ -7406,146 +7423,146 @@
       <c r="G20" s="60"/>
     </row>
     <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="18" t="s">
-        <v>401</v>
-      </c>
-      <c r="C22" s="18" t="s">
+      <c r="B22" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="C22" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="E22" s="18"/>
-      <c r="F22" s="18" t="s">
+      <c r="D22" s="19" t="s">
         <v>404</v>
       </c>
-      <c r="G22" s="18"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19" t="s">
+        <v>405</v>
+      </c>
+      <c r="G22" s="19"/>
     </row>
     <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="40" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="C23" s="61" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D23" s="62" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E23" s="62"/>
       <c r="F23" s="63" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="G23" s="63"/>
     </row>
     <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="40" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C24" s="61" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D24" s="62" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E24" s="62"/>
       <c r="F24" s="63" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="G24" s="63"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="40" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C25" s="61" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D25" s="62" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E25" s="62"/>
       <c r="F25" s="63" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="G25" s="63"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C26" s="61" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D26" s="62" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E26" s="62"/>
       <c r="F26" s="63" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="G26" s="63"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B27" s="40" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C27" s="61" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D27" s="62" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E27" s="62"/>
       <c r="F27" s="63" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="G27" s="63"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B28" s="40" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C28" s="61" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D28" s="62" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E28" s="62"/>
       <c r="F28" s="63" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="G28" s="63"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="40" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C29" s="61" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="D29" s="62" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E29" s="62"/>
       <c r="F29" s="63" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G29" s="63"/>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="40" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C31" s="10" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D31" s="10"/>
       <c r="E31" s="10"/>
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="64" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="C33" s="64"/>
       <c r="D33" s="64"/>
@@ -7687,30 +7704,36 @@
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
         <v>94</v>
       </c>
+      <c r="D2" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="17" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>95</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="20" t="s">
         <v>1</v>
       </c>
     </row>
@@ -7718,7 +7741,7 @@
       <c r="A6" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="20" t="s">
         <v>34</v>
       </c>
     </row>
@@ -7726,7 +7749,7 @@
       <c r="A7" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="20" t="s">
         <v>36</v>
       </c>
     </row>
@@ -7734,23 +7757,23 @@
       <c r="A8" s="11" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="20" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="B9" s="19" t="s">
         <v>97</v>
+      </c>
+      <c r="B9" s="20" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="B10" s="19" t="s">
+      <c r="B10" s="20" t="s">
         <v>44</v>
       </c>
     </row>
@@ -7758,694 +7781,694 @@
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="19" t="s">
+      <c r="B11" s="20" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="B12" s="19">
+        <v>99</v>
+      </c>
+      <c r="B12" s="20">
         <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B13" s="19">
+        <v>100</v>
+      </c>
+      <c r="B13" s="20">
         <v>200</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
+      <c r="A15" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="20" t="s">
+      <c r="A16" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B16" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C16" s="20" t="s">
+      <c r="B16" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D16" s="20" t="s">
+      <c r="C16" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E16" s="20" t="s">
+      <c r="D16" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="E16" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F16" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B17" s="21">
+        <v>107</v>
+      </c>
+      <c r="B17" s="22">
         <v>100</v>
       </c>
-      <c r="C17" s="21">
+      <c r="C17" s="22">
         <v>130</v>
       </c>
-      <c r="D17" s="21">
+      <c r="D17" s="22">
         <v>160</v>
       </c>
-      <c r="E17" s="21">
+      <c r="E17" s="22">
         <v>185</v>
       </c>
-      <c r="F17" s="21">
+      <c r="F17" s="22">
         <v>200</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="18" t="s">
-        <v>107</v>
-      </c>
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
+      <c r="A19" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B20" s="20" t="s">
+      <c r="A20" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="20" t="s">
+      <c r="B20" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D20" s="20" t="s">
+      <c r="C20" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="D20" s="21" t="s">
         <v>112</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D21" s="22">
+        <v>116</v>
+      </c>
+      <c r="D21" s="23">
         <v>10500</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="11" t="s">
         <v>116</v>
       </c>
-      <c r="B22" s="11" t="s">
-        <v>114</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D22" s="22">
+      <c r="D22" s="23">
         <v>350</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D23" s="22">
+        <v>116</v>
+      </c>
+      <c r="D23" s="23">
         <v>-1050</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D24" s="22">
+        <v>116</v>
+      </c>
+      <c r="D24" s="23">
         <v>8700</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D25" s="22">
+        <v>124</v>
+      </c>
+      <c r="D25" s="23">
         <v>50000</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C26" s="11" t="s">
         <v>124</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="C26" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D26" s="22">
+      <c r="D26" s="23">
         <v>25000</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D27" s="22">
+        <v>116</v>
+      </c>
+      <c r="D27" s="23">
         <v>500</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="18" t="s">
-        <v>127</v>
-      </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
+      <c r="A29" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B30" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C30" s="20" t="s">
+      <c r="A30" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="D30" s="20" t="s">
+      <c r="B30" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C30" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="E30" s="20" t="s">
+      <c r="D30" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="F30" s="20" t="s">
+      <c r="E30" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="G30" s="20" t="s">
+      <c r="F30" s="21" t="s">
         <v>133</v>
+      </c>
+      <c r="G30" s="21" t="s">
+        <v>134</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="24">
+        <v>137</v>
+      </c>
+      <c r="D31" s="25">
         <v>1</v>
       </c>
-      <c r="E31" s="22">
+      <c r="E31" s="23">
         <v>95000</v>
       </c>
-      <c r="F31" s="23">
+      <c r="F31" s="24">
         <v>0.25</v>
       </c>
-      <c r="G31" s="23">
+      <c r="G31" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="C32" s="11" t="s">
         <v>137</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D32" s="24">
+      <c r="D32" s="25">
         <v>1</v>
       </c>
-      <c r="E32" s="22">
+      <c r="E32" s="23">
         <v>75000</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="24">
         <v>0.25</v>
       </c>
-      <c r="G32" s="23">
+      <c r="G32" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D33" s="24">
+        <v>137</v>
+      </c>
+      <c r="D33" s="25">
         <v>6</v>
       </c>
-      <c r="E33" s="22">
+      <c r="E33" s="23">
         <v>48000</v>
       </c>
-      <c r="F33" s="23">
+      <c r="F33" s="24">
         <v>0.25</v>
       </c>
-      <c r="G33" s="23">
+      <c r="G33" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B34" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B34" s="11" t="s">
-        <v>139</v>
-      </c>
       <c r="C34" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D34" s="24">
+        <v>137</v>
+      </c>
+      <c r="D34" s="25">
         <v>3</v>
       </c>
-      <c r="E34" s="22">
+      <c r="E34" s="23">
         <v>32000</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="24">
         <v>0.2</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D35" s="24">
+        <v>137</v>
+      </c>
+      <c r="D35" s="25">
         <v>1</v>
       </c>
-      <c r="E35" s="22">
+      <c r="E35" s="23">
         <v>42000</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="24">
         <v>0.25</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>136</v>
-      </c>
-      <c r="D36" s="24">
+        <v>137</v>
+      </c>
+      <c r="D36" s="25">
         <v>1</v>
       </c>
-      <c r="E36" s="22">
+      <c r="E36" s="23">
         <v>52000</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="24">
         <v>0.25</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="24">
         <v>0.0765</v>
       </c>
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="18" t="s">
-        <v>145</v>
-      </c>
-      <c r="B38" s="18"/>
-      <c r="C38" s="18"/>
-      <c r="D38" s="18"/>
-      <c r="E38" s="18"/>
-      <c r="F38" s="18"/>
-      <c r="G38" s="18"/>
+      <c r="A38" s="19" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" s="19"/>
+      <c r="C38" s="19"/>
+      <c r="D38" s="19"/>
+      <c r="E38" s="19"/>
+      <c r="F38" s="19"/>
+      <c r="G38" s="19"/>
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="20" t="s">
-        <v>108</v>
-      </c>
-      <c r="B39" s="20" t="s">
+      <c r="A39" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C39" s="20" t="s">
+      <c r="B39" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="20" t="s">
+      <c r="C39" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="E39" s="20" t="s">
+      <c r="D39" s="21" t="s">
         <v>112</v>
+      </c>
+      <c r="E39" s="21" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D40" s="22">
+        <v>149</v>
+      </c>
+      <c r="D40" s="23">
         <v>8500</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="24">
         <v>0.03</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="11" t="s">
         <v>149</v>
       </c>
-      <c r="B41" s="11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C41" s="11" t="s">
-        <v>148</v>
-      </c>
-      <c r="D41" s="22">
+      <c r="D41" s="23">
         <v>1200</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D42" s="22">
+        <v>124</v>
+      </c>
+      <c r="D42" s="23">
         <v>12000</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D43" s="22">
+        <v>124</v>
+      </c>
+      <c r="D43" s="23">
         <v>8000</v>
       </c>
-      <c r="E43" s="23">
+      <c r="E43" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D44" s="22">
+        <v>116</v>
+      </c>
+      <c r="D44" s="23">
         <v>600</v>
       </c>
-      <c r="E44" s="23">
+      <c r="E44" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>115</v>
-      </c>
-      <c r="D45" s="22">
+        <v>116</v>
+      </c>
+      <c r="D45" s="23">
         <v>400</v>
       </c>
-      <c r="E45" s="23">
+      <c r="E45" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D46" s="22">
+        <v>124</v>
+      </c>
+      <c r="D46" s="23">
         <v>15000</v>
       </c>
-      <c r="E46" s="23">
+      <c r="E46" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>157</v>
       </c>
-      <c r="B47" s="11" t="s">
-        <v>156</v>
-      </c>
       <c r="C47" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D47" s="22">
+        <v>124</v>
+      </c>
+      <c r="D47" s="23">
         <v>8000</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D48" s="22">
+        <v>124</v>
+      </c>
+      <c r="D48" s="23">
         <v>12000</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="24">
         <v>0</v>
       </c>
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B50" s="18"/>
-      <c r="C50" s="18"/>
-      <c r="D50" s="18"/>
-      <c r="E50" s="18"/>
-      <c r="F50" s="18"/>
-      <c r="G50" s="18"/>
+      <c r="A50" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="B50" s="19"/>
+      <c r="C50" s="19"/>
+      <c r="D50" s="19"/>
+      <c r="E50" s="19"/>
+      <c r="F50" s="19"/>
+      <c r="G50" s="19"/>
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="B51" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C51" s="20" t="s">
+      <c r="A51" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="D51" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E51" s="20" t="s">
+      <c r="B51" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C51" s="21" t="s">
         <v>162</v>
+      </c>
+      <c r="D51" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="E51" s="21" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C52" s="22">
+        <v>165</v>
+      </c>
+      <c r="C52" s="23">
         <v>250000</v>
       </c>
-      <c r="D52" s="23">
+      <c r="D52" s="24">
         <v>0.065</v>
       </c>
-      <c r="E52" s="21">
+      <c r="E52" s="22">
         <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="C53" s="22">
+        <v>167</v>
+      </c>
+      <c r="C53" s="23">
         <v>25000</v>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="24">
         <v>0</v>
       </c>
-      <c r="E53" s="21">
+      <c r="E53" s="22">
         <v>0</v>
       </c>
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A55" s="18" t="s">
-        <v>167</v>
-      </c>
-      <c r="B55" s="18"/>
-      <c r="C55" s="18"/>
-      <c r="D55" s="18"/>
-      <c r="E55" s="18"/>
-      <c r="F55" s="18"/>
-      <c r="G55" s="18"/>
+      <c r="A55" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="B55" s="19"/>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>168</v>
-      </c>
-      <c r="B56" s="23">
+        <v>169</v>
+      </c>
+      <c r="B56" s="24">
         <v>0.03</v>
       </c>
-      <c r="C56" s="25" t="s">
-        <v>169</v>
+      <c r="C56" s="26" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>170</v>
-      </c>
-      <c r="B57" s="23">
+        <v>171</v>
+      </c>
+      <c r="B57" s="24">
         <v>0.03</v>
       </c>
-      <c r="C57" s="25" t="s">
-        <v>171</v>
+      <c r="C57" s="26" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>172</v>
-      </c>
-      <c r="B58" s="24">
+        <v>173</v>
+      </c>
+      <c r="B58" s="25">
         <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>173</v>
-      </c>
-      <c r="B59" s="22">
+        <v>174</v>
+      </c>
+      <c r="B59" s="23">
         <v>75000</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>174</v>
-      </c>
-      <c r="B60" s="19" t="s">
         <v>175</v>
+      </c>
+      <c r="B60" s="20" t="s">
+        <v>176</v>
       </c>
     </row>
   </sheetData>
@@ -8480,10 +8503,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8504,10 +8527,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -8520,7 +8543,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -8528,66 +8551,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -8626,122 +8649,122 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>193</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="C3" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="F3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="G3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="H3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="B5" s="18"/>
-      <c r="C5" s="18"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
+      <c r="A5" s="19" t="s">
+        <v>196</v>
+      </c>
+      <c r="B5" s="19"/>
+      <c r="C5" s="19"/>
+      <c r="D5" s="19"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>106</v>
-      </c>
-      <c r="B6" s="26">
+        <v>107</v>
+      </c>
+      <c r="B6" s="27">
         <v>85</v>
       </c>
-      <c r="C6" s="26">
+      <c r="C6" s="27">
         <v>0</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="28">
         <v>100</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="28">
         <v>130</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="28">
         <v>160</v>
       </c>
-      <c r="G6" s="27">
+      <c r="G6" s="28">
         <v>185</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="28">
         <v>200</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="B7" s="21">
+        <v>100</v>
+      </c>
+      <c r="B7" s="22">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>196</v>
-      </c>
-      <c r="D8" s="28">
+        <v>197</v>
+      </c>
+      <c r="D8" s="29">
         <f>D6/$B$7</f>
         <v>0.5</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>E6/$B$7</f>
         <v>0.65</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="29">
         <f>F6/$B$7</f>
         <v>0.8</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="29">
         <f>G6/$B$7</f>
         <v>0.925</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="29">
         <f>H6/$B$7</f>
         <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>198</v>
-      </c>
-      <c r="E10" s="29">
+        <v>199</v>
+      </c>
+      <c r="E10" s="30">
         <f>IF(D6=0,0,(E6-D6)/D6)</f>
         <v>0.3</v>
       </c>
-      <c r="F10" s="29">
+      <c r="F10" s="30">
         <f>IF(E6=0,0,(F6-E6)/E6)</f>
         <v>0.23076923</v>
       </c>
-      <c r="G10" s="29">
+      <c r="G10" s="30">
         <f>IF(F6=0,0,(G6-F6)/F6)</f>
         <v>0.15625</v>
       </c>
-      <c r="H10" s="29">
+      <c r="H10" s="30">
         <f>IF(G6=0,0,(H6-G6)/G6)</f>
         <v>0.08108108</v>
       </c>
@@ -8772,7 +8795,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8781,361 +8804,361 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>200</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5" s="30">
+        <v>114</v>
+      </c>
+      <c r="B5" s="31">
         <v>1050000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>1405950</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>1782312</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>2122622</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>2363569</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" s="30">
+        <v>117</v>
+      </c>
+      <c r="B6" s="31">
         <v>35000</v>
       </c>
-      <c r="C6" s="30">
+      <c r="C6" s="31">
         <v>46865</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="31">
         <v>59410</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="31">
         <v>70754</v>
       </c>
-      <c r="F6" s="30">
+      <c r="F6" s="31">
         <v>78786</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>201</v>
-      </c>
-      <c r="B7" s="31">
+        <v>202</v>
+      </c>
+      <c r="B7" s="32">
         <f>SUM(B5,B6)</f>
         <v>1085000</v>
       </c>
-      <c r="C7" s="31">
+      <c r="C7" s="32">
         <f>SUM(C5,C6)</f>
         <v>1452815</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="32">
         <f>SUM(D5,D6)</f>
         <v>1841722</v>
       </c>
-      <c r="E7" s="31">
+      <c r="E7" s="32">
         <f>SUM(E5,E6)</f>
         <v>2193376</v>
       </c>
-      <c r="F7" s="31">
+      <c r="F7" s="32">
         <f>SUM(F5,F6)</f>
         <v>2442354</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
+      <c r="A8" s="19" t="s">
+        <v>203</v>
+      </c>
+      <c r="B8" s="19"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>117</v>
-      </c>
-      <c r="B9" s="30">
+        <v>118</v>
+      </c>
+      <c r="B9" s="31">
         <v>105000</v>
       </c>
-      <c r="C9" s="30">
+      <c r="C9" s="31">
         <v>140595</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="31">
         <v>178231</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="31">
         <v>212262</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="31">
         <v>236357</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>203</v>
-      </c>
-      <c r="B10" s="31">
+        <v>204</v>
+      </c>
+      <c r="B10" s="32">
         <f>SUM(B9)</f>
         <v>105000</v>
       </c>
-      <c r="C10" s="31">
+      <c r="C10" s="32">
         <f>SUM(C9)</f>
         <v>140595</v>
       </c>
-      <c r="D10" s="31">
+      <c r="D10" s="32">
         <f>SUM(D9)</f>
         <v>178231</v>
       </c>
-      <c r="E10" s="31">
+      <c r="E10" s="32">
         <f>SUM(E9)</f>
         <v>212262</v>
       </c>
-      <c r="F10" s="31">
+      <c r="F10" s="32">
         <f>SUM(F9)</f>
         <v>236357</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>204</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>205</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>119</v>
-      </c>
-      <c r="B12" s="30">
+        <v>120</v>
+      </c>
+      <c r="B12" s="31">
         <v>870000</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>1164930</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>1476773</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>1758744</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>1958385</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>205</v>
-      </c>
-      <c r="B13" s="31">
+        <v>206</v>
+      </c>
+      <c r="B13" s="32">
         <f>SUM(B12)</f>
         <v>870000</v>
       </c>
-      <c r="C13" s="31">
+      <c r="C13" s="32">
         <f>SUM(C12)</f>
         <v>1164930</v>
       </c>
-      <c r="D13" s="31">
+      <c r="D13" s="32">
         <f>SUM(D12)</f>
         <v>1476773</v>
       </c>
-      <c r="E13" s="31">
+      <c r="E13" s="32">
         <f>SUM(E12)</f>
         <v>1758744</v>
       </c>
-      <c r="F13" s="31">
+      <c r="F13" s="32">
         <f>SUM(F12)</f>
         <v>1958385</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="18" t="s">
-        <v>206</v>
-      </c>
-      <c r="B14" s="18"/>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
+      <c r="A14" s="19" t="s">
+        <v>207</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>121</v>
-      </c>
-      <c r="B15" s="22">
+        <v>122</v>
+      </c>
+      <c r="B15" s="23">
         <v>50000</v>
       </c>
-      <c r="C15" s="30">
+      <c r="C15" s="31">
         <v>51500</v>
       </c>
-      <c r="D15" s="30">
+      <c r="D15" s="31">
         <v>53045</v>
       </c>
-      <c r="E15" s="30">
+      <c r="E15" s="31">
         <v>54636</v>
       </c>
-      <c r="F15" s="30">
+      <c r="F15" s="31">
         <v>56275</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B16" s="22">
+        <v>125</v>
+      </c>
+      <c r="B16" s="23">
         <v>25000</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C16" s="31">
         <v>25750</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D16" s="31">
         <v>26523</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E16" s="31">
         <v>27318</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F16" s="31">
         <v>28138</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="B17" s="31">
+        <v>208</v>
+      </c>
+      <c r="B17" s="32">
         <f>SUM(B15,B16)</f>
         <v>75000</v>
       </c>
-      <c r="C17" s="31">
+      <c r="C17" s="32">
         <f>SUM(C15,C16)</f>
         <v>77250</v>
       </c>
-      <c r="D17" s="31">
+      <c r="D17" s="32">
         <f>SUM(D15,D16)</f>
         <v>79568</v>
       </c>
-      <c r="E17" s="31">
+      <c r="E17" s="32">
         <f>SUM(E15,E16)</f>
         <v>81955</v>
       </c>
-      <c r="F17" s="31">
+      <c r="F17" s="32">
         <f>SUM(F15,F16)</f>
         <v>84413</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="18" t="s">
-        <v>208</v>
-      </c>
-      <c r="B18" s="18"/>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
+      <c r="A18" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>125</v>
-      </c>
-      <c r="B19" s="30">
+        <v>126</v>
+      </c>
+      <c r="B19" s="31">
         <v>50000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>66950</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>84872</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>101077</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>112551</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>209</v>
-      </c>
-      <c r="B20" s="31">
+        <v>210</v>
+      </c>
+      <c r="B20" s="32">
         <f>SUM(B19)</f>
         <v>50000</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>SUM(C19)</f>
         <v>66950</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="32">
         <f>SUM(D19)</f>
         <v>84872</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="32">
         <f>SUM(E19)</f>
         <v>101077</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <f>SUM(F19)</f>
         <v>112551</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>210</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="A22" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="B22" s="33">
         <f>SUM(B7,B10,B13,B17,B20)</f>
         <v>1975000</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <f>SUM(C7,C10,C13,C17,C20)</f>
         <v>2621350</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <f>SUM(D7,D10,D13,D17,D20)</f>
         <v>3304704</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <f>SUM(E7,E10,E13,E17,E20)</f>
         <v>3922890</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <f>SUM(F7,F10,F13,F17,F20)</f>
         <v>4361347</v>
       </c>
@@ -9180,45 +9203,45 @@
       <c r="G1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>128</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="20" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="E3" s="20" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="20" t="s">
+      <c r="A3" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>133</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>212</v>
+      <c r="F3" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>213</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="C4" s="33">
+        <v>136</v>
+      </c>
+      <c r="C4" s="25">
         <v>1</v>
       </c>
-      <c r="D4" s="30">
+      <c r="D4" s="23">
         <v>95000</v>
       </c>
-      <c r="E4" s="29">
+      <c r="E4" s="24">
         <v>0.25</v>
       </c>
-      <c r="F4" s="29">
+      <c r="F4" s="24">
         <v>0.0765</v>
       </c>
       <c r="G4" s="34">
@@ -9227,21 +9250,21 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="33">
+        <v>136</v>
+      </c>
+      <c r="C5" s="25">
         <v>1</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="23">
         <v>75000</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="24">
         <v>0.25</v>
       </c>
-      <c r="F5" s="29">
+      <c r="F5" s="24">
         <v>0.0765</v>
       </c>
       <c r="G5" s="34">
@@ -9250,21 +9273,21 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C6" s="33">
+        <v>140</v>
+      </c>
+      <c r="C6" s="25">
         <v>6</v>
       </c>
-      <c r="D6" s="30">
+      <c r="D6" s="23">
         <v>48000</v>
       </c>
-      <c r="E6" s="29">
+      <c r="E6" s="24">
         <v>0.25</v>
       </c>
-      <c r="F6" s="29">
+      <c r="F6" s="24">
         <v>0.0765</v>
       </c>
       <c r="G6" s="34">
@@ -9273,21 +9296,21 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="B7" s="11" t="s">
         <v>140</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>139</v>
-      </c>
-      <c r="C7" s="33">
+      <c r="C7" s="25">
         <v>3</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="23">
         <v>32000</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="24">
         <v>0.2</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="24">
         <v>0.0765</v>
       </c>
       <c r="G7" s="34">
@@ -9296,21 +9319,21 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>142</v>
-      </c>
-      <c r="C8" s="33">
+        <v>143</v>
+      </c>
+      <c r="C8" s="25">
         <v>1</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="23">
         <v>42000</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="24">
         <v>0.25</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="24">
         <v>0.0765</v>
       </c>
       <c r="G8" s="34">
@@ -9319,21 +9342,21 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>144</v>
-      </c>
-      <c r="C9" s="33">
+        <v>145</v>
+      </c>
+      <c r="C9" s="25">
         <v>1</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="23">
         <v>52000</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="24">
         <v>0.25</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="24">
         <v>0.0765</v>
       </c>
       <c r="G9" s="34">
@@ -9341,79 +9364,79 @@
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="18" t="s">
-        <v>213</v>
-      </c>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
+      <c r="A11" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B12" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C12" s="20" t="s">
+      <c r="B12" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="C12" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="D12" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>105</v>
+      </c>
+      <c r="F12" s="21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>214</v>
-      </c>
-      <c r="B13" s="32">
+        <v>215</v>
+      </c>
+      <c r="B13" s="33">
         <v>854772</v>
       </c>
-      <c r="C13" s="32">
+      <c r="C13" s="33">
         <v>880415</v>
       </c>
-      <c r="D13" s="32">
+      <c r="D13" s="33">
         <v>906828</v>
       </c>
-      <c r="E13" s="32">
+      <c r="E13" s="33">
         <v>934032</v>
       </c>
-      <c r="F13" s="32">
+      <c r="F13" s="33">
         <v>962053</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>215</v>
-      </c>
-      <c r="B14" s="29">
+        <v>216</v>
+      </c>
+      <c r="B14" s="30">
         <v>0.4327959493670886</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="30">
         <v>0.3358632612966601</v>
       </c>
-      <c r="D14" s="29">
+      <c r="D14" s="30">
         <v>0.2744051364365971</v>
       </c>
-      <c r="E14" s="29">
+      <c r="E14" s="30">
         <v>0.23809805013927576</v>
       </c>
-      <c r="F14" s="29">
+      <c r="F14" s="30">
         <v>0.22058632258064514</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B15" s="35">
         <v>7.7</v>
@@ -9457,7 +9480,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9466,366 +9489,366 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="20" t="s">
-        <v>101</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="B3" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="C3" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="D3" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="E3" s="21" t="s">
         <v>105</v>
       </c>
+      <c r="F3" s="21" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="18" t="s">
-        <v>153</v>
-      </c>
-      <c r="B4" s="18"/>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
-      <c r="F4" s="18"/>
+      <c r="A4" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="19"/>
+      <c r="C4" s="19"/>
+      <c r="D4" s="19"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>218</v>
-      </c>
-      <c r="B5" s="30">
+        <v>219</v>
+      </c>
+      <c r="B5" s="31">
         <v>60000</v>
       </c>
-      <c r="C5" s="30">
+      <c r="C5" s="31">
         <v>80340</v>
       </c>
-      <c r="D5" s="30">
+      <c r="D5" s="31">
         <v>101846</v>
       </c>
-      <c r="E5" s="30">
+      <c r="E5" s="31">
         <v>121293</v>
       </c>
-      <c r="F5" s="30">
+      <c r="F5" s="31">
         <v>135061</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>219</v>
-      </c>
-      <c r="B6" s="31">
+        <v>220</v>
+      </c>
+      <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
         <v>60000</v>
       </c>
-      <c r="C6" s="31">
+      <c r="C6" s="32">
         <f>SUM(C5:C5)</f>
         <v>80340</v>
       </c>
-      <c r="D6" s="31">
+      <c r="D6" s="32">
         <f>SUM(D5:D5)</f>
         <v>101846</v>
       </c>
-      <c r="E6" s="31">
+      <c r="E6" s="32">
         <f>SUM(E5:E5)</f>
         <v>121293</v>
       </c>
-      <c r="F6" s="31">
+      <c r="F6" s="32">
         <f>SUM(F5:F5)</f>
         <v>135061</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="18" t="s">
-        <v>154</v>
-      </c>
-      <c r="B7" s="18"/>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
+      <c r="A7" s="19" t="s">
+        <v>155</v>
+      </c>
+      <c r="B7" s="19"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="19"/>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="30">
+        <v>221</v>
+      </c>
+      <c r="B8" s="31">
         <v>40000</v>
       </c>
-      <c r="C8" s="30">
+      <c r="C8" s="31">
         <v>53560</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="31">
         <v>67898</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="31">
         <v>80862</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="31">
         <v>90041</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>221</v>
-      </c>
-      <c r="B9" s="31">
+        <v>222</v>
+      </c>
+      <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
         <v>40000</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C9" s="32">
         <f>SUM(C8:C8)</f>
         <v>53560</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="32">
         <f>SUM(D8:D8)</f>
         <v>67898</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E9" s="32">
         <f>SUM(E8:E8)</f>
         <v>80862</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F9" s="32">
         <f>SUM(F8:F8)</f>
         <v>90041</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="18" t="s">
-        <v>147</v>
-      </c>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
+      <c r="A10" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>222</v>
-      </c>
-      <c r="B11" s="30">
+        <v>223</v>
+      </c>
+      <c r="B11" s="31">
         <v>102000</v>
       </c>
-      <c r="C11" s="30">
+      <c r="C11" s="31">
         <v>105060</v>
       </c>
-      <c r="D11" s="30">
+      <c r="D11" s="31">
         <v>108212</v>
       </c>
-      <c r="E11" s="30">
+      <c r="E11" s="31">
         <v>111458</v>
       </c>
-      <c r="F11" s="30">
+      <c r="F11" s="31">
         <v>114802</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>223</v>
-      </c>
-      <c r="B12" s="30">
+        <v>224</v>
+      </c>
+      <c r="B12" s="31">
         <v>14400</v>
       </c>
-      <c r="C12" s="30">
+      <c r="C12" s="31">
         <v>14832</v>
       </c>
-      <c r="D12" s="30">
+      <c r="D12" s="31">
         <v>15277</v>
       </c>
-      <c r="E12" s="30">
+      <c r="E12" s="31">
         <v>15735</v>
       </c>
-      <c r="F12" s="30">
+      <c r="F12" s="31">
         <v>16207</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>224</v>
-      </c>
-      <c r="B13" s="30">
+        <v>225</v>
+      </c>
+      <c r="B13" s="31">
         <v>12000</v>
       </c>
-      <c r="C13" s="30">
+      <c r="C13" s="31">
         <v>12360</v>
       </c>
-      <c r="D13" s="30">
+      <c r="D13" s="31">
         <v>12731</v>
       </c>
-      <c r="E13" s="30">
+      <c r="E13" s="31">
         <v>13113</v>
       </c>
-      <c r="F13" s="30">
+      <c r="F13" s="31">
         <v>13506</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>225</v>
-      </c>
-      <c r="B14" s="30">
+        <v>226</v>
+      </c>
+      <c r="B14" s="31">
         <v>8000</v>
       </c>
-      <c r="C14" s="30">
+      <c r="C14" s="31">
         <v>8240</v>
       </c>
-      <c r="D14" s="30">
+      <c r="D14" s="31">
         <v>8487</v>
       </c>
-      <c r="E14" s="30">
+      <c r="E14" s="31">
         <v>8742</v>
       </c>
-      <c r="F14" s="30">
+      <c r="F14" s="31">
         <v>9004</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>226</v>
-      </c>
-      <c r="B15" s="31">
+        <v>227</v>
+      </c>
+      <c r="B15" s="32">
         <f>SUM(B11:B14)</f>
         <v>136400</v>
       </c>
-      <c r="C15" s="31">
+      <c r="C15" s="32">
         <f>SUM(C11:C14)</f>
         <v>140492</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="32">
         <f>SUM(D11:D14)</f>
         <v>144707</v>
       </c>
-      <c r="E15" s="31">
+      <c r="E15" s="32">
         <f>SUM(E11:E14)</f>
         <v>149048</v>
       </c>
-      <c r="F15" s="31">
+      <c r="F15" s="32">
         <f>SUM(F11:F14)</f>
         <v>153519</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="18" t="s">
-        <v>156</v>
-      </c>
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-      <c r="F16" s="18"/>
+      <c r="A16" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>227</v>
-      </c>
-      <c r="B17" s="30">
+        <v>228</v>
+      </c>
+      <c r="B17" s="31">
         <v>15000</v>
       </c>
-      <c r="C17" s="30">
+      <c r="C17" s="31">
         <v>15450</v>
       </c>
-      <c r="D17" s="30">
+      <c r="D17" s="31">
         <v>15914</v>
       </c>
-      <c r="E17" s="30">
+      <c r="E17" s="31">
         <v>16391</v>
       </c>
-      <c r="F17" s="30">
+      <c r="F17" s="31">
         <v>16883</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>228</v>
-      </c>
-      <c r="B18" s="30">
+        <v>229</v>
+      </c>
+      <c r="B18" s="31">
         <v>8000</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="31">
         <v>8240</v>
       </c>
-      <c r="D18" s="30">
+      <c r="D18" s="31">
         <v>8487</v>
       </c>
-      <c r="E18" s="30">
+      <c r="E18" s="31">
         <v>8742</v>
       </c>
-      <c r="F18" s="30">
+      <c r="F18" s="31">
         <v>9004</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>229</v>
-      </c>
-      <c r="B19" s="30">
+        <v>230</v>
+      </c>
+      <c r="B19" s="31">
         <v>12000</v>
       </c>
-      <c r="C19" s="30">
+      <c r="C19" s="31">
         <v>12360</v>
       </c>
-      <c r="D19" s="30">
+      <c r="D19" s="31">
         <v>12731</v>
       </c>
-      <c r="E19" s="30">
+      <c r="E19" s="31">
         <v>13113</v>
       </c>
-      <c r="F19" s="30">
+      <c r="F19" s="31">
         <v>13506</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>230</v>
-      </c>
-      <c r="B20" s="31">
+        <v>231</v>
+      </c>
+      <c r="B20" s="32">
         <f>SUM(B17:B19)</f>
         <v>35000</v>
       </c>
-      <c r="C20" s="31">
+      <c r="C20" s="32">
         <f>SUM(C17:C19)</f>
         <v>36050</v>
       </c>
-      <c r="D20" s="31">
+      <c r="D20" s="32">
         <f>SUM(D17:D19)</f>
         <v>37132</v>
       </c>
-      <c r="E20" s="31">
+      <c r="E20" s="32">
         <f>SUM(E17:E19)</f>
         <v>38245</v>
       </c>
-      <c r="F20" s="31">
+      <c r="F20" s="32">
         <f>SUM(F17:F19)</f>
         <v>39393</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="18" t="s">
-        <v>231</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="A22" s="19" t="s">
+        <v>232</v>
+      </c>
+      <c r="B22" s="33">
         <f>B6+B9+B15+B20</f>
         <v>271400</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <f>C6+C9+C15+C20</f>
         <v>310442</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <f>D6+D9+D15+D20</f>
         <v>351582</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <f>E6+E9+E15+E20</f>
         <v>389448</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <f>F6+F9+F15+F20</f>
         <v>418014</v>
       </c>
@@ -9857,7 +9880,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9866,39 +9889,39 @@
       <c r="F1" s="15"/>
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
-        <v>160</v>
-      </c>
-      <c r="B3" s="20" t="s">
-        <v>129</v>
-      </c>
-      <c r="C3" s="20" t="s">
+      <c r="A3" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="D3" s="20" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" s="20" t="s">
+      <c r="B3" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>233</v>
+      <c r="D3" s="21" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>163</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>234</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="22">
+        <v>165</v>
+      </c>
+      <c r="C4" s="23">
         <v>250000</v>
       </c>
-      <c r="D4" s="29">
+      <c r="D4" s="24">
         <v>0.065</v>
       </c>
-      <c r="E4" s="36">
+      <c r="E4" s="22">
         <v>10</v>
       </c>
       <c r="F4" s="34">
@@ -9907,15 +9930,15 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>234</v>
-      </c>
-      <c r="C5" s="22">
+        <v>235</v>
+      </c>
+      <c r="C5" s="23">
         <v>25000</v>
       </c>
-      <c r="D5" s="29">
+      <c r="D5" s="30">
         <v>0</v>
       </c>
       <c r="E5" s="36">
@@ -9927,17 +9950,17 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>235</v>
-      </c>
-      <c r="F7" s="32">
+        <v>236</v>
+      </c>
+      <c r="F7" s="33">
         <v>34064</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>236</v>
-      </c>
-      <c r="F8" s="31">
+        <v>237</v>
+      </c>
+      <c r="F8" s="32">
         <v>250000</v>
       </c>
     </row>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="442">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1201,6 +1201,15 @@
     <t>Generated March 26, 2026</t>
   </si>
   <si>
+    <t>● Green = healthy</t>
+  </si>
+  <si>
+    <t>◐ Yellow = monitor</t>
+  </si>
+  <si>
+    <t>○ Red = action needed</t>
+  </si>
+  <si>
     <t>Metric</t>
   </si>
   <si>
@@ -1219,16 +1228,40 @@
     <t>Year 5</t>
   </si>
   <si>
+    <t>Benchmark</t>
+  </si>
+  <si>
     <t>Net Income</t>
   </si>
   <si>
+    <t>≥ $10,000</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
+    <t>≤ 55%</t>
+  </si>
+  <si>
     <t>Facility %</t>
   </si>
   <si>
+    <t>≤ 15%</t>
+  </si>
+  <si>
     <t>Operating Margin</t>
+  </si>
+  <si>
+    <t>≥ 10%</t>
+  </si>
+  <si>
+    <t>Revenue Sources</t>
+  </si>
+  <si>
+    <t>≥ 3 sources</t>
+  </si>
+  <si>
+    <t>≥ 1.25x</t>
   </si>
   <si>
     <t>Break-even Year</t>
@@ -1338,7 +1371,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1456,6 +1489,18 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFD97706"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <color rgb="FFDC2626"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
       <i/>
       <color rgb="FF9CA3AF"/>
       <sz val="11"/>
@@ -1546,7 +1591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="71">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1615,6 +1660,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1630,6 +1678,11 @@
     <xf numFmtId="166" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1643,14 +1696,35 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="21">
+  <dxfs count="24">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFE8F5E9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFFF8E1"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFCE4EC"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -7086,19 +7160,20 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF0D9488"/>
+    <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
     <col min="3" max="7" width="16" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="20" customWidth="1"/>
+    <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>387</v>
       </c>
@@ -7107,8 +7182,9 @@
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="H2" s="1"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="53" t="s">
         <v>388</v>
       </c>
@@ -7117,559 +7193,632 @@
       <c r="E3" s="53"/>
       <c r="F3" s="53"/>
       <c r="G3" s="53"/>
-    </row>
-    <row r="5" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B5" s="19" t="s">
+      <c r="H3" s="53"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="54" t="s">
         <v>389</v>
       </c>
-      <c r="C5" s="54" t="s">
+      <c r="D4" s="55" t="s">
         <v>390</v>
       </c>
-      <c r="D5" s="54" t="s">
+      <c r="F4" s="56" t="s">
         <v>391</v>
       </c>
-      <c r="E5" s="54" t="s">
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="19" t="s">
         <v>392</v>
       </c>
-      <c r="F5" s="54" t="s">
+      <c r="C6" s="57" t="s">
         <v>393</v>
       </c>
-      <c r="G5" s="54" t="s">
+      <c r="D6" s="57" t="s">
         <v>394</v>
       </c>
-    </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B6" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="C6" s="55">
-        <v>100</v>
-      </c>
-      <c r="D6" s="55">
-        <v>130</v>
-      </c>
-      <c r="E6" s="55">
-        <v>160</v>
-      </c>
-      <c r="F6" s="55">
-        <v>185</v>
-      </c>
-      <c r="G6" s="55">
-        <v>200</v>
+      <c r="E6" s="57" t="s">
+        <v>395</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>396</v>
+      </c>
+      <c r="G6" s="57" t="s">
+        <v>397</v>
+      </c>
+      <c r="H6" s="57" t="s">
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="C7" s="56">
-        <v>1975000</v>
-      </c>
-      <c r="D7" s="56">
-        <v>2621350</v>
-      </c>
-      <c r="E7" s="56">
-        <v>3304703.5</v>
-      </c>
-      <c r="F7" s="56">
-        <v>3922889.9299999997</v>
-      </c>
-      <c r="G7" s="56">
-        <v>4361346.638750001</v>
+        <v>385</v>
+      </c>
+      <c r="C7" s="58">
+        <v>100</v>
+      </c>
+      <c r="D7" s="58">
+        <v>130</v>
+      </c>
+      <c r="E7" s="58">
+        <v>160</v>
+      </c>
+      <c r="F7" s="58">
+        <v>185</v>
+      </c>
+      <c r="G7" s="58">
+        <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="C8" s="56">
-        <v>854772</v>
-      </c>
-      <c r="D8" s="56">
-        <v>880415.16</v>
-      </c>
-      <c r="E8" s="56">
-        <v>906827.6148</v>
-      </c>
-      <c r="F8" s="56">
-        <v>934032.443244</v>
-      </c>
-      <c r="G8" s="56">
-        <v>962053.4165413202</v>
+        <v>342</v>
+      </c>
+      <c r="C8" s="59">
+        <v>1975000</v>
+      </c>
+      <c r="D8" s="59">
+        <v>2621350</v>
+      </c>
+      <c r="E8" s="59">
+        <v>3304703.5</v>
+      </c>
+      <c r="F8" s="59">
+        <v>3922889.9299999997</v>
+      </c>
+      <c r="G8" s="59">
+        <v>4361346.638750001</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="C9" s="56">
-        <v>271400</v>
-      </c>
-      <c r="D9" s="56">
-        <v>310442</v>
-      </c>
-      <c r="E9" s="56">
-        <v>351582.25999999995</v>
-      </c>
-      <c r="F9" s="56">
-        <v>389447.9028</v>
-      </c>
-      <c r="G9" s="56">
-        <v>418013.9720340001</v>
+        <v>304</v>
+      </c>
+      <c r="C9" s="59">
+        <v>854772</v>
+      </c>
+      <c r="D9" s="59">
+        <v>880415.16</v>
+      </c>
+      <c r="E9" s="59">
+        <v>906827.6148</v>
+      </c>
+      <c r="F9" s="59">
+        <v>934032.443244</v>
+      </c>
+      <c r="G9" s="59">
+        <v>962053.4165413202</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
+        <v>305</v>
+      </c>
+      <c r="C10" s="59">
+        <v>271400</v>
+      </c>
+      <c r="D10" s="59">
+        <v>310442</v>
+      </c>
+      <c r="E10" s="59">
+        <v>351582.25999999995</v>
+      </c>
+      <c r="F10" s="59">
+        <v>389447.9028</v>
+      </c>
+      <c r="G10" s="59">
+        <v>418013.9720340001</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="C10" s="56">
+      <c r="C11" s="59">
         <v>34064.39316600799</v>
       </c>
-      <c r="D10" s="56">
+      <c r="D11" s="59">
         <v>34064.39316600799</v>
       </c>
-      <c r="E10" s="56">
+      <c r="E11" s="59">
         <v>34064.39316600799</v>
       </c>
-      <c r="F10" s="56">
+      <c r="F11" s="59">
         <v>34064.39316600799</v>
       </c>
-      <c r="G10" s="56">
+      <c r="G11" s="59">
         <v>34064.39316600799</v>
-      </c>
-    </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B11" s="10" t="s">
-        <v>395</v>
-      </c>
-      <c r="C11" s="57">
-        <v>789763.6068339921</v>
-      </c>
-      <c r="D11" s="57">
-        <v>1386428.446833992</v>
-      </c>
-      <c r="E11" s="57">
-        <v>2002229.2320339922</v>
-      </c>
-      <c r="F11" s="57">
-        <v>2560345.190789992</v>
-      </c>
-      <c r="G11" s="57">
-        <v>2942214.857008673</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="C12" s="57">
-        <v>864756</v>
-      </c>
-      <c r="D12" s="57">
-        <v>2251184.446833992</v>
-      </c>
-      <c r="E12" s="57">
-        <v>4253413.678867985</v>
-      </c>
-      <c r="F12" s="57">
-        <v>6813758.869657977</v>
-      </c>
-      <c r="G12" s="57">
-        <v>9755973.72666665</v>
+        <v>399</v>
+      </c>
+      <c r="C12" s="60">
+        <v>789763.6068339921</v>
+      </c>
+      <c r="D12" s="60">
+        <v>1386428.446833992</v>
+      </c>
+      <c r="E12" s="60">
+        <v>2002229.2320339922</v>
+      </c>
+      <c r="F12" s="60">
+        <v>2560345.190789992</v>
+      </c>
+      <c r="G12" s="60">
+        <v>2942214.857008673</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="C13" s="58">
-        <v>0.3998803072577175</v>
-      </c>
-      <c r="D13" s="58">
-        <v>0.5288986388059557</v>
-      </c>
-      <c r="E13" s="58">
-        <v>0.6058725788967125</v>
-      </c>
-      <c r="F13" s="58">
-        <v>0.6526681187789514</v>
-      </c>
-      <c r="G13" s="58">
-        <v>0.6746115593902751</v>
+        <v>346</v>
+      </c>
+      <c r="C13" s="60">
+        <v>864756</v>
+      </c>
+      <c r="D13" s="60">
+        <v>2251184.446833992</v>
+      </c>
+      <c r="E13" s="60">
+        <v>4253413.678867985</v>
+      </c>
+      <c r="F13" s="60">
+        <v>6813758.869657977</v>
+      </c>
+      <c r="G13" s="60">
+        <v>9755973.72666665</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="C14" s="61">
+        <v>0.3998803072577175</v>
+      </c>
+      <c r="D14" s="61">
+        <v>0.5288986388059557</v>
+      </c>
+      <c r="E14" s="61">
+        <v>0.6058725788967125</v>
+      </c>
+      <c r="F14" s="61">
+        <v>0.6526681187789514</v>
+      </c>
+      <c r="G14" s="61">
+        <v>0.6746115593902751</v>
+      </c>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="56">
+      <c r="C15" s="62">
         <v>19750</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D15" s="62">
         <v>20164.23076923077</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E15" s="62">
         <v>20654.396875</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F15" s="62">
         <v>21204.81043243243</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G15" s="62">
         <v>21806.733193750006</v>
       </c>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B15" s="10" t="s">
-        <v>396</v>
-      </c>
-      <c r="C15" s="58">
+      <c r="H15" s="63" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="C16" s="61">
         <v>0.4327959493670886</v>
       </c>
-      <c r="D15" s="58">
+      <c r="D16" s="61">
         <v>0.3358632612966601</v>
       </c>
-      <c r="E15" s="58">
+      <c r="E16" s="61">
         <v>0.2744051364365971</v>
       </c>
-      <c r="F15" s="58">
+      <c r="F16" s="61">
         <v>0.23809805013927576</v>
       </c>
-      <c r="G15" s="58">
+      <c r="G16" s="61">
         <v>0.22058632258064514</v>
       </c>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B16" s="10" t="s">
-        <v>397</v>
-      </c>
-      <c r="C16" s="58">
+      <c r="H16" s="63" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>403</v>
+      </c>
+      <c r="C17" s="61">
         <v>0.0412253164556962</v>
       </c>
-      <c r="D16" s="58">
+      <c r="D17" s="61">
         <v>0.035528487229862474</v>
       </c>
-      <c r="E16" s="58">
+      <c r="E17" s="61">
         <v>0.031916532905296946</v>
       </c>
-      <c r="F16" s="58">
+      <c r="F17" s="61">
         <v>0.029782729805013928</v>
       </c>
-      <c r="G16" s="58">
+      <c r="G17" s="61">
         <v>0.028753548387096775</v>
       </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
-        <v>398</v>
-      </c>
-      <c r="C17" s="58">
+      <c r="H17" s="63" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="C18" s="61">
         <v>0.42978632911392406</v>
       </c>
-      <c r="D17" s="58">
+      <c r="D18" s="61">
         <v>0.5457084479371316</v>
       </c>
-      <c r="E17" s="58">
+      <c r="E18" s="61">
         <v>0.6192064205457464</v>
       </c>
-      <c r="F17" s="58">
+      <c r="F18" s="61">
         <v>0.6626261838440112</v>
       </c>
-      <c r="G17" s="58">
+      <c r="G18" s="61">
         <v>0.6835685161290322</v>
       </c>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
+      <c r="H18" s="63" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C19" s="64">
+        <v>1</v>
+      </c>
+      <c r="D19" s="64"/>
+      <c r="E19" s="64"/>
+      <c r="F19" s="64"/>
+      <c r="G19" s="64"/>
+      <c r="H19" s="63" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="20" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B20" s="10" t="s">
         <v>344</v>
       </c>
-      <c r="C18" s="59">
+      <c r="C20" s="65">
         <v>24.918336160088252</v>
       </c>
-      <c r="D18" s="59">
+      <c r="D20" s="65">
         <v>41.993786092965045</v>
       </c>
-      <c r="E18" s="59">
+      <c r="E20" s="65">
         <v>60.071336519270375</v>
       </c>
-      <c r="F18" s="59">
+      <c r="F20" s="65">
         <v>76.3087007388667</v>
       </c>
-      <c r="G18" s="59">
+      <c r="G20" s="65">
         <v>87.51893026967599</v>
       </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="C19" s="60" t="s">
-        <v>390</v>
-      </c>
-      <c r="D19" s="60"/>
-      <c r="E19" s="60"/>
-      <c r="F19" s="60"/>
-      <c r="G19" s="60"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B20" s="10" t="s">
-        <v>400</v>
-      </c>
-      <c r="C20" s="60" t="s">
-        <v>401</v>
-      </c>
-      <c r="D20" s="60"/>
-      <c r="E20" s="60"/>
-      <c r="F20" s="60"/>
-      <c r="G20" s="60"/>
-    </row>
-    <row r="22" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>404</v>
-      </c>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19" t="s">
-        <v>405</v>
-      </c>
-      <c r="G22" s="19"/>
-    </row>
-    <row r="23" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B23" s="40" t="s">
-        <v>406</v>
-      </c>
-      <c r="C23" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="D23" s="62" t="s">
-        <v>408</v>
-      </c>
-      <c r="E23" s="62"/>
-      <c r="F23" s="63" t="s">
+      <c r="H20" s="63" t="s">
         <v>409</v>
       </c>
-      <c r="G23" s="63"/>
-    </row>
-    <row r="24" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="40" t="s">
+    </row>
+    <row r="21" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B21" s="10" t="s">
         <v>410</v>
       </c>
-      <c r="C24" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="D24" s="62" t="s">
+      <c r="C21" s="66" t="s">
+        <v>393</v>
+      </c>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="66"/>
+      <c r="G21" s="66"/>
+      <c r="H21" s="63" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
         <v>411</v>
       </c>
-      <c r="E24" s="62"/>
-      <c r="F24" s="63" t="s">
+      <c r="C22" s="66" t="s">
         <v>412</v>
       </c>
-      <c r="G24" s="63"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66"/>
+      <c r="G22" s="66"/>
+      <c r="H22" s="63" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>414</v>
+      </c>
+      <c r="D24" s="19" t="s">
+        <v>415</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
+        <v>416</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="40" t="s">
-        <v>413</v>
-      </c>
-      <c r="C25" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="D25" s="62" t="s">
-        <v>414</v>
-      </c>
-      <c r="E25" s="62"/>
-      <c r="F25" s="63" t="s">
-        <v>415</v>
-      </c>
-      <c r="G25" s="63"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>417</v>
+      </c>
+      <c r="C25" s="67" t="s">
+        <v>418</v>
+      </c>
+      <c r="D25" s="68" t="s">
+        <v>419</v>
+      </c>
+      <c r="E25" s="68"/>
+      <c r="F25" s="69" t="s">
+        <v>420</v>
+      </c>
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="40" t="s">
-        <v>416</v>
-      </c>
-      <c r="C26" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="D26" s="62" t="s">
-        <v>417</v>
-      </c>
-      <c r="E26" s="62"/>
-      <c r="F26" s="63" t="s">
+        <v>421</v>
+      </c>
+      <c r="C26" s="67" t="s">
         <v>418</v>
       </c>
-      <c r="G26" s="63"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="D26" s="68" t="s">
+        <v>422</v>
+      </c>
+      <c r="E26" s="68"/>
+      <c r="F26" s="69" t="s">
+        <v>423</v>
+      </c>
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="40" t="s">
-        <v>419</v>
-      </c>
-      <c r="C27" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="D27" s="62" t="s">
-        <v>420</v>
-      </c>
-      <c r="E27" s="62"/>
-      <c r="F27" s="63" t="s">
-        <v>421</v>
-      </c>
-      <c r="G27" s="63"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>424</v>
+      </c>
+      <c r="C27" s="67" t="s">
+        <v>418</v>
+      </c>
+      <c r="D27" s="68" t="s">
+        <v>425</v>
+      </c>
+      <c r="E27" s="68"/>
+      <c r="F27" s="69" t="s">
+        <v>426</v>
+      </c>
+      <c r="G27" s="69"/>
+      <c r="H27" s="69"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="40" t="s">
-        <v>422</v>
-      </c>
-      <c r="C28" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="D28" s="62" t="s">
-        <v>423</v>
-      </c>
-      <c r="E28" s="62"/>
-      <c r="F28" s="63" t="s">
-        <v>424</v>
-      </c>
-      <c r="G28" s="63"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+        <v>427</v>
+      </c>
+      <c r="C28" s="67" t="s">
+        <v>418</v>
+      </c>
+      <c r="D28" s="68" t="s">
+        <v>428</v>
+      </c>
+      <c r="E28" s="68"/>
+      <c r="F28" s="69" t="s">
+        <v>429</v>
+      </c>
+      <c r="G28" s="69"/>
+      <c r="H28" s="69"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="40" t="s">
-        <v>425</v>
-      </c>
-      <c r="C29" s="61" t="s">
-        <v>407</v>
-      </c>
-      <c r="D29" s="62" t="s">
-        <v>426</v>
-      </c>
-      <c r="E29" s="62"/>
-      <c r="F29" s="63" t="s">
-        <v>427</v>
-      </c>
-      <c r="G29" s="63"/>
-    </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+        <v>430</v>
+      </c>
+      <c r="C29" s="67" t="s">
+        <v>418</v>
+      </c>
+      <c r="D29" s="68" t="s">
+        <v>431</v>
+      </c>
+      <c r="E29" s="68"/>
+      <c r="F29" s="69" t="s">
+        <v>432</v>
+      </c>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B30" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="C30" s="67" t="s">
+        <v>418</v>
+      </c>
+      <c r="D30" s="68" t="s">
+        <v>434</v>
+      </c>
+      <c r="E30" s="68"/>
+      <c r="F30" s="69" t="s">
+        <v>435</v>
+      </c>
+      <c r="G30" s="69"/>
+      <c r="H30" s="69"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="C31" s="10" t="s">
-        <v>429</v>
-      </c>
-      <c r="D31" s="10"/>
-      <c r="E31" s="10"/>
-    </row>
-    <row r="33" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B33" s="64" t="s">
-        <v>430</v>
-      </c>
-      <c r="C33" s="64"/>
-      <c r="D33" s="64"/>
-      <c r="E33" s="64"/>
-      <c r="F33" s="64"/>
-      <c r="G33" s="64"/>
+        <v>436</v>
+      </c>
+      <c r="C31" s="67" t="s">
+        <v>418</v>
+      </c>
+      <c r="D31" s="68" t="s">
+        <v>437</v>
+      </c>
+      <c r="E31" s="68"/>
+      <c r="F31" s="69" t="s">
+        <v>438</v>
+      </c>
+      <c r="G31" s="69"/>
+      <c r="H31" s="69"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B33" s="40" t="s">
+        <v>439</v>
+      </c>
+      <c r="C33" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="70" t="s">
+        <v>441</v>
+      </c>
+      <c r="C35" s="70"/>
+      <c r="D35" s="70"/>
+      <c r="E35" s="70"/>
+      <c r="F35" s="70"/>
+      <c r="G35" s="70"/>
+      <c r="H35" s="70"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B3:G3"/>
+  <mergeCells count="23">
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="D22:E22"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="D23:E23"/>
-    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:G25"/>
+    <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F26:H26"/>
     <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:G27"/>
+    <mergeCell ref="F27:H27"/>
     <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:G28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:G29"/>
-    <mergeCell ref="C31:E31"/>
-    <mergeCell ref="B33:G33"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
-  <conditionalFormatting sqref="C11:G11">
+  <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>C11&gt;=0</formula>
+      <formula>C12&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C11&gt;=-1</formula>
+      <formula>C12&gt;=-1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="2" priority="3">
-      <formula>C11&lt;-1</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:G12">
-    <cfRule type="expression" dxfId="3" priority="1">
-      <formula>C12&gt;=0</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>C12&gt;=-1</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="5" priority="3">
       <formula>C12&lt;-1</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C13:G13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>C13&gt;=0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="4" priority="2">
+      <formula>C13&gt;=-1</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="5" priority="3">
+      <formula>C13&lt;-1</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C14:G14">
     <cfRule type="expression" dxfId="6" priority="1">
-      <formula>C13&gt;=0.05</formula>
+      <formula>C14&gt;=0.05</formula>
     </cfRule>
     <cfRule type="expression" dxfId="7" priority="2">
-      <formula>C13&gt;=0</formula>
+      <formula>C14&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="8" priority="3">
-      <formula>C13&lt;0</formula>
+      <formula>C14&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C15:G15">
     <cfRule type="expression" dxfId="9" priority="1">
-      <formula>C15&lt;=0.55</formula>
+      <formula>C15&gt;=10000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="10" priority="2">
-      <formula>C15&lt;=0.65</formula>
+      <formula>C15&gt;=7000</formula>
     </cfRule>
     <cfRule type="expression" dxfId="11" priority="3">
-      <formula>C15&gt;0.65</formula>
+      <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.15</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.25</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.25</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&gt;=0.10</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&gt;=0</formula>
+      <formula>C17&lt;=0.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&lt;0</formula>
+      <formula>C17&gt;0.25</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=1.25</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=1.0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;1.0</formula>
+      <formula>C18&lt;0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C20:G20">
+    <cfRule type="expression" dxfId="21" priority="1">
+      <formula>C20&gt;=1.25</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="22" priority="2">
+      <formula>C20&gt;=1.0</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="23" priority="3">
+      <formula>C20&lt;1.0</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="445">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -980,6 +980,15 @@
   </si>
   <si>
     <t>BOTTOM LINE</t>
+  </si>
+  <si>
+    <t>Cumulative Profit</t>
+  </si>
+  <si>
+    <t>Break-even</t>
+  </si>
+  <si>
+    <t>✓ Break-even</t>
   </si>
   <si>
     <t>LOAN TERMS</t>
@@ -1466,6 +1475,12 @@
     </font>
     <font>
       <b/>
+      <color rgb="FF16A34A"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF328555"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1479,12 +1494,6 @@
     <font>
       <i/>
       <color rgb="FF6B7280"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
@@ -1591,7 +1600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1640,18 +1649,24 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1659,8 +1674,8 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1681,19 +1696,16 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -4583,7 +4595,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4803,6 +4815,51 @@
       <c r="F15" s="30">
         <f>IF(F5=0,0,F14/F5)</f>
         <v>0.67461156</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="10" t="s">
+        <v>316</v>
+      </c>
+      <c r="B16" s="34">
+        <f>B14</f>
+        <v>789764</v>
+      </c>
+      <c r="C16" s="34">
+        <f>B16+C14</f>
+        <v>2176192</v>
+      </c>
+      <c r="D16" s="34">
+        <f>C16+D14</f>
+        <v>4178421</v>
+      </c>
+      <c r="E16" s="34">
+        <f>D16+E14</f>
+        <v>6738766</v>
+      </c>
+      <c r="F16" s="34">
+        <f>E16+F14</f>
+        <v>9680981</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="B17" s="40" t="s">
+        <v>318</v>
+      </c>
+      <c r="C17" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="D17" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="41" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4861,7 +4918,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4870,19 +4927,19 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="40" t="s">
-        <v>317</v>
-      </c>
-      <c r="B5" s="41" t="s">
+      <c r="A5" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="B5" s="43" t="s">
         <v>162</v>
       </c>
-      <c r="C5" s="42" t="s">
-        <v>318</v>
-      </c>
-      <c r="D5" s="40" t="s">
-        <v>319</v>
-      </c>
-      <c r="E5" s="41" t="s">
+      <c r="C5" s="44" t="s">
+        <v>321</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="E5" s="43" t="s">
         <v>234</v>
       </c>
     </row>
@@ -4906,7 +4963,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -4916,7 +4973,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B9" s="31">
         <f>B6</f>
@@ -4941,7 +4998,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -4966,7 +5023,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -4991,7 +5048,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -5016,7 +5073,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -5065,7 +5122,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5095,7 +5152,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5105,32 +5162,32 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>328</v>
-      </c>
-      <c r="B5" s="43">
+        <v>331</v>
+      </c>
+      <c r="B5" s="45">
         <f>'Monthly Cash Flow Y1'!M14</f>
         <v>864756</v>
       </c>
-      <c r="C5" s="43">
+      <c r="C5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14</f>
         <v>2251184</v>
       </c>
-      <c r="D5" s="43">
+      <c r="D5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
         <v>4253414</v>
       </c>
-      <c r="E5" s="43">
+      <c r="E5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
         <v>6813759</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="45">
         <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
         <v>9755974</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="B6" s="31">
         <v>12000</v>
@@ -5150,7 +5207,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="B7" s="31">
         <v>180000</v>
@@ -5170,7 +5227,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B8" s="31">
         <v>5000</v>
@@ -5190,7 +5247,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
@@ -5215,7 +5272,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5225,7 +5282,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="B12" s="31">
         <v>8000</v>
@@ -5245,7 +5302,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
@@ -5270,7 +5327,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
@@ -5295,7 +5352,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5305,7 +5362,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
@@ -5330,25 +5387,25 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>339</v>
-      </c>
-      <c r="B19" s="44" t="str">
+        <v>342</v>
+      </c>
+      <c r="B19" s="46" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="44" t="str">
+      <c r="C19" s="46" t="str">
         <f>C9-C14-C17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="45">
+      <c r="D19" s="47">
         <f>D9-D14-D17</f>
         <v>1</v>
       </c>
-      <c r="E19" s="45">
+      <c r="E19" s="47">
         <f>E9-E14-E17</f>
         <v>1</v>
       </c>
-      <c r="F19" s="44" t="str">
+      <c r="F19" s="46" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -5379,7 +5436,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5409,7 +5466,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5419,7 +5476,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B5" s="31">
         <v>1975000</v>
@@ -5479,7 +5536,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B8" s="34">
         <f>B5-B6-B7</f>
@@ -5524,32 +5581,32 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="B10" s="46">
+        <v>347</v>
+      </c>
+      <c r="B10" s="48">
         <f>IF(B9=0,"N/A",B8/B9)</f>
         <v>24.92</v>
       </c>
-      <c r="C10" s="46">
+      <c r="C10" s="48">
         <f>IF(C9=0,"N/A",C8/C9)</f>
         <v>41.99</v>
       </c>
-      <c r="D10" s="46">
+      <c r="D10" s="48">
         <f>IF(D9=0,"N/A",D8/D9)</f>
         <v>60.07</v>
       </c>
-      <c r="E10" s="46">
+      <c r="E10" s="48">
         <f>IF(E9=0,"N/A",E8/E9)</f>
         <v>76.31</v>
       </c>
-      <c r="F10" s="46">
+      <c r="F10" s="48">
         <f>IF(F9=0,"N/A",F8/F9)</f>
         <v>87.52</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -5559,7 +5616,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="B13" s="31">
         <v>864756</v>
@@ -5579,7 +5636,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="B14" s="36">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5604,7 +5661,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5649,7 +5706,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -5679,7 +5736,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="B20" s="31">
         <v>888836</v>
@@ -5699,7 +5756,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B21" s="31">
         <v>2714</v>
@@ -5719,27 +5776,27 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>352</v>
-      </c>
-      <c r="B22" s="47">
+        <v>355</v>
+      </c>
+      <c r="B22" s="49">
         <v>53</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C22" s="49">
         <v>52</v>
       </c>
-      <c r="D22" s="47">
+      <c r="D22" s="49">
         <v>51</v>
       </c>
-      <c r="E22" s="47">
+      <c r="E22" s="49">
         <v>51</v>
       </c>
-      <c r="F22" s="47">
+      <c r="F22" s="49">
         <v>51</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -5749,102 +5806,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>354</v>
-      </c>
-      <c r="B25" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="C25" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="D25" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="E25" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="F25" s="48" t="s">
-        <v>355</v>
+        <v>357</v>
+      </c>
+      <c r="B25" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="C25" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="D25" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="E25" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="F25" s="50" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="B26" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="C26" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="D26" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="E26" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="F26" s="48" t="s">
-        <v>355</v>
+        <v>359</v>
+      </c>
+      <c r="B26" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="E26" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="F26" s="50" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="B27" s="49" t="s">
-        <v>358</v>
-      </c>
-      <c r="C27" s="49" t="s">
-        <v>358</v>
-      </c>
-      <c r="D27" s="49" t="s">
-        <v>358</v>
-      </c>
-      <c r="E27" s="49" t="s">
-        <v>358</v>
-      </c>
-      <c r="F27" s="49" t="s">
-        <v>358</v>
+        <v>360</v>
+      </c>
+      <c r="B27" s="51" t="s">
+        <v>361</v>
+      </c>
+      <c r="C27" s="51" t="s">
+        <v>361</v>
+      </c>
+      <c r="D27" s="51" t="s">
+        <v>361</v>
+      </c>
+      <c r="E27" s="51" t="s">
+        <v>361</v>
+      </c>
+      <c r="F27" s="51" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="B28" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="C28" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="D28" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="E28" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="F28" s="48" t="s">
-        <v>355</v>
+        <v>362</v>
+      </c>
+      <c r="B28" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="C28" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="D28" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="E28" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="F28" s="50" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="B29" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="C29" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="D29" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="E29" s="48" t="s">
-        <v>355</v>
-      </c>
-      <c r="F29" s="48" t="s">
-        <v>355</v>
+        <v>363</v>
+      </c>
+      <c r="B29" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="C29" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="D29" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="E29" s="50" t="s">
+        <v>358</v>
+      </c>
+      <c r="F29" s="50" t="s">
+        <v>358</v>
       </c>
     </row>
   </sheetData>
@@ -5884,16 +5941,16 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>361</v>
-      </c>
-      <c r="B3" s="50" t="s">
+      <c r="A3" s="52" t="s">
+        <v>364</v>
+      </c>
+      <c r="B3" s="52" t="s">
         <v>112</v>
       </c>
-      <c r="D3" s="50" t="s">
-        <v>362</v>
-      </c>
-      <c r="E3" s="50" t="s">
+      <c r="D3" s="52" t="s">
+        <v>365</v>
+      </c>
+      <c r="E3" s="52" t="s">
         <v>112</v>
       </c>
     </row>
@@ -5905,7 +5962,7 @@
         <v>250000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="E4" s="31">
         <v>200000</v>
@@ -5927,13 +5984,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="B6" s="31">
         <v>75000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="E6" s="31">
         <v>75000</v>
@@ -5941,7 +5998,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E7" s="31">
         <v>50000</v>
@@ -5949,13 +6006,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="B9" s="33">
         <v>375000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="E9" s="33">
         <v>375000</v>
@@ -5963,9 +6020,9 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>369</v>
-      </c>
-      <c r="B10" s="44">
+        <v>372</v>
+      </c>
+      <c r="B10" s="46">
         <v>0</v>
       </c>
     </row>
@@ -6311,7 +6368,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6321,7 +6378,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6331,7 +6388,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6356,7 +6413,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B6" s="31">
         <v>1975000</v>
@@ -6436,27 +6493,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="B10" s="51">
+        <v>347</v>
+      </c>
+      <c r="B10" s="53">
         <v>24.92</v>
       </c>
-      <c r="C10" s="51">
+      <c r="C10" s="53">
         <v>41.99</v>
       </c>
-      <c r="D10" s="51">
+      <c r="D10" s="53">
         <v>60.07</v>
       </c>
-      <c r="E10" s="51">
+      <c r="E10" s="53">
         <v>76.31</v>
       </c>
-      <c r="F10" s="51">
+      <c r="F10" s="53">
         <v>87.52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B11" s="36">
         <v>53</v>
@@ -6476,7 +6533,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6486,7 +6543,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6511,7 +6568,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B16" s="31">
         <v>1678750</v>
@@ -6591,27 +6648,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="B20" s="51">
+        <v>347</v>
+      </c>
+      <c r="B20" s="53">
         <v>16.22</v>
       </c>
-      <c r="C20" s="51">
+      <c r="C20" s="53">
         <v>30.45</v>
       </c>
-      <c r="D20" s="51">
+      <c r="D20" s="53">
         <v>45.52</v>
       </c>
-      <c r="E20" s="51">
+      <c r="E20" s="53">
         <v>59.03</v>
       </c>
-      <c r="F20" s="51">
+      <c r="F20" s="53">
         <v>68.31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B21" s="36">
         <v>54</v>
@@ -6631,7 +6688,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -6641,7 +6698,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6666,7 +6723,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="B26" s="31">
         <v>1975000</v>
@@ -6746,27 +6803,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="B30" s="51">
+        <v>347</v>
+      </c>
+      <c r="B30" s="53">
         <v>24.52</v>
       </c>
-      <c r="C30" s="51">
+      <c r="C30" s="53">
         <v>41.49</v>
       </c>
-      <c r="D30" s="51">
+      <c r="D30" s="53">
         <v>59.46</v>
       </c>
-      <c r="E30" s="51">
+      <c r="E30" s="53">
         <v>75.6</v>
       </c>
-      <c r="F30" s="51">
+      <c r="F30" s="53">
         <v>86.74</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="B31" s="36">
         <v>53</v>
@@ -6812,7 +6869,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6846,7 +6903,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6870,7 +6927,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6878,7 +6935,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6898,25 +6955,25 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="52" t="s">
+      <c r="D12" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="E12" s="52" t="s">
+      <c r="E12" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="F12" s="52" t="s">
+      <c r="F12" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="52" t="s">
+      <c r="G12" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="52" t="s">
+      <c r="H12" s="54" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="D13" s="31">
         <v>1975000</v>
@@ -6976,7 +7033,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D16" s="31">
         <v>864756</v>
@@ -6996,7 +7053,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="D17" s="31">
         <v>231645</v>
@@ -7016,7 +7073,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7036,25 +7093,25 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="52" t="s">
+      <c r="D20" s="54" t="s">
         <v>102</v>
       </c>
-      <c r="E20" s="52" t="s">
+      <c r="E20" s="54" t="s">
         <v>103</v>
       </c>
-      <c r="F20" s="52" t="s">
+      <c r="F20" s="54" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="52" t="s">
+      <c r="G20" s="54" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="52" t="s">
+      <c r="H20" s="54" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="D21" s="30">
         <v>0.3998803072577175</v>
@@ -7074,21 +7131,21 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>344</v>
-      </c>
-      <c r="D22" s="51">
+        <v>347</v>
+      </c>
+      <c r="D22" s="53">
         <v>24.92</v>
       </c>
-      <c r="E22" s="51">
+      <c r="E22" s="53">
         <v>41.99</v>
       </c>
-      <c r="F22" s="51">
+      <c r="F22" s="53">
         <v>60.07</v>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="53">
         <v>76.31</v>
       </c>
-      <c r="H22" s="51">
+      <c r="H22" s="53">
         <v>87.52</v>
       </c>
     </row>
@@ -7114,7 +7171,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D24" s="36">
         <v>100</v>
@@ -7134,7 +7191,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7175,7 +7232,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7185,87 +7242,87 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="53" t="s">
-        <v>388</v>
-      </c>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="53"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="53"/>
-      <c r="H3" s="53"/>
+      <c r="B3" s="55" t="s">
+        <v>391</v>
+      </c>
+      <c r="C3" s="55"/>
+      <c r="D3" s="55"/>
+      <c r="E3" s="55"/>
+      <c r="F3" s="55"/>
+      <c r="G3" s="55"/>
+      <c r="H3" s="55"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="54" t="s">
-        <v>389</v>
-      </c>
-      <c r="D4" s="55" t="s">
-        <v>390</v>
-      </c>
-      <c r="F4" s="56" t="s">
-        <v>391</v>
+      <c r="B4" s="56" t="s">
+        <v>392</v>
+      </c>
+      <c r="D4" s="57" t="s">
+        <v>393</v>
+      </c>
+      <c r="F4" s="58" t="s">
+        <v>394</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>392</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>393</v>
-      </c>
-      <c r="D6" s="57" t="s">
-        <v>394</v>
-      </c>
-      <c r="E6" s="57" t="s">
         <v>395</v>
       </c>
-      <c r="F6" s="57" t="s">
+      <c r="C6" s="59" t="s">
         <v>396</v>
       </c>
-      <c r="G6" s="57" t="s">
+      <c r="D6" s="59" t="s">
         <v>397</v>
       </c>
-      <c r="H6" s="57" t="s">
+      <c r="E6" s="59" t="s">
         <v>398</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>399</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>400</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>385</v>
-      </c>
-      <c r="C7" s="58">
+        <v>388</v>
+      </c>
+      <c r="C7" s="60">
         <v>100</v>
       </c>
-      <c r="D7" s="58">
+      <c r="D7" s="60">
         <v>130</v>
       </c>
-      <c r="E7" s="58">
+      <c r="E7" s="60">
         <v>160</v>
       </c>
-      <c r="F7" s="58">
+      <c r="F7" s="60">
         <v>185</v>
       </c>
-      <c r="G7" s="58">
+      <c r="G7" s="60">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>342</v>
-      </c>
-      <c r="C8" s="59">
+        <v>345</v>
+      </c>
+      <c r="C8" s="61">
         <v>1975000</v>
       </c>
-      <c r="D8" s="59">
+      <c r="D8" s="61">
         <v>2621350</v>
       </c>
-      <c r="E8" s="59">
+      <c r="E8" s="61">
         <v>3304703.5</v>
       </c>
-      <c r="F8" s="59">
+      <c r="F8" s="61">
         <v>3922889.9299999997</v>
       </c>
-      <c r="G8" s="59">
+      <c r="G8" s="61">
         <v>4361346.638750001</v>
       </c>
     </row>
@@ -7273,19 +7330,19 @@
       <c r="B9" s="11" t="s">
         <v>304</v>
       </c>
-      <c r="C9" s="59">
+      <c r="C9" s="61">
         <v>854772</v>
       </c>
-      <c r="D9" s="59">
+      <c r="D9" s="61">
         <v>880415.16</v>
       </c>
-      <c r="E9" s="59">
+      <c r="E9" s="61">
         <v>906827.6148</v>
       </c>
-      <c r="F9" s="59">
+      <c r="F9" s="61">
         <v>934032.443244</v>
       </c>
-      <c r="G9" s="59">
+      <c r="G9" s="61">
         <v>962053.4165413202</v>
       </c>
     </row>
@@ -7293,19 +7350,19 @@
       <c r="B10" s="11" t="s">
         <v>305</v>
       </c>
-      <c r="C10" s="59">
+      <c r="C10" s="61">
         <v>271400</v>
       </c>
-      <c r="D10" s="59">
+      <c r="D10" s="61">
         <v>310442</v>
       </c>
-      <c r="E10" s="59">
+      <c r="E10" s="61">
         <v>351582.25999999995</v>
       </c>
-      <c r="F10" s="59">
+      <c r="F10" s="61">
         <v>389447.9028</v>
       </c>
-      <c r="G10" s="59">
+      <c r="G10" s="61">
         <v>418013.9720340001</v>
       </c>
     </row>
@@ -7313,79 +7370,79 @@
       <c r="B11" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="C11" s="59">
+      <c r="C11" s="61">
         <v>34064.39316600799</v>
       </c>
-      <c r="D11" s="59">
+      <c r="D11" s="61">
         <v>34064.39316600799</v>
       </c>
-      <c r="E11" s="59">
+      <c r="E11" s="61">
         <v>34064.39316600799</v>
       </c>
-      <c r="F11" s="59">
+      <c r="F11" s="61">
         <v>34064.39316600799</v>
       </c>
-      <c r="G11" s="59">
+      <c r="G11" s="61">
         <v>34064.39316600799</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>399</v>
-      </c>
-      <c r="C12" s="60">
+        <v>402</v>
+      </c>
+      <c r="C12" s="62">
         <v>789763.6068339921</v>
       </c>
-      <c r="D12" s="60">
+      <c r="D12" s="62">
         <v>1386428.446833992</v>
       </c>
-      <c r="E12" s="60">
+      <c r="E12" s="62">
         <v>2002229.2320339922</v>
       </c>
-      <c r="F12" s="60">
+      <c r="F12" s="62">
         <v>2560345.190789992</v>
       </c>
-      <c r="G12" s="60">
+      <c r="G12" s="62">
         <v>2942214.857008673</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>346</v>
-      </c>
-      <c r="C13" s="60">
+        <v>349</v>
+      </c>
+      <c r="C13" s="62">
         <v>864756</v>
       </c>
-      <c r="D13" s="60">
+      <c r="D13" s="62">
         <v>2251184.446833992</v>
       </c>
-      <c r="E13" s="60">
+      <c r="E13" s="62">
         <v>4253413.678867985</v>
       </c>
-      <c r="F13" s="60">
+      <c r="F13" s="62">
         <v>6813758.869657977</v>
       </c>
-      <c r="G13" s="60">
+      <c r="G13" s="62">
         <v>9755973.72666665</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>384</v>
-      </c>
-      <c r="C14" s="61">
+        <v>387</v>
+      </c>
+      <c r="C14" s="63">
         <v>0.3998803072577175</v>
       </c>
-      <c r="D14" s="61">
+      <c r="D14" s="63">
         <v>0.5288986388059557</v>
       </c>
-      <c r="E14" s="61">
+      <c r="E14" s="63">
         <v>0.6058725788967125</v>
       </c>
-      <c r="F14" s="61">
+      <c r="F14" s="63">
         <v>0.6526681187789514</v>
       </c>
-      <c r="G14" s="61">
+      <c r="G14" s="63">
         <v>0.6746115593902751</v>
       </c>
     </row>
@@ -7393,319 +7450,319 @@
       <c r="B15" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="C15" s="62">
+      <c r="C15" s="64">
         <v>19750</v>
       </c>
-      <c r="D15" s="62">
+      <c r="D15" s="64">
         <v>20164.23076923077</v>
       </c>
-      <c r="E15" s="62">
+      <c r="E15" s="64">
         <v>20654.396875</v>
       </c>
-      <c r="F15" s="62">
+      <c r="F15" s="64">
         <v>21204.81043243243</v>
       </c>
-      <c r="G15" s="62">
+      <c r="G15" s="64">
         <v>21806.733193750006</v>
       </c>
-      <c r="H15" s="63" t="s">
-        <v>400</v>
+      <c r="H15" s="65" t="s">
+        <v>403</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>401</v>
-      </c>
-      <c r="C16" s="61">
+        <v>404</v>
+      </c>
+      <c r="C16" s="63">
         <v>0.4327959493670886</v>
       </c>
-      <c r="D16" s="61">
+      <c r="D16" s="63">
         <v>0.3358632612966601</v>
       </c>
-      <c r="E16" s="61">
+      <c r="E16" s="63">
         <v>0.2744051364365971</v>
       </c>
-      <c r="F16" s="61">
+      <c r="F16" s="63">
         <v>0.23809805013927576</v>
       </c>
-      <c r="G16" s="61">
+      <c r="G16" s="63">
         <v>0.22058632258064514</v>
       </c>
-      <c r="H16" s="63" t="s">
-        <v>402</v>
+      <c r="H16" s="65" t="s">
+        <v>405</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>403</v>
-      </c>
-      <c r="C17" s="61">
+        <v>406</v>
+      </c>
+      <c r="C17" s="63">
         <v>0.0412253164556962</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="63">
         <v>0.035528487229862474</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="63">
         <v>0.031916532905296946</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="63">
         <v>0.029782729805013928</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="63">
         <v>0.028753548387096775</v>
       </c>
-      <c r="H17" s="63" t="s">
-        <v>404</v>
+      <c r="H17" s="65" t="s">
+        <v>407</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>405</v>
-      </c>
-      <c r="C18" s="61">
+        <v>408</v>
+      </c>
+      <c r="C18" s="63">
         <v>0.42978632911392406</v>
       </c>
-      <c r="D18" s="61">
+      <c r="D18" s="63">
         <v>0.5457084479371316</v>
       </c>
-      <c r="E18" s="61">
+      <c r="E18" s="63">
         <v>0.6192064205457464</v>
       </c>
-      <c r="F18" s="61">
+      <c r="F18" s="63">
         <v>0.6626261838440112</v>
       </c>
-      <c r="G18" s="61">
+      <c r="G18" s="63">
         <v>0.6835685161290322</v>
       </c>
-      <c r="H18" s="63" t="s">
-        <v>406</v>
+      <c r="H18" s="65" t="s">
+        <v>409</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>407</v>
-      </c>
-      <c r="C19" s="64">
-        <v>1</v>
-      </c>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
-      <c r="F19" s="64"/>
-      <c r="G19" s="64"/>
-      <c r="H19" s="63" t="s">
-        <v>408</v>
+        <v>410</v>
+      </c>
+      <c r="C19" s="66">
+        <v>4</v>
+      </c>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="65" t="s">
+        <v>411</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>344</v>
-      </c>
-      <c r="C20" s="65">
+        <v>347</v>
+      </c>
+      <c r="C20" s="67">
         <v>24.918336160088252</v>
       </c>
-      <c r="D20" s="65">
+      <c r="D20" s="67">
         <v>41.993786092965045</v>
       </c>
-      <c r="E20" s="65">
+      <c r="E20" s="67">
         <v>60.071336519270375</v>
       </c>
-      <c r="F20" s="65">
+      <c r="F20" s="67">
         <v>76.3087007388667</v>
       </c>
-      <c r="G20" s="65">
+      <c r="G20" s="67">
         <v>87.51893026967599</v>
       </c>
-      <c r="H20" s="63" t="s">
-        <v>409</v>
+      <c r="H20" s="65" t="s">
+        <v>412</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>410</v>
-      </c>
-      <c r="C21" s="66" t="s">
-        <v>393</v>
-      </c>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="63" t="s">
-        <v>393</v>
+        <v>413</v>
+      </c>
+      <c r="C21" s="68" t="s">
+        <v>396</v>
+      </c>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="65" t="s">
+        <v>396</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>411</v>
-      </c>
-      <c r="C22" s="66" t="s">
-        <v>412</v>
-      </c>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66"/>
-      <c r="G22" s="66"/>
-      <c r="H22" s="63" t="s">
-        <v>412</v>
+        <v>414</v>
+      </c>
+      <c r="C22" s="68" t="s">
+        <v>415</v>
+      </c>
+      <c r="D22" s="68"/>
+      <c r="E22" s="68"/>
+      <c r="F22" s="68"/>
+      <c r="G22" s="68"/>
+      <c r="H22" s="65" t="s">
+        <v>415</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="40" t="s">
-        <v>417</v>
-      </c>
-      <c r="C25" s="67" t="s">
-        <v>418</v>
-      </c>
-      <c r="D25" s="68" t="s">
-        <v>419</v>
-      </c>
-      <c r="E25" s="68"/>
-      <c r="F25" s="69" t="s">
+      <c r="B25" s="42" t="s">
         <v>420</v>
       </c>
-      <c r="G25" s="69"/>
-      <c r="H25" s="69"/>
+      <c r="C25" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="D25" s="69" t="s">
+        <v>422</v>
+      </c>
+      <c r="E25" s="69"/>
+      <c r="F25" s="70" t="s">
+        <v>423</v>
+      </c>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="40" t="s">
+      <c r="B26" s="42" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="C26" s="67" t="s">
-        <v>418</v>
-      </c>
-      <c r="D26" s="68" t="s">
-        <v>422</v>
-      </c>
-      <c r="E26" s="68"/>
-      <c r="F26" s="69" t="s">
-        <v>423</v>
-      </c>
-      <c r="G26" s="69"/>
-      <c r="H26" s="69"/>
+      <c r="D26" s="69" t="s">
+        <v>425</v>
+      </c>
+      <c r="E26" s="69"/>
+      <c r="F26" s="70" t="s">
+        <v>426</v>
+      </c>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="40" t="s">
-        <v>424</v>
-      </c>
-      <c r="C27" s="67" t="s">
-        <v>418</v>
-      </c>
-      <c r="D27" s="68" t="s">
-        <v>425</v>
-      </c>
-      <c r="E27" s="68"/>
-      <c r="F27" s="69" t="s">
-        <v>426</v>
-      </c>
-      <c r="G27" s="69"/>
-      <c r="H27" s="69"/>
+      <c r="B27" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="C27" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="D27" s="69" t="s">
+        <v>428</v>
+      </c>
+      <c r="E27" s="69"/>
+      <c r="F27" s="70" t="s">
+        <v>429</v>
+      </c>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="40" t="s">
-        <v>427</v>
-      </c>
-      <c r="C28" s="67" t="s">
-        <v>418</v>
-      </c>
-      <c r="D28" s="68" t="s">
-        <v>428</v>
-      </c>
-      <c r="E28" s="68"/>
-      <c r="F28" s="69" t="s">
-        <v>429</v>
-      </c>
-      <c r="G28" s="69"/>
-      <c r="H28" s="69"/>
+      <c r="B28" s="42" t="s">
+        <v>430</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="D28" s="69" t="s">
+        <v>431</v>
+      </c>
+      <c r="E28" s="69"/>
+      <c r="F28" s="70" t="s">
+        <v>432</v>
+      </c>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="40" t="s">
-        <v>430</v>
-      </c>
-      <c r="C29" s="67" t="s">
-        <v>418</v>
-      </c>
-      <c r="D29" s="68" t="s">
-        <v>431</v>
-      </c>
-      <c r="E29" s="68"/>
-      <c r="F29" s="69" t="s">
-        <v>432</v>
-      </c>
-      <c r="G29" s="69"/>
-      <c r="H29" s="69"/>
+      <c r="B29" s="42" t="s">
+        <v>433</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>434</v>
+      </c>
+      <c r="E29" s="69"/>
+      <c r="F29" s="70" t="s">
+        <v>435</v>
+      </c>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="C30" s="67" t="s">
-        <v>418</v>
-      </c>
-      <c r="D30" s="68" t="s">
-        <v>434</v>
-      </c>
-      <c r="E30" s="68"/>
-      <c r="F30" s="69" t="s">
-        <v>435</v>
-      </c>
-      <c r="G30" s="69"/>
-      <c r="H30" s="69"/>
+      <c r="B30" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="C30" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="D30" s="69" t="s">
+        <v>437</v>
+      </c>
+      <c r="E30" s="69"/>
+      <c r="F30" s="70" t="s">
+        <v>438</v>
+      </c>
+      <c r="G30" s="70"/>
+      <c r="H30" s="70"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="40" t="s">
-        <v>436</v>
-      </c>
-      <c r="C31" s="67" t="s">
-        <v>418</v>
-      </c>
-      <c r="D31" s="68" t="s">
-        <v>437</v>
-      </c>
-      <c r="E31" s="68"/>
-      <c r="F31" s="69" t="s">
-        <v>438</v>
-      </c>
-      <c r="G31" s="69"/>
-      <c r="H31" s="69"/>
+      <c r="B31" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>421</v>
+      </c>
+      <c r="D31" s="69" t="s">
+        <v>440</v>
+      </c>
+      <c r="E31" s="69"/>
+      <c r="F31" s="70" t="s">
+        <v>441</v>
+      </c>
+      <c r="G31" s="70"/>
+      <c r="H31" s="70"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="40" t="s">
-        <v>439</v>
+      <c r="B33" s="42" t="s">
+        <v>442</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="70" t="s">
-        <v>441</v>
-      </c>
-      <c r="C35" s="70"/>
-      <c r="D35" s="70"/>
-      <c r="E35" s="70"/>
-      <c r="F35" s="70"/>
-      <c r="G35" s="70"/>
-      <c r="H35" s="70"/>
+      <c r="B35" s="71" t="s">
+        <v>444</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="71"/>
+      <c r="F35" s="71"/>
+      <c r="G35" s="71"/>
+      <c r="H35" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="23">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -7872,10 +7872,10 @@
       <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1.0</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1.0</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="445">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1600,7 +1600,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1700,6 +1700,9 @@
     <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7580,13 +7583,26 @@
       <c r="B21" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="C21" s="68" t="s">
-        <v>396</v>
-      </c>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
+      <c r="C21" s="40" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="68" t="str">
+        <f>IF('5-Year Operating Stmt'!C16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="68" t="str">
+        <f>IF('5-Year Operating Stmt'!D16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="68" t="str">
+        <f>IF('5-Year Operating Stmt'!E16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="68" t="str">
+        <f>IF('5-Year Operating Stmt'!F16&gt;=0,"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
       <c r="H21" s="65" t="s">
         <v>396</v>
       </c>
@@ -7595,13 +7611,13 @@
       <c r="B22" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="C22" s="68" t="s">
+      <c r="C22" s="69" t="s">
         <v>415</v>
       </c>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69"/>
+      <c r="G22" s="69"/>
       <c r="H22" s="65" t="s">
         <v>415</v>
       </c>
@@ -7630,15 +7646,15 @@
       <c r="C25" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="D25" s="69" t="s">
+      <c r="D25" s="70" t="s">
         <v>422</v>
       </c>
-      <c r="E25" s="69"/>
-      <c r="F25" s="70" t="s">
+      <c r="E25" s="70"/>
+      <c r="F25" s="71" t="s">
         <v>423</v>
       </c>
-      <c r="G25" s="70"/>
-      <c r="H25" s="70"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="71"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
@@ -7647,15 +7663,15 @@
       <c r="C26" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="D26" s="69" t="s">
+      <c r="D26" s="70" t="s">
         <v>425</v>
       </c>
-      <c r="E26" s="69"/>
-      <c r="F26" s="70" t="s">
+      <c r="E26" s="70"/>
+      <c r="F26" s="71" t="s">
         <v>426</v>
       </c>
-      <c r="G26" s="70"/>
-      <c r="H26" s="70"/>
+      <c r="G26" s="71"/>
+      <c r="H26" s="71"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
@@ -7664,15 +7680,15 @@
       <c r="C27" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="D27" s="69" t="s">
+      <c r="D27" s="70" t="s">
         <v>428</v>
       </c>
-      <c r="E27" s="69"/>
-      <c r="F27" s="70" t="s">
+      <c r="E27" s="70"/>
+      <c r="F27" s="71" t="s">
         <v>429</v>
       </c>
-      <c r="G27" s="70"/>
-      <c r="H27" s="70"/>
+      <c r="G27" s="71"/>
+      <c r="H27" s="71"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
@@ -7681,15 +7697,15 @@
       <c r="C28" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="D28" s="69" t="s">
+      <c r="D28" s="70" t="s">
         <v>431</v>
       </c>
-      <c r="E28" s="69"/>
-      <c r="F28" s="70" t="s">
+      <c r="E28" s="70"/>
+      <c r="F28" s="71" t="s">
         <v>432</v>
       </c>
-      <c r="G28" s="70"/>
-      <c r="H28" s="70"/>
+      <c r="G28" s="71"/>
+      <c r="H28" s="71"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
@@ -7698,15 +7714,15 @@
       <c r="C29" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="D29" s="69" t="s">
+      <c r="D29" s="70" t="s">
         <v>434</v>
       </c>
-      <c r="E29" s="69"/>
-      <c r="F29" s="70" t="s">
+      <c r="E29" s="70"/>
+      <c r="F29" s="71" t="s">
         <v>435</v>
       </c>
-      <c r="G29" s="70"/>
-      <c r="H29" s="70"/>
+      <c r="G29" s="71"/>
+      <c r="H29" s="71"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
@@ -7715,15 +7731,15 @@
       <c r="C30" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="D30" s="69" t="s">
+      <c r="D30" s="70" t="s">
         <v>437</v>
       </c>
-      <c r="E30" s="69"/>
-      <c r="F30" s="70" t="s">
+      <c r="E30" s="70"/>
+      <c r="F30" s="71" t="s">
         <v>438</v>
       </c>
-      <c r="G30" s="70"/>
-      <c r="H30" s="70"/>
+      <c r="G30" s="71"/>
+      <c r="H30" s="71"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
@@ -7732,15 +7748,15 @@
       <c r="C31" s="40" t="s">
         <v>421</v>
       </c>
-      <c r="D31" s="69" t="s">
+      <c r="D31" s="70" t="s">
         <v>440</v>
       </c>
-      <c r="E31" s="69"/>
-      <c r="F31" s="70" t="s">
+      <c r="E31" s="70"/>
+      <c r="F31" s="71" t="s">
         <v>441</v>
       </c>
-      <c r="G31" s="70"/>
-      <c r="H31" s="70"/>
+      <c r="G31" s="71"/>
+      <c r="H31" s="71"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="42" t="s">
@@ -7754,22 +7770,21 @@
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="71" t="s">
+      <c r="B35" s="72" t="s">
         <v>444</v>
       </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="71"/>
-      <c r="F35" s="71"/>
-      <c r="G35" s="71"/>
-      <c r="H35" s="71"/>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="72"/>
+      <c r="F35" s="72"/>
+      <c r="G35" s="72"/>
+      <c r="H35" s="72"/>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="22">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
     <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C21:G21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
@@ -7850,10 +7865,10 @@
       <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.25</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.25</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C18:G18">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="794" uniqueCount="445">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="446">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1276,10 +1276,13 @@
     <t>Break-even Year</t>
   </si>
   <si>
-    <t>Cash Runway</t>
-  </si>
-  <si>
-    <t>60+ months</t>
+    <t>Cash Runway (Months)</t>
+  </si>
+  <si>
+    <t>60+</t>
+  </si>
+  <si>
+    <t>≥ 24 months</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1516,7 +1519,7 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1546,6 +1549,16 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF1E293B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCE4EC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1600,7 +1613,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1697,14 +1710,24 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="9" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -7548,10 +7571,18 @@
       <c r="C19" s="66">
         <v>4</v>
       </c>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
+      <c r="D19" s="66">
+        <v>4</v>
+      </c>
+      <c r="E19" s="66">
+        <v>4</v>
+      </c>
+      <c r="F19" s="66">
+        <v>4</v>
+      </c>
+      <c r="G19" s="66">
+        <v>4</v>
+      </c>
       <c r="H19" s="65" t="s">
         <v>411</v>
       </c>
@@ -7588,19 +7619,19 @@
         <v>✓ Break-even</v>
       </c>
       <c r="D21" s="68" t="str">
-        <f>IF('5-Year Operating Stmt'!C16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="E21" s="68" t="str">
-        <f>IF('5-Year Operating Stmt'!D16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="F21" s="68" t="str">
-        <f>IF('5-Year Operating Stmt'!E16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="G21" s="68" t="str">
-        <f>IF('5-Year Operating Stmt'!F16&gt;=0,"✓ Break-even","")</f>
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
@@ -7611,181 +7642,187 @@
       <c r="B22" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="C22" s="69" t="s">
+      <c r="C22" s="69">
+        <v>9</v>
+      </c>
+      <c r="D22" s="70">
+        <v>22</v>
+      </c>
+      <c r="E22" s="66">
+        <v>39</v>
+      </c>
+      <c r="F22" s="71" t="s">
         <v>415</v>
       </c>
-      <c r="D22" s="69"/>
-      <c r="E22" s="69"/>
-      <c r="F22" s="69"/>
-      <c r="G22" s="69"/>
+      <c r="G22" s="71" t="s">
+        <v>415</v>
+      </c>
       <c r="H22" s="65" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="42" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="D25" s="70" t="s">
         <v>422</v>
       </c>
-      <c r="E25" s="70"/>
-      <c r="F25" s="71" t="s">
+      <c r="D25" s="72" t="s">
         <v>423</v>
       </c>
-      <c r="G25" s="71"/>
-      <c r="H25" s="71"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="73" t="s">
+        <v>424</v>
+      </c>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="D26" s="70" t="s">
-        <v>425</v>
-      </c>
-      <c r="E26" s="70"/>
-      <c r="F26" s="71" t="s">
+        <v>422</v>
+      </c>
+      <c r="D26" s="72" t="s">
         <v>426</v>
       </c>
-      <c r="G26" s="71"/>
-      <c r="H26" s="71"/>
+      <c r="E26" s="72"/>
+      <c r="F26" s="73" t="s">
+        <v>427</v>
+      </c>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="D27" s="70" t="s">
-        <v>428</v>
-      </c>
-      <c r="E27" s="70"/>
-      <c r="F27" s="71" t="s">
+        <v>422</v>
+      </c>
+      <c r="D27" s="72" t="s">
         <v>429</v>
       </c>
-      <c r="G27" s="71"/>
-      <c r="H27" s="71"/>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73" t="s">
+        <v>430</v>
+      </c>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="D28" s="70" t="s">
-        <v>431</v>
-      </c>
-      <c r="E28" s="70"/>
-      <c r="F28" s="71" t="s">
+        <v>422</v>
+      </c>
+      <c r="D28" s="72" t="s">
         <v>432</v>
       </c>
-      <c r="G28" s="71"/>
-      <c r="H28" s="71"/>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73" t="s">
+        <v>433</v>
+      </c>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="D29" s="70" t="s">
-        <v>434</v>
-      </c>
-      <c r="E29" s="70"/>
-      <c r="F29" s="71" t="s">
+        <v>422</v>
+      </c>
+      <c r="D29" s="72" t="s">
         <v>435</v>
       </c>
-      <c r="G29" s="71"/>
-      <c r="H29" s="71"/>
+      <c r="E29" s="72"/>
+      <c r="F29" s="73" t="s">
+        <v>436</v>
+      </c>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="D30" s="70" t="s">
-        <v>437</v>
-      </c>
-      <c r="E30" s="70"/>
-      <c r="F30" s="71" t="s">
+        <v>422</v>
+      </c>
+      <c r="D30" s="72" t="s">
         <v>438</v>
       </c>
-      <c r="G30" s="71"/>
-      <c r="H30" s="71"/>
+      <c r="E30" s="72"/>
+      <c r="F30" s="73" t="s">
+        <v>439</v>
+      </c>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>421</v>
-      </c>
-      <c r="D31" s="70" t="s">
-        <v>440</v>
-      </c>
-      <c r="E31" s="70"/>
-      <c r="F31" s="71" t="s">
+        <v>422</v>
+      </c>
+      <c r="D31" s="72" t="s">
         <v>441</v>
       </c>
-      <c r="G31" s="71"/>
-      <c r="H31" s="71"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="73" t="s">
+        <v>442</v>
+      </c>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="42" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
       <c r="F33" s="10"/>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="72" t="s">
-        <v>444</v>
-      </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="72"/>
-      <c r="F35" s="72"/>
-      <c r="G35" s="72"/>
-      <c r="H35" s="72"/>
+      <c r="B35" s="74" t="s">
+        <v>445</v>
+      </c>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
     </row>
   </sheetData>
-  <mergeCells count="22">
+  <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C22:G22"/>
     <mergeCell ref="D24:E24"/>
     <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -1330,7 +1330,7 @@
     <t>Facility Burden</t>
   </si>
   <si>
-    <t>Facility costs at 3% of revenue are well-managed and leave budget for programs.</t>
+    <t>Facility costs at 4% of revenue are well-managed and leave budget for programs.</t>
   </si>
   <si>
     <t>Watch for rent escalation clauses that could push this higher over time.</t>
@@ -7523,19 +7523,19 @@
         <v>406</v>
       </c>
       <c r="C17" s="63">
-        <v>0.0412253164556962</v>
+        <v>0.0690632911392405</v>
       </c>
       <c r="D17" s="63">
-        <v>0.035528487229862474</v>
+        <v>0.05359528487229862</v>
       </c>
       <c r="E17" s="63">
-        <v>0.031916532905296946</v>
+        <v>0.043788121990369175</v>
       </c>
       <c r="F17" s="63">
-        <v>0.029782729805013928</v>
+        <v>0.03799442896935934</v>
       </c>
       <c r="G17" s="63">
-        <v>0.028753548387096775</v>
+        <v>0.035199999999999995</v>
       </c>
       <c r="H17" s="65" t="s">
         <v>407</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -40,7 +40,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated March 26, 2026 · nonprofit_501c3</t>
+    <t>Generated March 27, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +160,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 26, 2026</t>
+    <t>March 27, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1207,7 +1207,7 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 26, 2026</t>
+    <t>Generated March 27, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="452">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -763,70 +763,88 @@
     <t>Staffing Costs Forecast</t>
   </si>
   <si>
+    <t xml:space="preserve">  Teachers [6 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Paraprofessionals [3 FTE]</t>
+  </si>
+  <si>
+    <t>Total Instructional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Head of School [1 FTE]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Assistant Principal [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total School Leadership</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  School Counselor [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total Student Support</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Office Manager [1 FTE]</t>
+  </si>
+  <si>
+    <t>Total Administrative</t>
+  </si>
+  <si>
+    <t>TOTAL PERSONNEL</t>
+  </si>
+  <si>
+    <t>Heritage Academy - Budget Detail</t>
+  </si>
+  <si>
+    <t>REVENUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Tuition</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Registration Fee</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Scholarship Discount</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  FL FTC Scholarship</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Foundation Grant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Annual Fund</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  After-School Programs</t>
+  </si>
+  <si>
+    <t>Total Revenue</t>
+  </si>
+  <si>
+    <t>PERSONNEL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Head of School</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Assistant Principal</t>
+  </si>
+  <si>
     <t xml:space="preserve">  Teachers</t>
   </si>
   <si>
     <t xml:space="preserve">  Paraprofessionals</t>
   </si>
   <si>
-    <t>Total Instructional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Head of School</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Assistant Principal</t>
-  </si>
-  <si>
-    <t>Total School Leadership</t>
+    <t xml:space="preserve">  Office Manager</t>
   </si>
   <si>
     <t xml:space="preserve">  School Counselor</t>
-  </si>
-  <si>
-    <t>Total Student Support</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Office Manager</t>
-  </si>
-  <si>
-    <t>Total Administrative</t>
-  </si>
-  <si>
-    <t>TOTAL PERSONNEL</t>
-  </si>
-  <si>
-    <t>Heritage Academy - Budget Detail</t>
-  </si>
-  <si>
-    <t>REVENUE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Tuition</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Registration Fee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Scholarship Discount</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  FL FTC Scholarship</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Foundation Grant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Annual Fund</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  After-School Programs</t>
-  </si>
-  <si>
-    <t>Total Revenue</t>
-  </si>
-  <si>
-    <t>PERSONNEL</t>
   </si>
   <si>
     <t xml:space="preserve">    Curriculum</t>
@@ -3277,7 +3295,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>246</v>
+        <v>265</v>
       </c>
       <c r="B15" s="31">
         <v>126018</v>
@@ -3297,7 +3315,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>247</v>
+        <v>266</v>
       </c>
       <c r="B16" s="31">
         <v>99488</v>
@@ -3317,7 +3335,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>243</v>
+        <v>267</v>
       </c>
       <c r="B17" s="31">
         <v>382032</v>
@@ -3337,7 +3355,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B18" s="31">
         <v>122544</v>
@@ -3357,7 +3375,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B19" s="31">
         <v>55713</v>
@@ -3377,7 +3395,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>249</v>
+        <v>270</v>
       </c>
       <c r="B20" s="31">
         <v>68978</v>
@@ -3437,7 +3455,7 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B25" s="31">
         <v>60000</v>
@@ -3462,7 +3480,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="B27" s="31">
         <v>40000</v>
@@ -3487,7 +3505,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B29" s="31">
         <v>102000</v>
@@ -3507,7 +3525,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B30" s="31">
         <v>14400</v>
@@ -3527,7 +3545,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B31" s="31">
         <v>12000</v>
@@ -3547,7 +3565,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="B32" s="31">
         <v>8000</v>
@@ -3567,7 +3585,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B33" s="32">
         <f>SUM(B29:B32)</f>
@@ -3597,7 +3615,7 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="B35" s="31">
         <v>15000</v>
@@ -3617,7 +3635,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B36" s="31">
         <v>8000</v>
@@ -3637,7 +3655,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="B37" s="31">
         <v>12000</v>
@@ -3657,7 +3675,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B38" s="32">
         <f>SUM(B35:B37)</f>
@@ -3682,7 +3700,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B39" s="32">
         <f>B25+B27+B33+B38</f>
@@ -3707,7 +3725,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
@@ -3717,7 +3735,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="B42" s="31">
         <v>34064</v>
@@ -3737,7 +3755,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B43" s="31">
         <v>25000</v>
@@ -3757,7 +3775,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B44" s="32">
         <f>SUM(B42:B43)</f>
@@ -3806,7 +3824,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3886,7 +3904,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
@@ -3911,7 +3929,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
@@ -3936,7 +3954,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
@@ -3961,7 +3979,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -3971,7 +3989,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B11" s="33">
         <f>B4-B8</f>
@@ -3996,7 +4014,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -4021,7 +4039,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B13" s="31">
         <v>789764</v>
@@ -4061,7 +4079,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="B15" s="31">
         <v>11852</v>
@@ -4106,7 +4124,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4127,43 +4145,43 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -4231,7 +4249,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -4249,7 +4267,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B7" s="31">
         <v>71231</v>
@@ -4294,7 +4312,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B8" s="31">
         <v>22617</v>
@@ -4339,7 +4357,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B9" s="31">
         <v>4922</v>
@@ -4384,7 +4402,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4402,7 +4420,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
@@ -4459,7 +4477,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
@@ -4516,7 +4534,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
@@ -4573,7 +4591,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -4588,7 +4606,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
@@ -4597,7 +4615,7 @@
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
@@ -4630,7 +4648,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4690,7 +4708,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4700,7 +4718,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B8" s="34">
         <v>854772</v>
@@ -4720,7 +4738,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B9" s="34">
         <v>271400</v>
@@ -4740,7 +4758,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="B10" s="34">
         <v>59064</v>
@@ -4760,7 +4778,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="39" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B11" s="32">
         <f>SUM(B8:B10)</f>
@@ -4785,7 +4803,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -4795,7 +4813,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="39" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B14" s="33">
         <f>B5-B11</f>
@@ -4820,7 +4838,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B15" s="30">
         <f>IF(B5=0,0,B14/B5)</f>
@@ -4845,7 +4863,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="B16" s="34">
         <f>B14</f>
@@ -4870,10 +4888,10 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B17" s="40" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="C17" s="41" t="s">
         <v>7</v>
@@ -4944,7 +4962,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4954,16 +4972,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="42" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="B5" s="43" t="s">
         <v>162</v>
       </c>
       <c r="C5" s="44" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="E5" s="43" t="s">
         <v>234</v>
@@ -4989,7 +5007,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -4999,7 +5017,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="B9" s="31">
         <f>B6</f>
@@ -5024,7 +5042,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5049,7 +5067,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5074,7 +5092,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -5099,7 +5117,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -5148,7 +5166,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5178,7 +5196,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5188,7 +5206,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="B5" s="45">
         <f>'Monthly Cash Flow Y1'!M14</f>
@@ -5213,7 +5231,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="B6" s="31">
         <v>12000</v>
@@ -5233,7 +5251,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="B7" s="31">
         <v>180000</v>
@@ -5253,7 +5271,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="B8" s="31">
         <v>5000</v>
@@ -5273,7 +5291,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
@@ -5298,7 +5316,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5308,7 +5326,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="B12" s="31">
         <v>8000</v>
@@ -5328,7 +5346,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
@@ -5353,7 +5371,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
@@ -5378,7 +5396,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5388,7 +5406,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
@@ -5413,7 +5431,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="B19" s="46" t="str">
         <f>B9-B14-B17</f>
@@ -5462,7 +5480,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5492,7 +5510,7 @@
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5502,7 +5520,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B5" s="31">
         <v>1975000</v>
@@ -5522,7 +5540,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="B6" s="31">
         <v>854772</v>
@@ -5542,7 +5560,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B7" s="31">
         <v>271400</v>
@@ -5562,7 +5580,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="B8" s="34">
         <f>B5-B6-B7</f>
@@ -5587,7 +5605,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="B9" s="31">
         <v>34064</v>
@@ -5607,7 +5625,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B10" s="48">
         <f>IF(B9=0,"N/A",B8/B9)</f>
@@ -5632,7 +5650,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -5642,7 +5660,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B13" s="31">
         <v>864756</v>
@@ -5662,7 +5680,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="B14" s="36">
         <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
@@ -5687,7 +5705,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B15" s="35">
         <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
@@ -5732,7 +5750,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -5762,7 +5780,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B20" s="31">
         <v>888836</v>
@@ -5782,7 +5800,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="B21" s="31">
         <v>2714</v>
@@ -5802,7 +5820,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B22" s="49">
         <v>53</v>
@@ -5822,7 +5840,7 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="19" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="B24" s="19"/>
       <c r="C24" s="19"/>
@@ -5832,102 +5850,102 @@
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="B25" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C25" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D25" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E25" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F25" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B26" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C26" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D26" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E26" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F26" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="B27" s="51" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="D27" s="51" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="E27" s="51" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="F27" s="51" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="B28" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C28" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D28" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E28" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F28" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B29" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="C29" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D29" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="E29" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F29" s="50" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -5968,13 +5986,13 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="52" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="B3" s="52" t="s">
         <v>112</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="E3" s="52" t="s">
         <v>112</v>
@@ -5988,7 +6006,7 @@
         <v>250000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="E4" s="31">
         <v>200000</v>
@@ -6010,13 +6028,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B6" s="31">
         <v>75000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="E6" s="31">
         <v>75000</v>
@@ -6024,7 +6042,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="E7" s="31">
         <v>50000</v>
@@ -6032,13 +6050,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="B9" s="33">
         <v>375000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="E9" s="33">
         <v>375000</v>
@@ -6046,7 +6064,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="B10" s="46">
         <v>0</v>
@@ -6394,7 +6412,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6404,7 +6422,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6414,7 +6432,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6439,7 +6457,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B6" s="31">
         <v>1975000</v>
@@ -6459,7 +6477,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B7" s="31">
         <v>1160236</v>
@@ -6479,7 +6497,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B8" s="33">
         <v>814764</v>
@@ -6499,7 +6517,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B9" s="30">
         <v>0.4125385351058188</v>
@@ -6519,7 +6537,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B10" s="53">
         <v>24.92</v>
@@ -6539,7 +6557,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B11" s="36">
         <v>53</v>
@@ -6559,7 +6577,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6569,7 +6587,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6594,7 +6612,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B16" s="31">
         <v>1678750</v>
@@ -6614,7 +6632,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B17" s="31">
         <v>1160236</v>
@@ -6634,7 +6652,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B18" s="33">
         <v>518514</v>
@@ -6654,7 +6672,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B19" s="30">
         <v>0.308868864830375</v>
@@ -6674,7 +6692,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B20" s="53">
         <v>16.22</v>
@@ -6694,7 +6712,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B21" s="36">
         <v>54</v>
@@ -6714,7 +6732,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -6724,7 +6742,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6749,7 +6767,7 @@
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B26" s="31">
         <v>1975000</v>
@@ -6769,7 +6787,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B27" s="31">
         <v>1173736</v>
@@ -6789,7 +6807,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B28" s="33">
         <v>801264</v>
@@ -6809,7 +6827,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B29" s="30">
         <v>0.4057030920678441</v>
@@ -6829,7 +6847,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B30" s="53">
         <v>24.52</v>
@@ -6849,7 +6867,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B31" s="36">
         <v>53</v>
@@ -6895,7 +6913,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6929,7 +6947,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6953,7 +6971,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -6961,7 +6979,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -6999,7 +7017,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D13" s="31">
         <v>1975000</v>
@@ -7019,7 +7037,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D14" s="31">
         <v>1160236</v>
@@ -7039,7 +7057,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D15" s="31">
         <v>789764</v>
@@ -7059,7 +7077,7 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="D16" s="31">
         <v>864756</v>
@@ -7079,7 +7097,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D17" s="31">
         <v>231645</v>
@@ -7099,7 +7117,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7137,7 +7155,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D21" s="30">
         <v>0.3998803072577175</v>
@@ -7157,7 +7175,7 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="D22" s="53">
         <v>24.92</v>
@@ -7197,7 +7215,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="D24" s="36">
         <v>100</v>
@@ -7217,7 +7235,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7258,7 +7276,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7269,7 +7287,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="55" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="C3" s="55"/>
       <c r="D3" s="55"/>
@@ -7280,41 +7298,41 @@
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="56" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="D4" s="57" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="F4" s="58" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D6" s="59" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="G6" s="59" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="H6" s="59" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="C7" s="60">
         <v>100</v>
@@ -7334,7 +7352,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="C8" s="61">
         <v>1975000</v>
@@ -7354,7 +7372,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="C9" s="61">
         <v>854772</v>
@@ -7374,7 +7392,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="C10" s="61">
         <v>271400</v>
@@ -7394,7 +7412,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="C11" s="61">
         <v>34064.39316600799</v>
@@ -7414,7 +7432,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="C12" s="62">
         <v>789763.6068339921</v>
@@ -7434,7 +7452,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="C13" s="62">
         <v>864756</v>
@@ -7454,7 +7472,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="C14" s="63">
         <v>0.3998803072577175</v>
@@ -7492,12 +7510,12 @@
         <v>21806.733193750006</v>
       </c>
       <c r="H15" s="65" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
       <c r="C16" s="63">
         <v>0.4327959493670886</v>
@@ -7515,12 +7533,12 @@
         <v>0.22058632258064514</v>
       </c>
       <c r="H16" s="65" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B17" s="10" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="C17" s="63">
         <v>0.0690632911392405</v>
@@ -7538,12 +7556,12 @@
         <v>0.035199999999999995</v>
       </c>
       <c r="H17" s="65" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="10" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="C18" s="63">
         <v>0.42978632911392406</v>
@@ -7561,12 +7579,12 @@
         <v>0.6835685161290322</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="C19" s="66">
         <v>4</v>
@@ -7584,12 +7602,12 @@
         <v>4</v>
       </c>
       <c r="H19" s="65" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="C20" s="67">
         <v>24.918336160088252</v>
@@ -7607,12 +7625,12 @@
         <v>87.51893026967599</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="C21" s="40" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
@@ -7635,12 +7653,12 @@
         <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="C22" s="69">
         <v>9</v>
@@ -7652,157 +7670,157 @@
         <v>39</v>
       </c>
       <c r="F22" s="71" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="G22" s="71" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="19" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="D24" s="19" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="E24" s="19"/>
       <c r="F24" s="19" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="G24" s="19"/>
       <c r="H24" s="19"/>
     </row>
     <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="42" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D25" s="72" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="E25" s="72"/>
       <c r="F25" s="73" t="s">
-        <v>424</v>
+        <v>430</v>
       </c>
       <c r="G25" s="73"/>
       <c r="H25" s="73"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D26" s="72" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="E26" s="72"/>
       <c r="F26" s="73" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="G26" s="73"/>
       <c r="H26" s="73"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
+        <v>434</v>
+      </c>
+      <c r="C27" s="40" t="s">
         <v>428</v>
       </c>
-      <c r="C27" s="40" t="s">
-        <v>422</v>
-      </c>
       <c r="D27" s="72" t="s">
-        <v>429</v>
+        <v>435</v>
       </c>
       <c r="E27" s="72"/>
       <c r="F27" s="73" t="s">
-        <v>430</v>
+        <v>436</v>
       </c>
       <c r="G27" s="73"/>
       <c r="H27" s="73"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
-        <v>431</v>
+        <v>437</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>432</v>
+        <v>438</v>
       </c>
       <c r="E28" s="72"/>
       <c r="F28" s="73" t="s">
-        <v>433</v>
+        <v>439</v>
       </c>
       <c r="G28" s="73"/>
       <c r="H28" s="73"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
-        <v>434</v>
+        <v>440</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>435</v>
+        <v>441</v>
       </c>
       <c r="E29" s="72"/>
       <c r="F29" s="73" t="s">
-        <v>436</v>
+        <v>442</v>
       </c>
       <c r="G29" s="73"/>
       <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>437</v>
+        <v>443</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D30" s="72" t="s">
-        <v>438</v>
+        <v>444</v>
       </c>
       <c r="E30" s="72"/>
       <c r="F30" s="73" t="s">
-        <v>439</v>
+        <v>445</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="D31" s="72" t="s">
-        <v>441</v>
+        <v>447</v>
       </c>
       <c r="E31" s="72"/>
       <c r="F31" s="73" t="s">
-        <v>442</v>
+        <v>448</v>
       </c>
       <c r="G31" s="73"/>
       <c r="H31" s="73"/>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="42" t="s">
-        <v>443</v>
+        <v>449</v>
       </c>
       <c r="C33" s="10" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="D33" s="10"/>
       <c r="E33" s="10"/>
@@ -7810,7 +7828,7 @@
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="74" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="C35" s="74"/>
       <c r="D35" s="74"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="453">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1301,6 +1301,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -7264,7 +7267,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H36"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7679,170 +7682,191 @@
         <v>422</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C23" s="66">
+        <v>272</v>
+      </c>
+      <c r="D23" s="66">
+        <v>671</v>
+      </c>
+      <c r="E23" s="66">
+        <v>1201</v>
+      </c>
+      <c r="F23" s="66">
+        <v>1832</v>
+      </c>
+      <c r="G23" s="66">
+        <v>2518</v>
+      </c>
+      <c r="H23" s="65" t="s">
         <v>423</v>
       </c>
-      <c r="C24" s="19" t="s">
+    </row>
+    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="D24" s="19" t="s">
+      <c r="C25" s="19" t="s">
         <v>425</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="D25" s="19" t="s">
         <v>426</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+      <c r="E25" s="19"/>
+      <c r="F25" s="19" t="s">
         <v>427</v>
       </c>
-      <c r="C25" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="D25" s="72" t="s">
-        <v>429</v>
-      </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73" t="s">
-        <v>430</v>
-      </c>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
     </row>
     <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="42" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D26" s="72" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="E26" s="72"/>
       <c r="F26" s="73" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="G26" s="73"/>
       <c r="H26" s="73"/>
     </row>
     <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="42" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D27" s="72" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="E27" s="72"/>
       <c r="F27" s="73" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="G27" s="73"/>
       <c r="H27" s="73"/>
     </row>
     <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B28" s="42" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D28" s="72" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E28" s="72"/>
       <c r="F28" s="73" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="G28" s="73"/>
       <c r="H28" s="73"/>
     </row>
     <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="42" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D29" s="72" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E29" s="72"/>
       <c r="F29" s="73" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="G29" s="73"/>
       <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D30" s="72" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E30" s="72"/>
       <c r="F30" s="73" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G30" s="73"/>
       <c r="H30" s="73"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D31" s="72" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E31" s="72"/>
       <c r="F31" s="73" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="G31" s="73"/>
       <c r="H31" s="73"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="42" t="s">
+        <v>447</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>429</v>
+      </c>
+      <c r="D32" s="72" t="s">
+        <v>448</v>
+      </c>
+      <c r="E32" s="72"/>
+      <c r="F32" s="73" t="s">
         <v>449</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B34" s="42" t="s">
         <v>450</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
+      <c r="C34" s="10" t="s">
         <v>451</v>
       </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
+      <c r="D34" s="10"/>
+      <c r="E34" s="10"/>
+      <c r="F34" s="10"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="74" t="s">
+        <v>452</v>
+      </c>
+      <c r="C36" s="74"/>
+      <c r="D36" s="74"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
     <mergeCell ref="D25:E25"/>
     <mergeCell ref="F25:H25"/>
     <mergeCell ref="D26:E26"/>
@@ -7857,8 +7881,10 @@
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="C34:F34"/>
+    <mergeCell ref="B36:H36"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="453">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="457">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1262,6 +1262,18 @@
   </si>
   <si>
     <t>≥ $10,000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
   </si>
   <si>
     <t>Payroll %</t>
@@ -1634,7 +1646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1731,6 +1743,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7267,7 +7285,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H36"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7516,365 +7534,440 @@
         <v>409</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="66">
+        <v>11602.36393166008</v>
+      </c>
+      <c r="D16" s="66">
+        <v>9422.47348589237</v>
+      </c>
+      <c r="E16" s="66">
+        <v>8077.9641747875485</v>
+      </c>
+      <c r="F16" s="66">
+        <v>7338.079671405449</v>
+      </c>
+      <c r="G16" s="66">
+        <v>7070.65890870664</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="C16" s="63">
-        <v>0.4327959493670886</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.3358632612966601</v>
-      </c>
-      <c r="E16" s="63">
-        <v>0.2744051364365971</v>
-      </c>
-      <c r="F16" s="63">
-        <v>0.23809805013927576</v>
-      </c>
-      <c r="G16" s="63">
-        <v>0.22058632258064514</v>
-      </c>
-      <c r="H16" s="65" t="s">
+      <c r="C17" s="61">
+        <v>600</v>
+      </c>
+      <c r="D17" s="61">
+        <v>618</v>
+      </c>
+      <c r="E17" s="61">
+        <v>636.54</v>
+      </c>
+      <c r="F17" s="61">
+        <v>655.6362</v>
+      </c>
+      <c r="G17" s="61">
+        <v>675.3052860000003</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="64">
+        <v>1364</v>
+      </c>
+      <c r="D18" s="64">
+        <v>1080.7076923076922</v>
+      </c>
+      <c r="E18" s="64">
+        <v>904.4172499999999</v>
+      </c>
+      <c r="F18" s="64">
+        <v>805.6646637837838</v>
+      </c>
+      <c r="G18" s="64">
+        <v>767.5970084200001</v>
+      </c>
+      <c r="H18" s="65" t="s">
         <v>412</v>
       </c>
-      <c r="C17" s="63">
-        <v>0.0690632911392405</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.05359528487229862</v>
-      </c>
-      <c r="E17" s="63">
-        <v>0.043788121990369175</v>
-      </c>
-      <c r="F17" s="63">
-        <v>0.03799442896935934</v>
-      </c>
-      <c r="G17" s="63">
-        <v>0.035199999999999995</v>
-      </c>
-      <c r="H17" s="65" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0.42978632911392406</v>
-      </c>
-      <c r="D18" s="63">
-        <v>0.5457084479371316</v>
-      </c>
-      <c r="E18" s="63">
-        <v>0.6192064205457464</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0.6626261838440112</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0.6835685161290322</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C19" s="66">
-        <v>4</v>
-      </c>
-      <c r="D19" s="66">
-        <v>4</v>
-      </c>
-      <c r="E19" s="66">
-        <v>4</v>
-      </c>
-      <c r="F19" s="66">
-        <v>4</v>
-      </c>
-      <c r="G19" s="66">
-        <v>4</v>
-      </c>
-      <c r="H19" s="65" t="s">
-        <v>417</v>
+      <c r="C19" s="67">
+        <v>7897.636068339921</v>
+      </c>
+      <c r="D19" s="67">
+        <v>10664.834206415322</v>
+      </c>
+      <c r="E19" s="67">
+        <v>12513.932700212452</v>
+      </c>
+      <c r="F19" s="67">
+        <v>13839.703733999957</v>
+      </c>
+      <c r="G19" s="67">
+        <v>14711.074285043363</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C20" s="67">
-        <v>24.918336160088252</v>
-      </c>
-      <c r="D20" s="67">
-        <v>41.993786092965045</v>
-      </c>
-      <c r="E20" s="67">
-        <v>60.071336519270375</v>
-      </c>
-      <c r="F20" s="67">
-        <v>76.3087007388667</v>
-      </c>
-      <c r="G20" s="67">
-        <v>87.51893026967599</v>
+        <v>414</v>
+      </c>
+      <c r="C20" s="63">
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="D20" s="63">
+        <v>0.3358632612966601</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0.2744051364365971</v>
+      </c>
+      <c r="F20" s="63">
+        <v>0.23809805013927576</v>
+      </c>
+      <c r="G20" s="63">
+        <v>0.22058632258064514</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" s="63">
+        <v>0.0690632911392405</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.05359528487229862</v>
+      </c>
+      <c r="E21" s="63">
+        <v>0.043788121990369175</v>
+      </c>
+      <c r="F21" s="63">
+        <v>0.03799442896935934</v>
+      </c>
+      <c r="G21" s="63">
+        <v>0.035199999999999995</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="C22" s="63">
+        <v>0.42978632911392406</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.5457084479371316</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.6192064205457464</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0.6626261838440112</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0.6835685161290322</v>
+      </c>
+      <c r="H22" s="65" t="s">
         <v>419</v>
       </c>
-      <c r="C21" s="40" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="C23" s="68">
+        <v>4</v>
+      </c>
+      <c r="D23" s="68">
+        <v>4</v>
+      </c>
+      <c r="E23" s="68">
+        <v>4</v>
+      </c>
+      <c r="F23" s="68">
+        <v>4</v>
+      </c>
+      <c r="G23" s="68">
+        <v>4</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C24" s="69">
+        <v>24.918336160088252</v>
+      </c>
+      <c r="D24" s="69">
+        <v>41.993786092965045</v>
+      </c>
+      <c r="E24" s="69">
+        <v>60.071336519270375</v>
+      </c>
+      <c r="F24" s="69">
+        <v>76.3087007388667</v>
+      </c>
+      <c r="G24" s="69">
+        <v>87.51893026967599</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="C25" s="40" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="68" t="str">
+      <c r="D25" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="68" t="str">
+      <c r="E25" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="68" t="str">
+      <c r="F25" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="68" t="str">
+      <c r="G25" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H25" s="65" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C22" s="69">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" s="71">
         <v>9</v>
       </c>
-      <c r="D22" s="70">
+      <c r="D26" s="72">
         <v>22</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E26" s="68">
         <v>39</v>
       </c>
-      <c r="F22" s="71" t="s">
-        <v>421</v>
-      </c>
-      <c r="G22" s="71" t="s">
-        <v>421</v>
-      </c>
-      <c r="H22" s="65" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
+      <c r="F26" s="73" t="s">
+        <v>425</v>
+      </c>
+      <c r="G26" s="73" t="s">
+        <v>425</v>
+      </c>
+      <c r="H26" s="65" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="C23" s="66">
+      <c r="C27" s="68">
         <v>272</v>
       </c>
-      <c r="D23" s="66">
+      <c r="D27" s="68">
         <v>671</v>
       </c>
-      <c r="E23" s="66">
+      <c r="E27" s="68">
         <v>1201</v>
       </c>
-      <c r="F23" s="66">
+      <c r="F27" s="68">
         <v>1832</v>
       </c>
-      <c r="G23" s="66">
+      <c r="G27" s="68">
         <v>2518</v>
       </c>
-      <c r="H23" s="65" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="25" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="19" t="s">
-        <v>424</v>
-      </c>
-      <c r="C25" s="19" t="s">
-        <v>425</v>
-      </c>
-      <c r="D25" s="19" t="s">
-        <v>426</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19" t="s">
+      <c r="H27" s="65" t="s">
         <v>427</v>
       </c>
-      <c r="G25" s="19"/>
-      <c r="H25" s="19"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C29" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="D26" s="72" t="s">
+      <c r="D29" s="19" t="s">
         <v>430</v>
       </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
-        <v>432</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>429</v>
-      </c>
-      <c r="D27" s="72" t="s">
-        <v>433</v>
-      </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73" t="s">
-        <v>434</v>
-      </c>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
-        <v>435</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>429</v>
-      </c>
-      <c r="D28" s="72" t="s">
-        <v>436</v>
-      </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="s">
-        <v>437</v>
-      </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
-        <v>438</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>429</v>
-      </c>
-      <c r="D29" s="72" t="s">
-        <v>439</v>
-      </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73" t="s">
-        <v>440</v>
-      </c>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>441</v>
+        <v>432</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>429</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>442</v>
-      </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73" t="s">
-        <v>443</v>
-      </c>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
+        <v>433</v>
+      </c>
+      <c r="D30" s="74" t="s">
+        <v>434</v>
+      </c>
+      <c r="E30" s="74"/>
+      <c r="F30" s="75" t="s">
+        <v>435</v>
+      </c>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>429</v>
-      </c>
-      <c r="D31" s="72" t="s">
-        <v>445</v>
-      </c>
-      <c r="E31" s="72"/>
-      <c r="F31" s="73" t="s">
-        <v>446</v>
-      </c>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
+        <v>433</v>
+      </c>
+      <c r="D31" s="74" t="s">
+        <v>437</v>
+      </c>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75" t="s">
+        <v>438</v>
+      </c>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D32" s="74" t="s">
+        <v>440</v>
+      </c>
+      <c r="E32" s="74"/>
+      <c r="F32" s="75" t="s">
+        <v>441</v>
+      </c>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D33" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="E33" s="74"/>
+      <c r="F33" s="75" t="s">
+        <v>444</v>
+      </c>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D34" s="74" t="s">
+        <v>446</v>
+      </c>
+      <c r="E34" s="74"/>
+      <c r="F34" s="75" t="s">
         <v>447</v>
       </c>
-      <c r="C32" s="40" t="s">
-        <v>429</v>
-      </c>
-      <c r="D32" s="72" t="s">
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="42" t="s">
         <v>448</v>
       </c>
-      <c r="E32" s="72"/>
-      <c r="F32" s="73" t="s">
+      <c r="C35" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D35" s="74" t="s">
         <v>449</v>
       </c>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
+      <c r="E35" s="74"/>
+      <c r="F35" s="75" t="s">
         <v>450</v>
       </c>
-      <c r="C34" s="10" t="s">
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="42" t="s">
         <v>451</v>
       </c>
-      <c r="D34" s="10"/>
-      <c r="E34" s="10"/>
-      <c r="F34" s="10"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="74" t="s">
+      <c r="C36" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D36" s="74" t="s">
         <v>452</v>
       </c>
-      <c r="C36" s="74"/>
-      <c r="D36" s="74"/>
       <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="74"/>
+      <c r="F36" s="75" t="s">
+        <v>453</v>
+      </c>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="42" t="s">
+        <v>454</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="76" t="s">
+        <v>456</v>
+      </c>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
@@ -7883,8 +7976,16 @@
     <mergeCell ref="F31:H31"/>
     <mergeCell ref="D32:E32"/>
     <mergeCell ref="F32:H32"/>
-    <mergeCell ref="C34:F34"/>
-    <mergeCell ref="B36:H36"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7930,48 +8031,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="452">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1264,18 +1264,6 @@
     <t>≥ $10,000</t>
   </si>
   <si>
-    <t xml:space="preserve">  Instructional / Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  Facility / Student</t>
-  </si>
-  <si>
-    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
-  </si>
-  <si>
-    <t>Surplus per Student</t>
-  </si>
-  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1313,9 +1301,6 @@
   </si>
   <si>
     <t>≥ 24 months</t>
-  </si>
-  <si>
-    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1646,7 +1631,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1743,12 +1728,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7285,7 +7264,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:H35"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7534,458 +7513,352 @@
         <v>409</v>
       </c>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="C16" s="66">
-        <v>11602.36393166008</v>
-      </c>
-      <c r="D16" s="66">
-        <v>9422.47348589237</v>
-      </c>
-      <c r="E16" s="66">
-        <v>8077.9641747875485</v>
-      </c>
-      <c r="F16" s="66">
-        <v>7338.079671405449</v>
-      </c>
-      <c r="G16" s="66">
-        <v>7070.65890870664</v>
-      </c>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B17" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="C17" s="61">
-        <v>600</v>
-      </c>
-      <c r="D17" s="61">
-        <v>618</v>
-      </c>
-      <c r="E17" s="61">
-        <v>636.54</v>
-      </c>
-      <c r="F17" s="61">
-        <v>655.6362</v>
-      </c>
-      <c r="G17" s="61">
-        <v>675.3052860000003</v>
+      <c r="C16" s="63">
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="D16" s="63">
+        <v>0.3358632612966601</v>
+      </c>
+      <c r="E16" s="63">
+        <v>0.2744051364365971</v>
+      </c>
+      <c r="F16" s="63">
+        <v>0.23809805013927576</v>
+      </c>
+      <c r="G16" s="63">
+        <v>0.22058632258064514</v>
+      </c>
+      <c r="H16" s="65" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="C17" s="63">
+        <v>0.0690632911392405</v>
+      </c>
+      <c r="D17" s="63">
+        <v>0.05359528487229862</v>
+      </c>
+      <c r="E17" s="63">
+        <v>0.043788121990369175</v>
+      </c>
+      <c r="F17" s="63">
+        <v>0.03799442896935934</v>
+      </c>
+      <c r="G17" s="63">
+        <v>0.035199999999999995</v>
+      </c>
+      <c r="H17" s="65" t="s">
+        <v>413</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="C18" s="64">
-        <v>1364</v>
-      </c>
-      <c r="D18" s="64">
-        <v>1080.7076923076922</v>
-      </c>
-      <c r="E18" s="64">
-        <v>904.4172499999999</v>
-      </c>
-      <c r="F18" s="64">
-        <v>805.6646637837838</v>
-      </c>
-      <c r="G18" s="64">
-        <v>767.5970084200001</v>
+      <c r="B18" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="C18" s="63">
+        <v>0.42978632911392406</v>
+      </c>
+      <c r="D18" s="63">
+        <v>0.5457084479371316</v>
+      </c>
+      <c r="E18" s="63">
+        <v>0.6192064205457464</v>
+      </c>
+      <c r="F18" s="63">
+        <v>0.6626261838440112</v>
+      </c>
+      <c r="G18" s="63">
+        <v>0.6835685161290322</v>
       </c>
       <c r="H18" s="65" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="C19" s="67">
-        <v>7897.636068339921</v>
-      </c>
-      <c r="D19" s="67">
-        <v>10664.834206415322</v>
-      </c>
-      <c r="E19" s="67">
-        <v>12513.932700212452</v>
-      </c>
-      <c r="F19" s="67">
-        <v>13839.703733999957</v>
-      </c>
-      <c r="G19" s="67">
-        <v>14711.074285043363</v>
+        <v>416</v>
+      </c>
+      <c r="C19" s="66">
+        <v>4</v>
+      </c>
+      <c r="D19" s="66">
+        <v>4</v>
+      </c>
+      <c r="E19" s="66">
+        <v>4</v>
+      </c>
+      <c r="F19" s="66">
+        <v>4</v>
+      </c>
+      <c r="G19" s="66">
+        <v>4</v>
+      </c>
+      <c r="H19" s="65" t="s">
+        <v>417</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="C20" s="63">
-        <v>0.4327959493670886</v>
-      </c>
-      <c r="D20" s="63">
-        <v>0.3358632612966601</v>
-      </c>
-      <c r="E20" s="63">
-        <v>0.2744051364365971</v>
-      </c>
-      <c r="F20" s="63">
-        <v>0.23809805013927576</v>
-      </c>
-      <c r="G20" s="63">
-        <v>0.22058632258064514</v>
+        <v>353</v>
+      </c>
+      <c r="C20" s="67">
+        <v>24.918336160088252</v>
+      </c>
+      <c r="D20" s="67">
+        <v>41.993786092965045</v>
+      </c>
+      <c r="E20" s="67">
+        <v>60.071336519270375</v>
+      </c>
+      <c r="F20" s="67">
+        <v>76.3087007388667</v>
+      </c>
+      <c r="G20" s="67">
+        <v>87.51893026967599</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C21" s="63">
-        <v>0.0690632911392405</v>
-      </c>
-      <c r="D21" s="63">
-        <v>0.05359528487229862</v>
-      </c>
-      <c r="E21" s="63">
-        <v>0.043788121990369175</v>
-      </c>
-      <c r="F21" s="63">
-        <v>0.03799442896935934</v>
-      </c>
-      <c r="G21" s="63">
-        <v>0.035199999999999995</v>
+        <v>419</v>
+      </c>
+      <c r="C21" s="40" t="str">
+        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>✓ Break-even</v>
+      </c>
+      <c r="D21" s="68" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="E21" s="68" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="F21" s="68" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
+      </c>
+      <c r="G21" s="68" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+        <v>0</v>
       </c>
       <c r="H21" s="65" t="s">
-        <v>417</v>
+        <v>402</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C22" s="63">
-        <v>0.42978632911392406</v>
-      </c>
-      <c r="D22" s="63">
-        <v>0.5457084479371316</v>
-      </c>
-      <c r="E22" s="63">
-        <v>0.6192064205457464</v>
-      </c>
-      <c r="F22" s="63">
-        <v>0.6626261838440112</v>
-      </c>
-      <c r="G22" s="63">
-        <v>0.6835685161290322</v>
+        <v>420</v>
+      </c>
+      <c r="C22" s="69">
+        <v>9</v>
+      </c>
+      <c r="D22" s="70">
+        <v>22</v>
+      </c>
+      <c r="E22" s="66">
+        <v>39</v>
+      </c>
+      <c r="F22" s="71" t="s">
+        <v>421</v>
+      </c>
+      <c r="G22" s="71" t="s">
+        <v>421</v>
       </c>
       <c r="H22" s="65" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B23" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C23" s="68">
-        <v>4</v>
-      </c>
-      <c r="D23" s="68">
-        <v>4</v>
-      </c>
-      <c r="E23" s="68">
-        <v>4</v>
-      </c>
-      <c r="F23" s="68">
-        <v>4</v>
-      </c>
-      <c r="G23" s="68">
-        <v>4</v>
-      </c>
-      <c r="H23" s="65" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C24" s="69">
-        <v>24.918336160088252</v>
-      </c>
-      <c r="D24" s="69">
-        <v>41.993786092965045</v>
-      </c>
-      <c r="E24" s="69">
-        <v>60.071336519270375</v>
-      </c>
-      <c r="F24" s="69">
-        <v>76.3087007388667</v>
-      </c>
-      <c r="G24" s="69">
-        <v>87.51893026967599</v>
-      </c>
-      <c r="H24" s="65" t="s">
         <v>422</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="10" t="s">
+    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="19" t="s">
         <v>423</v>
       </c>
-      <c r="C25" s="40" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
-        <v>✓ Break-even</v>
-      </c>
-      <c r="D25" s="70" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="E25" s="70" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="F25" s="70" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="G25" s="70" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
-        <v>0</v>
-      </c>
-      <c r="H25" s="65" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="10" t="s">
+      <c r="C24" s="19" t="s">
         <v>424</v>
       </c>
-      <c r="C26" s="71">
-        <v>9</v>
-      </c>
-      <c r="D26" s="72">
-        <v>22</v>
-      </c>
-      <c r="E26" s="68">
-        <v>39</v>
-      </c>
+      <c r="D24" s="19" t="s">
+        <v>425</v>
+      </c>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19" t="s">
+        <v>426</v>
+      </c>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+    </row>
+    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="42" t="s">
+        <v>427</v>
+      </c>
+      <c r="C25" s="40" t="s">
+        <v>428</v>
+      </c>
+      <c r="D25" s="72" t="s">
+        <v>429</v>
+      </c>
+      <c r="E25" s="72"/>
+      <c r="F25" s="73" t="s">
+        <v>430</v>
+      </c>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+    </row>
+    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="42" t="s">
+        <v>431</v>
+      </c>
+      <c r="C26" s="40" t="s">
+        <v>428</v>
+      </c>
+      <c r="D26" s="72" t="s">
+        <v>432</v>
+      </c>
+      <c r="E26" s="72"/>
       <c r="F26" s="73" t="s">
-        <v>425</v>
-      </c>
-      <c r="G26" s="73" t="s">
-        <v>425</v>
-      </c>
-      <c r="H26" s="65" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="C27" s="68">
-        <v>272</v>
-      </c>
-      <c r="D27" s="68">
-        <v>671</v>
-      </c>
-      <c r="E27" s="68">
-        <v>1201</v>
-      </c>
-      <c r="F27" s="68">
-        <v>1832</v>
-      </c>
-      <c r="G27" s="68">
-        <v>2518</v>
-      </c>
-      <c r="H27" s="65" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="19" t="s">
+        <v>433</v>
+      </c>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+    </row>
+    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="42" t="s">
+        <v>434</v>
+      </c>
+      <c r="C27" s="40" t="s">
         <v>428</v>
       </c>
-      <c r="C29" s="19" t="s">
-        <v>429</v>
-      </c>
-      <c r="D29" s="19" t="s">
-        <v>430</v>
-      </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19" t="s">
-        <v>431</v>
-      </c>
-      <c r="G29" s="19"/>
-      <c r="H29" s="19"/>
+      <c r="D27" s="72" t="s">
+        <v>435</v>
+      </c>
+      <c r="E27" s="72"/>
+      <c r="F27" s="73" t="s">
+        <v>436</v>
+      </c>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+    </row>
+    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B28" s="42" t="s">
+        <v>437</v>
+      </c>
+      <c r="C28" s="40" t="s">
+        <v>428</v>
+      </c>
+      <c r="D28" s="72" t="s">
+        <v>438</v>
+      </c>
+      <c r="E28" s="72"/>
+      <c r="F28" s="73" t="s">
+        <v>439</v>
+      </c>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+    </row>
+    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="42" t="s">
+        <v>440</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>428</v>
+      </c>
+      <c r="D29" s="72" t="s">
+        <v>441</v>
+      </c>
+      <c r="E29" s="72"/>
+      <c r="F29" s="73" t="s">
+        <v>442</v>
+      </c>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D30" s="74" t="s">
-        <v>434</v>
-      </c>
-      <c r="E30" s="74"/>
-      <c r="F30" s="75" t="s">
-        <v>435</v>
-      </c>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
+        <v>428</v>
+      </c>
+      <c r="D30" s="72" t="s">
+        <v>444</v>
+      </c>
+      <c r="E30" s="72"/>
+      <c r="F30" s="73" t="s">
+        <v>445</v>
+      </c>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
-        <v>436</v>
+        <v>446</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>437</v>
-      </c>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75" t="s">
-        <v>438</v>
-      </c>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
-        <v>439</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D32" s="74" t="s">
-        <v>440</v>
-      </c>
-      <c r="E32" s="74"/>
-      <c r="F32" s="75" t="s">
-        <v>441</v>
-      </c>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+        <v>428</v>
+      </c>
+      <c r="D31" s="72" t="s">
+        <v>447</v>
+      </c>
+      <c r="E31" s="72"/>
+      <c r="F31" s="73" t="s">
+        <v>448</v>
+      </c>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D33" s="74" t="s">
-        <v>443</v>
-      </c>
-      <c r="E33" s="74"/>
-      <c r="F33" s="75" t="s">
-        <v>444</v>
-      </c>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
-        <v>445</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D34" s="74" t="s">
-        <v>446</v>
-      </c>
-      <c r="E34" s="74"/>
-      <c r="F34" s="75" t="s">
-        <v>447</v>
-      </c>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="42" t="s">
-        <v>448</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D35" s="74" t="s">
         <v>449</v>
       </c>
+      <c r="C33" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="74" t="s">
+        <v>451</v>
+      </c>
+      <c r="C35" s="74"/>
+      <c r="D35" s="74"/>
       <c r="E35" s="74"/>
-      <c r="F35" s="75" t="s">
-        <v>450</v>
-      </c>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D36" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="E36" s="74"/>
-      <c r="F36" s="75" t="s">
-        <v>453</v>
-      </c>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="42" t="s">
-        <v>454</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>455</v>
-      </c>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="76" t="s">
-        <v>456</v>
-      </c>
-      <c r="C40" s="76"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F24:H24"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
-    <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="C33:F33"/>
+    <mergeCell ref="B35:H35"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8031,48 +7904,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C16:G16">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C20&lt;=0.55</formula>
+      <formula>C16&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C20&lt;=0.65</formula>
+      <formula>C16&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C20&gt;0.65</formula>
+      <formula>C16&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:G21">
+  <conditionalFormatting sqref="C17:G17">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C21&lt;=0.15</formula>
+      <formula>C17&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C21&lt;=0.22</formula>
+      <formula>C17&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C21&gt;0.22</formula>
+      <formula>C17&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C22:G22">
+  <conditionalFormatting sqref="C18:G18">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C22&gt;=0.10</formula>
+      <formula>C18&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C22&gt;=0</formula>
+      <formula>C18&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C22&lt;0</formula>
+      <formula>C18&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:G24">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C24&gt;=1.25</formula>
+      <formula>C20&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C20&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C20&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="452">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="457">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -1264,6 +1264,18 @@
     <t>≥ $10,000</t>
   </si>
   <si>
+    <t xml:space="preserve">  Instructional / Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  Facility / Student</t>
+  </si>
+  <si>
+    <t>≤ $2,000 / $2k–$3.5k / &gt; $3,500</t>
+  </si>
+  <si>
+    <t>Surplus per Student</t>
+  </si>
+  <si>
     <t>Payroll %</t>
   </si>
   <si>
@@ -1301,6 +1313,9 @@
   </si>
   <si>
     <t>≥ 24 months</t>
+  </si>
+  <si>
+    <t>≥ 90 days</t>
   </si>
   <si>
     <t>FINANCIAL HEALTH SIGNALS</t>
@@ -1631,7 +1646,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1728,6 +1743,12 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -7264,7 +7285,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H35"/>
+  <dimension ref="B2:H40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7513,352 +7534,458 @@
         <v>409</v>
       </c>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="C16" s="66">
+        <v>11602.36393166008</v>
+      </c>
+      <c r="D16" s="66">
+        <v>9422.47348589237</v>
+      </c>
+      <c r="E16" s="66">
+        <v>8077.9641747875485</v>
+      </c>
+      <c r="F16" s="66">
+        <v>7338.079671405449</v>
+      </c>
+      <c r="G16" s="66">
+        <v>7070.65890870664</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="11" t="s">
         <v>410</v>
       </c>
-      <c r="C16" s="63">
-        <v>0.4327959493670886</v>
-      </c>
-      <c r="D16" s="63">
-        <v>0.3358632612966601</v>
-      </c>
-      <c r="E16" s="63">
-        <v>0.2744051364365971</v>
-      </c>
-      <c r="F16" s="63">
-        <v>0.23809805013927576</v>
-      </c>
-      <c r="G16" s="63">
-        <v>0.22058632258064514</v>
-      </c>
-      <c r="H16" s="65" t="s">
+      <c r="C17" s="61">
+        <v>600</v>
+      </c>
+      <c r="D17" s="61">
+        <v>618</v>
+      </c>
+      <c r="E17" s="61">
+        <v>636.54</v>
+      </c>
+      <c r="F17" s="61">
+        <v>655.6362</v>
+      </c>
+      <c r="G17" s="61">
+        <v>675.3052860000003</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="11" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B17" s="10" t="s">
+      <c r="C18" s="64">
+        <v>1364</v>
+      </c>
+      <c r="D18" s="64">
+        <v>1080.7076923076922</v>
+      </c>
+      <c r="E18" s="64">
+        <v>904.4172499999999</v>
+      </c>
+      <c r="F18" s="64">
+        <v>805.6646637837838</v>
+      </c>
+      <c r="G18" s="64">
+        <v>767.5970084200001</v>
+      </c>
+      <c r="H18" s="65" t="s">
         <v>412</v>
       </c>
-      <c r="C17" s="63">
-        <v>0.0690632911392405</v>
-      </c>
-      <c r="D17" s="63">
-        <v>0.05359528487229862</v>
-      </c>
-      <c r="E17" s="63">
-        <v>0.043788121990369175</v>
-      </c>
-      <c r="F17" s="63">
-        <v>0.03799442896935934</v>
-      </c>
-      <c r="G17" s="63">
-        <v>0.035199999999999995</v>
-      </c>
-      <c r="H17" s="65" t="s">
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B19" s="10" t="s">
         <v>413</v>
       </c>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B18" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="C18" s="63">
-        <v>0.42978632911392406</v>
-      </c>
-      <c r="D18" s="63">
-        <v>0.5457084479371316</v>
-      </c>
-      <c r="E18" s="63">
-        <v>0.6192064205457464</v>
-      </c>
-      <c r="F18" s="63">
-        <v>0.6626261838440112</v>
-      </c>
-      <c r="G18" s="63">
-        <v>0.6835685161290322</v>
-      </c>
-      <c r="H18" s="65" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B19" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C19" s="66">
-        <v>4</v>
-      </c>
-      <c r="D19" s="66">
-        <v>4</v>
-      </c>
-      <c r="E19" s="66">
-        <v>4</v>
-      </c>
-      <c r="F19" s="66">
-        <v>4</v>
-      </c>
-      <c r="G19" s="66">
-        <v>4</v>
-      </c>
-      <c r="H19" s="65" t="s">
-        <v>417</v>
+      <c r="C19" s="67">
+        <v>7897.636068339921</v>
+      </c>
+      <c r="D19" s="67">
+        <v>10664.834206415322</v>
+      </c>
+      <c r="E19" s="67">
+        <v>12513.932700212452</v>
+      </c>
+      <c r="F19" s="67">
+        <v>13839.703733999957</v>
+      </c>
+      <c r="G19" s="67">
+        <v>14711.074285043363</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C20" s="67">
-        <v>24.918336160088252</v>
-      </c>
-      <c r="D20" s="67">
-        <v>41.993786092965045</v>
-      </c>
-      <c r="E20" s="67">
-        <v>60.071336519270375</v>
-      </c>
-      <c r="F20" s="67">
-        <v>76.3087007388667</v>
-      </c>
-      <c r="G20" s="67">
-        <v>87.51893026967599</v>
+        <v>414</v>
+      </c>
+      <c r="C20" s="63">
+        <v>0.4327959493670886</v>
+      </c>
+      <c r="D20" s="63">
+        <v>0.3358632612966601</v>
+      </c>
+      <c r="E20" s="63">
+        <v>0.2744051364365971</v>
+      </c>
+      <c r="F20" s="63">
+        <v>0.23809805013927576</v>
+      </c>
+      <c r="G20" s="63">
+        <v>0.22058632258064514</v>
       </c>
       <c r="H20" s="65" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="C21" s="63">
+        <v>0.0690632911392405</v>
+      </c>
+      <c r="D21" s="63">
+        <v>0.05359528487229862</v>
+      </c>
+      <c r="E21" s="63">
+        <v>0.043788121990369175</v>
+      </c>
+      <c r="F21" s="63">
+        <v>0.03799442896935934</v>
+      </c>
+      <c r="G21" s="63">
+        <v>0.035199999999999995</v>
+      </c>
+      <c r="H21" s="65" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B22" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="C22" s="63">
+        <v>0.42978632911392406</v>
+      </c>
+      <c r="D22" s="63">
+        <v>0.5457084479371316</v>
+      </c>
+      <c r="E22" s="63">
+        <v>0.6192064205457464</v>
+      </c>
+      <c r="F22" s="63">
+        <v>0.6626261838440112</v>
+      </c>
+      <c r="G22" s="63">
+        <v>0.6835685161290322</v>
+      </c>
+      <c r="H22" s="65" t="s">
         <v>419</v>
       </c>
-      <c r="C21" s="40" t="str">
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B23" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="C23" s="68">
+        <v>4</v>
+      </c>
+      <c r="D23" s="68">
+        <v>4</v>
+      </c>
+      <c r="E23" s="68">
+        <v>4</v>
+      </c>
+      <c r="F23" s="68">
+        <v>4</v>
+      </c>
+      <c r="G23" s="68">
+        <v>4</v>
+      </c>
+      <c r="H23" s="65" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B24" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="C24" s="69">
+        <v>24.918336160088252</v>
+      </c>
+      <c r="D24" s="69">
+        <v>41.993786092965045</v>
+      </c>
+      <c r="E24" s="69">
+        <v>60.071336519270375</v>
+      </c>
+      <c r="F24" s="69">
+        <v>76.3087007388667</v>
+      </c>
+      <c r="G24" s="69">
+        <v>87.51893026967599</v>
+      </c>
+      <c r="H24" s="65" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="25" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B25" s="10" t="s">
+        <v>423</v>
+      </c>
+      <c r="C25" s="40" t="str">
         <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D21" s="68" t="str">
+      <c r="D25" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E21" s="68" t="str">
+      <c r="E25" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F21" s="68" t="str">
+      <c r="F25" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G21" s="68" t="str">
+      <c r="G25" s="70" t="str">
         <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H21" s="65" t="s">
+      <c r="H25" s="65" t="s">
         <v>402</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B22" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C22" s="69">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B26" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="C26" s="71">
         <v>9</v>
       </c>
-      <c r="D22" s="70">
+      <c r="D26" s="72">
         <v>22</v>
       </c>
-      <c r="E22" s="66">
+      <c r="E26" s="68">
         <v>39</v>
       </c>
-      <c r="F22" s="71" t="s">
-        <v>421</v>
-      </c>
-      <c r="G22" s="71" t="s">
-        <v>421</v>
-      </c>
-      <c r="H22" s="65" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="24" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B24" s="19" t="s">
-        <v>423</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>424</v>
-      </c>
-      <c r="D24" s="19" t="s">
+      <c r="F26" s="73" t="s">
         <v>425</v>
       </c>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19" t="s">
+      <c r="G26" s="73" t="s">
+        <v>425</v>
+      </c>
+      <c r="H26" s="65" t="s">
         <v>426</v>
       </c>
-      <c r="G24" s="19"/>
-      <c r="H24" s="19"/>
-    </row>
-    <row r="25" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B25" s="42" t="s">
+    </row>
+    <row r="27" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B27" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="C27" s="68">
+        <v>272</v>
+      </c>
+      <c r="D27" s="68">
+        <v>671</v>
+      </c>
+      <c r="E27" s="68">
+        <v>1201</v>
+      </c>
+      <c r="F27" s="68">
+        <v>1832</v>
+      </c>
+      <c r="G27" s="68">
+        <v>2518</v>
+      </c>
+      <c r="H27" s="65" t="s">
         <v>427</v>
       </c>
-      <c r="C25" s="40" t="s">
+    </row>
+    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B29" s="19" t="s">
         <v>428</v>
       </c>
-      <c r="D25" s="72" t="s">
+      <c r="C29" s="19" t="s">
         <v>429</v>
       </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="73" t="s">
+      <c r="D29" s="19" t="s">
         <v>430</v>
       </c>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-    </row>
-    <row r="26" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B26" s="42" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="C26" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="D26" s="72" t="s">
-        <v>432</v>
-      </c>
-      <c r="E26" s="72"/>
-      <c r="F26" s="73" t="s">
-        <v>433</v>
-      </c>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-    </row>
-    <row r="27" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B27" s="42" t="s">
-        <v>434</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="D27" s="72" t="s">
-        <v>435</v>
-      </c>
-      <c r="E27" s="72"/>
-      <c r="F27" s="73" t="s">
-        <v>436</v>
-      </c>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-    </row>
-    <row r="28" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B28" s="42" t="s">
-        <v>437</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="D28" s="72" t="s">
-        <v>438</v>
-      </c>
-      <c r="E28" s="72"/>
-      <c r="F28" s="73" t="s">
-        <v>439</v>
-      </c>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-    </row>
-    <row r="29" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B29" s="42" t="s">
-        <v>440</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="D29" s="72" t="s">
-        <v>441</v>
-      </c>
-      <c r="E29" s="72"/>
-      <c r="F29" s="73" t="s">
-        <v>442</v>
-      </c>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B30" s="42" t="s">
-        <v>443</v>
+        <v>432</v>
       </c>
       <c r="C30" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="D30" s="72" t="s">
-        <v>444</v>
-      </c>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73" t="s">
-        <v>445</v>
-      </c>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
+        <v>433</v>
+      </c>
+      <c r="D30" s="74" t="s">
+        <v>434</v>
+      </c>
+      <c r="E30" s="74"/>
+      <c r="F30" s="75" t="s">
+        <v>435</v>
+      </c>
+      <c r="G30" s="75"/>
+      <c r="H30" s="75"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B31" s="42" t="s">
+        <v>436</v>
+      </c>
+      <c r="C31" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D31" s="74" t="s">
+        <v>437</v>
+      </c>
+      <c r="E31" s="74"/>
+      <c r="F31" s="75" t="s">
+        <v>438</v>
+      </c>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B32" s="42" t="s">
+        <v>439</v>
+      </c>
+      <c r="C32" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D32" s="74" t="s">
+        <v>440</v>
+      </c>
+      <c r="E32" s="74"/>
+      <c r="F32" s="75" t="s">
+        <v>441</v>
+      </c>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B33" s="42" t="s">
+        <v>442</v>
+      </c>
+      <c r="C33" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D33" s="74" t="s">
+        <v>443</v>
+      </c>
+      <c r="E33" s="74"/>
+      <c r="F33" s="75" t="s">
+        <v>444</v>
+      </c>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B34" s="42" t="s">
+        <v>445</v>
+      </c>
+      <c r="C34" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D34" s="74" t="s">
         <v>446</v>
       </c>
-      <c r="C31" s="40" t="s">
-        <v>428</v>
-      </c>
-      <c r="D31" s="72" t="s">
+      <c r="E34" s="74"/>
+      <c r="F34" s="75" t="s">
         <v>447</v>
       </c>
-      <c r="E31" s="72"/>
-      <c r="F31" s="73" t="s">
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B35" s="42" t="s">
         <v>448</v>
       </c>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
+      <c r="C35" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D35" s="74" t="s">
         <v>449</v>
       </c>
-      <c r="C33" s="10" t="s">
+      <c r="E35" s="74"/>
+      <c r="F35" s="75" t="s">
         <v>450</v>
       </c>
-      <c r="D33" s="10"/>
-      <c r="E33" s="10"/>
-      <c r="F33" s="10"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="74" t="s">
+      <c r="G35" s="75"/>
+      <c r="H35" s="75"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B36" s="42" t="s">
         <v>451</v>
       </c>
-      <c r="C35" s="74"/>
-      <c r="D35" s="74"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
+      <c r="C36" s="40" t="s">
+        <v>433</v>
+      </c>
+      <c r="D36" s="74" t="s">
+        <v>452</v>
+      </c>
+      <c r="E36" s="74"/>
+      <c r="F36" s="75" t="s">
+        <v>453</v>
+      </c>
+      <c r="G36" s="75"/>
+      <c r="H36" s="75"/>
+    </row>
+    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B38" s="42" t="s">
+        <v>454</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>455</v>
+      </c>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B40" s="76" t="s">
+        <v>456</v>
+      </c>
+      <c r="C40" s="76"/>
+      <c r="D40" s="76"/>
+      <c r="E40" s="76"/>
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="20">
     <mergeCell ref="B2:H2"/>
     <mergeCell ref="B3:H3"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F24:H24"/>
-    <mergeCell ref="D25:E25"/>
-    <mergeCell ref="F25:H25"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="F28:H28"/>
     <mergeCell ref="D29:E29"/>
     <mergeCell ref="F29:H29"/>
     <mergeCell ref="D30:E30"/>
     <mergeCell ref="F30:H30"/>
     <mergeCell ref="D31:E31"/>
     <mergeCell ref="F31:H31"/>
-    <mergeCell ref="C33:F33"/>
-    <mergeCell ref="B35:H35"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="D35:E35"/>
+    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="C38:F38"/>
+    <mergeCell ref="B40:H40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -7904,48 +8031,48 @@
       <formula>C15&lt;7000</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C16:G16">
+  <conditionalFormatting sqref="C20:G20">
     <cfRule type="expression" dxfId="12" priority="1">
-      <formula>C16&lt;=0.55</formula>
+      <formula>C20&lt;=0.55</formula>
     </cfRule>
     <cfRule type="expression" dxfId="13" priority="2">
-      <formula>C16&lt;=0.65</formula>
+      <formula>C20&lt;=0.65</formula>
     </cfRule>
     <cfRule type="expression" dxfId="14" priority="3">
-      <formula>C16&gt;0.65</formula>
+      <formula>C20&gt;0.65</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C17:G17">
+  <conditionalFormatting sqref="C21:G21">
     <cfRule type="expression" dxfId="15" priority="1">
-      <formula>C17&lt;=0.15</formula>
+      <formula>C21&lt;=0.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="16" priority="2">
-      <formula>C17&lt;=0.22</formula>
+      <formula>C21&lt;=0.22</formula>
     </cfRule>
     <cfRule type="expression" dxfId="17" priority="3">
-      <formula>C17&gt;0.22</formula>
+      <formula>C21&gt;0.22</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C18:G18">
+  <conditionalFormatting sqref="C22:G22">
     <cfRule type="expression" dxfId="18" priority="1">
-      <formula>C18&gt;=0.10</formula>
+      <formula>C22&gt;=0.10</formula>
     </cfRule>
     <cfRule type="expression" dxfId="19" priority="2">
-      <formula>C18&gt;=0</formula>
+      <formula>C22&gt;=0</formula>
     </cfRule>
     <cfRule type="expression" dxfId="20" priority="3">
-      <formula>C18&lt;0</formula>
+      <formula>C22&lt;0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C20:G20">
+  <conditionalFormatting sqref="C24:G24">
     <cfRule type="expression" dxfId="21" priority="1">
-      <formula>C20&gt;=1.25</formula>
+      <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C20&gt;=1</formula>
+      <formula>C24&gt;=1</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C20&lt;1</formula>
+      <formula>C24&lt;1</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -26,13 +26,15 @@
     <sheet sheetId="20" name="Scenarios" state="visible" r:id="rId23"/>
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
+    <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
+    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="802" uniqueCount="457">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="495">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -40,7 +42,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated March 27, 2026 · nonprofit_501c3</t>
+    <t>Generated April 29, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -160,7 +162,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>March 27, 2026</t>
+    <t>April 29, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -310,6 +312,12 @@
     <t>Financial Health</t>
   </si>
   <si>
+    <t>23.</t>
+  </si>
+  <si>
+    <t>Budget Narrative</t>
+  </si>
+  <si>
     <t>CONFIDENTIAL - Prepared by SchoolStack Budget (budget.schoolstack.ai)</t>
   </si>
   <si>
@@ -376,6 +384,9 @@
     <t>Escalation %</t>
   </si>
   <si>
+    <t>Timing</t>
+  </si>
+  <si>
     <t>Tuition</t>
   </si>
   <si>
@@ -385,6 +396,9 @@
     <t>Per Student</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
     <t>Registration Fee</t>
   </si>
   <si>
@@ -565,6 +579,48 @@
     <t>Yes</t>
   </si>
   <si>
+    <t>Enrollment Growth Rate</t>
+  </si>
+  <si>
+    <t>Rent Escalation Rate</t>
+  </si>
+  <si>
+    <t>Tuition Escalation Rate</t>
+  </si>
+  <si>
+    <t>Default Benefits Rate</t>
+  </si>
+  <si>
+    <t>Default Payroll Tax Rate</t>
+  </si>
+  <si>
+    <t>Student Retention Rate</t>
+  </si>
+  <si>
+    <t>REVENUE COLLECTION DEFAULTS</t>
+  </si>
+  <si>
+    <t>Default Billing Months</t>
+  </si>
+  <si>
+    <t>10 months (Aug-May)</t>
+  </si>
+  <si>
+    <t>Default Collection Method</t>
+  </si>
+  <si>
+    <t>Autopay</t>
+  </si>
+  <si>
+    <t>Default Collection Rate</t>
+  </si>
+  <si>
+    <t>Default Collection Delay</t>
+  </si>
+  <si>
+    <t>0 days</t>
+  </si>
+  <si>
     <t>School Model</t>
   </si>
   <si>
@@ -628,9 +684,6 @@
     <t>Capacity Utilization</t>
   </si>
   <si>
-    <t>Enrollment Growth Rate</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -676,6 +729,9 @@
     <t>Loaded Cost</t>
   </si>
   <si>
+    <t>Rates</t>
+  </si>
+  <si>
     <t>5-YEAR TOTAL PERSONNEL COST</t>
   </si>
   <si>
@@ -991,12 +1047,24 @@
     <t>Minimum Cash Month</t>
   </si>
   <si>
+    <t>Cash Trough: July (Month 1)</t>
+  </si>
+  <si>
+    <t>Your lowest cash point is the month lenders focus on to ensure you won't run out of money before collections start. Plan reserves to cover this trough.</t>
+  </si>
+  <si>
     <t>Heritage Academy - 5-Year Operating Statement</t>
   </si>
   <si>
+    <t>Projections prepared on an accrual basis. School currently keeps books on a undetermined basis.</t>
+  </si>
+  <si>
     <t>Capital &amp; Debt Service</t>
   </si>
   <si>
+    <t>Depreciation</t>
+  </si>
+  <si>
     <t>BOTTOM LINE</t>
   </si>
   <si>
@@ -1051,7 +1119,7 @@
     <t>Accounts Receivable</t>
   </si>
   <si>
-    <t>Fixed Assets</t>
+    <t>Fixed Assets (Net of Depreciation)</t>
   </si>
   <si>
     <t>Other Assets</t>
@@ -1090,7 +1158,16 @@
     <t>Revenue</t>
   </si>
   <si>
-    <t>CFADS (Rev - Pers - OpEx)</t>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>Depreciation Add-Back</t>
+  </si>
+  <si>
+    <t>Debt Service (Loan)</t>
+  </si>
+  <si>
+    <t>CFADS (NI + Depr + DS)</t>
   </si>
   <si>
     <t>DSCR</t>
@@ -1132,6 +1209,9 @@
     <t>Positive Net Income</t>
   </si>
   <si>
+    <t>Current Ratio ≥ 1.1x</t>
+  </si>
+  <si>
     <t>Capacity ≥ 7500%</t>
   </si>
   <si>
@@ -1225,7 +1305,7 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated March 27, 2026</t>
+    <t>Generated April 29, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1258,9 +1338,6 @@
     <t>Benchmark</t>
   </si>
   <si>
-    <t>Net Income</t>
-  </si>
-  <si>
     <t>≥ $10,000</t>
   </si>
   <si>
@@ -1390,7 +1467,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>82.8 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>82.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -1403,6 +1480,45 @@
   </si>
   <si>
     <t>Built by SchoolStack Budget  •  budget.schoolstack.ai</t>
+  </si>
+  <si>
+    <t>Enrollment Strategy</t>
+  </si>
+  <si>
+    <t>(Not provided)</t>
+  </si>
+  <si>
+    <t>Retention Plan</t>
+  </si>
+  <si>
+    <t>Risk Mitigation</t>
+  </si>
+  <si>
+    <t>Mission &amp; Vision</t>
+  </si>
+  <si>
+    <t>Revenue Assumptions</t>
+  </si>
+  <si>
+    <t>Staffing Philosophy</t>
+  </si>
+  <si>
+    <t>Expense Assumptions</t>
+  </si>
+  <si>
+    <t>Growth Strategy</t>
+  </si>
+  <si>
+    <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Decision History</t>
+  </si>
+  <si>
+    <t>No decisions have been tracked with an outcome yet. As the team marks saved scenarios as Pursued, Declined, or On hold, those outcomes (and any retrospective notes) will appear here so reviewers can see what actually happened versus what was modeled.</t>
+  </si>
+  <si>
+    <t>Once decisions are saved with a Pursued / Declined / On hold outcome inside the planner, they will be summarized here.</t>
   </si>
 </sst>
 </file>
@@ -1416,7 +1532,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1507,6 +1623,18 @@
       <i/>
       <color rgb="FF808080"/>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF9CA3AF"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF64748B"/>
+      <sz val="10"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1646,7 +1774,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1694,8 +1822,10 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="165" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1705,14 +1835,14 @@
     <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="17" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="168" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1720,10 +1850,10 @@
     <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1742,7 +1872,7 @@
     <xf numFmtId="165" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1770,11 +1900,20 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2493,7 +2632,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2506,24 +2645,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B4" s="27">
         <v>100</v>
@@ -2543,7 +2682,7 @@
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2553,7 +2692,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B7" s="31">
         <v>1050000</v>
@@ -2573,7 +2712,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B8" s="31">
         <v>35000</v>
@@ -2593,7 +2732,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B9" s="31">
         <v>105000</v>
@@ -2613,7 +2752,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B10" s="31">
         <v>870000</v>
@@ -2633,7 +2772,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B11" s="31">
         <v>50000</v>
@@ -2653,7 +2792,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B12" s="31">
         <v>25000</v>
@@ -2673,7 +2812,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B13" s="31">
         <v>50000</v>
@@ -2693,7 +2832,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B14" s="33">
         <f>SUM(B7:B13)</f>
@@ -2718,7 +2857,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B16" s="31">
         <v>19750</v>
@@ -2762,7 +2901,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -2775,24 +2914,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -2802,7 +2941,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="B5" s="31">
         <v>382032</v>
@@ -2822,7 +2961,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B6" s="31">
         <v>122544</v>
@@ -2842,7 +2981,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="B7" s="32">
         <f>SUM(B5:B6)</f>
@@ -2867,7 +3006,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -2877,7 +3016,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B9" s="31">
         <v>126018</v>
@@ -2897,7 +3036,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B10" s="31">
         <v>99488</v>
@@ -2917,7 +3056,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B11" s="32">
         <f>SUM(B9:B10)</f>
@@ -2942,7 +3081,7 @@
     </row>
     <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B12" s="19"/>
       <c r="C12" s="19"/>
@@ -2952,7 +3091,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B13" s="31">
         <v>68978</v>
@@ -2972,7 +3111,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B13:B13)</f>
@@ -2997,7 +3136,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -3007,7 +3146,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B16" s="31">
         <v>55713</v>
@@ -3027,7 +3166,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B17" s="32">
         <f>SUM(B16:B16)</f>
@@ -3052,7 +3191,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B19" s="33">
         <f>B7+B11+B14+B17</f>
@@ -3101,7 +3240,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3114,24 +3253,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -3141,7 +3280,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B5" s="31">
         <v>1050000</v>
@@ -3161,7 +3300,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B6" s="31">
         <v>35000</v>
@@ -3181,7 +3320,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="B7" s="31">
         <v>105000</v>
@@ -3201,7 +3340,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B8" s="31">
         <v>870000</v>
@@ -3221,7 +3360,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="B9" s="31">
         <v>50000</v>
@@ -3241,7 +3380,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B10" s="31">
         <v>25000</v>
@@ -3261,7 +3400,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B11" s="31">
         <v>50000</v>
@@ -3281,7 +3420,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B12" s="32">
         <f>SUM(B5:B11)</f>
@@ -3306,7 +3445,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -3316,7 +3455,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B15" s="31">
         <v>126018</v>
@@ -3336,7 +3475,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B16" s="31">
         <v>99488</v>
@@ -3356,7 +3495,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="B17" s="31">
         <v>382032</v>
@@ -3376,7 +3515,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B18" s="31">
         <v>122544</v>
@@ -3396,7 +3535,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="B19" s="31">
         <v>55713</v>
@@ -3416,7 +3555,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B20" s="31">
         <v>68978</v>
@@ -3436,7 +3575,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B21" s="32">
         <f>SUM(B15:B20)</f>
@@ -3461,7 +3600,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -3471,12 +3610,12 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="37" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="B25" s="31">
         <v>60000</v>
@@ -3496,12 +3635,12 @@
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="37" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B27" s="31">
         <v>40000</v>
@@ -3521,12 +3660,12 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="37" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B29" s="31">
         <v>102000</v>
@@ -3546,7 +3685,7 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B30" s="31">
         <v>14400</v>
@@ -3566,7 +3705,7 @@
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B31" s="31">
         <v>12000</v>
@@ -3586,7 +3725,7 @@
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B32" s="31">
         <v>8000</v>
@@ -3606,7 +3745,7 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B33" s="32">
         <f>SUM(B29:B32)</f>
@@ -3631,12 +3770,12 @@
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="37" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B35" s="31">
         <v>15000</v>
@@ -3656,7 +3795,7 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="B36" s="31">
         <v>8000</v>
@@ -3676,7 +3815,7 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="B37" s="31">
         <v>12000</v>
@@ -3696,7 +3835,7 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="B38" s="32">
         <f>SUM(B35:B37)</f>
@@ -3721,7 +3860,7 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B39" s="32">
         <f>B25+B27+B33+B38</f>
@@ -3746,7 +3885,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="19" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B41" s="19"/>
       <c r="C41" s="19"/>
@@ -3756,7 +3895,7 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="B42" s="31">
         <v>34064</v>
@@ -3776,7 +3915,7 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="B43" s="31">
         <v>25000</v>
@@ -3796,7 +3935,7 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B44" s="32">
         <f>SUM(B42:B43)</f>
@@ -3845,7 +3984,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -3858,24 +3997,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B4" s="34">
         <f>'Budget Detail'!B12</f>
@@ -3900,7 +4039,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B5" s="34">
         <f>'Budget Detail'!B21</f>
@@ -3925,7 +4064,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B6" s="34">
         <f>'Budget Detail'!B39</f>
@@ -3950,7 +4089,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B7" s="34">
         <f>'Budget Detail'!B44</f>
@@ -3975,7 +4114,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B8" s="32">
         <f>SUM(B5:B7)</f>
@@ -4000,7 +4139,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -4010,7 +4149,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B11" s="33">
         <f>B4-B8</f>
@@ -4035,7 +4174,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B12" s="30">
         <f>IF(B4=0,0,B11/B4)</f>
@@ -4060,7 +4199,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="B13" s="31">
         <v>789764</v>
@@ -4080,7 +4219,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B14" s="31">
         <v>19750</v>
@@ -4100,7 +4239,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="B15" s="31">
         <v>11852</v>
@@ -4135,7 +4274,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:N19"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -4145,7 +4284,7 @@
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4166,48 +4305,48 @@
         <v>7</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="F2" s="21" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="G2" s="21" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="H2" s="21" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="I2" s="21" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="J2" s="21" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="K2" s="21" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="L2" s="21" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="M2" s="21" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="N2" s="21" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -4225,52 +4364,52 @@
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B4" s="32">
         <v>85833</v>
       </c>
       <c r="C4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="D4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="E4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="F4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="G4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="H4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="I4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="J4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="K4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="L4" s="32">
-        <v>180333</v>
+        <v>175083</v>
       </c>
       <c r="M4" s="32">
         <v>85833</v>
       </c>
       <c r="N4" s="32">
         <f>SUM(B4:M4)</f>
-        <v>1974996</v>
+        <v>1922496</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="19" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -4288,7 +4427,7 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B7" s="31">
         <v>71231</v>
@@ -4333,7 +4472,7 @@
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B8" s="31">
         <v>22617</v>
@@ -4378,7 +4517,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="B9" s="31">
         <v>4922</v>
@@ -4423,7 +4562,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -4441,7 +4580,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B12" s="34">
         <f>B7+B8+B9</f>
@@ -4498,7 +4637,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="B13" s="34">
         <f>B4-B12</f>
@@ -4506,43 +4645,43 @@
       </c>
       <c r="C13" s="34">
         <f>C4-C12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="D13" s="34">
         <f>D4-D12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="E13" s="34">
         <f>E4-E12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="F13" s="34">
         <f>F4-F12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="G13" s="34">
         <f>G4-G12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="H13" s="34">
         <f>H4-H12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="I13" s="34">
         <f>I4-I12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="J13" s="34">
         <f>J4-J12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="K13" s="34">
         <f>K4-K12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="L13" s="34">
         <f>L4-L12</f>
-        <v>81563</v>
+        <v>76313</v>
       </c>
       <c r="M13" s="34">
         <f>M4-M12</f>
@@ -4550,12 +4689,12 @@
       </c>
       <c r="N13" s="34">
         <f>SUM(B13:M13)</f>
-        <v>789756</v>
+        <v>737256</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B14" s="38">
         <f>B17+B13</f>
@@ -4563,63 +4702,63 @@
       </c>
       <c r="C14" s="38">
         <f>B14+C13</f>
-        <v>143626</v>
+        <v>138376</v>
       </c>
       <c r="D14" s="38">
         <f>C14+D13</f>
-        <v>225189</v>
+        <v>214689</v>
       </c>
       <c r="E14" s="38">
         <f>D14+E13</f>
-        <v>306752</v>
+        <v>291002</v>
       </c>
       <c r="F14" s="38">
         <f>E14+F13</f>
-        <v>388315</v>
+        <v>367315</v>
       </c>
       <c r="G14" s="38">
         <f>F14+G13</f>
-        <v>469878</v>
+        <v>443628</v>
       </c>
       <c r="H14" s="38">
         <f>G14+H13</f>
-        <v>551441</v>
+        <v>519941</v>
       </c>
       <c r="I14" s="38">
         <f>H14+I13</f>
-        <v>633004</v>
+        <v>596254</v>
       </c>
       <c r="J14" s="38">
         <f>I14+J13</f>
-        <v>714567</v>
+        <v>672567</v>
       </c>
       <c r="K14" s="38">
         <f>J14+K13</f>
-        <v>796130</v>
+        <v>748880</v>
       </c>
       <c r="L14" s="38">
         <f>K14+L13</f>
-        <v>877693</v>
+        <v>825193</v>
       </c>
       <c r="M14" s="38">
         <f>L14+M13</f>
-        <v>864756</v>
+        <v>812256</v>
       </c>
       <c r="N14" s="33">
         <f>M14</f>
-        <v>864756</v>
+        <v>812256</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
     </row>
     <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B17" s="23">
         <v>75000</v>
@@ -4627,25 +4766,49 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B18" s="38">
         <f>M14</f>
-        <v>864756</v>
+        <v>812256</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="B19" s="31">
         <f>MIN(B14:M14)</f>
         <v>62063</v>
       </c>
     </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="39" t="s">
+        <v>338</v>
+      </c>
+      <c r="B21" s="39"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="39"/>
+      <c r="G21" s="39"/>
+      <c r="H21" s="39"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="A1:N1"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A21:H21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4660,7 +4823,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -4669,7 +4832,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>319</v>
+        <v>339</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -4677,29 +4840,39 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
     </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="40" t="s">
+        <v>340</v>
+      </c>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+    </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4708,8 +4881,8 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="39" t="s">
-        <v>263</v>
+      <c r="A5" s="41" t="s">
+        <v>281</v>
       </c>
       <c r="B5" s="32">
         <v>1975000</v>
@@ -4729,7 +4902,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -4739,7 +4912,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B8" s="34">
         <v>854772</v>
@@ -4759,7 +4932,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B9" s="34">
         <v>271400</v>
@@ -4779,7 +4952,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="B10" s="34">
         <v>59064</v>
@@ -4798,138 +4971,159 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A11" s="39" t="s">
-        <v>289</v>
-      </c>
-      <c r="B11" s="32">
-        <f>SUM(B8:B10)</f>
-        <v>1185236</v>
-      </c>
-      <c r="C11" s="32">
-        <f>SUM(C8:C10)</f>
-        <v>1234922</v>
-      </c>
-      <c r="D11" s="32">
-        <f>SUM(D8:D10)</f>
-        <v>1302474</v>
-      </c>
-      <c r="E11" s="32">
-        <f>SUM(E8:E10)</f>
-        <v>1362545</v>
-      </c>
-      <c r="F11" s="32">
-        <f>SUM(F8:F10)</f>
-        <v>1419132</v>
-      </c>
-    </row>
-    <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="19" t="s">
-        <v>321</v>
-      </c>
-      <c r="B13" s="19"/>
-      <c r="C13" s="19"/>
-      <c r="D13" s="19"/>
-      <c r="E13" s="19"/>
-      <c r="F13" s="19"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="B14" s="33">
-        <f>B5-B11</f>
-        <v>789764</v>
-      </c>
-      <c r="C14" s="33">
-        <f>C5-C11</f>
-        <v>1386428</v>
-      </c>
-      <c r="D14" s="33">
-        <f>D5-D11</f>
-        <v>2002229</v>
-      </c>
-      <c r="E14" s="33">
-        <f>E5-E11</f>
-        <v>2560345</v>
-      </c>
-      <c r="F14" s="33">
-        <f>F5-F11</f>
-        <v>2942215</v>
-      </c>
+      <c r="A11" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="B11" s="34">
+        <v>25714</v>
+      </c>
+      <c r="C11" s="34">
+        <v>25714</v>
+      </c>
+      <c r="D11" s="34">
+        <v>25714</v>
+      </c>
+      <c r="E11" s="34">
+        <v>25714</v>
+      </c>
+      <c r="F11" s="34">
+        <v>25714</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="41" t="s">
+        <v>307</v>
+      </c>
+      <c r="B12" s="32">
+        <f>SUM(B8:B11)</f>
+        <v>1210951</v>
+      </c>
+      <c r="C12" s="32">
+        <f>SUM(C8:C11)</f>
+        <v>1260636</v>
+      </c>
+      <c r="D12" s="32">
+        <f>SUM(D8:D11)</f>
+        <v>1328189</v>
+      </c>
+      <c r="E12" s="32">
+        <f>SUM(E8:E11)</f>
+        <v>1388259</v>
+      </c>
+      <c r="F12" s="32">
+        <f>SUM(F8:F11)</f>
+        <v>1444846</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="11" t="s">
-        <v>292</v>
-      </c>
-      <c r="B15" s="30">
-        <f>IF(B5=0,0,B14/B5)</f>
-        <v>0.39988031</v>
-      </c>
-      <c r="C15" s="30">
-        <f>IF(C5=0,0,C14/C5)</f>
-        <v>0.52889864</v>
-      </c>
-      <c r="D15" s="30">
-        <f>IF(D5=0,0,D14/D5)</f>
-        <v>0.60587258</v>
-      </c>
-      <c r="E15" s="30">
-        <f>IF(E5=0,0,E14/E5)</f>
-        <v>0.65266812</v>
-      </c>
-      <c r="F15" s="30">
-        <f>IF(F5=0,0,F14/F5)</f>
-        <v>0.67461156</v>
+      <c r="A15" s="41" t="s">
+        <v>309</v>
+      </c>
+      <c r="B15" s="33">
+        <f>B5-B12</f>
+        <v>764049</v>
+      </c>
+      <c r="C15" s="33">
+        <f>C5-C12</f>
+        <v>1360714</v>
+      </c>
+      <c r="D15" s="33">
+        <f>D5-D12</f>
+        <v>1976515</v>
+      </c>
+      <c r="E15" s="33">
+        <f>E5-E12</f>
+        <v>2534631</v>
+      </c>
+      <c r="F15" s="33">
+        <f>F5-F12</f>
+        <v>2916501</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>322</v>
-      </c>
-      <c r="B16" s="34">
-        <f>B14</f>
-        <v>789764</v>
-      </c>
-      <c r="C16" s="34">
-        <f>B16+C14</f>
-        <v>2176192</v>
-      </c>
-      <c r="D16" s="34">
-        <f>C16+D14</f>
-        <v>4178421</v>
-      </c>
-      <c r="E16" s="34">
-        <f>D16+E14</f>
-        <v>6738766</v>
-      </c>
-      <c r="F16" s="34">
-        <f>E16+F14</f>
-        <v>9680981</v>
+      <c r="A16" s="11" t="s">
+        <v>310</v>
+      </c>
+      <c r="B16" s="30">
+        <f>IF(B5=0,0,B15/B5)</f>
+        <v>0.38686042</v>
+      </c>
+      <c r="C16" s="30">
+        <f>IF(C5=0,0,C15/C5)</f>
+        <v>0.51908908</v>
+      </c>
+      <c r="D16" s="30">
+        <f>IF(D5=0,0,D15/D5)</f>
+        <v>0.59809146</v>
+      </c>
+      <c r="E16" s="30">
+        <f>IF(E5=0,0,E15/E5)</f>
+        <v>0.64611318</v>
+      </c>
+      <c r="F16" s="30">
+        <f>IF(F5=0,0,F15/F5)</f>
+        <v>0.66871561</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>323</v>
-      </c>
-      <c r="B17" s="40" t="s">
-        <v>324</v>
-      </c>
-      <c r="C17" s="41" t="s">
+        <v>344</v>
+      </c>
+      <c r="B17" s="34">
+        <f>B15</f>
+        <v>764049</v>
+      </c>
+      <c r="C17" s="34">
+        <f>B17+C15</f>
+        <v>2124763</v>
+      </c>
+      <c r="D17" s="34">
+        <f>C17+D15</f>
+        <v>4101278</v>
+      </c>
+      <c r="E17" s="34">
+        <f>D17+E15</f>
+        <v>6635909</v>
+      </c>
+      <c r="F17" s="34">
+        <f>E17+F15</f>
+        <v>9552410</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="B18" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="C18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="D17" s="41" t="s">
+      <c r="D18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="41" t="s">
+      <c r="E18" s="43" t="s">
         <v>7</v>
       </c>
-      <c r="F17" s="41" t="s">
+      <c r="F18" s="43" t="s">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -4966,24 +5160,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>325</v>
+        <v>347</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -4992,25 +5186,25 @@
       <c r="F4" s="19"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="42" t="s">
-        <v>326</v>
-      </c>
-      <c r="B5" s="43" t="s">
-        <v>162</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>327</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>328</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>234</v>
+      <c r="A5" s="44" t="s">
+        <v>348</v>
+      </c>
+      <c r="B5" s="45" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="46" t="s">
+        <v>349</v>
+      </c>
+      <c r="D5" s="44" t="s">
+        <v>350</v>
+      </c>
+      <c r="E5" s="45" t="s">
+        <v>252</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="20" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B6" s="23">
         <v>250000</v>
@@ -5028,7 +5222,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>329</v>
+        <v>351</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -5038,7 +5232,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>330</v>
+        <v>352</v>
       </c>
       <c r="B9" s="31">
         <f>B6</f>
@@ -5063,7 +5257,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>331</v>
+        <v>353</v>
       </c>
       <c r="B10" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,0,-CUMIPMT(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5088,7 +5282,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>332</v>
+        <v>354</v>
       </c>
       <c r="B11" s="31">
         <f>IF(OR(D6=0,1&gt;D6*12),0,IF(C6=0,B6/D6,-CUMPRINC(C6/12,D6*12,B6,1,12,0)))</f>
@@ -5113,7 +5307,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>333</v>
+        <v>355</v>
       </c>
       <c r="B12" s="34">
         <f>B10+B11</f>
@@ -5138,7 +5332,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>334</v>
+        <v>356</v>
       </c>
       <c r="B13" s="38">
         <f>MAX(0,B9-B11)</f>
@@ -5187,7 +5381,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>335</v>
+        <v>357</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5200,24 +5394,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>336</v>
+        <v>358</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5227,72 +5421,72 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>337</v>
-      </c>
-      <c r="B5" s="45">
+        <v>359</v>
+      </c>
+      <c r="B5" s="47">
         <f>'Monthly Cash Flow Y1'!M14</f>
-        <v>864756</v>
-      </c>
-      <c r="C5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14</f>
-        <v>2251184</v>
-      </c>
-      <c r="D5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14</f>
-        <v>4253414</v>
-      </c>
-      <c r="E5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14</f>
-        <v>6813759</v>
-      </c>
-      <c r="F5" s="45">
-        <f>B5+'5-Year Operating Stmt'!C14+'5-Year Operating Stmt'!D14+'5-Year Operating Stmt'!E14+'5-Year Operating Stmt'!F14</f>
-        <v>9755974</v>
+        <v>812256</v>
+      </c>
+      <c r="C5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15</f>
+        <v>2198684</v>
+      </c>
+      <c r="D5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
+        <v>4200914</v>
+      </c>
+      <c r="E5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
+        <v>6761259</v>
+      </c>
+      <c r="F5" s="47">
+        <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
+        <v>9703474</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>338</v>
+        <v>360</v>
       </c>
       <c r="B6" s="31">
-        <v>12000</v>
+        <v>892</v>
       </c>
       <c r="C6" s="31">
-        <v>12000</v>
+        <v>918</v>
       </c>
       <c r="D6" s="31">
-        <v>12000</v>
+        <v>944</v>
       </c>
       <c r="E6" s="31">
-        <v>12000</v>
+        <v>972</v>
       </c>
       <c r="F6" s="31">
-        <v>12000</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>339</v>
+        <v>361</v>
       </c>
       <c r="B7" s="31">
-        <v>180000</v>
+        <v>154286</v>
       </c>
       <c r="C7" s="31">
-        <v>180000</v>
+        <v>128571</v>
       </c>
       <c r="D7" s="31">
-        <v>180000</v>
+        <v>102857</v>
       </c>
       <c r="E7" s="31">
-        <v>180000</v>
+        <v>77143</v>
       </c>
       <c r="F7" s="31">
-        <v>180000</v>
+        <v>51429</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>340</v>
+        <v>362</v>
       </c>
       <c r="B8" s="31">
         <v>5000</v>
@@ -5312,32 +5506,32 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>341</v>
+        <v>363</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B5:B8)</f>
-        <v>1061756</v>
+        <v>972433</v>
       </c>
       <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v>2448184</v>
+        <v>2333174</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
-        <v>4450414</v>
+        <v>4309715</v>
       </c>
       <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
-        <v>7010759</v>
+        <v>6844374</v>
       </c>
       <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
-        <v>9952974</v>
+        <v>9760902</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>342</v>
+        <v>364</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -5347,7 +5541,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>343</v>
+        <v>365</v>
       </c>
       <c r="B12" s="31">
         <v>8000</v>
@@ -5367,7 +5561,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>344</v>
+        <v>366</v>
       </c>
       <c r="B13" s="31">
         <f>'Debt Schedule'!B13</f>
@@ -5392,7 +5586,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>345</v>
+        <v>367</v>
       </c>
       <c r="B14" s="32">
         <f>SUM(B12:B13)</f>
@@ -5417,7 +5611,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>346</v>
+        <v>368</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -5427,50 +5621,50 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="B17" s="33">
         <f>B9-B14</f>
-        <v>822111</v>
+        <v>732788</v>
       </c>
       <c r="C17" s="33">
         <f>C9-C14</f>
-        <v>2228123</v>
+        <v>2113112</v>
       </c>
       <c r="D17" s="33">
         <f>D9-D14</f>
-        <v>4251248</v>
+        <v>4110550</v>
       </c>
       <c r="E17" s="33">
         <f>E9-E14</f>
-        <v>6833888</v>
+        <v>6667503</v>
       </c>
       <c r="F17" s="33">
         <f>F9-F14</f>
-        <v>9799892</v>
+        <v>9607820</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
-        <v>348</v>
-      </c>
-      <c r="B19" s="46" t="str">
+        <v>370</v>
+      </c>
+      <c r="B19" s="48" t="str">
         <f>B9-B14-B17</f>
         <v>0</v>
       </c>
-      <c r="C19" s="46" t="str">
+      <c r="C19" s="49">
         <f>C9-C14-C17</f>
+        <v>1</v>
+      </c>
+      <c r="D19" s="48" t="str">
+        <f>D9-D14-D17</f>
         <v>0</v>
       </c>
-      <c r="D19" s="47">
-        <f>D9-D14-D17</f>
-        <v>1</v>
-      </c>
-      <c r="E19" s="47">
+      <c r="E19" s="49">
         <f>E9-E14-E17</f>
         <v>1</v>
       </c>
-      <c r="F19" s="46" t="str">
+      <c r="F19" s="48" t="str">
         <f>F9-F14-F17</f>
         <v>0</v>
       </c>
@@ -5492,7 +5686,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -5501,7 +5695,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -5514,24 +5708,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>350</v>
+        <v>372</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -5541,7 +5735,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B5" s="31">
         <v>1975000</v>
@@ -5561,7 +5755,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B6" s="31">
         <v>854772</v>
@@ -5581,7 +5775,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B7" s="31">
         <v>271400</v>
@@ -5601,372 +5795,432 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>352</v>
+        <v>374</v>
       </c>
       <c r="B8" s="34">
-        <f>B5-B6-B7</f>
-        <v>848828</v>
+        <v>789764</v>
       </c>
       <c r="C8" s="34">
-        <f>C5-C6-C7</f>
-        <v>1430493</v>
+        <v>1386428</v>
       </c>
       <c r="D8" s="34">
-        <f>D5-D6-D7</f>
-        <v>2046294</v>
+        <v>2002229</v>
       </c>
       <c r="E8" s="34">
-        <f>E5-E6-E7</f>
-        <v>2599410</v>
+        <v>2560345</v>
       </c>
       <c r="F8" s="34">
-        <f>F5-F6-F7</f>
-        <v>2981279</v>
+        <v>2942215</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>312</v>
+        <v>375</v>
       </c>
       <c r="B9" s="31">
+        <v>25714</v>
+      </c>
+      <c r="C9" s="31">
+        <v>25714</v>
+      </c>
+      <c r="D9" s="31">
+        <v>25714</v>
+      </c>
+      <c r="E9" s="31">
+        <v>25714</v>
+      </c>
+      <c r="F9" s="31">
+        <v>25714</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="11" t="s">
+        <v>376</v>
+      </c>
+      <c r="B10" s="31">
         <v>34064</v>
       </c>
-      <c r="C9" s="31">
+      <c r="C10" s="31">
         <v>34064</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D10" s="31">
         <v>34064</v>
       </c>
-      <c r="E9" s="31">
+      <c r="E10" s="31">
         <v>34064</v>
       </c>
-      <c r="F9" s="31">
+      <c r="F10" s="31">
         <v>34064</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="B10" s="48">
-        <f>IF(B9=0,"N/A",B8/B9)</f>
-        <v>24.92</v>
-      </c>
-      <c r="C10" s="48">
-        <f>IF(C9=0,"N/A",C8/C9)</f>
-        <v>41.99</v>
-      </c>
-      <c r="D10" s="48">
-        <f>IF(D9=0,"N/A",D8/D9)</f>
-        <v>60.07</v>
-      </c>
-      <c r="E10" s="48">
-        <f>IF(E9=0,"N/A",E8/E9)</f>
-        <v>76.31</v>
-      </c>
-      <c r="F10" s="48">
-        <f>IF(F9=0,"N/A",F8/F9)</f>
-        <v>87.52</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="19"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="B13" s="31">
-        <v>864756</v>
-      </c>
-      <c r="C13" s="31">
-        <v>2251184</v>
-      </c>
-      <c r="D13" s="31">
-        <v>4253414</v>
-      </c>
-      <c r="E13" s="31">
-        <v>6813759</v>
-      </c>
-      <c r="F13" s="31">
-        <v>9755974</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="B14" s="36">
-        <f>IF((B6+B7+B9)=0,0,(B13/(B6+B7+B9))*365)</f>
-        <v>272</v>
-      </c>
-      <c r="C14" s="36">
-        <f>IF((C6+C7+C9)=0,0,(C13/(C6+C7+C9))*365)</f>
-        <v>671</v>
-      </c>
-      <c r="D14" s="36">
-        <f>IF((D6+D7+D9)=0,0,(D13/(D6+D7+D9))*365)</f>
-        <v>1201</v>
-      </c>
-      <c r="E14" s="36">
-        <f>IF((E6+E7+E9)=0,0,(E13/(E6+E7+E9))*365)</f>
-        <v>1832</v>
-      </c>
-      <c r="F14" s="36">
-        <f>IF((F6+F7+F9)=0,0,(F13/(F6+F7+F9))*365)</f>
-        <v>2518</v>
-      </c>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="B11" s="34">
+        <f>B8+B9+B10</f>
+        <v>849542</v>
+      </c>
+      <c r="C11" s="34">
+        <f>C8+C9+C10</f>
+        <v>1446207</v>
+      </c>
+      <c r="D11" s="34">
+        <f>D8+D9+D10</f>
+        <v>2062008</v>
+      </c>
+      <c r="E11" s="34">
+        <f>E8+E9+E10</f>
+        <v>2620124</v>
+      </c>
+      <c r="F11" s="34">
+        <f>F8+F9+F10</f>
+        <v>3001994</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="B12" s="50">
+        <f>IF(B10=0,"N/A",B11/B10)</f>
+        <v>24.94</v>
+      </c>
+      <c r="C12" s="50">
+        <f>IF(C10=0,"N/A",C11/C10)</f>
+        <v>42.46</v>
+      </c>
+      <c r="D12" s="50">
+        <f>IF(D10=0,"N/A",D11/D10)</f>
+        <v>60.53</v>
+      </c>
+      <c r="E12" s="50">
+        <f>IF(E10=0,"N/A",E11/E10)</f>
+        <v>76.92</v>
+      </c>
+      <c r="F12" s="50">
+        <f>IF(F10=0,"N/A",F11/F10)</f>
+        <v>88.13</v>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="19" t="s">
+        <v>379</v>
+      </c>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="B15" s="35">
-        <f>IF((B6+B7+B9)=0,0,B13/((B6+B7+B9)/12))</f>
-        <v>8.9</v>
-      </c>
-      <c r="C15" s="35">
-        <f>IF((C6+C7+C9)=0,0,C13/((C6+C7+C9)/12))</f>
-        <v>22.1</v>
-      </c>
-      <c r="D15" s="35">
-        <f>IF((D6+D7+D9)=0,0,D13/((D6+D7+D9)/12))</f>
-        <v>39.5</v>
-      </c>
-      <c r="E15" s="35">
-        <f>IF((E6+E7+E9)=0,0,E13/((E6+E7+E9)/12))</f>
-        <v>60.2</v>
-      </c>
-      <c r="F15" s="35">
-        <f>IF((F6+F7+F9)=0,0,F13/((F6+F7+F9)/12))</f>
-        <v>82.8</v>
+        <v>380</v>
+      </c>
+      <c r="B15" s="31">
+        <v>812256</v>
+      </c>
+      <c r="C15" s="31">
+        <v>2198684</v>
+      </c>
+      <c r="D15" s="31">
+        <v>4200914</v>
+      </c>
+      <c r="E15" s="31">
+        <v>6761259</v>
+      </c>
+      <c r="F15" s="31">
+        <v>9703474</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>197</v>
-      </c>
-      <c r="B16" s="30">
+        <v>381</v>
+      </c>
+      <c r="B16" s="36">
+        <f>IF((B5-B8)=0,0,(B15/(B5-B8))*365)</f>
+        <v>250</v>
+      </c>
+      <c r="C16" s="36">
+        <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
+        <v>650</v>
+      </c>
+      <c r="D16" s="36">
+        <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
+        <v>1177</v>
+      </c>
+      <c r="E16" s="36">
+        <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
+        <v>1811</v>
+      </c>
+      <c r="F16" s="36">
+        <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
+        <v>2496</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="11" t="s">
+        <v>382</v>
+      </c>
+      <c r="B17" s="35">
+        <f>IF((B5-B8)=0,0,B15/((B5-B8)/12))</f>
+        <v>8.2</v>
+      </c>
+      <c r="C17" s="35">
+        <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
+        <v>21.4</v>
+      </c>
+      <c r="D17" s="35">
+        <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
+        <v>38.7</v>
+      </c>
+      <c r="E17" s="35">
+        <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
+        <v>59.5</v>
+      </c>
+      <c r="F17" s="35">
+        <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
+        <v>82.1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="11" t="s">
+        <v>215</v>
+      </c>
+      <c r="B18" s="30">
         <v>0.5</v>
       </c>
-      <c r="C16" s="30">
+      <c r="C18" s="30">
         <v>0.65</v>
       </c>
-      <c r="D16" s="30">
+      <c r="D18" s="30">
         <v>0.8</v>
       </c>
-      <c r="E16" s="30">
+      <c r="E18" s="30">
         <v>0.925</v>
       </c>
-      <c r="F16" s="30">
+      <c r="F18" s="30">
         <v>1</v>
       </c>
     </row>
-    <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="19" t="s">
-        <v>358</v>
-      </c>
-      <c r="B18" s="19"/>
-      <c r="C18" s="19"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
-        <v>241</v>
-      </c>
-      <c r="B19" s="31">
-        <v>19750</v>
-      </c>
-      <c r="C19" s="31">
-        <v>20164</v>
-      </c>
-      <c r="D19" s="31">
-        <v>20654</v>
-      </c>
-      <c r="E19" s="31">
-        <v>21205</v>
-      </c>
-      <c r="F19" s="31">
-        <v>21807</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="11" t="s">
-        <v>359</v>
-      </c>
-      <c r="B20" s="31">
-        <v>888836</v>
-      </c>
-      <c r="C20" s="31">
-        <v>914480</v>
-      </c>
-      <c r="D20" s="31">
-        <v>940892</v>
-      </c>
-      <c r="E20" s="31">
-        <v>968097</v>
-      </c>
-      <c r="F20" s="31">
-        <v>996118</v>
-      </c>
+    <row r="20" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>360</v>
+        <v>259</v>
       </c>
       <c r="B21" s="31">
+        <v>19750</v>
+      </c>
+      <c r="C21" s="31">
+        <v>20164</v>
+      </c>
+      <c r="D21" s="31">
+        <v>20654</v>
+      </c>
+      <c r="E21" s="31">
+        <v>21205</v>
+      </c>
+      <c r="F21" s="31">
+        <v>21807</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="11" t="s">
+        <v>384</v>
+      </c>
+      <c r="B22" s="31">
+        <v>888836</v>
+      </c>
+      <c r="C22" s="31">
+        <v>914480</v>
+      </c>
+      <c r="D22" s="31">
+        <v>940892</v>
+      </c>
+      <c r="E22" s="31">
+        <v>968097</v>
+      </c>
+      <c r="F22" s="31">
+        <v>996118</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="11" t="s">
+        <v>385</v>
+      </c>
+      <c r="B23" s="31">
         <v>2714</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C23" s="31">
         <v>2388</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D23" s="31">
         <v>2197</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E23" s="31">
         <v>2105</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F23" s="31">
         <v>2090</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="10" t="s">
-        <v>361</v>
-      </c>
-      <c r="B22" s="49">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="B24" s="51">
         <v>53</v>
       </c>
-      <c r="C22" s="49">
+      <c r="C24" s="51">
         <v>52</v>
       </c>
-      <c r="D22" s="49">
+      <c r="D24" s="51">
         <v>51</v>
       </c>
-      <c r="E22" s="49">
+      <c r="E24" s="51">
         <v>51</v>
       </c>
-      <c r="F22" s="49">
+      <c r="F24" s="51">
         <v>51</v>
       </c>
     </row>
-    <row r="24" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="B25" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="C25" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="D25" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="E25" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="F25" s="50" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="11" t="s">
-        <v>365</v>
-      </c>
-      <c r="B26" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="C26" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="D26" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="E26" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="F26" s="50" t="s">
-        <v>364</v>
-      </c>
+    <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="19" t="s">
+        <v>387</v>
+      </c>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>366</v>
-      </c>
-      <c r="B27" s="51" t="s">
-        <v>367</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>367</v>
-      </c>
-      <c r="D27" s="51" t="s">
-        <v>367</v>
-      </c>
-      <c r="E27" s="51" t="s">
-        <v>367</v>
-      </c>
-      <c r="F27" s="51" t="s">
-        <v>367</v>
+        <v>388</v>
+      </c>
+      <c r="B27" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="E27" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="F27" s="52" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>368</v>
-      </c>
-      <c r="B28" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="C28" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="D28" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="E28" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="F28" s="50" t="s">
-        <v>364</v>
+        <v>390</v>
+      </c>
+      <c r="B28" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="E28" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="F28" s="52" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="B29" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="C29" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="D29" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="E29" s="50" t="s">
-        <v>364</v>
-      </c>
-      <c r="F29" s="50" t="s">
-        <v>364</v>
+        <v>391</v>
+      </c>
+      <c r="B29" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="E29" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="F29" s="52" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="11" t="s">
+        <v>392</v>
+      </c>
+      <c r="B30" s="53" t="s">
+        <v>393</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>393</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>393</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>393</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="11" t="s">
+        <v>394</v>
+      </c>
+      <c r="B31" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="D31" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="E31" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="F31" s="52" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="11" t="s">
+        <v>395</v>
+      </c>
+      <c r="B32" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="D32" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="E32" s="52" t="s">
+        <v>389</v>
+      </c>
+      <c r="F32" s="52" t="s">
+        <v>389</v>
       </c>
     </row>
   </sheetData>
@@ -6006,28 +6260,28 @@
       <c r="E1" s="15"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="52" t="s">
-        <v>370</v>
-      </c>
-      <c r="B3" s="52" t="s">
-        <v>112</v>
-      </c>
-      <c r="D3" s="52" t="s">
-        <v>371</v>
-      </c>
-      <c r="E3" s="52" t="s">
-        <v>112</v>
+      <c r="A3" s="54" t="s">
+        <v>396</v>
+      </c>
+      <c r="B3" s="54" t="s">
+        <v>114</v>
+      </c>
+      <c r="D3" s="54" t="s">
+        <v>397</v>
+      </c>
+      <c r="E3" s="54" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B4" s="31">
         <v>250000</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>372</v>
+        <v>398</v>
       </c>
       <c r="E4" s="31">
         <v>200000</v>
@@ -6035,13 +6289,13 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B5" s="31">
         <v>50000</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="E5" s="31">
         <v>50000</v>
@@ -6049,13 +6303,13 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>373</v>
+        <v>399</v>
       </c>
       <c r="B6" s="31">
         <v>75000</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>374</v>
+        <v>400</v>
       </c>
       <c r="E6" s="31">
         <v>75000</v>
@@ -6063,7 +6317,7 @@
     </row>
     <row r="7" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D7" s="11" t="s">
-        <v>375</v>
+        <v>401</v>
       </c>
       <c r="E7" s="31">
         <v>50000</v>
@@ -6071,13 +6325,13 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>376</v>
+        <v>402</v>
       </c>
       <c r="B9" s="33">
         <v>375000</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>377</v>
+        <v>403</v>
       </c>
       <c r="E9" s="33">
         <v>375000</v>
@@ -6085,9 +6339,9 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>378</v>
-      </c>
-      <c r="B10" s="46">
+        <v>404</v>
+      </c>
+      <c r="B10" s="48">
         <v>0</v>
       </c>
     </row>
@@ -6108,7 +6362,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B3:C43"/>
+  <dimension ref="B3:C44"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -6374,18 +6628,26 @@
         <v>91</v>
       </c>
     </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B43" s="14" t="s">
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="C43" s="14"/>
+      <c r="C41" s="13" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C44" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B43:C43"/>
+    <mergeCell ref="B44:C44"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C19" r:id="rId1" location="#'Instructions'!A1"/>
@@ -6410,6 +6672,7 @@
     <hyperlink ref="C38" r:id="rId20" location="#'Scenarios'!A1"/>
     <hyperlink ref="C39" r:id="rId21" location="#'Underwriting Snapshot'!A1"/>
     <hyperlink ref="C40" r:id="rId22" location="#'Financial Health'!A1"/>
+    <hyperlink ref="C41" r:id="rId23" location="#'Budget Narrative'!A1"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -6433,7 +6696,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>379</v>
+        <v>405</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6443,7 +6706,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>380</v>
+        <v>406</v>
       </c>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
@@ -6453,7 +6716,7 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
-        <v>381</v>
+        <v>407</v>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6461,24 +6724,24 @@
         <v>7</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E5" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B6" s="31">
         <v>1975000</v>
@@ -6498,7 +6761,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B7" s="31">
         <v>1160236</v>
@@ -6518,7 +6781,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B8" s="33">
         <v>814764</v>
@@ -6538,7 +6801,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B9" s="30">
         <v>0.4125385351058188</v>
@@ -6558,27 +6821,27 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B10" s="53">
+        <v>378</v>
+      </c>
+      <c r="B10" s="55">
         <v>24.92</v>
       </c>
-      <c r="C10" s="53">
+      <c r="C10" s="55">
         <v>41.99</v>
       </c>
-      <c r="D10" s="53">
+      <c r="D10" s="55">
         <v>60.07</v>
       </c>
-      <c r="E10" s="53">
+      <c r="E10" s="55">
         <v>76.31</v>
       </c>
-      <c r="F10" s="53">
+      <c r="F10" s="55">
         <v>87.52</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="B11" s="36">
         <v>53</v>
@@ -6598,7 +6861,7 @@
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="19" t="s">
-        <v>382</v>
+        <v>408</v>
       </c>
       <c r="B13" s="19"/>
       <c r="C13" s="19"/>
@@ -6608,7 +6871,7 @@
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="17" t="s">
-        <v>383</v>
+        <v>409</v>
       </c>
     </row>
     <row r="15" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6616,24 +6879,24 @@
         <v>7</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E15" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B16" s="31">
         <v>1678750</v>
@@ -6653,7 +6916,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B17" s="31">
         <v>1160236</v>
@@ -6673,7 +6936,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="10" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B18" s="33">
         <v>518514</v>
@@ -6693,7 +6956,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B19" s="30">
         <v>0.308868864830375</v>
@@ -6713,27 +6976,27 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B20" s="53">
+        <v>378</v>
+      </c>
+      <c r="B20" s="55">
         <v>16.22</v>
       </c>
-      <c r="C20" s="53">
+      <c r="C20" s="55">
         <v>30.45</v>
       </c>
-      <c r="D20" s="53">
+      <c r="D20" s="55">
         <v>45.52</v>
       </c>
-      <c r="E20" s="53">
+      <c r="E20" s="55">
         <v>59.03</v>
       </c>
-      <c r="F20" s="53">
+      <c r="F20" s="55">
         <v>68.31</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="B21" s="36">
         <v>54</v>
@@ -6753,7 +7016,7 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="19" t="s">
-        <v>384</v>
+        <v>410</v>
       </c>
       <c r="B23" s="19"/>
       <c r="C23" s="19"/>
@@ -6763,7 +7026,7 @@
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="17" t="s">
-        <v>385</v>
+        <v>411</v>
       </c>
     </row>
     <row r="25" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6771,24 +7034,24 @@
         <v>7</v>
       </c>
       <c r="B25" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D25" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E25" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F25" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="B26" s="31">
         <v>1975000</v>
@@ -6808,7 +7071,7 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B27" s="31">
         <v>1173736</v>
@@ -6828,7 +7091,7 @@
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B28" s="33">
         <v>801264</v>
@@ -6848,7 +7111,7 @@
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B29" s="30">
         <v>0.4057030920678441</v>
@@ -6868,27 +7131,27 @@
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="B30" s="53">
+        <v>378</v>
+      </c>
+      <c r="B30" s="55">
         <v>24.52</v>
       </c>
-      <c r="C30" s="53">
+      <c r="C30" s="55">
         <v>41.49</v>
       </c>
-      <c r="D30" s="53">
+      <c r="D30" s="55">
         <v>59.46</v>
       </c>
-      <c r="E30" s="53">
+      <c r="E30" s="55">
         <v>75.6</v>
       </c>
-      <c r="F30" s="53">
+      <c r="F30" s="55">
         <v>86.74</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>361</v>
+        <v>386</v>
       </c>
       <c r="B31" s="36">
         <v>53</v>
@@ -6934,7 +7197,7 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>386</v>
+        <v>412</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -6946,7 +7209,7 @@
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B3" s="19"/>
     </row>
@@ -6960,7 +7223,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="B5" s="11" t="s">
         <v>34</v>
@@ -6968,7 +7231,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>387</v>
+        <v>413</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>36</v>
@@ -6992,7 +7255,7 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>388</v>
+        <v>414</v>
       </c>
       <c r="B9" s="11" t="s">
         <v>46</v>
@@ -7000,7 +7263,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>389</v>
+        <v>415</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -7020,25 +7283,25 @@
       <c r="C12" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="E12" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="F12" s="54" t="s">
+      <c r="D12" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="G12" s="54" t="s">
+      <c r="E12" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="H12" s="54" t="s">
+      <c r="F12" s="56" t="s">
         <v>106</v>
+      </c>
+      <c r="G12" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="56" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>351</v>
+        <v>373</v>
       </c>
       <c r="D13" s="31">
         <v>1975000</v>
@@ -7058,7 +7321,7 @@
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="D14" s="31">
         <v>1160236</v>
@@ -7078,7 +7341,7 @@
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="D15" s="31">
         <v>789764</v>
@@ -7098,27 +7361,27 @@
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>390</v>
+        <v>416</v>
       </c>
       <c r="D16" s="31">
-        <v>864756</v>
+        <v>812256</v>
       </c>
       <c r="E16" s="31">
-        <v>2251184</v>
+        <v>2198684</v>
       </c>
       <c r="F16" s="31">
-        <v>4253414</v>
+        <v>4200914</v>
       </c>
       <c r="G16" s="31">
-        <v>6813759</v>
+        <v>6761259</v>
       </c>
       <c r="H16" s="31">
-        <v>9755974</v>
+        <v>9703474</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>391</v>
+        <v>417</v>
       </c>
       <c r="D17" s="31">
         <v>231645</v>
@@ -7138,7 +7401,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>392</v>
+        <v>418</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -7158,25 +7421,25 @@
       <c r="C20" t="s">
         <v>7</v>
       </c>
-      <c r="D20" s="54" t="s">
-        <v>102</v>
-      </c>
-      <c r="E20" s="54" t="s">
-        <v>103</v>
-      </c>
-      <c r="F20" s="54" t="s">
+      <c r="D20" s="56" t="s">
         <v>104</v>
       </c>
-      <c r="G20" s="54" t="s">
+      <c r="E20" s="56" t="s">
         <v>105</v>
       </c>
-      <c r="H20" s="54" t="s">
+      <c r="F20" s="56" t="s">
         <v>106</v>
+      </c>
+      <c r="G20" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="H20" s="56" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>393</v>
+        <v>419</v>
       </c>
       <c r="D21" s="30">
         <v>0.3998803072577175</v>
@@ -7196,27 +7459,27 @@
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="D22" s="53">
-        <v>24.92</v>
-      </c>
-      <c r="E22" s="53">
-        <v>41.99</v>
-      </c>
-      <c r="F22" s="53">
-        <v>60.07</v>
-      </c>
-      <c r="G22" s="53">
-        <v>76.31</v>
-      </c>
-      <c r="H22" s="53">
-        <v>87.52</v>
+        <v>378</v>
+      </c>
+      <c r="D22" s="55">
+        <v>24.18</v>
+      </c>
+      <c r="E22" s="55">
+        <v>41.7</v>
+      </c>
+      <c r="F22" s="55">
+        <v>59.78</v>
+      </c>
+      <c r="G22" s="55">
+        <v>76.16</v>
+      </c>
+      <c r="H22" s="55">
+        <v>87.37</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D23" s="30">
         <v>0.5</v>
@@ -7236,7 +7499,7 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>394</v>
+        <v>420</v>
       </c>
       <c r="D24" s="36">
         <v>100</v>
@@ -7256,7 +7519,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>395</v>
+        <v>421</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -7297,7 +7560,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>396</v>
+        <v>422</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -7307,662 +7570,662 @@
       <c r="H2" s="1"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B3" s="55" t="s">
-        <v>397</v>
-      </c>
-      <c r="C3" s="55"/>
-      <c r="D3" s="55"/>
-      <c r="E3" s="55"/>
-      <c r="F3" s="55"/>
-      <c r="G3" s="55"/>
-      <c r="H3" s="55"/>
+      <c r="B3" s="57" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="56" t="s">
-        <v>398</v>
-      </c>
-      <c r="D4" s="57" t="s">
-        <v>399</v>
-      </c>
-      <c r="F4" s="58" t="s">
-        <v>400</v>
+      <c r="B4" s="58" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="59" t="s">
+        <v>425</v>
+      </c>
+      <c r="F4" s="60" t="s">
+        <v>426</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="C6" s="59" t="s">
-        <v>402</v>
-      </c>
-      <c r="D6" s="59" t="s">
-        <v>403</v>
-      </c>
-      <c r="E6" s="59" t="s">
-        <v>404</v>
-      </c>
-      <c r="F6" s="59" t="s">
-        <v>405</v>
-      </c>
-      <c r="G6" s="59" t="s">
-        <v>406</v>
-      </c>
-      <c r="H6" s="59" t="s">
-        <v>407</v>
+        <v>427</v>
+      </c>
+      <c r="C6" s="61" t="s">
+        <v>428</v>
+      </c>
+      <c r="D6" s="61" t="s">
+        <v>429</v>
+      </c>
+      <c r="E6" s="61" t="s">
+        <v>430</v>
+      </c>
+      <c r="F6" s="61" t="s">
+        <v>431</v>
+      </c>
+      <c r="G6" s="61" t="s">
+        <v>432</v>
+      </c>
+      <c r="H6" s="61" t="s">
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="11" t="s">
-        <v>394</v>
-      </c>
-      <c r="C7" s="60">
+        <v>420</v>
+      </c>
+      <c r="C7" s="62">
         <v>100</v>
       </c>
-      <c r="D7" s="60">
+      <c r="D7" s="62">
         <v>130</v>
       </c>
-      <c r="E7" s="60">
+      <c r="E7" s="62">
         <v>160</v>
       </c>
-      <c r="F7" s="60">
+      <c r="F7" s="62">
         <v>185</v>
       </c>
-      <c r="G7" s="60">
+      <c r="G7" s="62">
         <v>200</v>
       </c>
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="11" t="s">
-        <v>351</v>
-      </c>
-      <c r="C8" s="61">
+        <v>373</v>
+      </c>
+      <c r="C8" s="63">
         <v>1975000</v>
       </c>
-      <c r="D8" s="61">
+      <c r="D8" s="63">
         <v>2621350</v>
       </c>
-      <c r="E8" s="61">
+      <c r="E8" s="63">
         <v>3304703.5</v>
       </c>
-      <c r="F8" s="61">
+      <c r="F8" s="63">
         <v>3922889.9299999997</v>
       </c>
-      <c r="G8" s="61">
+      <c r="G8" s="63">
         <v>4361346.638750001</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="11" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="61">
+        <v>328</v>
+      </c>
+      <c r="C9" s="63">
         <v>854772</v>
       </c>
-      <c r="D9" s="61">
+      <c r="D9" s="63">
         <v>880415.16</v>
       </c>
-      <c r="E9" s="61">
+      <c r="E9" s="63">
         <v>906827.6148</v>
       </c>
-      <c r="F9" s="61">
+      <c r="F9" s="63">
         <v>934032.443244</v>
       </c>
-      <c r="G9" s="61">
+      <c r="G9" s="63">
         <v>962053.4165413202</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="11" t="s">
-        <v>311</v>
-      </c>
-      <c r="C10" s="61">
+        <v>329</v>
+      </c>
+      <c r="C10" s="63">
         <v>271400</v>
       </c>
-      <c r="D10" s="61">
+      <c r="D10" s="63">
         <v>310442</v>
       </c>
-      <c r="E10" s="61">
+      <c r="E10" s="63">
         <v>351582.25999999995</v>
       </c>
-      <c r="F10" s="61">
+      <c r="F10" s="63">
         <v>389447.9028</v>
       </c>
-      <c r="G10" s="61">
+      <c r="G10" s="63">
         <v>418013.9720340001</v>
       </c>
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="11" t="s">
-        <v>312</v>
-      </c>
-      <c r="C11" s="61">
+        <v>330</v>
+      </c>
+      <c r="C11" s="63">
         <v>34064.39316600799</v>
       </c>
-      <c r="D11" s="61">
+      <c r="D11" s="63">
         <v>34064.39316600799</v>
       </c>
-      <c r="E11" s="61">
+      <c r="E11" s="63">
         <v>34064.39316600799</v>
       </c>
-      <c r="F11" s="61">
+      <c r="F11" s="63">
         <v>34064.39316600799</v>
       </c>
-      <c r="G11" s="61">
+      <c r="G11" s="63">
         <v>34064.39316600799</v>
       </c>
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="10" t="s">
-        <v>408</v>
-      </c>
-      <c r="C12" s="62">
+        <v>374</v>
+      </c>
+      <c r="C12" s="64">
         <v>789763.6068339921</v>
       </c>
-      <c r="D12" s="62">
+      <c r="D12" s="64">
         <v>1386428.446833992</v>
       </c>
-      <c r="E12" s="62">
+      <c r="E12" s="64">
         <v>2002229.2320339922</v>
       </c>
-      <c r="F12" s="62">
+      <c r="F12" s="64">
         <v>2560345.190789992</v>
       </c>
-      <c r="G12" s="62">
+      <c r="G12" s="64">
         <v>2942214.857008673</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="10" t="s">
-        <v>355</v>
-      </c>
-      <c r="C13" s="62">
-        <v>864756</v>
-      </c>
-      <c r="D13" s="62">
-        <v>2251184.446833992</v>
-      </c>
-      <c r="E13" s="62">
-        <v>4253413.678867985</v>
-      </c>
-      <c r="F13" s="62">
-        <v>6813758.869657977</v>
-      </c>
-      <c r="G13" s="62">
-        <v>9755973.72666665</v>
+        <v>380</v>
+      </c>
+      <c r="C13" s="64">
+        <v>812256</v>
+      </c>
+      <c r="D13" s="64">
+        <v>2198684.446833992</v>
+      </c>
+      <c r="E13" s="64">
+        <v>4200913.678867985</v>
+      </c>
+      <c r="F13" s="64">
+        <v>6761258.869657977</v>
+      </c>
+      <c r="G13" s="64">
+        <v>9703473.72666665</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="10" t="s">
-        <v>393</v>
-      </c>
-      <c r="C14" s="63">
+        <v>419</v>
+      </c>
+      <c r="C14" s="65">
         <v>0.3998803072577175</v>
       </c>
-      <c r="D14" s="63">
+      <c r="D14" s="65">
         <v>0.5288986388059557</v>
       </c>
-      <c r="E14" s="63">
+      <c r="E14" s="65">
         <v>0.6058725788967125</v>
       </c>
-      <c r="F14" s="63">
+      <c r="F14" s="65">
         <v>0.6526681187789514</v>
       </c>
-      <c r="G14" s="63">
+      <c r="G14" s="65">
         <v>0.6746115593902751</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
-        <v>241</v>
-      </c>
-      <c r="C15" s="64">
+        <v>259</v>
+      </c>
+      <c r="C15" s="66">
         <v>19750</v>
       </c>
-      <c r="D15" s="64">
+      <c r="D15" s="66">
         <v>20164.23076923077</v>
       </c>
-      <c r="E15" s="64">
+      <c r="E15" s="66">
         <v>20654.396875</v>
       </c>
-      <c r="F15" s="64">
+      <c r="F15" s="66">
         <v>21204.81043243243</v>
       </c>
-      <c r="G15" s="64">
+      <c r="G15" s="66">
         <v>21806.733193750006</v>
       </c>
-      <c r="H15" s="65" t="s">
-        <v>409</v>
+      <c r="H15" s="67" t="s">
+        <v>434</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="10" t="s">
-        <v>294</v>
-      </c>
-      <c r="C16" s="66">
+        <v>312</v>
+      </c>
+      <c r="C16" s="68">
         <v>11602.36393166008</v>
       </c>
-      <c r="D16" s="66">
+      <c r="D16" s="68">
         <v>9422.47348589237</v>
       </c>
-      <c r="E16" s="66">
+      <c r="E16" s="68">
         <v>8077.9641747875485</v>
       </c>
-      <c r="F16" s="66">
+      <c r="F16" s="68">
         <v>7338.079671405449</v>
       </c>
-      <c r="G16" s="66">
+      <c r="G16" s="68">
         <v>7070.65890870664</v>
       </c>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="11" t="s">
-        <v>410</v>
-      </c>
-      <c r="C17" s="61">
+        <v>435</v>
+      </c>
+      <c r="C17" s="63">
         <v>600</v>
       </c>
-      <c r="D17" s="61">
+      <c r="D17" s="63">
         <v>618</v>
       </c>
-      <c r="E17" s="61">
+      <c r="E17" s="63">
         <v>636.54</v>
       </c>
-      <c r="F17" s="61">
+      <c r="F17" s="63">
         <v>655.6362</v>
       </c>
-      <c r="G17" s="61">
+      <c r="G17" s="63">
         <v>675.3052860000003</v>
       </c>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="11" t="s">
-        <v>411</v>
-      </c>
-      <c r="C18" s="64">
+        <v>436</v>
+      </c>
+      <c r="C18" s="66">
         <v>1364</v>
       </c>
-      <c r="D18" s="64">
+      <c r="D18" s="66">
         <v>1080.7076923076922</v>
       </c>
-      <c r="E18" s="64">
+      <c r="E18" s="66">
         <v>904.4172499999999</v>
       </c>
-      <c r="F18" s="64">
+      <c r="F18" s="66">
         <v>805.6646637837838</v>
       </c>
-      <c r="G18" s="64">
+      <c r="G18" s="66">
         <v>767.5970084200001</v>
       </c>
-      <c r="H18" s="65" t="s">
-        <v>412</v>
+      <c r="H18" s="67" t="s">
+        <v>437</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="10" t="s">
-        <v>413</v>
-      </c>
-      <c r="C19" s="67">
+        <v>438</v>
+      </c>
+      <c r="C19" s="69">
         <v>7897.636068339921</v>
       </c>
-      <c r="D19" s="67">
+      <c r="D19" s="69">
         <v>10664.834206415322</v>
       </c>
-      <c r="E19" s="67">
+      <c r="E19" s="69">
         <v>12513.932700212452</v>
       </c>
-      <c r="F19" s="67">
+      <c r="F19" s="69">
         <v>13839.703733999957</v>
       </c>
-      <c r="G19" s="67">
+      <c r="G19" s="69">
         <v>14711.074285043363</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="10" t="s">
-        <v>414</v>
-      </c>
-      <c r="C20" s="63">
+        <v>439</v>
+      </c>
+      <c r="C20" s="65">
         <v>0.4327959493670886</v>
       </c>
-      <c r="D20" s="63">
+      <c r="D20" s="65">
         <v>0.3358632612966601</v>
       </c>
-      <c r="E20" s="63">
+      <c r="E20" s="65">
         <v>0.2744051364365971</v>
       </c>
-      <c r="F20" s="63">
+      <c r="F20" s="65">
         <v>0.23809805013927576</v>
       </c>
-      <c r="G20" s="63">
+      <c r="G20" s="65">
         <v>0.22058632258064514</v>
       </c>
-      <c r="H20" s="65" t="s">
-        <v>415</v>
+      <c r="H20" s="67" t="s">
+        <v>440</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="10" t="s">
-        <v>416</v>
-      </c>
-      <c r="C21" s="63">
+        <v>441</v>
+      </c>
+      <c r="C21" s="65">
         <v>0.0690632911392405</v>
       </c>
-      <c r="D21" s="63">
+      <c r="D21" s="65">
         <v>0.05359528487229862</v>
       </c>
-      <c r="E21" s="63">
+      <c r="E21" s="65">
         <v>0.043788121990369175</v>
       </c>
-      <c r="F21" s="63">
+      <c r="F21" s="65">
         <v>0.03799442896935934</v>
       </c>
-      <c r="G21" s="63">
+      <c r="G21" s="65">
         <v>0.035199999999999995</v>
       </c>
-      <c r="H21" s="65" t="s">
-        <v>417</v>
+      <c r="H21" s="67" t="s">
+        <v>442</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="C22" s="63">
+        <v>443</v>
+      </c>
+      <c r="C22" s="65">
         <v>0.42978632911392406</v>
       </c>
-      <c r="D22" s="63">
+      <c r="D22" s="65">
         <v>0.5457084479371316</v>
       </c>
-      <c r="E22" s="63">
+      <c r="E22" s="65">
         <v>0.6192064205457464</v>
       </c>
-      <c r="F22" s="63">
+      <c r="F22" s="65">
         <v>0.6626261838440112</v>
       </c>
-      <c r="G22" s="63">
+      <c r="G22" s="65">
         <v>0.6835685161290322</v>
       </c>
-      <c r="H22" s="65" t="s">
-        <v>419</v>
+      <c r="H22" s="67" t="s">
+        <v>444</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="10" t="s">
-        <v>420</v>
-      </c>
-      <c r="C23" s="68">
+        <v>445</v>
+      </c>
+      <c r="C23" s="70">
         <v>4</v>
       </c>
-      <c r="D23" s="68">
+      <c r="D23" s="70">
         <v>4</v>
       </c>
-      <c r="E23" s="68">
+      <c r="E23" s="70">
         <v>4</v>
       </c>
-      <c r="F23" s="68">
+      <c r="F23" s="70">
         <v>4</v>
       </c>
-      <c r="G23" s="68">
+      <c r="G23" s="70">
         <v>4</v>
       </c>
-      <c r="H23" s="65" t="s">
-        <v>421</v>
+      <c r="H23" s="67" t="s">
+        <v>446</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="10" t="s">
-        <v>353</v>
-      </c>
-      <c r="C24" s="69">
+        <v>378</v>
+      </c>
+      <c r="C24" s="71">
         <v>24.918336160088252</v>
       </c>
-      <c r="D24" s="69">
+      <c r="D24" s="71">
         <v>41.993786092965045</v>
       </c>
-      <c r="E24" s="69">
+      <c r="E24" s="71">
         <v>60.071336519270375</v>
       </c>
-      <c r="F24" s="69">
+      <c r="F24" s="71">
         <v>76.3087007388667</v>
       </c>
-      <c r="G24" s="69">
+      <c r="G24" s="71">
         <v>87.51893026967599</v>
       </c>
-      <c r="H24" s="65" t="s">
-        <v>422</v>
+      <c r="H24" s="67" t="s">
+        <v>447</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="10" t="s">
-        <v>423</v>
-      </c>
-      <c r="C25" s="40" t="str">
-        <f>IF('5-Year Operating Stmt'!B16&gt;=0,"✓ Break-even","")</f>
+        <v>448</v>
+      </c>
+      <c r="C25" s="42" t="str">
+        <f>IF('5-Year Operating Stmt'!B17&gt;=0,"✓ Break-even","")</f>
         <v>✓ Break-even</v>
       </c>
-      <c r="D25" s="70" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!C16&gt;=0,'5-Year Operating Stmt'!B16&lt;0),"✓ Break-even","")</f>
+      <c r="D25" s="72" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!C17&gt;=0,'5-Year Operating Stmt'!B17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="70" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!D16&gt;=0,'5-Year Operating Stmt'!C16&lt;0),"✓ Break-even","")</f>
+      <c r="E25" s="72" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!D17&gt;=0,'5-Year Operating Stmt'!C17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="70" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!E16&gt;=0,'5-Year Operating Stmt'!D16&lt;0),"✓ Break-even","")</f>
+      <c r="F25" s="72" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!E17&gt;=0,'5-Year Operating Stmt'!D17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="70" t="str">
-        <f>IF(AND('5-Year Operating Stmt'!F16&gt;=0,'5-Year Operating Stmt'!E16&lt;0),"✓ Break-even","")</f>
+      <c r="G25" s="72" t="str">
+        <f>IF(AND('5-Year Operating Stmt'!F17&gt;=0,'5-Year Operating Stmt'!E17&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="65" t="s">
-        <v>402</v>
+      <c r="H25" s="67" t="s">
+        <v>428</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="10" t="s">
-        <v>424</v>
-      </c>
-      <c r="C26" s="71">
-        <v>9</v>
-      </c>
-      <c r="D26" s="72">
+        <v>449</v>
+      </c>
+      <c r="C26" s="73">
+        <v>8</v>
+      </c>
+      <c r="D26" s="74">
         <v>22</v>
       </c>
-      <c r="E26" s="68">
+      <c r="E26" s="70">
         <v>39</v>
       </c>
-      <c r="F26" s="73" t="s">
-        <v>425</v>
-      </c>
-      <c r="G26" s="73" t="s">
-        <v>425</v>
-      </c>
-      <c r="H26" s="65" t="s">
-        <v>426</v>
+      <c r="F26" s="75" t="s">
+        <v>450</v>
+      </c>
+      <c r="G26" s="75" t="s">
+        <v>450</v>
+      </c>
+      <c r="H26" s="67" t="s">
+        <v>451</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="10" t="s">
-        <v>356</v>
-      </c>
-      <c r="C27" s="68">
-        <v>272</v>
-      </c>
-      <c r="D27" s="68">
-        <v>671</v>
-      </c>
-      <c r="E27" s="68">
-        <v>1201</v>
-      </c>
-      <c r="F27" s="68">
-        <v>1832</v>
-      </c>
-      <c r="G27" s="68">
-        <v>2518</v>
-      </c>
-      <c r="H27" s="65" t="s">
-        <v>427</v>
+        <v>381</v>
+      </c>
+      <c r="C27" s="70">
+        <v>256</v>
+      </c>
+      <c r="D27" s="70">
+        <v>655</v>
+      </c>
+      <c r="E27" s="70">
+        <v>1186</v>
+      </c>
+      <c r="F27" s="70">
+        <v>1818</v>
+      </c>
+      <c r="G27" s="70">
+        <v>2505</v>
+      </c>
+      <c r="H27" s="67" t="s">
+        <v>452</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
-        <v>428</v>
+        <v>453</v>
       </c>
       <c r="C29" s="19" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="D29" s="19" t="s">
-        <v>430</v>
+        <v>455</v>
       </c>
       <c r="E29" s="19"/>
       <c r="F29" s="19" t="s">
-        <v>431</v>
+        <v>456</v>
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B30" s="42" t="s">
-        <v>432</v>
-      </c>
-      <c r="C30" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D30" s="74" t="s">
-        <v>434</v>
-      </c>
-      <c r="E30" s="74"/>
-      <c r="F30" s="75" t="s">
-        <v>435</v>
-      </c>
-      <c r="G30" s="75"/>
-      <c r="H30" s="75"/>
+      <c r="B30" s="44" t="s">
+        <v>457</v>
+      </c>
+      <c r="C30" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D30" s="76" t="s">
+        <v>459</v>
+      </c>
+      <c r="E30" s="76"/>
+      <c r="F30" s="77" t="s">
+        <v>460</v>
+      </c>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B31" s="42" t="s">
-        <v>436</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D31" s="74" t="s">
-        <v>437</v>
-      </c>
-      <c r="E31" s="74"/>
-      <c r="F31" s="75" t="s">
-        <v>438</v>
-      </c>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
+      <c r="B31" s="44" t="s">
+        <v>461</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D31" s="76" t="s">
+        <v>462</v>
+      </c>
+      <c r="E31" s="76"/>
+      <c r="F31" s="77" t="s">
+        <v>463</v>
+      </c>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B32" s="42" t="s">
-        <v>439</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D32" s="74" t="s">
-        <v>440</v>
-      </c>
-      <c r="E32" s="74"/>
-      <c r="F32" s="75" t="s">
-        <v>441</v>
-      </c>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
+      <c r="B32" s="44" t="s">
+        <v>464</v>
+      </c>
+      <c r="C32" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D32" s="76" t="s">
+        <v>465</v>
+      </c>
+      <c r="E32" s="76"/>
+      <c r="F32" s="77" t="s">
+        <v>466</v>
+      </c>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B33" s="42" t="s">
-        <v>442</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D33" s="74" t="s">
-        <v>443</v>
-      </c>
-      <c r="E33" s="74"/>
-      <c r="F33" s="75" t="s">
-        <v>444</v>
-      </c>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
+      <c r="B33" s="44" t="s">
+        <v>467</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D33" s="76" t="s">
+        <v>468</v>
+      </c>
+      <c r="E33" s="76"/>
+      <c r="F33" s="77" t="s">
+        <v>469</v>
+      </c>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B34" s="42" t="s">
-        <v>445</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D34" s="74" t="s">
-        <v>446</v>
-      </c>
-      <c r="E34" s="74"/>
-      <c r="F34" s="75" t="s">
-        <v>447</v>
-      </c>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
+      <c r="B34" s="44" t="s">
+        <v>470</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D34" s="76" t="s">
+        <v>471</v>
+      </c>
+      <c r="E34" s="76"/>
+      <c r="F34" s="77" t="s">
+        <v>472</v>
+      </c>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B35" s="42" t="s">
-        <v>448</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D35" s="74" t="s">
-        <v>449</v>
-      </c>
-      <c r="E35" s="74"/>
-      <c r="F35" s="75" t="s">
-        <v>450</v>
-      </c>
-      <c r="G35" s="75"/>
-      <c r="H35" s="75"/>
+      <c r="B35" s="44" t="s">
+        <v>473</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D35" s="76" t="s">
+        <v>474</v>
+      </c>
+      <c r="E35" s="76"/>
+      <c r="F35" s="77" t="s">
+        <v>475</v>
+      </c>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B36" s="42" t="s">
-        <v>451</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>433</v>
-      </c>
-      <c r="D36" s="74" t="s">
-        <v>452</v>
-      </c>
-      <c r="E36" s="74"/>
-      <c r="F36" s="75" t="s">
-        <v>453</v>
-      </c>
-      <c r="G36" s="75"/>
-      <c r="H36" s="75"/>
+      <c r="B36" s="44" t="s">
+        <v>476</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>458</v>
+      </c>
+      <c r="D36" s="76" t="s">
+        <v>477</v>
+      </c>
+      <c r="E36" s="76"/>
+      <c r="F36" s="77" t="s">
+        <v>478</v>
+      </c>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="42" t="s">
-        <v>454</v>
+      <c r="B38" s="44" t="s">
+        <v>479</v>
       </c>
       <c r="C38" s="10" t="s">
-        <v>455</v>
+        <v>480</v>
       </c>
       <c r="D38" s="10"/>
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B40" s="76" t="s">
-        <v>456</v>
-      </c>
-      <c r="C40" s="76"/>
-      <c r="D40" s="76"/>
-      <c r="E40" s="76"/>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
+      <c r="B40" s="78" t="s">
+        <v>481</v>
+      </c>
+      <c r="C40" s="78"/>
+      <c r="D40" s="78"/>
+      <c r="E40" s="78"/>
+      <c r="F40" s="78"/>
+      <c r="G40" s="78"/>
+      <c r="H40" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -8069,12 +8332,225 @@
       <formula>C24&gt;=1.25</formula>
     </cfRule>
     <cfRule type="expression" dxfId="22" priority="2">
-      <formula>C24&gt;=1</formula>
+      <formula>C24&gt;=1.15</formula>
     </cfRule>
     <cfRule type="expression" dxfId="23" priority="3">
-      <formula>C24&lt;1</formula>
+      <formula>C24&lt;1.15</formula>
     </cfRule>
   </conditionalFormatting>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:B28"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="2" max="2" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="21"/>
+    </row>
+    <row r="3" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>482</v>
+      </c>
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B4" s="79"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="19" t="s">
+        <v>484</v>
+      </c>
+      <c r="B6" s="19"/>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B7" s="79"/>
+    </row>
+    <row r="9" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="B9" s="19"/>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B10" s="79"/>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="19" t="s">
+        <v>486</v>
+      </c>
+      <c r="B12" s="19"/>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B13" s="79"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="19" t="s">
+        <v>487</v>
+      </c>
+      <c r="B15" s="19"/>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B16" s="79"/>
+    </row>
+    <row r="18" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="B18" s="19"/>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B19" s="79"/>
+    </row>
+    <row r="21" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" s="19" t="s">
+        <v>489</v>
+      </c>
+      <c r="B21" s="19"/>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B22" s="79"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" s="19" t="s">
+        <v>490</v>
+      </c>
+      <c r="B24" s="19"/>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B25" s="79"/>
+    </row>
+    <row r="27" ht="24" customHeight="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" s="19" t="s">
+        <v>491</v>
+      </c>
+      <c r="B27" s="19"/>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" s="79" t="s">
+        <v>483</v>
+      </c>
+      <c r="B28" s="79"/>
+    </row>
+  </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A25:B25"/>
+    <mergeCell ref="A28:B28"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:H4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="14" customWidth="1"/>
+    <col min="5" max="5" width="30" customWidth="1"/>
+    <col min="6" max="6" width="18" customWidth="1"/>
+    <col min="7" max="7" width="38" customWidth="1"/>
+    <col min="8" max="8" width="50" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B1" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="C1" s="15"/>
+      <c r="D1" s="15"/>
+      <c r="E1" s="15"/>
+      <c r="F1" s="15"/>
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+    </row>
+    <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="80" t="s">
+        <v>493</v>
+      </c>
+      <c r="C2" s="80"/>
+      <c r="D2" s="80"/>
+      <c r="E2" s="80"/>
+      <c r="F2" s="80"/>
+      <c r="G2" s="80"/>
+      <c r="H2" s="80"/>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="81" t="s">
+        <v>494</v>
+      </c>
+      <c r="C4" s="81"/>
+      <c r="D4" s="81"/>
+      <c r="E4" s="81"/>
+      <c r="F4" s="81"/>
+      <c r="G4" s="81"/>
+      <c r="H4" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B1:H1"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B4:H4"/>
+  </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
   <headerFooter>
@@ -8088,7 +8564,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G60"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
@@ -8098,7 +8574,7 @@
   <sheetData>
     <row r="1" ht="32" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -8112,18 +8588,18 @@
         <v>7</v>
       </c>
       <c r="B2" s="17" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="D2" s="18" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="17" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -8166,10 +8642,10 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
@@ -8190,7 +8666,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="20">
         <v>7</v>
@@ -8198,7 +8674,7 @@
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="20">
         <v>200</v>
@@ -8206,7 +8682,7 @@
     </row>
     <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B15" s="19"/>
       <c r="C15" s="19"/>
@@ -8220,24 +8696,24 @@
         <v>7</v>
       </c>
       <c r="B16" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C16" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E16" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F16" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B17" s="22">
         <v>100</v>
@@ -8257,7 +8733,7 @@
     </row>
     <row r="19" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="B19" s="19"/>
       <c r="C19" s="19"/>
@@ -8266,32 +8742,35 @@
       <c r="F19" s="19"/>
       <c r="G19" s="19"/>
     </row>
-    <row r="20" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C20" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E20" s="21" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D21" s="23">
         <v>10500</v>
@@ -8299,16 +8778,19 @@
       <c r="E21" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D22" s="23">
         <v>350</v>
@@ -8316,16 +8798,19 @@
       <c r="E22" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B23" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="C23" s="11" t="s">
         <v>119</v>
-      </c>
-      <c r="C23" s="11" t="s">
-        <v>116</v>
       </c>
       <c r="D23" s="23">
         <v>-1050</v>
@@ -8333,16 +8818,19 @@
       <c r="E23" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D24" s="23">
         <v>8700</v>
@@ -8350,16 +8838,19 @@
       <c r="E24" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D25" s="23">
         <v>50000</v>
@@ -8367,16 +8858,19 @@
       <c r="E25" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D26" s="23">
         <v>25000</v>
@@ -8384,16 +8878,19 @@
       <c r="E26" s="24">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D27" s="23">
         <v>500</v>
@@ -8401,10 +8898,13 @@
       <c r="E27" s="24">
         <v>0</v>
       </c>
+      <c r="F27" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="19" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B29" s="19"/>
       <c r="C29" s="19"/>
@@ -8415,36 +8915,36 @@
     </row>
     <row r="30" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B30" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C30" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="D30" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="E30" s="21" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F30" s="21" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G30" s="21" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D31" s="25">
         <v>1</v>
@@ -8461,13 +8961,13 @@
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D32" s="25">
         <v>1</v>
@@ -8484,13 +8984,13 @@
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B33" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D33" s="25">
         <v>6</v>
@@ -8507,13 +9007,13 @@
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="C34" s="11" t="s">
         <v>141</v>
-      </c>
-      <c r="B34" s="11" t="s">
-        <v>140</v>
-      </c>
-      <c r="C34" s="11" t="s">
-        <v>137</v>
       </c>
       <c r="D34" s="25">
         <v>3</v>
@@ -8530,13 +9030,13 @@
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B35" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C35" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D35" s="25">
         <v>1</v>
@@ -8553,13 +9053,13 @@
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B36" s="11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D36" s="25">
         <v>1</v>
@@ -8576,7 +9076,7 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="19" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="B38" s="19"/>
       <c r="C38" s="19"/>
@@ -8587,30 +9087,30 @@
     </row>
     <row r="39" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="21" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D39" s="21" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E39" s="21" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="11" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C40" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D40" s="23">
         <v>8500</v>
@@ -8621,13 +9121,13 @@
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="11" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B41" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C41" s="11" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D41" s="23">
         <v>1200</v>
@@ -8638,13 +9138,13 @@
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C42" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D42" s="23">
         <v>12000</v>
@@ -8655,13 +9155,13 @@
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
+        <v>156</v>
+      </c>
+      <c r="B43" s="11" t="s">
         <v>152</v>
       </c>
-      <c r="B43" s="11" t="s">
-        <v>148</v>
-      </c>
       <c r="C43" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D43" s="23">
         <v>8000</v>
@@ -8672,13 +9172,13 @@
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="11" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C44" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D44" s="23">
         <v>600</v>
@@ -8689,13 +9189,13 @@
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C45" s="11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D45" s="23">
         <v>400</v>
@@ -8706,13 +9206,13 @@
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="11" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D46" s="23">
         <v>15000</v>
@@ -8723,13 +9223,13 @@
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="11" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C47" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D47" s="23">
         <v>8000</v>
@@ -8740,13 +9240,13 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="B48" s="11" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C48" s="11" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D48" s="23">
         <v>12000</v>
@@ -8757,7 +9257,7 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="19" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="B50" s="19"/>
       <c r="C50" s="19"/>
@@ -8768,27 +9268,27 @@
     </row>
     <row r="51" ht="28" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="21" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B51" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C51" s="21" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C52" s="23">
         <v>250000</v>
@@ -8802,10 +9302,10 @@
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B53" s="11" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C53" s="23">
         <v>25000</v>
@@ -8819,7 +9319,7 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="19" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B55" s="19"/>
       <c r="C55" s="19"/>
@@ -8830,29 +9330,29 @@
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="B56" s="24">
         <v>0.03</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B57" s="24">
         <v>0.03</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B58" s="25">
         <v>1</v>
@@ -8860,7 +9360,7 @@
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" s="11" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="B59" s="23">
         <v>75000</v>
@@ -8868,10 +9368,101 @@
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B60" s="20" t="s">
-        <v>176</v>
+        <v>180</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A61" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B61" s="24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="B62" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B63" s="24">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B64" s="24">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A65" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="B65" s="24">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A66" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="B66" s="24">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A68" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="B68" s="19"/>
+      <c r="C68" s="19"/>
+      <c r="D68" s="19"/>
+      <c r="E68" s="19"/>
+      <c r="F68" s="19"/>
+      <c r="G68" s="19"/>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A69" s="11" t="s">
+        <v>188</v>
+      </c>
+      <c r="B69" s="20" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A70" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="B70" s="20" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A71" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="B71" s="24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A72" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="B72" s="20" t="s">
+        <v>194</v>
       </c>
     </row>
   </sheetData>
@@ -8906,10 +9497,10 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -8930,10 +9521,10 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -8946,7 +9537,7 @@
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B8" s="11" t="s">
         <v>46</v>
@@ -8954,66 +9545,66 @@
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="10" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="10" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -9056,30 +9647,30 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="19" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
@@ -9091,7 +9682,7 @@
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="B6" s="27">
         <v>85</v>
@@ -9117,7 +9708,7 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="B7" s="22">
         <v>200</v>
@@ -9125,7 +9716,7 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="D8" s="29">
         <f>D6/$B$7</f>
@@ -9150,10 +9741,10 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="11" t="s">
-        <v>198</v>
+        <v>181</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>199</v>
+        <v>216</v>
       </c>
       <c r="E10" s="30">
         <f>IF(D6=0,0,(E6-D6)/D6)</f>
@@ -9198,7 +9789,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>200</v>
+        <v>217</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9211,24 +9802,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -9238,7 +9829,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B5" s="31">
         <v>1050000</v>
@@ -9258,7 +9849,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B6" s="31">
         <v>35000</v>
@@ -9278,7 +9869,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="B7" s="32">
         <f>SUM(B5,B6)</f>
@@ -9303,7 +9894,7 @@
     </row>
     <row r="8" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="19" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="B8" s="19"/>
       <c r="C8" s="19"/>
@@ -9313,7 +9904,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B9" s="31">
         <v>105000</v>
@@ -9333,7 +9924,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="10" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
       <c r="B10" s="32">
         <f>SUM(B9)</f>
@@ -9358,7 +9949,7 @@
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -9368,7 +9959,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B12" s="31">
         <v>870000</v>
@@ -9388,7 +9979,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>206</v>
+        <v>223</v>
       </c>
       <c r="B13" s="32">
         <f>SUM(B12)</f>
@@ -9413,7 +10004,7 @@
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="19" t="s">
-        <v>207</v>
+        <v>224</v>
       </c>
       <c r="B14" s="19"/>
       <c r="C14" s="19"/>
@@ -9423,7 +10014,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="B15" s="23">
         <v>50000</v>
@@ -9443,7 +10034,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B16" s="23">
         <v>25000</v>
@@ -9463,7 +10054,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
-        <v>208</v>
+        <v>225</v>
       </c>
       <c r="B17" s="32">
         <f>SUM(B15,B16)</f>
@@ -9488,7 +10079,7 @@
     </row>
     <row r="18" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>209</v>
+        <v>226</v>
       </c>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -9498,7 +10089,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="B19" s="31">
         <v>50000</v>
@@ -9518,7 +10109,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>210</v>
+        <v>227</v>
       </c>
       <c r="B20" s="32">
         <f>SUM(B19)</f>
@@ -9543,7 +10134,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="B22" s="33">
         <f>SUM(B7,B10,B13,B17,B20)</f>
@@ -9583,7 +10174,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -9592,9 +10183,10 @@
     <col min="4" max="4" width="14" customWidth="1"/>
     <col min="5" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
         <v>61</v>
       </c>
@@ -9604,36 +10196,40 @@
       <c r="E1" s="15"/>
       <c r="F1" s="15"/>
       <c r="G1" s="15"/>
-    </row>
-    <row r="3" ht="28" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H1" s="15"/>
+    </row>
+    <row r="3" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>212</v>
+        <v>229</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="G3" s="21" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+      <c r="H3" s="21" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C4" s="25">
         <v>1</v>
@@ -9650,13 +10246,16 @@
       <c r="G4" s="34">
         <v>126018</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H4" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C5" s="25">
         <v>1</v>
@@ -9673,13 +10272,16 @@
       <c r="G5" s="34">
         <v>99488</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H5" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C6" s="25">
         <v>6</v>
@@ -9696,13 +10298,16 @@
       <c r="G6" s="34">
         <v>382032</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H6" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C7" s="25">
         <v>3</v>
@@ -9719,13 +10324,16 @@
       <c r="G7" s="34">
         <v>122544</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H7" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C8" s="25">
         <v>1</v>
@@ -9742,13 +10350,16 @@
       <c r="G8" s="34">
         <v>55713</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="H8" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="11" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C9" s="25">
         <v>1</v>
@@ -9765,10 +10376,13 @@
       <c r="G9" s="34">
         <v>68978</v>
       </c>
+      <c r="H9" s="11" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B11" s="19"/>
       <c r="C11" s="19"/>
@@ -9782,24 +10396,24 @@
         <v>7</v>
       </c>
       <c r="B12" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C12" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B13" s="33">
         <v>854772</v>
@@ -9819,7 +10433,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B14" s="30">
         <v>0.4327959493670886</v>
@@ -9839,7 +10453,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B15" s="35">
         <v>7.7</v>
@@ -9859,7 +10473,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
@@ -9883,7 +10497,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -9896,24 +10510,24 @@
         <v>7</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
@@ -9923,7 +10537,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B5" s="31">
         <v>60000</v>
@@ -9943,7 +10557,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="B6" s="32">
         <f>SUM(B5:B5)</f>
@@ -9968,7 +10582,7 @@
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="19" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B7" s="19"/>
       <c r="C7" s="19"/>
@@ -9978,7 +10592,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="11" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B8" s="31">
         <v>40000</v>
@@ -9998,7 +10612,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B9" s="32">
         <f>SUM(B8:B8)</f>
@@ -10023,7 +10637,7 @@
     </row>
     <row r="10" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="B10" s="19"/>
       <c r="C10" s="19"/>
@@ -10033,7 +10647,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="11" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B11" s="31">
         <v>102000</v>
@@ -10053,7 +10667,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B12" s="31">
         <v>14400</v>
@@ -10073,7 +10687,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B13" s="31">
         <v>12000</v>
@@ -10093,7 +10707,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B14" s="31">
         <v>8000</v>
@@ -10113,7 +10727,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="10" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B15" s="32">
         <f>SUM(B11:B14)</f>
@@ -10138,7 +10752,7 @@
     </row>
     <row r="16" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="19" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="B16" s="19"/>
       <c r="C16" s="19"/>
@@ -10148,7 +10762,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B17" s="31">
         <v>15000</v>
@@ -10168,7 +10782,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B18" s="31">
         <v>8000</v>
@@ -10188,7 +10802,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B19" s="31">
         <v>12000</v>
@@ -10208,7 +10822,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="B20" s="32">
         <f>SUM(B17:B19)</f>
@@ -10233,7 +10847,7 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B22" s="33">
         <f>B6+B9+B15+B20</f>
@@ -10283,7 +10897,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="15" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -10293,30 +10907,30 @@
     </row>
     <row r="3" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="21" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="C3" s="21" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="E3" s="21" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="F3" s="21" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="11" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C4" s="23">
         <v>250000</v>
@@ -10333,10 +10947,10 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="11" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="C5" s="23">
         <v>25000</v>
@@ -10353,7 +10967,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="F7" s="33">
         <v>34064</v>
@@ -10361,7 +10975,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="F8" s="32">
         <v>250000</v>

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -27,14 +27,15 @@
     <sheet sheetId="21" name="Underwriting Snapshot" state="visible" r:id="rId24"/>
     <sheet sheetId="22" name="Financial Health" state="visible" r:id="rId25"/>
     <sheet sheetId="23" name="Budget Narrative" state="visible" r:id="rId26"/>
-    <sheet sheetId="24" name="Decision History" state="visible" r:id="rId27"/>
+    <sheet sheetId="24" name="Assumptions Memo" state="visible" r:id="rId27"/>
+    <sheet sheetId="25" name="Decision History" state="visible" r:id="rId28"/>
   </sheets>
   <calcPr calcId="171027" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="867" uniqueCount="495">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="498">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -42,7 +43,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · nonprofit_501c3</t>
+    <t>Generated May 1, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -162,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>April 29, 2026</t>
+    <t>May 1, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -1305,7 +1306,7 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1510,6 +1511,15 @@
   </si>
   <si>
     <t>Additional Context</t>
+  </si>
+  <si>
+    <t>Assumptions Memo</t>
+  </si>
+  <si>
+    <t>Founder-supplied reasoning for each assumption captured during the wizard. Empty when no rationale was entered for that area.</t>
+  </si>
+  <si>
+    <t>No founder rationale captured.</t>
   </si>
   <si>
     <t>Decision History</t>
@@ -1532,7 +1542,7 @@
     <numFmt numFmtId="167" formatCode="0.0"/>
     <numFmt numFmtId="168" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -1679,6 +1689,11 @@
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -1774,7 +1789,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1909,6 +1924,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -8496,6 +8515,54 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="70" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
+        <v>492</v>
+      </c>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="80" t="s">
+        <v>493</v>
+      </c>
+      <c r="B2" s="80"/>
+      <c r="C2" s="80"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="81" t="s">
+        <v>494</v>
+      </c>
+      <c r="B4" s="81"/>
+      <c r="C4" s="81"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="A4:C4"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -8514,7 +8581,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="15" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -8524,26 +8591,26 @@
       <c r="H1" s="15"/>
     </row>
     <row r="2" ht="60" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="80" t="s">
-        <v>493</v>
-      </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
-      <c r="E2" s="80"/>
-      <c r="F2" s="80"/>
-      <c r="G2" s="80"/>
-      <c r="H2" s="80"/>
+      <c r="B2" s="82" t="s">
+        <v>496</v>
+      </c>
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="82"/>
+      <c r="F2" s="82"/>
+      <c r="G2" s="82"/>
+      <c r="H2" s="82"/>
     </row>
     <row r="4" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="81" t="s">
-        <v>494</v>
-      </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="81"/>
-      <c r="F4" s="81"/>
-      <c r="G4" s="81"/>
-      <c r="H4" s="81"/>
+      <c r="B4" s="83" t="s">
+        <v>497</v>
+      </c>
+      <c r="C4" s="83"/>
+      <c r="D4" s="83"/>
+      <c r="E4" s="83"/>
+      <c r="F4" s="83"/>
+      <c r="G4" s="83"/>
+      <c r="H4" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
+++ b/artifacts/api-server/qa-output/Underwriting_V2_(21-tab)_Private_School_+_ESA.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="498">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="869" uniqueCount="498">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -43,7 +43,7 @@
     <t>Heritage Academy</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · nonprofit_501c3</t>
+    <t>Generated May 7, 2026 · nonprofit_501c3</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -163,7 +163,7 @@
     <t>Model Date</t>
   </si>
   <si>
-    <t>May 1, 2026</t>
+    <t>May 7, 2026</t>
   </si>
   <si>
     <t>Stage</t>
@@ -388,7 +388,7 @@
     <t>Timing</t>
   </si>
   <si>
-    <t>Tuition</t>
+    <t>Gross Tuition</t>
   </si>
   <si>
     <t>Tuition &amp; Fees</t>
@@ -859,7 +859,7 @@
     <t>REVENUE</t>
   </si>
   <si>
-    <t xml:space="preserve">  Tuition</t>
+    <t xml:space="preserve">  Gross Tuition</t>
   </si>
   <si>
     <t xml:space="preserve">  Registration Fee</t>
@@ -1306,7 +1306,7 @@
     <t>Heritage Academy — Financial Health Dashboard</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>● Green = healthy</t>
@@ -1417,7 +1417,7 @@
     <t>The model reaches net income early and sustains strong margins through Year 5.</t>
   </si>
   <si>
-    <t>Monitor enrollment actuals vs. projections in Year 1.</t>
+    <t>Compare your real Year 1 enrollment against this projection as students enroll.</t>
   </si>
   <si>
     <t>Liquidity</t>
@@ -1450,7 +1450,7 @@
     <t>Debt Affordability</t>
   </si>
   <si>
-    <t>DSCR of 87.52x provides comfortable coverage of debt payments with room to spare.</t>
+    <t>DSCR of 86.39x provides comfortable coverage of debt payments with room to spare.</t>
   </si>
   <si>
     <t>Maintain this ratio as you take on any additional debt.</t>
@@ -1468,7 +1468,7 @@
     <t>Reserve Strength</t>
   </si>
   <si>
-    <t>82.3 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
+    <t>81.6 months of reserves by Year 5 — a strong buffer for unexpected costs.</t>
   </si>
   <si>
     <t>Continue growing reserves toward 6 months for best-in-class financial health.</t>
@@ -3447,19 +3447,19 @@
       </c>
       <c r="C12" s="32">
         <f>SUM(C5:C11)</f>
-        <v>2621350</v>
+        <v>2612670</v>
       </c>
       <c r="D12" s="32">
         <f>SUM(D5:D11)</f>
-        <v>3304704</v>
+        <v>3286760</v>
       </c>
       <c r="E12" s="32">
         <f>SUM(E5:E11)</f>
-        <v>3922890</v>
+        <v>3895050</v>
       </c>
       <c r="F12" s="32">
         <f>SUM(F5:F11)</f>
-        <v>4361347</v>
+        <v>4323000</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -4041,19 +4041,19 @@
       </c>
       <c r="C4" s="34">
         <f>'Budget Detail'!C12</f>
-        <v>2621350</v>
+        <v>2612670</v>
       </c>
       <c r="D4" s="34">
         <f>'Budget Detail'!D12</f>
-        <v>3304704</v>
+        <v>3286760</v>
       </c>
       <c r="E4" s="34">
         <f>'Budget Detail'!E12</f>
-        <v>3922890</v>
+        <v>3895050</v>
       </c>
       <c r="F4" s="34">
         <f>'Budget Detail'!F12</f>
-        <v>4361347</v>
+        <v>4323000</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
@@ -4176,19 +4176,19 @@
       </c>
       <c r="C11" s="33">
         <f>C4-C8</f>
-        <v>1386428</v>
+        <v>1377748</v>
       </c>
       <c r="D11" s="33">
         <f>D4-D8</f>
-        <v>2002229</v>
+        <v>1984286</v>
       </c>
       <c r="E11" s="33">
         <f>E4-E8</f>
-        <v>2560345</v>
+        <v>2532505</v>
       </c>
       <c r="F11" s="33">
         <f>F4-F8</f>
-        <v>2942215</v>
+        <v>2903868</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4201,19 +4201,19 @@
       </c>
       <c r="C12" s="30">
         <f>IF(C4=0,0,C11/C4)</f>
-        <v>0.52889864</v>
+        <v>0.52733351</v>
       </c>
       <c r="D12" s="30">
         <f>IF(D4=0,0,D11/D4)</f>
-        <v>0.60587258</v>
+        <v>0.60372091</v>
       </c>
       <c r="E12" s="30">
         <f>IF(E4=0,0,E11/E4)</f>
-        <v>0.65266812</v>
+        <v>0.65018556</v>
       </c>
       <c r="F12" s="30">
         <f>IF(F4=0,0,F11/F4)</f>
-        <v>0.67461156</v>
+        <v>0.67172524</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4224,16 +4224,16 @@
         <v>789764</v>
       </c>
       <c r="C13" s="31">
-        <v>2176192</v>
+        <v>2167512</v>
       </c>
       <c r="D13" s="31">
-        <v>4178421</v>
+        <v>4151798</v>
       </c>
       <c r="E13" s="31">
-        <v>6738766</v>
+        <v>6684303</v>
       </c>
       <c r="F13" s="31">
-        <v>9680981</v>
+        <v>9588171</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -4244,16 +4244,16 @@
         <v>19750</v>
       </c>
       <c r="C14" s="31">
-        <v>20164</v>
+        <v>20097</v>
       </c>
       <c r="D14" s="31">
-        <v>20654</v>
+        <v>20542</v>
       </c>
       <c r="E14" s="31">
-        <v>21205</v>
+        <v>21054</v>
       </c>
       <c r="F14" s="31">
-        <v>21807</v>
+        <v>21615</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
@@ -4907,16 +4907,16 @@
         <v>1975000</v>
       </c>
       <c r="C5" s="32">
-        <v>2621350</v>
+        <v>2612670</v>
       </c>
       <c r="D5" s="32">
-        <v>3304704</v>
+        <v>3286760</v>
       </c>
       <c r="E5" s="32">
-        <v>3922890</v>
+        <v>3895050</v>
       </c>
       <c r="F5" s="32">
-        <v>4361347</v>
+        <v>4323000</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5054,19 +5054,19 @@
       </c>
       <c r="C15" s="33">
         <f>C5-C12</f>
-        <v>1360714</v>
+        <v>1352034</v>
       </c>
       <c r="D15" s="33">
         <f>D5-D12</f>
-        <v>1976515</v>
+        <v>1958571</v>
       </c>
       <c r="E15" s="33">
         <f>E5-E12</f>
-        <v>2534631</v>
+        <v>2506791</v>
       </c>
       <c r="F15" s="33">
         <f>F5-F12</f>
-        <v>2916501</v>
+        <v>2878154</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5079,19 +5079,19 @@
       </c>
       <c r="C16" s="30">
         <f>IF(C5=0,0,C15/C5)</f>
-        <v>0.51908908</v>
+        <v>0.51749136</v>
       </c>
       <c r="D16" s="30">
         <f>IF(D5=0,0,D15/D5)</f>
-        <v>0.59809146</v>
+        <v>0.59589731</v>
       </c>
       <c r="E16" s="30">
         <f>IF(E5=0,0,E15/E5)</f>
-        <v>0.64611318</v>
+        <v>0.64358377</v>
       </c>
       <c r="F16" s="30">
         <f>IF(F5=0,0,F15/F5)</f>
-        <v>0.66871561</v>
+        <v>0.66577699</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5104,19 +5104,19 @@
       </c>
       <c r="C17" s="34">
         <f>B17+C15</f>
-        <v>2124763</v>
+        <v>2116083</v>
       </c>
       <c r="D17" s="34">
         <f>C17+D15</f>
-        <v>4101278</v>
+        <v>4074655</v>
       </c>
       <c r="E17" s="34">
         <f>D17+E15</f>
-        <v>6635909</v>
+        <v>6581446</v>
       </c>
       <c r="F17" s="34">
         <f>E17+F15</f>
-        <v>9552410</v>
+        <v>9459600</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -5448,19 +5448,19 @@
       </c>
       <c r="C5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15</f>
-        <v>2198684</v>
+        <v>2190004</v>
       </c>
       <c r="D5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15</f>
-        <v>4200914</v>
+        <v>4174290</v>
       </c>
       <c r="E5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15</f>
-        <v>6761259</v>
+        <v>6706795</v>
       </c>
       <c r="F5" s="47">
         <f>B5+'5-Year Operating Stmt'!C15+'5-Year Operating Stmt'!D15+'5-Year Operating Stmt'!E15+'5-Year Operating Stmt'!F15</f>
-        <v>9703474</v>
+        <v>9610664</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5533,19 +5533,19 @@
       </c>
       <c r="C9" s="32">
         <f>SUM(C5:C8)</f>
-        <v>2333174</v>
+        <v>2324494</v>
       </c>
       <c r="D9" s="32">
         <f>SUM(D5:D8)</f>
-        <v>4309715</v>
+        <v>4283092</v>
       </c>
       <c r="E9" s="32">
         <f>SUM(E5:E8)</f>
-        <v>6844374</v>
+        <v>6789910</v>
       </c>
       <c r="F9" s="32">
         <f>SUM(F5:F8)</f>
-        <v>9760902</v>
+        <v>9668092</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5648,19 +5648,19 @@
       </c>
       <c r="C17" s="33">
         <f>C9-C14</f>
-        <v>2113112</v>
+        <v>2104432</v>
       </c>
       <c r="D17" s="33">
         <f>D9-D14</f>
-        <v>4110550</v>
+        <v>4083926</v>
       </c>
       <c r="E17" s="33">
         <f>E9-E14</f>
-        <v>6667503</v>
+        <v>6613040</v>
       </c>
       <c r="F17" s="33">
         <f>F9-F14</f>
-        <v>9607820</v>
+        <v>9515010</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -5675,13 +5675,13 @@
         <f>C9-C14-C17</f>
         <v>1</v>
       </c>
-      <c r="D19" s="48" t="str">
+      <c r="D19" s="49">
         <f>D9-D14-D17</f>
+        <v>1</v>
+      </c>
+      <c r="E19" s="48" t="str">
+        <f>E9-E14-E17</f>
         <v>0</v>
-      </c>
-      <c r="E19" s="49">
-        <f>E9-E14-E17</f>
-        <v>1</v>
       </c>
       <c r="F19" s="48" t="str">
         <f>F9-F14-F17</f>
@@ -5760,16 +5760,16 @@
         <v>1975000</v>
       </c>
       <c r="C5" s="31">
-        <v>2621350</v>
+        <v>2612670</v>
       </c>
       <c r="D5" s="31">
-        <v>3304704</v>
+        <v>3286760</v>
       </c>
       <c r="E5" s="31">
-        <v>3922890</v>
+        <v>3895050</v>
       </c>
       <c r="F5" s="31">
-        <v>4361347</v>
+        <v>4323000</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -5820,16 +5820,16 @@
         <v>789764</v>
       </c>
       <c r="C8" s="34">
-        <v>1386428</v>
+        <v>1377748</v>
       </c>
       <c r="D8" s="34">
-        <v>2002229</v>
+        <v>1984286</v>
       </c>
       <c r="E8" s="34">
-        <v>2560345</v>
+        <v>2532505</v>
       </c>
       <c r="F8" s="34">
-        <v>2942215</v>
+        <v>2903868</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5882,19 +5882,19 @@
       </c>
       <c r="C11" s="34">
         <f>C8+C9+C10</f>
-        <v>1446207</v>
+        <v>1437527</v>
       </c>
       <c r="D11" s="34">
         <f>D8+D9+D10</f>
-        <v>2062008</v>
+        <v>2044064</v>
       </c>
       <c r="E11" s="34">
         <f>E8+E9+E10</f>
-        <v>2620124</v>
+        <v>2592284</v>
       </c>
       <c r="F11" s="34">
         <f>F8+F9+F10</f>
-        <v>3001994</v>
+        <v>2963647</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5907,19 +5907,19 @@
       </c>
       <c r="C12" s="50">
         <f>IF(C10=0,"N/A",C11/C10)</f>
-        <v>42.46</v>
+        <v>42.2</v>
       </c>
       <c r="D12" s="50">
         <f>IF(D10=0,"N/A",D11/D10)</f>
-        <v>60.53</v>
+        <v>60.01</v>
       </c>
       <c r="E12" s="50">
         <f>IF(E10=0,"N/A",E11/E10)</f>
-        <v>76.92</v>
+        <v>76.1</v>
       </c>
       <c r="F12" s="50">
         <f>IF(F10=0,"N/A",F11/F10)</f>
-        <v>88.13</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5940,16 +5940,16 @@
         <v>812256</v>
       </c>
       <c r="C15" s="31">
-        <v>2198684</v>
+        <v>2190004</v>
       </c>
       <c r="D15" s="31">
-        <v>4200914</v>
+        <v>4174290</v>
       </c>
       <c r="E15" s="31">
-        <v>6761259</v>
+        <v>6706795</v>
       </c>
       <c r="F15" s="31">
-        <v>9703474</v>
+        <v>9610664</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
@@ -5962,19 +5962,19 @@
       </c>
       <c r="C16" s="36">
         <f>IF((C5-C8)=0,0,(C15/(C5-C8))*365)</f>
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D16" s="36">
         <f>IF((D5-D8)=0,0,(D15/(D5-D8))*365)</f>
-        <v>1177</v>
+        <v>1170</v>
       </c>
       <c r="E16" s="36">
         <f>IF((E5-E8)=0,0,(E15/(E5-E8))*365)</f>
-        <v>1811</v>
+        <v>1797</v>
       </c>
       <c r="F16" s="36">
         <f>IF((F5-F8)=0,0,(F15/(F5-F8))*365)</f>
-        <v>2496</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -5987,19 +5987,19 @@
       </c>
       <c r="C17" s="35">
         <f>IF((C5-C8)=0,0,C15/((C5-C8)/12))</f>
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="D17" s="35">
         <f>IF((D5-D8)=0,0,D15/((D5-D8)/12))</f>
-        <v>38.7</v>
+        <v>38.5</v>
       </c>
       <c r="E17" s="35">
         <f>IF((E5-E8)=0,0,E15/((E5-E8)/12))</f>
-        <v>59.5</v>
+        <v>59.1</v>
       </c>
       <c r="F17" s="35">
         <f>IF((F5-F8)=0,0,F15/((F5-F8)/12))</f>
-        <v>82.1</v>
+        <v>81.3</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -6040,16 +6040,16 @@
         <v>19750</v>
       </c>
       <c r="C21" s="31">
-        <v>20164</v>
+        <v>20097</v>
       </c>
       <c r="D21" s="31">
-        <v>20654</v>
+        <v>20542</v>
       </c>
       <c r="E21" s="31">
-        <v>21205</v>
+        <v>21054</v>
       </c>
       <c r="F21" s="31">
-        <v>21807</v>
+        <v>21615</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6103,13 +6103,13 @@
         <v>52</v>
       </c>
       <c r="D24" s="51">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E24" s="51">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F24" s="51">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6766,16 +6766,16 @@
         <v>1975000</v>
       </c>
       <c r="C6" s="31">
-        <v>2621350</v>
+        <v>2612670</v>
       </c>
       <c r="D6" s="31">
-        <v>3304704</v>
+        <v>3286760</v>
       </c>
       <c r="E6" s="31">
-        <v>3922890</v>
+        <v>3895050</v>
       </c>
       <c r="F6" s="31">
-        <v>4361347</v>
+        <v>4323000</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
@@ -6806,16 +6806,16 @@
         <v>814764</v>
       </c>
       <c r="C8" s="33">
-        <v>1396428</v>
+        <v>1387748</v>
       </c>
       <c r="D8" s="33">
-        <v>2012229</v>
+        <v>1994286</v>
       </c>
       <c r="E8" s="33">
-        <v>2565345</v>
+        <v>2537505</v>
       </c>
       <c r="F8" s="33">
-        <v>2947215</v>
+        <v>2908868</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -6826,16 +6826,16 @@
         <v>0.4125385351058188</v>
       </c>
       <c r="C9" s="30">
-        <v>0.5327134670433142</v>
+        <v>0.5311610141479759</v>
       </c>
       <c r="D9" s="30">
-        <v>0.6088985689741885</v>
+        <v>0.6067634180877193</v>
       </c>
       <c r="E9" s="30">
-        <v>0.6539426893351535</v>
+        <v>0.6514692393653464</v>
       </c>
       <c r="F9" s="30">
-        <v>0.6757579942908114</v>
+        <v>0.6728818455375137</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -6846,16 +6846,16 @@
         <v>24.92</v>
       </c>
       <c r="C10" s="55">
-        <v>41.99</v>
+        <v>41.74</v>
       </c>
       <c r="D10" s="55">
-        <v>60.07</v>
+        <v>59.54</v>
       </c>
       <c r="E10" s="55">
-        <v>76.31</v>
+        <v>75.49</v>
       </c>
       <c r="F10" s="55">
-        <v>87.52</v>
+        <v>86.39</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -6869,13 +6869,13 @@
         <v>52</v>
       </c>
       <c r="D11" s="36">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E11" s="36">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F11" s="36">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6921,16 +6921,16 @@
         <v>1678750</v>
       </c>
       <c r="C16" s="31">
-        <v>2228148</v>
+        <v>2220770</v>
       </c>
       <c r="D16" s="31">
-        <v>2808998</v>
+        <v>2793746</v>
       </c>
       <c r="E16" s="31">
-        <v>3334456</v>
+        <v>3310793</v>
       </c>
       <c r="F16" s="31">
-        <v>3707145</v>
+        <v>3674550</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -6961,16 +6961,16 @@
         <v>518514</v>
       </c>
       <c r="C18" s="33">
-        <v>1003226</v>
+        <v>995848</v>
       </c>
       <c r="D18" s="33">
-        <v>1516524</v>
+        <v>1501272</v>
       </c>
       <c r="E18" s="33">
-        <v>1976912</v>
+        <v>1953248</v>
       </c>
       <c r="F18" s="33">
-        <v>2293013</v>
+        <v>2260418</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6981,16 +6981,16 @@
         <v>0.308868864830375</v>
       </c>
       <c r="C19" s="30">
-        <v>0.45025113769801683</v>
+        <v>0.4484247225270305</v>
       </c>
       <c r="D19" s="30">
-        <v>0.5398806693813982</v>
+        <v>0.5373687271620227</v>
       </c>
       <c r="E19" s="30">
-        <v>0.5928737521590041</v>
+        <v>0.5899638110180545</v>
       </c>
       <c r="F19" s="30">
-        <v>0.6185388168127194</v>
+        <v>0.615155112397075</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -7001,16 +7001,16 @@
         <v>16.22</v>
       </c>
       <c r="C20" s="55">
-        <v>30.45</v>
+        <v>30.23</v>
       </c>
       <c r="D20" s="55">
-        <v>45.52</v>
+        <v>45.07</v>
       </c>
       <c r="E20" s="55">
-        <v>59.03</v>
+        <v>58.34</v>
       </c>
       <c r="F20" s="55">
-        <v>68.31</v>
+        <v>67.36</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -7021,16 +7021,16 @@
         <v>54</v>
       </c>
       <c r="C21" s="36">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D21" s="36">
         <v>53</v>
       </c>
       <c r="E21" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -7076,16 +7076,16 @@
         <v>1975000</v>
       </c>
       <c r="C26" s="31">
-        <v>2621350</v>
+        <v>2612670</v>
       </c>
       <c r="D26" s="31">
-        <v>3304704</v>
+        <v>3286760</v>
       </c>
       <c r="E26" s="31">
-        <v>3922890</v>
+        <v>3895050</v>
       </c>
       <c r="F26" s="31">
-        <v>4361347</v>
+        <v>4323000</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -7116,16 +7116,16 @@
         <v>801264</v>
       </c>
       <c r="C28" s="33">
-        <v>1379433</v>
+        <v>1370753</v>
       </c>
       <c r="D28" s="33">
-        <v>1991542</v>
+        <v>1973598</v>
       </c>
       <c r="E28" s="33">
-        <v>2541305</v>
+        <v>2513465</v>
       </c>
       <c r="F28" s="33">
-        <v>2920765</v>
+        <v>2882419</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
@@ -7136,16 +7136,16 @@
         <v>0.4057030920678441</v>
       </c>
       <c r="C29" s="30">
-        <v>0.5262301664539233</v>
+        <v>0.5246561742715277</v>
       </c>
       <c r="D29" s="30">
-        <v>0.6026385368714597</v>
+        <v>0.6004692104181601</v>
       </c>
       <c r="E29" s="30">
-        <v>0.6478145556304181</v>
+        <v>0.645297304730361</v>
       </c>
       <c r="F29" s="30">
-        <v>0.6696934781617792</v>
+        <v>0.6667635348655268</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -7156,16 +7156,16 @@
         <v>24.52</v>
       </c>
       <c r="C30" s="55">
-        <v>41.49</v>
+        <v>41.24</v>
       </c>
       <c r="D30" s="55">
-        <v>59.46</v>
+        <v>58.94</v>
       </c>
       <c r="E30" s="55">
-        <v>75.6</v>
+        <v>74.79</v>
       </c>
       <c r="F30" s="55">
-        <v>86.74</v>
+        <v>85.62</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -7176,7 +7176,7 @@
         <v>53</v>
       </c>
       <c r="C31" s="36">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D31" s="36">
         <v>52</v>
@@ -7185,7 +7185,7 @@
         <v>52</v>
       </c>
       <c r="F31" s="36">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
   </sheetData>
@@ -7326,16 +7326,16 @@
         <v>1975000</v>
       </c>
       <c r="E13" s="31">
-        <v>2621350</v>
+        <v>2612670</v>
       </c>
       <c r="F13" s="31">
-        <v>3304704</v>
+        <v>3286760</v>
       </c>
       <c r="G13" s="31">
-        <v>3922890</v>
+        <v>3895050</v>
       </c>
       <c r="H13" s="31">
-        <v>4361347</v>
+        <v>4323000</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -7366,16 +7366,16 @@
         <v>789764</v>
       </c>
       <c r="E15" s="31">
-        <v>1386428</v>
+        <v>1377748</v>
       </c>
       <c r="F15" s="31">
-        <v>2002229</v>
+        <v>1984286</v>
       </c>
       <c r="G15" s="31">
-        <v>2560345</v>
+        <v>2532505</v>
       </c>
       <c r="H15" s="31">
-        <v>2942215</v>
+        <v>2903868</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -7386,16 +7386,16 @@
         <v>812256</v>
       </c>
       <c r="E16" s="31">
-        <v>2198684</v>
+        <v>2190004</v>
       </c>
       <c r="F16" s="31">
-        <v>4200914</v>
+        <v>4174290</v>
       </c>
       <c r="G16" s="31">
-        <v>6761259</v>
+        <v>6706795</v>
       </c>
       <c r="H16" s="31">
-        <v>9703474</v>
+        <v>9610664</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -7464,16 +7464,16 @@
         <v>0.3998803072577175</v>
       </c>
       <c r="E21" s="30">
-        <v>0.5288986388059557</v>
+        <v>0.5273335120141435</v>
       </c>
       <c r="F21" s="30">
-        <v>0.6058725788967125</v>
+        <v>0.6037209081387117</v>
       </c>
       <c r="G21" s="30">
-        <v>0.6526681187789514</v>
+        <v>0.6501855587964191</v>
       </c>
       <c r="H21" s="30">
-        <v>0.6746115593902751</v>
+        <v>0.6717252413274745</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -7484,16 +7484,16 @@
         <v>24.18</v>
       </c>
       <c r="E22" s="55">
-        <v>41.7</v>
+        <v>41.45</v>
       </c>
       <c r="F22" s="55">
-        <v>59.78</v>
+        <v>59.25</v>
       </c>
       <c r="G22" s="55">
-        <v>76.16</v>
+        <v>75.34</v>
       </c>
       <c r="H22" s="55">
-        <v>87.37</v>
+        <v>86.25</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -7567,7 +7567,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -7577,7 +7577,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>422</v>
       </c>
@@ -7587,8 +7587,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="57" t="s">
         <v>423</v>
       </c>
@@ -7598,6 +7599,7 @@
       <c r="F3" s="57"/>
       <c r="G3" s="57"/>
       <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="58" t="s">
@@ -7661,16 +7663,16 @@
         <v>1975000</v>
       </c>
       <c r="D8" s="63">
-        <v>2621350</v>
+        <v>2612670</v>
       </c>
       <c r="E8" s="63">
-        <v>3304703.5</v>
+        <v>3286760</v>
       </c>
       <c r="F8" s="63">
-        <v>3922889.9299999997</v>
+        <v>3895050</v>
       </c>
       <c r="G8" s="63">
-        <v>4361346.638750001</v>
+        <v>4323000</v>
       </c>
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
@@ -7681,7 +7683,7 @@
         <v>854772</v>
       </c>
       <c r="D9" s="63">
-        <v>880415.16</v>
+        <v>880415.1599999999</v>
       </c>
       <c r="E9" s="63">
         <v>906827.6148</v>
@@ -7690,7 +7692,7 @@
         <v>934032.443244</v>
       </c>
       <c r="G9" s="63">
-        <v>962053.4165413202</v>
+        <v>962053.41654132</v>
       </c>
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
@@ -7704,7 +7706,7 @@
         <v>310442</v>
       </c>
       <c r="E10" s="63">
-        <v>351582.25999999995</v>
+        <v>351582.26</v>
       </c>
       <c r="F10" s="63">
         <v>389447.9028</v>
@@ -7741,16 +7743,16 @@
         <v>789763.6068339921</v>
       </c>
       <c r="D12" s="64">
-        <v>1386428.446833992</v>
+        <v>1377748.4468339921</v>
       </c>
       <c r="E12" s="64">
-        <v>2002229.2320339922</v>
+        <v>1984285.7320339922</v>
       </c>
       <c r="F12" s="64">
-        <v>2560345.190789992</v>
+        <v>2532505.2607899923</v>
       </c>
       <c r="G12" s="64">
-        <v>2942214.857008673</v>
+        <v>2903868.218258672</v>
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
@@ -7761,16 +7763,16 @@
         <v>812256</v>
       </c>
       <c r="D13" s="64">
-        <v>2198684.446833992</v>
+        <v>2190004.4468339924</v>
       </c>
       <c r="E13" s="64">
-        <v>4200913.678867985</v>
+        <v>4174290.1788679846</v>
       </c>
       <c r="F13" s="64">
-        <v>6761258.869657977</v>
+        <v>6706795.439657977</v>
       </c>
       <c r="G13" s="64">
-        <v>9703473.72666665</v>
+        <v>9610663.657916648</v>
       </c>
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
@@ -7781,16 +7783,16 @@
         <v>0.3998803072577175</v>
       </c>
       <c r="D14" s="65">
-        <v>0.5288986388059557</v>
+        <v>0.5273335120141435</v>
       </c>
       <c r="E14" s="65">
-        <v>0.6058725788967125</v>
+        <v>0.6037209081387117</v>
       </c>
       <c r="F14" s="65">
-        <v>0.6526681187789514</v>
+        <v>0.6501855587964191</v>
       </c>
       <c r="G14" s="65">
-        <v>0.6746115593902751</v>
+        <v>0.6717252413274745</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
@@ -7801,16 +7803,16 @@
         <v>19750</v>
       </c>
       <c r="D15" s="66">
-        <v>20164.23076923077</v>
+        <v>20097.46153846154</v>
       </c>
       <c r="E15" s="66">
-        <v>20654.396875</v>
+        <v>20542.25</v>
       </c>
       <c r="F15" s="66">
-        <v>21204.81043243243</v>
+        <v>21054.324324324323</v>
       </c>
       <c r="G15" s="66">
-        <v>21806.733193750006</v>
+        <v>21615</v>
       </c>
       <c r="H15" s="67" t="s">
         <v>434</v>
@@ -7824,7 +7826,7 @@
         <v>11602.36393166008</v>
       </c>
       <c r="D16" s="68">
-        <v>9422.47348589237</v>
+        <v>9422.473485892368</v>
       </c>
       <c r="E16" s="68">
         <v>8077.9641747875485</v>
@@ -7887,16 +7889,16 @@
         <v>7897.636068339921</v>
       </c>
       <c r="D19" s="69">
-        <v>10664.834206415322</v>
+        <v>10598.064975646093</v>
       </c>
       <c r="E19" s="69">
-        <v>12513.932700212452</v>
+        <v>12401.785825212452</v>
       </c>
       <c r="F19" s="69">
-        <v>13839.703733999957</v>
+        <v>13689.21762589185</v>
       </c>
       <c r="G19" s="69">
-        <v>14711.074285043363</v>
+        <v>14519.34109129336</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
@@ -7907,16 +7909,16 @@
         <v>0.4327959493670886</v>
       </c>
       <c r="D20" s="65">
-        <v>0.3358632612966601</v>
+        <v>0.33697909035584284</v>
       </c>
       <c r="E20" s="65">
-        <v>0.2744051364365971</v>
+        <v>0.2759032040063771</v>
       </c>
       <c r="F20" s="65">
-        <v>0.23809805013927576</v>
+        <v>0.23979985962798936</v>
       </c>
       <c r="G20" s="65">
-        <v>0.22058632258064514</v>
+        <v>0.22254300637088134</v>
       </c>
       <c r="H20" s="67" t="s">
         <v>440</v>
@@ -7930,16 +7932,16 @@
         <v>0.0690632911392405</v>
       </c>
       <c r="D21" s="65">
-        <v>0.05359528487229862</v>
+        <v>0.053773342978638713</v>
       </c>
       <c r="E21" s="65">
-        <v>0.043788121990369175</v>
+        <v>0.04402717569886453</v>
       </c>
       <c r="F21" s="65">
-        <v>0.03799442896935934</v>
+        <v>0.03826599473690967</v>
       </c>
       <c r="G21" s="65">
-        <v>0.035199999999999995</v>
+        <v>0.035512237262086514</v>
       </c>
       <c r="H21" s="67" t="s">
         <v>442</v>
@@ -7953,16 +7955,16 @@
         <v>0.42978632911392406</v>
       </c>
       <c r="D22" s="65">
-        <v>0.5457084479371316</v>
+        <v>0.5441991679010362</v>
       </c>
       <c r="E22" s="65">
-        <v>0.6192064205457464</v>
+        <v>0.6171275435991675</v>
       </c>
       <c r="F22" s="65">
-        <v>0.6626261838440112</v>
+        <v>0.6602147992852467</v>
       </c>
       <c r="G22" s="65">
-        <v>0.6835685161290322</v>
+        <v>0.6807616496471617</v>
       </c>
       <c r="H22" s="67" t="s">
         <v>444</v>
@@ -7999,16 +8001,16 @@
         <v>24.918336160088252</v>
       </c>
       <c r="D24" s="71">
-        <v>41.993786092965045</v>
+        <v>41.738974567108734</v>
       </c>
       <c r="E24" s="71">
-        <v>60.071336519270375</v>
+        <v>59.54458414436221</v>
       </c>
       <c r="F24" s="71">
-        <v>76.3087007388667</v>
+        <v>75.49142711639747</v>
       </c>
       <c r="G24" s="71">
-        <v>87.51893026967599</v>
+        <v>86.39321995500448</v>
       </c>
       <c r="H24" s="67" t="s">
         <v>447</v>
@@ -8050,13 +8052,13 @@
         <v>8</v>
       </c>
       <c r="D26" s="74">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" s="70">
         <v>39</v>
       </c>
-      <c r="F26" s="75" t="s">
-        <v>450</v>
+      <c r="F26" s="70">
+        <v>59</v>
       </c>
       <c r="G26" s="75" t="s">
         <v>450</v>
@@ -8073,22 +8075,22 @@
         <v>256</v>
       </c>
       <c r="D27" s="70">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="E27" s="70">
-        <v>1186</v>
+        <v>1179</v>
       </c>
       <c r="F27" s="70">
-        <v>1818</v>
+        <v>1803</v>
       </c>
       <c r="G27" s="70">
-        <v>2505</v>
+        <v>2481</v>
       </c>
       <c r="H27" s="67" t="s">
         <v>452</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="19" t="s">
         <v>453</v>
       </c>
@@ -8104,8 +8106,9 @@
       </c>
       <c r="G29" s="19"/>
       <c r="H29" s="19"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="44" t="s">
         <v>457</v>
       </c>
@@ -8121,8 +8124,9 @@
       </c>
       <c r="G30" s="77"/>
       <c r="H30" s="77"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="77"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="44" t="s">
         <v>461</v>
       </c>
@@ -8138,8 +8142,9 @@
       </c>
       <c r="G31" s="77"/>
       <c r="H31" s="77"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="77"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="44" t="s">
         <v>464</v>
       </c>
@@ -8155,8 +8160,9 @@
       </c>
       <c r="G32" s="77"/>
       <c r="H32" s="77"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="77"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="44" t="s">
         <v>467</v>
       </c>
@@ -8172,8 +8178,9 @@
       </c>
       <c r="G33" s="77"/>
       <c r="H33" s="77"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="77"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="44" t="s">
         <v>470</v>
       </c>
@@ -8189,8 +8196,9 @@
       </c>
       <c r="G34" s="77"/>
       <c r="H34" s="77"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="77"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="44" t="s">
         <v>473</v>
       </c>
@@ -8206,8 +8214,9 @@
       </c>
       <c r="G35" s="77"/>
       <c r="H35" s="77"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="77"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="44" t="s">
         <v>476</v>
       </c>
@@ -8223,6 +8232,7 @@
       </c>
       <c r="G36" s="77"/>
       <c r="H36" s="77"/>
+      <c r="I36" s="77"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="44" t="s">
@@ -8235,7 +8245,7 @@
       <c r="E38" s="10"/>
       <c r="F38" s="10"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="78" t="s">
         <v>481</v>
       </c>
@@ -8245,29 +8255,30 @@
       <c r="F40" s="78"/>
       <c r="G40" s="78"/>
       <c r="H40" s="78"/>
+      <c r="I40" s="78"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -8747,7 +8758,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="19" t="s">
         <v>103</v>
       </c>
@@ -8756,7 +8767,6 @@
       <c r="D15" s="19"/>
       <c r="E15" s="19"/>
       <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
     </row>
     <row r="16" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
@@ -9851,7 +9861,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -10447,7 +10457,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="11" ht="24" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>232</v>
       </c>
@@ -10456,7 +10466,6 @@
       <c r="D11" s="19"/>
       <c r="E11" s="19"/>
       <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="21" t="s">
@@ -10559,7 +10568,7 @@
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="7" width="16" customWidth="1"/>
+    <col min="2" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
